--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>53.33</v>
+        <v>53</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.33</v>
+        <v>50.16</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2270,127 +2270,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>91</v>
+        <v>92.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.67</v>
+        <v>52.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.67</v>
+        <v>9.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.67</v>
+        <v>6.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>25.67</v>
+        <v>25.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.67</v>
+        <v>3.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.17</v>
+        <v>3.71</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY4" t="n">
         <v>2.16</v>
@@ -2408,28 +2408,28 @@
         <v>2.28</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.63</v>
+        <v>3.96</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.28</v>
+        <v>4.5</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="CG4" t="n">
         <v>2.38</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI4" t="n">
         <v>1.67</v>
@@ -2438,135 +2438,139 @@
         <v>2.15</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.9</v>
+        <v>4.78</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CS4" t="inlineStr"/>
+        <v>1.58</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>3.39</v>
+      </c>
       <c r="CT4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CU4" t="inlineStr"/>
+        <v>2.43</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1.32</v>
+      </c>
       <c r="CV4" t="n">
         <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.34</v>
+        <v>5.27</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="DH4" t="n">
-        <v>83.34</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DM4" t="n">
-        <v>56</v>
+        <v>57.57</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.16</v>
+        <v>13.28</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.84</v>
+        <v>12.57</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>7.57</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.34</v>
+        <v>50.29</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.84</v>
+        <v>12.57</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.67</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.16</v>
+        <v>3.86</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.83</v>
+        <v>25</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2979,10 +2983,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -2991,82 +2995,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H6" t="n">
-        <v>93.33</v>
+        <v>102.75</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>45.67</v>
+        <v>49.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>13.33</v>
+        <v>14.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="R6" t="n">
-        <v>11.33</v>
+        <v>10.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>43.67</v>
+        <v>46.25</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.67</v>
+        <v>11.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.67</v>
+        <v>7.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.33</v>
+        <v>18.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3150,46 +3154,46 @@
         <v>1.33</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3201,19 +3205,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="CA6" t="n">
         <v>2.88</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="CC6" t="n">
         <v>4.67</v>
@@ -3225,10 +3229,10 @@
         <v>1.7</v>
       </c>
       <c r="CF6" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CH6" t="n">
         <v>1.18</v>
@@ -3237,28 +3241,28 @@
         <v>1.49</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CO6" t="n">
         <v>1.67</v>
       </c>
       <c r="CP6" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CQ6" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="CR6" t="n">
         <v>1.62</v>
@@ -3269,106 +3273,106 @@
       </c>
       <c r="CU6" t="inlineStr"/>
       <c r="CV6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CX6" t="n">
         <v>1.88</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DA6" t="n">
         <v>1.56</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DC6" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.29</v>
+        <v>6.51</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.66</v>
+        <v>93</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM6" t="n">
-        <v>52.34</v>
+        <v>53.43</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="DO6" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DP6" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="DQ6" t="n">
         <v>13</v>
       </c>
-      <c r="DQ6" t="n">
-        <v>13.33</v>
-      </c>
       <c r="DR6" t="n">
-        <v>9.67</v>
+        <v>9.43</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>8.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.34</v>
+        <v>5.43</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="EA6" t="n">
-        <v>21</v>
+        <v>20.43</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="7">
@@ -3378,10 +3382,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -3390,13 +3394,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>102.5</v>
+        <v>101</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3405,34 +3409,34 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>11.5</v>
+        <v>10.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.5</v>
+        <v>10.33</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3444,25 +3448,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>61.5</v>
+        <v>57.67</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.5</v>
+        <v>8.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>25.5</v>
+        <v>22.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -3549,49 +3553,49 @@
         <v>1.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="BH7" t="n">
-        <v>9</v>
+        <v>8.43</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BR7" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT7" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3600,19 +3604,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="CC7" t="n">
         <v>4.1</v>
@@ -3621,52 +3625,56 @@
         <v>4.25</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CJ7" t="n">
         <v>2.13</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CL7" t="n">
         <v>2.33</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CS7" t="inlineStr"/>
+        <v>1.56</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>3.39</v>
+      </c>
       <c r="CT7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CU7" t="inlineStr"/>
+        <v>2.46</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>1.32</v>
+      </c>
       <c r="CV7" t="n">
         <v>1.64</v>
       </c>
@@ -3674,67 +3682,67 @@
         <v>2.34</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.44</v>
+        <v>5.36</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.33</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DK7" t="n">
-        <v>5</v>
+        <v>4.29</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>56.5</v>
+        <v>55</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.83</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>8.5</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3746,28 +3754,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.33</v>
+        <v>51.14</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.83</v>
+        <v>12.57</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.33</v>
+        <v>19.86</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="8">
@@ -4176,10 +4184,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -4188,13 +4196,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
-        <v>98.33</v>
+        <v>90.75</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4203,64 +4211,64 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>65.67</v>
+        <v>54</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>11.67</v>
+        <v>11.25</v>
       </c>
       <c r="Q9" t="n">
+        <v>11</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="R9" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>13</v>
-      </c>
       <c r="AA9" t="n">
-        <v>10.33</v>
+        <v>9.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.33</v>
+        <v>18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -4347,43 +4355,43 @@
         <v>4.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.5</v>
+        <v>8.57</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BM9" t="n">
         <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>4.43</v>
       </c>
       <c r="BR9" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -4401,16 +4409,16 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="CB9" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CC9" t="n">
         <v>4.61</v>
@@ -4419,13 +4427,13 @@
         <v>5.11</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CH9" t="n">
         <v>1.21</v>
@@ -4434,13 +4442,13 @@
         <v>1.59</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CK9" t="n">
         <v>1.82</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CM9" t="n">
         <v>1.92</v>
@@ -4449,16 +4457,16 @@
         <v>1.54</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CP9" t="n">
         <v>2.76</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.84</v>
+        <v>5.91</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="n">
@@ -4466,73 +4474,73 @@
       </c>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DC9" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="DD9" t="n">
-        <v>6.34</v>
+        <v>6.47</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="DH9" t="n">
-        <v>91.16</v>
+        <v>87.86</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.34</v>
+        <v>4.72</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DM9" t="n">
-        <v>57.34</v>
+        <v>51.86</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.67</v>
+        <v>13.14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.5</v>
+        <v>13.57</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.5</v>
+        <v>10.43</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4544,28 +4552,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.33</v>
+        <v>47.57</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="EA9" t="n">
-        <v>18</v>
+        <v>18.29</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="10">
@@ -4575,13 +4583,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4668,50 +4676,50 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>71.67</v>
+        <v>74.25</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>39</v>
+        <v>40.75</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU10" t="n">
         <v>1</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AV10" t="n">
         <v>0</v>
       </c>
@@ -4722,82 +4730,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.67</v>
+        <v>48.75</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.67</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>23.67</v>
+        <v>24.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="BH10" t="n">
-        <v>6.67</v>
+        <v>6.86</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BP10" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BR10" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BT10" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY10" t="n">
         <v>3.28</v>
@@ -4806,165 +4814,165 @@
         <v>3.52</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.87</v>
+        <v>4.08</v>
       </c>
       <c r="CE10" t="n">
         <v>1.63</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CH10" t="n">
         <v>1.22</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
         <v>2.17</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CO10" t="n">
         <v>1.55</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CS10" t="inlineStr"/>
       <c r="CT10" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.08</v>
+        <v>6.2</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DH10" t="n">
-        <v>74.67</v>
+        <v>75.72</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>42</v>
+        <v>42.57</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DP10" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.33</v>
+        <v>12.43</v>
       </c>
       <c r="DR10" t="n">
-        <v>10</v>
+        <v>9.43</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.5</v>
+        <v>49.86</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.17</v>
+        <v>23</v>
       </c>
       <c r="EB10" t="n">
         <v>1.06</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11">
@@ -4974,13 +4982,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5067,121 +5075,121 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>85</v>
+        <v>85.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>1</v>
       </c>
-      <c r="AU11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BH11" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BP11" t="n">
         <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="BR11" t="n">
-        <v>83.33</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5196,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY11" t="n">
         <v>2.41</v>
@@ -5205,25 +5213,25 @@
         <v>2.49</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CB11" t="n">
         <v>2.89</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.78</v>
+        <v>4.73</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CF11" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CH11" t="n">
         <v>1.18</v>
@@ -5232,28 +5240,28 @@
         <v>1.47</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>6.69</v>
+        <v>6.59</v>
       </c>
       <c r="CR11" t="n">
         <v>1.76</v>
@@ -5264,73 +5272,73 @@
       </c>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="DD11" t="n">
-        <v>6.74</v>
+        <v>6.95</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="DH11" t="n">
-        <v>81.67</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
       <c r="DK11" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.84</v>
+        <v>54.72</v>
       </c>
       <c r="DN11" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DP11" t="n">
-        <v>19.5</v>
+        <v>18.86</v>
       </c>
       <c r="DQ11" t="n">
-        <v>8.33</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>10.34</v>
+        <v>10.29</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5342,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>39.84</v>
+        <v>38.29</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
@@ -5351,19 +5359,19 @@
         <v>10</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.5</v>
+        <v>7.28</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.67</v>
+        <v>19.57</v>
       </c>
       <c r="EB11" t="n">
         <v>1.22</v>
       </c>
       <c r="EC11" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="12">
@@ -5373,13 +5381,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5466,49 +5474,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>77.67</v>
+        <v>85.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>36</v>
+        <v>40.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP12" t="n">
         <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.67</v>
+        <v>10.25</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5520,70 +5528,70 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>52</v>
+        <v>54.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.33</v>
+        <v>12.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.67</v>
+        <v>17.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="BR12" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT12" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5595,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY12" t="n">
         <v>2.22</v>
@@ -5604,55 +5612,55 @@
         <v>2.21</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CB12" t="n">
         <v>2.94</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.71</v>
+        <v>4.04</v>
       </c>
       <c r="CR12" t="n">
         <v>1.63</v>
@@ -5666,70 +5674,70 @@
         <v>1.56</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.3</v>
+        <v>6.41</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="DH12" t="n">
-        <v>77</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM12" t="n">
-        <v>47.16</v>
+        <v>48.14</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.34</v>
+        <v>10.57</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5741,28 +5749,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.84</v>
+        <v>52.43</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.33</v>
+        <v>13</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.84</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.5</v>
+        <v>4.86</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.67</v>
+        <v>17.72</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="13">
@@ -6171,94 +6179,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>16</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H14" t="n">
-        <v>69</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M14" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="R14" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.67</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>39</v>
+        <v>40.5</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.67</v>
+        <v>11.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>15.33</v>
+        <v>17.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6342,49 +6350,49 @@
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="BN14" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BO14" t="n">
         <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU14" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6393,19 +6401,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="CA14" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CC14" t="n">
         <v>4.33</v>
@@ -6414,43 +6422,43 @@
         <v>4.27</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CH14" t="n">
         <v>1.22</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="CO14" t="n">
         <v>1.59</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CQ14" t="n">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="CR14" t="n">
         <v>1.64</v>
@@ -6465,43 +6473,43 @@
         <v>1.32</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CX14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DA14" t="n">
         <v>1.7</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>1.72</v>
       </c>
       <c r="DB14" t="n">
         <v>1.62</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="DD14" t="n">
-        <v>6.08</v>
+        <v>6.14</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="DH14" t="n">
-        <v>82.34</v>
+        <v>81</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
@@ -6510,61 +6518,61 @@
         <v>3</v>
       </c>
       <c r="DK14" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.5</v>
+        <v>40.86</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.84</v>
+        <v>13</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.84</v>
+        <v>14.71</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.17</v>
+        <v>10.14</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>42.16</v>
+        <v>42.57</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY14" t="n">
-        <v>6</v>
+        <v>6.14</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.5</v>
+        <v>17.43</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="15">
@@ -6574,31 +6582,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
-        <v>110</v>
+        <v>107.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
@@ -6607,28 +6615,28 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>50.67</v>
+        <v>52.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="R15" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6640,28 +6648,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>54.33</v>
+        <v>52.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>14.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.33</v>
+        <v>9.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>28</v>
+        <v>26.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.33</v>
@@ -6745,49 +6753,49 @@
         <v>1</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.33</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT15" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU15" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6796,19 +6804,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CC15" t="n">
         <v>4.62</v>
@@ -6817,13 +6825,13 @@
         <v>5.4</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CH15" t="n">
         <v>1.19</v>
@@ -6832,13 +6840,13 @@
         <v>1.53</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="CM15" t="n">
         <v>1.95</v>
@@ -6847,27 +6855,27 @@
         <v>1.58</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CQ15" t="n">
-        <v>6.33</v>
+        <v>6.21</v>
       </c>
       <c r="CR15" t="n">
         <v>1.68</v>
       </c>
       <c r="CS15" t="inlineStr"/>
       <c r="CT15" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CX15" t="n">
         <v>1.84</v>
@@ -6885,52 +6893,52 @@
         <v>1.68</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="DD15" t="n">
-        <v>6.61</v>
+        <v>6.66</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="DH15" t="n">
-        <v>90.34</v>
+        <v>91.72</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>38</v>
+        <v>40.86</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.66</v>
+        <v>11.57</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.67</v>
+        <v>8.57</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6942,28 +6950,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.5</v>
+        <v>45.72</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.34</v>
+        <v>11.43</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.33</v>
+        <v>7.43</v>
       </c>
       <c r="DZ15" t="n">
         <v>4</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.67</v>
+        <v>22.71</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="16">
@@ -7372,13 +7380,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7465,34 +7473,34 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>57</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
         <v>2</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>97.67</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.67</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -7501,13 +7509,13 @@
         <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.33</v>
+        <v>7.75</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7519,82 +7527,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.33</v>
+        <v>53.25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BA17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BD17" t="n">
-        <v>27.33</v>
+        <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY17" t="n">
         <v>2.2</v>
@@ -7603,55 +7611,55 @@
         <v>2.33</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.19</v>
+        <v>3.29</v>
       </c>
       <c r="CG17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CJ17" t="n">
         <v>2.24</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="CO17" t="n">
         <v>1.62</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="CR17" t="n">
         <v>1.65</v>
@@ -7662,73 +7670,73 @@
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CZ17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DA17" t="n">
         <v>1.57</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DC17" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="DD17" t="n">
-        <v>6.37</v>
+        <v>6.48</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="DG17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.17</v>
+        <v>95.86</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.5</v>
+        <v>5.29</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.66</v>
+        <v>51.86</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="DO17" t="n">
         <v>3</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.34</v>
+        <v>12.29</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.33</v>
+        <v>6.71</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7740,28 +7748,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.5</v>
+        <v>50.86</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.66</v>
+        <v>12.14</v>
       </c>
       <c r="DY17" t="n">
-        <v>9</v>
+        <v>8.57</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="EA17" t="n">
-        <v>27.67</v>
+        <v>26.29</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="18">
@@ -8170,13 +8178,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -8263,127 +8271,127 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM19" t="n">
         <v>1</v>
       </c>
-      <c r="AH19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
+      <c r="AN19" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>59</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF19" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BH19" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU19" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8392,7 +8400,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY19" t="n">
         <v>2.35</v>
@@ -8404,99 +8412,99 @@
         <v>2.81</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CC19" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CH19" t="n">
         <v>1.2</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CJ19" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CN19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CO19" t="n">
         <v>1.63</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>1.62</v>
       </c>
       <c r="CP19" t="n">
         <v>2.9</v>
       </c>
       <c r="CQ19" t="n">
-        <v>6.11</v>
+        <v>6.33</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CS19" t="inlineStr"/>
       <c r="CT19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="DD19" t="n">
-        <v>6.29</v>
+        <v>6.49</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DG19" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DH19" t="n">
-        <v>88.67</v>
+        <v>87</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
@@ -8505,58 +8513,58 @@
         <v>2</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="DM19" t="n">
-        <v>53.17</v>
+        <v>50.28</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.33</v>
+        <v>11.86</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.67</v>
+        <v>12.57</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.83</v>
+        <v>51.43</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.83</v>
+        <v>12.29</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.67</v>
+        <v>21.43</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
         <v>2</v>
@@ -8968,10 +8976,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
@@ -8980,49 +8988,49 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>99.5</v>
+        <v>95.67</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="K21" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M21" t="n">
-        <v>74.5</v>
+        <v>64</v>
       </c>
       <c r="N21" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>12.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9034,28 +9042,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>54.5</v>
+        <v>49</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>17.5</v>
+        <v>16.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AB21" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9139,37 +9147,37 @@
         <v>2.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.17</v>
+        <v>7.71</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BN21" t="n">
         <v>2</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9178,31 +9186,31 @@
         <v>100</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU21" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV21" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.93</v>
+        <v>3.21</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CC21" t="n">
         <v>4.47</v>
@@ -9211,16 +9219,16 @@
         <v>5.34</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CI21" t="n">
         <v>1.58</v>
@@ -9229,25 +9237,25 @@
         <v>2.24</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="CM21" t="n">
         <v>2.11</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO21" t="n">
         <v>1.59</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.36</v>
+        <v>5.45</v>
       </c>
       <c r="CR21" t="n">
         <v>1.64</v>
@@ -9261,103 +9269,103 @@
         <v>1.57</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CX21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DA21" t="n">
         <v>1.7</v>
       </c>
-      <c r="CY21" t="n">
+      <c r="DB21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG21" t="n">
         <v>2.14</v>
       </c>
-      <c r="CZ21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DA21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DC21" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="DD21" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="DE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DG21" t="n">
-        <v>2.33</v>
-      </c>
       <c r="DH21" t="n">
-        <v>72</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="DK21" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DM21" t="n">
-        <v>56.83</v>
+        <v>54.86</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.83</v>
+        <v>13.29</v>
       </c>
       <c r="DQ21" t="n">
-        <v>14.83</v>
+        <v>14.43</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.67</v>
+        <v>44.57</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.33</v>
+        <v>11.71</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.67</v>
+        <v>8.43</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.67</v>
+        <v>3.28</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.83</v>
+        <v>20.86</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="22">
@@ -9367,10 +9375,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
@@ -9379,13 +9387,13 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="H22" t="n">
-        <v>96</v>
+        <v>93.25</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -9394,34 +9402,34 @@
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>59.67</v>
+        <v>57.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="P22" t="n">
-        <v>13.33</v>
+        <v>11.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>12.67</v>
+        <v>11.25</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -9433,25 +9441,25 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>54</v>
+        <v>52.5</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>18.67</v>
+        <v>16.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -9538,46 +9546,46 @@
         <v>2</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN22" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BP22" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="BR22" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BS22" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BT22" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
@@ -9589,16 +9597,16 @@
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY22" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="CA22" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CB22" t="n">
         <v>2.97</v>
@@ -9613,25 +9621,25 @@
         <v>1.7</v>
       </c>
       <c r="CF22" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CG22" t="n">
         <v>2.09</v>
       </c>
       <c r="CH22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CJ22" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="CK22" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="CM22" t="n">
         <v>1.85</v>
@@ -9640,13 +9648,13 @@
         <v>1.49</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CP22" t="n">
-        <v>3.09</v>
+        <v>3.03</v>
       </c>
       <c r="CQ22" t="n">
-        <v>6.05</v>
+        <v>5.9</v>
       </c>
       <c r="CR22" t="n">
         <v>1.7</v>
@@ -9660,40 +9668,40 @@
         <v>1.52</v>
       </c>
       <c r="CW22" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CZ22" t="n">
         <v>1.9</v>
       </c>
       <c r="DA22" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DC22" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DD22" t="n">
-        <v>6.76</v>
+        <v>6.79</v>
       </c>
       <c r="DE22" t="n">
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DG22" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DH22" t="n">
-        <v>88</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
@@ -9702,58 +9710,58 @@
         <v>2</v>
       </c>
       <c r="DK22" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="DL22" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="DM22" t="n">
-        <v>47</v>
+        <v>47.57</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DO22" t="n">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="DP22" t="n">
-        <v>11.16</v>
+        <v>10.57</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11.17</v>
+        <v>10.57</v>
       </c>
       <c r="DR22" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>47.84</v>
+        <v>47.86</v>
       </c>
       <c r="DW22" t="n">
         <v>0</v>
       </c>
       <c r="DX22" t="n">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.34</v>
+        <v>6.72</v>
       </c>
       <c r="DZ22" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="EA22" t="n">
-        <v>20.67</v>
+        <v>19.29</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="EC22" t="n">
         <v>2</v>
@@ -10572,13 +10580,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -10662,52 +10670,52 @@
         <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AG25" t="n">
         <v>2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" t="n">
-        <v>87.5</v>
+        <v>87.33</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10.5</v>
+        <v>11.33</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>16.67</v>
       </c>
       <c r="AS25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>1</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AV25" t="n">
         <v>0</v>
@@ -10719,70 +10727,70 @@
         <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>45.5</v>
+        <v>48.67</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
       </c>
       <c r="BA25" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH25" t="n">
         <v>8</v>
       </c>
-      <c r="BB25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>7.83</v>
-      </c>
       <c r="BI25" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BN25" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BO25" t="n">
         <v>1</v>
       </c>
       <c r="BP25" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="BR25" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS25" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT25" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
@@ -10794,7 +10802,7 @@
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY25" t="n">
         <v>2.01</v>
@@ -10803,25 +10811,25 @@
         <v>2.02</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB25" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="CC25" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="CD25" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="CE25" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="CF25" t="n">
         <v>3.65</v>
       </c>
       <c r="CG25" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CH25" t="n">
         <v>1.24</v>
@@ -10830,138 +10838,138 @@
         <v>1.6</v>
       </c>
       <c r="CJ25" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CK25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CL25" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="CM25" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CN25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CP25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CQ25" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="CR25" t="n">
         <v>1.6</v>
-      </c>
-      <c r="CO25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CP25" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="CQ25" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>1.59</v>
       </c>
       <c r="CS25" t="inlineStr"/>
       <c r="CT25" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CU25" t="inlineStr"/>
       <c r="CV25" t="n">
         <v>1.62</v>
       </c>
       <c r="CW25" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CX25" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY25" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CZ25" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DA25" t="n">
         <v>1.58</v>
       </c>
       <c r="DB25" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DC25" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="DD25" t="n">
-        <v>5.71</v>
+        <v>5.82</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DG25" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="DH25" t="n">
-        <v>102.17</v>
+        <v>100</v>
       </c>
       <c r="DI25" t="n">
         <v>0</v>
       </c>
       <c r="DJ25" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DK25" t="n">
-        <v>5.17</v>
+        <v>4.86</v>
       </c>
       <c r="DL25" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DM25" t="n">
-        <v>64.17</v>
+        <v>61.29</v>
       </c>
       <c r="DN25" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="DO25" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DP25" t="n">
-        <v>8.67</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DQ25" t="n">
-        <v>16</v>
+        <v>15.72</v>
       </c>
       <c r="DR25" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="DS25" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT25" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU25" t="n">
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>51.67</v>
+        <v>52.14</v>
       </c>
       <c r="DW25" t="n">
         <v>0</v>
       </c>
       <c r="DX25" t="n">
-        <v>12.67</v>
+        <v>12.14</v>
       </c>
       <c r="DY25" t="n">
-        <v>7.67</v>
+        <v>7.57</v>
       </c>
       <c r="DZ25" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="EA25" t="n">
-        <v>18.5</v>
+        <v>18.43</v>
       </c>
       <c r="EB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="EC25" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="26">
@@ -10971,52 +10979,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F26" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="G26" t="n">
-        <v>3.67</v>
+        <v>2.75</v>
       </c>
       <c r="H26" t="n">
-        <v>90.33</v>
+        <v>90.25</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K26" t="n">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M26" t="n">
-        <v>58.33</v>
+        <v>54.75</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>13.33</v>
+        <v>11.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>16.33</v>
+        <v>14.75</v>
       </c>
       <c r="R26" t="n">
         <v>6</v>
@@ -11025,40 +11033,40 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U26" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="V26" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>54</v>
+        <v>54.75</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>20.33</v>
+        <v>22.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -11142,70 +11150,70 @@
         <v>4</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BH26" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BL26" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BN26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BP26" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="BR26" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS26" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT26" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU26" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV26" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW26" t="n">
         <v>0</v>
       </c>
       <c r="BX26" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BY26" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="BZ26" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="CA26" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CC26" t="n">
         <v>3.35</v>
@@ -11214,10 +11222,10 @@
         <v>3.66</v>
       </c>
       <c r="CE26" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CF26" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="CG26" t="n">
         <v>2.06</v>
@@ -11226,34 +11234,34 @@
         <v>1.16</v>
       </c>
       <c r="CI26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CJ26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CL26" t="n">
         <v>2.59</v>
       </c>
-      <c r="CK26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CL26" t="n">
-        <v>2.67</v>
-      </c>
       <c r="CM26" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CN26" t="n">
         <v>1.52</v>
       </c>
       <c r="CO26" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CP26" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="CQ26" t="n">
-        <v>7.13</v>
+        <v>7.21</v>
       </c>
       <c r="CR26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CS26" t="inlineStr"/>
       <c r="CT26" t="n">
@@ -11264,19 +11272,19 @@
         <v>1.46</v>
       </c>
       <c r="CW26" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CX26" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CY26" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CZ26" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DA26" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DB26" t="n">
         <v>1.8</v>
@@ -11285,82 +11293,82 @@
         <v>3.49</v>
       </c>
       <c r="DD26" t="n">
-        <v>7.16</v>
+        <v>7.28</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DG26" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="DH26" t="n">
-        <v>90.33</v>
+        <v>90.28</v>
       </c>
       <c r="DI26" t="n">
         <v>0</v>
       </c>
       <c r="DJ26" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="DK26" t="n">
-        <v>3.83</v>
+        <v>3.28</v>
       </c>
       <c r="DL26" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM26" t="n">
-        <v>46</v>
+        <v>45.72</v>
       </c>
       <c r="DN26" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="DO26" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="DP26" t="n">
-        <v>14.66</v>
+        <v>13.57</v>
       </c>
       <c r="DQ26" t="n">
-        <v>14.5</v>
+        <v>13.86</v>
       </c>
       <c r="DR26" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="DS26" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU26" t="n">
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>50.34</v>
+        <v>51.29</v>
       </c>
       <c r="DW26" t="n">
         <v>0</v>
       </c>
       <c r="DX26" t="n">
-        <v>9.17</v>
+        <v>9.43</v>
       </c>
       <c r="DY26" t="n">
-        <v>6.66</v>
+        <v>6.86</v>
       </c>
       <c r="DZ26" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="EA26" t="n">
-        <v>21.83</v>
+        <v>22.71</v>
       </c>
       <c r="EB26" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="EC26" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="27">
@@ -11769,13 +11777,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -11862,49 +11870,49 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AI28" t="n">
-        <v>93</v>
+        <v>90.25</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>53.67</v>
+        <v>47</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12.67</v>
+        <v>11.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AU28" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV28" t="n">
         <v>0</v>
@@ -11916,70 +11924,70 @@
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>44</v>
+        <v>48.75</v>
       </c>
       <c r="AZ28" t="n">
         <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>13.67</v>
+        <v>12.75</v>
       </c>
       <c r="BB28" t="n">
         <v>8</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="BD28" t="n">
-        <v>17.67</v>
+        <v>19.75</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BH28" t="n">
-        <v>9.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL28" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN28" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BP28" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="BQ28" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="BR28" t="n">
         <v>100</v>
       </c>
       <c r="BS28" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT28" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BU28" t="n">
         <v>0</v>
@@ -11991,7 +11999,7 @@
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>83.33</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY28" t="n">
         <v>1.8</v>
@@ -12000,25 +12008,25 @@
         <v>1.89</v>
       </c>
       <c r="CA28" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="CB28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CC28" t="n">
-        <v>3.95</v>
+        <v>3.54</v>
       </c>
       <c r="CD28" t="n">
-        <v>4.54</v>
+        <v>4.01</v>
       </c>
       <c r="CE28" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CF28" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="CG28" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CH28" t="n">
         <v>1.22</v>
@@ -12030,102 +12038,102 @@
         <v>2.26</v>
       </c>
       <c r="CK28" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL28" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="CM28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN28" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO28" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CP28" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CQ28" t="n">
-        <v>5.84</v>
+        <v>5.9</v>
       </c>
       <c r="CR28" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CS28" t="inlineStr"/>
       <c r="CT28" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CW28" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CX28" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CY28" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CZ28" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="DA28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DB28" t="n">
         <v>1.62</v>
       </c>
-      <c r="DB28" t="n">
-        <v>1.6</v>
-      </c>
       <c r="DC28" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="DD28" t="n">
-        <v>5.86</v>
+        <v>6.06</v>
       </c>
       <c r="DE28" t="n">
         <v>0</v>
       </c>
       <c r="DF28" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DG28" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="DH28" t="n">
-        <v>85.5</v>
+        <v>85</v>
       </c>
       <c r="DI28" t="n">
         <v>0</v>
       </c>
       <c r="DJ28" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DK28" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="DL28" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="DM28" t="n">
-        <v>48.17</v>
+        <v>45.14</v>
       </c>
       <c r="DN28" t="n">
         <v>1</v>
       </c>
       <c r="DO28" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="DP28" t="n">
-        <v>10.5</v>
+        <v>10.14</v>
       </c>
       <c r="DQ28" t="n">
-        <v>10.34</v>
+        <v>10.43</v>
       </c>
       <c r="DR28" t="n">
-        <v>6.66</v>
+        <v>6.57</v>
       </c>
       <c r="DS28" t="n">
         <v>0</v>
@@ -12137,28 +12145,28 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>54.5</v>
+        <v>55.71</v>
       </c>
       <c r="DW28" t="n">
         <v>0</v>
       </c>
       <c r="DX28" t="n">
-        <v>13.67</v>
+        <v>13.14</v>
       </c>
       <c r="DY28" t="n">
-        <v>8.5</v>
+        <v>8.43</v>
       </c>
       <c r="DZ28" t="n">
-        <v>5.17</v>
+        <v>4.72</v>
       </c>
       <c r="EA28" t="n">
-        <v>20.84</v>
+        <v>21.57</v>
       </c>
       <c r="EB28" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="EC28" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="29">
@@ -12168,13 +12176,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -12258,52 +12266,52 @@
         <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>79</v>
+        <v>84.75</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.33</v>
+        <v>-0.25</v>
       </c>
       <c r="AN29" t="n">
-        <v>38.67</v>
+        <v>46</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9.67</v>
+        <v>9.75</v>
       </c>
       <c r="AR29" t="n">
-        <v>11.33</v>
+        <v>13</v>
       </c>
       <c r="AS29" t="n">
-        <v>10.67</v>
+        <v>9.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV29" t="n">
         <v>0</v>
@@ -12315,82 +12323,82 @@
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>43.33</v>
+        <v>44</v>
       </c>
       <c r="AZ29" t="n">
         <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB29" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>15.33</v>
+        <v>15.75</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="BF29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BH29" t="n">
-        <v>9.83</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BL29" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN29" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BP29" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.17</v>
+        <v>3.71</v>
       </c>
       <c r="BR29" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS29" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT29" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU29" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV29" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY29" t="n">
         <v>2.36</v>
@@ -12399,55 +12407,55 @@
         <v>2.6</v>
       </c>
       <c r="CA29" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="CC29" t="n">
-        <v>4.27</v>
+        <v>3.84</v>
       </c>
       <c r="CD29" t="n">
-        <v>4.58</v>
+        <v>4.12</v>
       </c>
       <c r="CE29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CF29" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="CG29" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CH29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CI29" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CJ29" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CK29" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CL29" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CM29" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CN29" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CO29" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CP29" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CQ29" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="CR29" t="n">
         <v>1.67</v>
@@ -12458,16 +12466,16 @@
       </c>
       <c r="CU29" t="inlineStr"/>
       <c r="CV29" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CW29" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CX29" t="n">
         <v>1.93</v>
       </c>
       <c r="CY29" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CZ29" t="n">
         <v>1.88</v>
@@ -12476,55 +12484,55 @@
         <v>1.56</v>
       </c>
       <c r="DB29" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DC29" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="DD29" t="n">
-        <v>6.27</v>
+        <v>6.46</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG29" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="DH29" t="n">
-        <v>75.33</v>
+        <v>79.14</v>
       </c>
       <c r="DI29" t="n">
         <v>0</v>
       </c>
       <c r="DJ29" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DK29" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="DL29" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DM29" t="n">
-        <v>40.34</v>
+        <v>44.29</v>
       </c>
       <c r="DN29" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DO29" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="DP29" t="n">
-        <v>10.67</v>
+        <v>10.57</v>
       </c>
       <c r="DQ29" t="n">
-        <v>12.16</v>
+        <v>13</v>
       </c>
       <c r="DR29" t="n">
-        <v>10.67</v>
+        <v>10</v>
       </c>
       <c r="DS29" t="n">
         <v>0</v>
@@ -12536,28 +12544,28 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>43.16</v>
+        <v>43.57</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
       </c>
       <c r="DX29" t="n">
-        <v>11.84</v>
+        <v>12.29</v>
       </c>
       <c r="DY29" t="n">
-        <v>7</v>
+        <v>7.29</v>
       </c>
       <c r="DZ29" t="n">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="EA29" t="n">
-        <v>14.83</v>
+        <v>15.14</v>
       </c>
       <c r="EB29" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="EC29" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="30">
@@ -12633,7 +12641,7 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>52.5</v>
+        <v>52.75</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -12935,7 +12943,7 @@
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>50.17</v>
+        <v>50.33</v>
       </c>
       <c r="DW30" t="n">
         <v>0.17</v>
@@ -12966,61 +12974,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F31" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="G31" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="H31" t="n">
-        <v>95.67</v>
+        <v>107</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="L31" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M31" t="n">
-        <v>48.67</v>
+        <v>48.75</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P31" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="Q31" t="n">
-        <v>11.67</v>
+        <v>13.25</v>
       </c>
       <c r="R31" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="S31" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -13032,28 +13040,28 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>46.67</v>
+        <v>52.75</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>7.33</v>
+        <v>7.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>20.33</v>
+        <v>21</v>
       </c>
       <c r="AD31" t="n">
         <v>1.35</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -13137,46 +13145,46 @@
         <v>2.67</v>
       </c>
       <c r="BG31" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="BH31" t="n">
-        <v>9.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI31" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN31" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BP31" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="BQ31" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="BR31" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS31" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT31" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU31" t="n">
         <v>0</v>
@@ -13188,16 +13196,16 @@
         <v>0</v>
       </c>
       <c r="BX31" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BY31" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="BZ31" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="CA31" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CB31" t="n">
         <v>2.87</v>
@@ -13212,40 +13220,40 @@
         <v>1.61</v>
       </c>
       <c r="CF31" t="n">
-        <v>3.76</v>
+        <v>3.81</v>
       </c>
       <c r="CG31" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CH31" t="n">
         <v>1.22</v>
       </c>
       <c r="CI31" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CJ31" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CK31" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL31" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CM31" t="n">
         <v>2.04</v>
       </c>
       <c r="CN31" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CO31" t="n">
         <v>1.58</v>
       </c>
       <c r="CP31" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="CQ31" t="n">
-        <v>5.81</v>
+        <v>5.84</v>
       </c>
       <c r="CR31" t="n">
         <v>1.64</v>
@@ -13256,73 +13264,73 @@
       </c>
       <c r="CU31" t="inlineStr"/>
       <c r="CV31" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="CW31" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="CX31" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY31" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ31" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB31" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="DC31" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="DD31" t="n">
-        <v>6.21</v>
+        <v>6.47</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF31" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DG31" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DH31" t="n">
-        <v>88.17</v>
+        <v>95.72</v>
       </c>
       <c r="DI31" t="n">
         <v>0</v>
       </c>
       <c r="DJ31" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="DK31" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DM31" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="DN31" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="DP31" t="n">
-        <v>10.67</v>
+        <v>10.57</v>
       </c>
       <c r="DQ31" t="n">
-        <v>11.34</v>
+        <v>12.29</v>
       </c>
       <c r="DR31" t="n">
-        <v>6.16</v>
+        <v>6</v>
       </c>
       <c r="DS31" t="n">
         <v>0</v>
@@ -13334,28 +13342,28 @@
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>51</v>
+        <v>53.86</v>
       </c>
       <c r="DW31" t="n">
         <v>0</v>
       </c>
       <c r="DX31" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="DY31" t="n">
-        <v>7.16</v>
+        <v>7.43</v>
       </c>
       <c r="DZ31" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="EA31" t="n">
-        <v>19.83</v>
+        <v>20.28</v>
       </c>
       <c r="EB31" t="n">
         <v>1.32</v>
       </c>
       <c r="EC31" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2673,34 +2673,34 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>87.33</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
         <v>13</v>
@@ -2709,13 +2709,13 @@
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>9.33</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2727,73 +2727,73 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>21.67</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="BF5" t="n">
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY5" t="n">
         <v>2.64</v>
@@ -2811,136 +2811,136 @@
         <v>2.85</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.25</v>
+        <v>4.17</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.83</v>
+        <v>4.51</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CM5" t="n">
         <v>1.97</v>
       </c>
       <c r="CN5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="CR5" t="n">
         <v>1.58</v>
       </c>
-      <c r="CO5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.61</v>
-      </c>
       <c r="CS5" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CV5" t="n">
         <v>1.64</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CZ5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>46.43</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DO5" t="n">
         <v>2</v>
       </c>
-      <c r="DA5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>48.67</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="DP5" t="n">
-        <v>9.83</v>
+        <v>10.29</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.83</v>
+        <v>14.86</v>
       </c>
       <c r="DR5" t="n">
-        <v>7</v>
+        <v>7.71</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2952,28 +2952,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.33</v>
+        <v>43</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.83</v>
+        <v>11</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.83</v>
+        <v>7.29</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="EA5" t="n">
-        <v>26.83</v>
+        <v>26.57</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="6">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -3797,82 +3797,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>97.75</v>
+        <v>102.8</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>46.25</v>
+        <v>54.8</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q8" t="n">
         <v>17</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>62.5</v>
+        <v>64.2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>10.25</v>
+        <v>11.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.75</v>
+        <v>21.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3956,46 +3956,46 @@
         <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BN8" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="BR8" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4007,19 +4007,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="CC8" t="n">
         <v>2.51</v>
@@ -4028,57 +4028,61 @@
         <v>2.74</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="CG8" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CS8" t="inlineStr"/>
+        <v>1.55</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>3.29</v>
+      </c>
       <c r="CT8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CU8" t="inlineStr"/>
+        <v>2.48</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1.3</v>
+      </c>
       <c r="CV8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CX8" t="n">
         <v>1.74</v>
@@ -4093,88 +4097,88 @@
         <v>1.69</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.36</v>
+        <v>5.27</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.17</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.17</v>
+        <v>6.57</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DM8" t="n">
-        <v>51.5</v>
+        <v>56.86</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.67</v>
+        <v>15.86</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.33</v>
+        <v>7.86</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61</v>
+        <v>62.43</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>10</v>
+        <v>11.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.17</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.33</v>
+        <v>21.57</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="9">
@@ -4184,13 +4188,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4277,46 +4281,46 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>84</v>
+        <v>80.75</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>49</v>
+        <v>39.25</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.67</v>
+        <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.33</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
@@ -4331,67 +4335,67 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.33</v>
+        <v>41.25</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.67</v>
+        <v>19</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BM9" t="n">
         <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.14</v>
+        <v>4.62</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BS9" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -4415,69 +4419,69 @@
         <v>3.42</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="CB9" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.61</v>
+        <v>4.89</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.11</v>
+        <v>5.68</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CH9" t="n">
         <v>1.21</v>
       </c>
       <c r="CI9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CO9" t="n">
         <v>1.59</v>
       </c>
-      <c r="CJ9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="CP9" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.91</v>
+        <v>5.79</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="CX9" t="n">
         <v>1.87</v>
@@ -4492,55 +4496,55 @@
         <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DC9" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="DD9" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DH9" t="n">
-        <v>87.86</v>
+        <v>85.75</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.72</v>
+        <v>4.38</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>51.86</v>
+        <v>46.62</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.14</v>
+        <v>12.38</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.57</v>
+        <v>12.75</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.43</v>
+        <v>11.25</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4552,28 +4556,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.57</v>
+        <v>44.88</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.57</v>
+        <v>9.25</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.29</v>
+        <v>18.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="10">
@@ -5780,10 +5784,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
@@ -5792,49 +5796,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="H13" t="n">
-        <v>83</v>
+        <v>72.67</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3.33</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53</v>
+        <v>46.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="R13" t="n">
-        <v>9.5</v>
+        <v>8.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5846,28 +5850,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.5</v>
+        <v>12.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>19</v>
+        <v>18.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.98</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5954,46 +5958,46 @@
         <v>2</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI13" t="n">
         <v>2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="BR13" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU13" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6002,19 +6006,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.38</v>
+        <v>4.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.91</v>
+        <v>4.61</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="CC13" t="n">
         <v>5.09</v>
@@ -6023,43 +6027,43 @@
         <v>5.7</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.84</v>
+        <v>3.99</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.96</v>
+        <v>6.23</v>
       </c>
       <c r="CR13" t="n">
         <v>1.63</v>
@@ -6070,22 +6074,22 @@
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="CX13" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DB13" t="n">
         <v>1.64</v>
@@ -6100,43 +6104,43 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.17</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>56</v>
+        <v>52.71</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.83</v>
+        <v>11.86</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.83</v>
+        <v>11.57</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.67</v>
+        <v>7.43</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6148,28 +6152,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.5</v>
+        <v>43.29</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.83</v>
+        <v>11</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1.83</v>
+        <v>2.57</v>
       </c>
       <c r="EA13" t="n">
-        <v>25.17</v>
+        <v>24</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="14">
@@ -6582,13 +6586,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>0.25</v>
@@ -6672,52 +6676,52 @@
         <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>70.67</v>
+        <v>70.5</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>25.33</v>
+        <v>28.25</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.67</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.33</v>
+        <v>11.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6729,73 +6733,73 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>36.67</v>
+        <v>34.75</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.67</v>
+        <v>7.25</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.33</v>
+        <v>16.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="BF15" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.43</v>
+        <v>4.75</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BT15" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU15" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6804,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BY15" t="n">
         <v>2.95</v>
@@ -6813,69 +6817,73 @@
         <v>3.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.62</v>
+        <v>5.31</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.4</v>
+        <v>6.18</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CJ15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CL15" t="n">
         <v>2.34</v>
       </c>
-      <c r="CK15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>2.38</v>
-      </c>
       <c r="CM15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="CR15" t="n">
         <v>1.65</v>
       </c>
-      <c r="CP15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CS15" t="inlineStr"/>
+      <c r="CS15" t="n">
+        <v>3.29</v>
+      </c>
       <c r="CT15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CU15" t="inlineStr"/>
+        <v>2.28</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>1.3</v>
+      </c>
       <c r="CV15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CX15" t="n">
         <v>1.84</v>
@@ -6890,55 +6898,55 @@
         <v>1.58</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="DD15" t="n">
-        <v>6.66</v>
+        <v>6.44</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DH15" t="n">
-        <v>91.72</v>
+        <v>89</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.86</v>
+        <v>40.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DP15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.57</v>
+        <v>11.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.57</v>
+        <v>8.75</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6950,28 +6958,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.72</v>
+        <v>43.62</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.43</v>
+        <v>10.75</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.43</v>
+        <v>6.88</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.71</v>
+        <v>21.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="16">
@@ -6981,13 +6989,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7074,124 +7082,124 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP16" t="n">
         <v>3</v>
       </c>
-      <c r="AH16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>87</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AM16" t="n">
+      <c r="AQ16" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT16" t="n">
         <v>1</v>
       </c>
-      <c r="AN16" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AU16" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>55</v>
+        <v>57.25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.33</v>
+        <v>6.75</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>25</v>
+        <v>24.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT16" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
@@ -7203,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY16" t="n">
         <v>2.16</v>
@@ -7212,55 +7220,55 @@
         <v>2.18</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CB16" t="n">
         <v>2.8</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.03</v>
+        <v>2.84</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CF16" t="n">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CH16" t="n">
         <v>1.16</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CP16" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.48</v>
+        <v>6.67</v>
       </c>
       <c r="CR16" t="n">
         <v>1.76</v>
@@ -7271,22 +7279,22 @@
       </c>
       <c r="CU16" t="inlineStr"/>
       <c r="CV16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CZ16" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DB16" t="n">
         <v>1.81</v>
@@ -7301,76 +7309,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DH16" t="n">
-        <v>91.5</v>
+        <v>87</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.34</v>
+        <v>41</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="DO16" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.34</v>
+        <v>12.86</v>
       </c>
       <c r="DQ16" t="n">
-        <v>16</v>
+        <v>15.57</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.84</v>
+        <v>7.71</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.84</v>
+        <v>56.14</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="DX16" t="n">
-        <v>8.67</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DY16" t="n">
-        <v>5.83</v>
+        <v>6.14</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="EA16" t="n">
-        <v>22.67</v>
+        <v>22.57</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="17">
@@ -7380,10 +7388,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
@@ -7392,49 +7400,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>94.67</v>
+        <v>103.75</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>6.67</v>
+        <v>7.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>45</v>
+        <v>45.75</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="O17" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.67</v>
+        <v>13.25</v>
       </c>
       <c r="R17" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7446,28 +7454,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.67</v>
+        <v>54.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.33</v>
+        <v>17.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>11</v>
+        <v>13.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.33</v>
+        <v>4.5</v>
       </c>
       <c r="AC17" t="n">
         <v>28</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7551,70 +7559,70 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.57</v>
+        <v>10</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.71</v>
+        <v>5.12</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="CC17" t="n">
         <v>2.51</v>
@@ -7623,57 +7631,57 @@
         <v>2.79</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CG17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CS17" t="inlineStr"/>
       <c r="CT17" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="CX17" t="n">
         <v>1.87</v>
@@ -7688,55 +7696,55 @@
         <v>1.57</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DC17" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="DD17" t="n">
-        <v>6.48</v>
+        <v>6.39</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.86</v>
+        <v>100.25</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.29</v>
+        <v>6</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.86</v>
+        <v>51.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DO17" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.43</v>
+        <v>10.5</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.29</v>
+        <v>12.62</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7748,28 +7756,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.86</v>
+        <v>53.75</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.14</v>
+        <v>14.12</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.57</v>
+        <v>10</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.57</v>
+        <v>4.12</v>
       </c>
       <c r="EA17" t="n">
-        <v>26.29</v>
+        <v>26.5</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -7779,13 +7787,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>0.25</v>
@@ -7872,49 +7880,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="AO18" t="n">
         <v>1</v>
       </c>
-      <c r="AH18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.5</v>
+        <v>10.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>11.67</v>
       </c>
       <c r="AS18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7926,82 +7934,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>10.67</v>
       </c>
       <c r="BB18" t="n">
         <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="BD18" t="n">
-        <v>22</v>
+        <v>20.33</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="BH18" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BM18" t="n">
         <v>1</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BO18" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.83</v>
+        <v>5.29</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY18" t="n">
         <v>2.1</v>
@@ -8010,55 +8018,55 @@
         <v>2.16</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.32</v>
+        <v>3.96</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.39</v>
+        <v>3.99</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.81</v>
+        <v>3.72</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM18" t="n">
         <v>2.02</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="CQ18" t="n">
-        <v>5.76</v>
+        <v>5.49</v>
       </c>
       <c r="CR18" t="n">
         <v>1.63</v>
@@ -8069,10 +8077,10 @@
       </c>
       <c r="CU18" t="inlineStr"/>
       <c r="CV18" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="CX18" t="n">
         <v>1.81</v>
@@ -8087,55 +8095,55 @@
         <v>1.62</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="DD18" t="n">
-        <v>6.12</v>
+        <v>5.84</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="DH18" t="n">
-        <v>87</v>
+        <v>88.14</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DM18" t="n">
-        <v>54.67</v>
+        <v>56</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.83</v>
+        <v>10.57</v>
       </c>
       <c r="DR18" t="n">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8147,28 +8155,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>43.17</v>
+        <v>43.86</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.33</v>
+        <v>13.57</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="EA18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -9057,7 +9065,7 @@
         <v>4.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="AD21" t="n">
         <v>1.8</v>
@@ -9359,7 +9367,7 @@
         <v>3.28</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.86</v>
+        <v>21</v>
       </c>
       <c r="EB21" t="n">
         <v>1.37</v>
@@ -9774,10 +9782,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
@@ -9786,82 +9794,82 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>91.5</v>
+        <v>92.33</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
       <c r="P23" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>12</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z23" t="n">
         <v>16</v>
       </c>
-      <c r="Q23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AA23" t="n">
-        <v>12.5</v>
+        <v>11.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>24.5</v>
+        <v>23.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -9945,49 +9953,49 @@
         <v>4.25</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BH23" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN23" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BP23" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5</v>
+        <v>5.43</v>
       </c>
       <c r="BR23" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS23" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BU23" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -9996,19 +10004,19 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY23" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="BZ23" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="CA23" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="CC23" t="n">
         <v>2.5</v>
@@ -10020,40 +10028,40 @@
         <v>1.54</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CH23" t="n">
         <v>1.26</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CL23" t="n">
         <v>2.46</v>
       </c>
       <c r="CM23" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.93</v>
+        <v>4.78</v>
       </c>
       <c r="CR23" t="n">
         <v>1.54</v>
@@ -10068,10 +10076,10 @@
         <v>1.32</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CX23" t="n">
         <v>1.83</v>
@@ -10086,88 +10094,88 @@
         <v>1.62</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="DD23" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="DE23" t="n">
         <v>0</v>
       </c>
       <c r="DF23" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="DH23" t="n">
-        <v>101.33</v>
+        <v>100.28</v>
       </c>
       <c r="DI23" t="n">
         <v>0</v>
       </c>
       <c r="DJ23" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="DK23" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DM23" t="n">
-        <v>48.5</v>
+        <v>51</v>
       </c>
       <c r="DN23" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DP23" t="n">
-        <v>14.67</v>
+        <v>13.86</v>
       </c>
       <c r="DQ23" t="n">
         <v>11</v>
       </c>
       <c r="DR23" t="n">
-        <v>6.5</v>
+        <v>6.72</v>
       </c>
       <c r="DS23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU23" t="n">
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>61.83</v>
+        <v>60.43</v>
       </c>
       <c r="DW23" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DX23" t="n">
         <v>13</v>
       </c>
       <c r="DY23" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="EA23" t="n">
-        <v>22.5</v>
+        <v>22.28</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC23" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="24">
@@ -10177,10 +10185,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
@@ -10189,50 +10197,50 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H24" t="n">
-        <v>120</v>
+        <v>114.67</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="K24" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>41</v>
+        <v>39.67</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="P24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>5.67</v>
       </c>
       <c r="S24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="T24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
@@ -10243,28 +10251,28 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>19.67</v>
       </c>
       <c r="AA24" t="n">
-        <v>10.5</v>
+        <v>12.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AC24" t="n">
-        <v>20.5</v>
+        <v>19.33</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -10348,70 +10356,70 @@
         <v>3.25</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BH24" t="n">
         <v>9</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BO24" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BP24" t="n">
-        <v>3.33</v>
+        <v>3.86</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.67</v>
+        <v>5.14</v>
       </c>
       <c r="BR24" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS24" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT24" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BU24" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BV24" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW24" t="n">
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="CC24" t="n">
         <v>2.64</v>
@@ -10423,52 +10431,52 @@
         <v>1.51</v>
       </c>
       <c r="CF24" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="CG24" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CH24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CJ24" t="n">
         <v>2.17</v>
       </c>
       <c r="CK24" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CL24" t="n">
         <v>2.28</v>
       </c>
       <c r="CM24" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CN24" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO24" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CP24" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CQ24" t="n">
-        <v>4.84</v>
+        <v>4.71</v>
       </c>
       <c r="CR24" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CS24" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="CT24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CU24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CV24" t="n">
         <v>1.67</v>
@@ -10480,64 +10488,64 @@
         <v>1.76</v>
       </c>
       <c r="CY24" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ24" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA24" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB24" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DC24" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DD24" t="n">
-        <v>5.1</v>
+        <v>4.99</v>
       </c>
       <c r="DE24" t="n">
         <v>0</v>
       </c>
       <c r="DF24" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="DG24" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DH24" t="n">
-        <v>112.17</v>
+        <v>111</v>
       </c>
       <c r="DI24" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DJ24" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DK24" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="DM24" t="n">
-        <v>53.67</v>
+        <v>51.29</v>
       </c>
       <c r="DN24" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DO24" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="DP24" t="n">
-        <v>12</v>
+        <v>12.43</v>
       </c>
       <c r="DQ24" t="n">
-        <v>11.17</v>
+        <v>11.43</v>
       </c>
       <c r="DR24" t="n">
-        <v>6</v>
+        <v>6.43</v>
       </c>
       <c r="DS24" t="n">
         <v>0</v>
@@ -10549,28 +10557,28 @@
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>65.17</v>
+        <v>65.14</v>
       </c>
       <c r="DW24" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DX24" t="n">
-        <v>15.33</v>
+        <v>16.72</v>
       </c>
       <c r="DY24" t="n">
-        <v>10.33</v>
+        <v>11.29</v>
       </c>
       <c r="DZ24" t="n">
-        <v>5</v>
+        <v>5.43</v>
       </c>
       <c r="EA24" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="EC24" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="25">
@@ -11378,10 +11386,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
@@ -11393,79 +11401,79 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>102.5</v>
+        <v>101.33</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="N27" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="P27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Q27" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="R27" t="n">
-        <v>9</v>
+        <v>7.67</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="T27" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>55</v>
+        <v>57.67</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>17.5</v>
+        <v>16.33</v>
       </c>
       <c r="AA27" t="n">
-        <v>10</v>
+        <v>9.33</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AC27" t="n">
-        <v>22.5</v>
+        <v>22.33</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -11549,49 +11557,49 @@
         <v>4.75</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BH27" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BM27" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BN27" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="BP27" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.5</v>
+        <v>3.71</v>
       </c>
       <c r="BR27" t="n">
         <v>100</v>
       </c>
       <c r="BS27" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT27" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BV27" t="n">
         <v>0</v>
@@ -11600,19 +11608,19 @@
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BZ27" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="CA27" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="CB27" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="CC27" t="n">
         <v>6.21</v>
@@ -11621,66 +11629,66 @@
         <v>7.48</v>
       </c>
       <c r="CE27" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CF27" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="CG27" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CH27" t="n">
         <v>1.23</v>
       </c>
       <c r="CI27" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CJ27" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CK27" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL27" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CM27" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN27" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO27" t="n">
         <v>1.56</v>
       </c>
       <c r="CP27" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="CQ27" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="CR27" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CS27" t="inlineStr"/>
       <c r="CT27" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CW27" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="CX27" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY27" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CZ27" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DA27" t="n">
         <v>1.66</v>
@@ -11689,85 +11697,85 @@
         <v>1.58</v>
       </c>
       <c r="DC27" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="DD27" t="n">
-        <v>5.7</v>
+        <v>5.77</v>
       </c>
       <c r="DE27" t="n">
         <v>0</v>
       </c>
       <c r="DF27" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="DG27" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH27" t="n">
-        <v>93</v>
+        <v>93.86</v>
       </c>
       <c r="DI27" t="n">
         <v>0</v>
       </c>
       <c r="DJ27" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="DK27" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="DM27" t="n">
-        <v>50.17</v>
+        <v>52.29</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DO27" t="n">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="DP27" t="n">
-        <v>15</v>
+        <v>14.86</v>
       </c>
       <c r="DQ27" t="n">
-        <v>12.17</v>
+        <v>12.86</v>
       </c>
       <c r="DR27" t="n">
-        <v>10.17</v>
+        <v>9.43</v>
       </c>
       <c r="DS27" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT27" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU27" t="n">
         <v>0</v>
       </c>
       <c r="DV27" t="n">
-        <v>50.17</v>
+        <v>52</v>
       </c>
       <c r="DW27" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DX27" t="n">
-        <v>11.17</v>
+        <v>11.57</v>
       </c>
       <c r="DY27" t="n">
-        <v>6.83</v>
+        <v>7</v>
       </c>
       <c r="DZ27" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="EA27" t="n">
-        <v>23.67</v>
+        <v>23.43</v>
       </c>
       <c r="EB27" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="EC27" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="28">
@@ -11933,16 +11941,16 @@
         <v>12.75</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="BD28" t="n">
         <v>19.75</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BF28" t="n">
         <v>2.25</v>
@@ -12154,16 +12162,16 @@
         <v>13.14</v>
       </c>
       <c r="DY28" t="n">
-        <v>8.43</v>
+        <v>8.57</v>
       </c>
       <c r="DZ28" t="n">
-        <v>4.72</v>
+        <v>4.57</v>
       </c>
       <c r="EA28" t="n">
         <v>21.57</v>
       </c>
       <c r="EB28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC28" t="n">
         <v>1.86</v>
@@ -12575,13 +12583,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>0.25</v>
@@ -12665,130 +12673,130 @@
         <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF30" t="n">
         <v>2</v>
       </c>
-      <c r="AI30" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>51</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BG30" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="BH30" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="BL30" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BN30" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BO30" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BP30" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="BQ30" t="n">
-        <v>3.17</v>
+        <v>2.57</v>
       </c>
       <c r="BR30" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS30" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT30" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU30" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BV30" t="n">
         <v>0</v>
@@ -12797,7 +12805,7 @@
         <v>0</v>
       </c>
       <c r="BX30" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BY30" t="n">
         <v>1.88</v>
@@ -12806,16 +12814,16 @@
         <v>1.88</v>
       </c>
       <c r="CA30" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CC30" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="CD30" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="CE30" t="n">
         <v>1.65</v>
@@ -12830,16 +12838,16 @@
         <v>1.2</v>
       </c>
       <c r="CI30" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CJ30" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CK30" t="n">
         <v>1.82</v>
       </c>
       <c r="CL30" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="CM30" t="n">
         <v>1.94</v>
@@ -12854,30 +12862,30 @@
         <v>2.88</v>
       </c>
       <c r="CQ30" t="n">
-        <v>5.78</v>
+        <v>5.75</v>
       </c>
       <c r="CR30" t="n">
         <v>1.63</v>
       </c>
       <c r="CS30" t="inlineStr"/>
       <c r="CT30" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CU30" t="inlineStr"/>
       <c r="CV30" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CW30" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CY30" t="n">
         <v>2.32</v>
       </c>
       <c r="CZ30" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DA30" t="n">
         <v>1.59</v>
@@ -12886,85 +12894,85 @@
         <v>1.66</v>
       </c>
       <c r="DC30" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="DD30" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="DF30" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="DG30" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="DH30" t="n">
-        <v>91.5</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="DI30" t="n">
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DK30" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="DL30" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
       <c r="DM30" t="n">
-        <v>54.67</v>
+        <v>51.14</v>
       </c>
       <c r="DN30" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="DO30" t="n">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="DP30" t="n">
-        <v>11</v>
+        <v>11.72</v>
       </c>
       <c r="DQ30" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="DR30" t="n">
-        <v>7.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS30" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT30" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU30" t="n">
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>50.33</v>
+        <v>48.43</v>
       </c>
       <c r="DW30" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DX30" t="n">
-        <v>18.33</v>
+        <v>18</v>
       </c>
       <c r="DY30" t="n">
-        <v>13.5</v>
+        <v>12.72</v>
       </c>
       <c r="DZ30" t="n">
-        <v>4.83</v>
+        <v>5.29</v>
       </c>
       <c r="EA30" t="n">
-        <v>21.17</v>
+        <v>20.28</v>
       </c>
       <c r="EB30" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="EC30" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,127 +1472,127 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>93.33</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.33</v>
+        <v>59.75</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.33</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.67</v>
+        <v>12.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>10.25</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.67</v>
+        <v>12.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.33</v>
+        <v>11.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BD2" t="n">
         <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BH2" t="n">
-        <v>7.17</v>
+        <v>7.43</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.67</v>
+        <v>4.43</v>
       </c>
       <c r="BR2" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT2" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY2" t="n">
         <v>2.97</v>
@@ -1610,22 +1610,22 @@
         <v>3.15</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB2" t="n">
         <v>3.07</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.31</v>
+        <v>4.98</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.92</v>
+        <v>5.46</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CG2" t="n">
         <v>2.25</v>
@@ -1634,31 +1634,31 @@
         <v>1.21</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="CQ2" t="n">
-        <v>5.81</v>
+        <v>5.73</v>
       </c>
       <c r="CR2" t="n">
         <v>1.64</v>
@@ -1669,10 +1669,10 @@
       </c>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="CX2" t="n">
         <v>1.85</v>
@@ -1687,88 +1687,88 @@
         <v>1.59</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DC2" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.52</v>
+        <v>6.37</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="DH2" t="n">
-        <v>90.33</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.17</v>
+        <v>14.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.16</v>
+        <v>52.28</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.17</v>
+        <v>11.57</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.83</v>
+        <v>9.57</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.83</v>
+        <v>25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC2" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="3">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1790,49 +1790,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="H3" t="n">
-        <v>110.33</v>
+        <v>107.75</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.33</v>
+        <v>-0.25</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>79.67</v>
+        <v>81.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P3" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.67</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
         <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1844,25 +1844,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>59.33</v>
+        <v>62.75</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.33</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
         <v>11</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.67</v>
+        <v>18.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1949,46 +1949,46 @@
         <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BR3" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2000,19 +2000,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.17</v>
+        <v>3.32</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="CC3" t="n">
         <v>2.42</v>
@@ -2021,120 +2021,124 @@
         <v>2.32</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CH3" t="n">
         <v>1.26</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.95</v>
+        <v>4.84</v>
       </c>
       <c r="CR3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CV3" t="n">
         <v>1.58</v>
       </c>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="n">
+      <c r="CW3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DA3" t="n">
         <v>1.6</v>
       </c>
-      <c r="CW3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>1.62</v>
-      </c>
       <c r="DB3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.32</v>
+        <v>5.21</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="DH3" t="n">
-        <v>104</v>
+        <v>103.33</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.6</v>
+        <v>5.83</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="DM3" t="n">
-        <v>72.8</v>
+        <v>75</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DO3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.4</v>
+        <v>14.17</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.4</v>
+        <v>6.17</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2146,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>60.6</v>
+        <v>62.67</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.2</v>
+        <v>19.17</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="4">
@@ -2580,10 +2584,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -2592,49 +2596,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>91.25</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="P5" t="n">
-        <v>8.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.75</v>
+        <v>13.2</v>
       </c>
       <c r="R5" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2646,28 +2650,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>47.5</v>
+        <v>45</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z5" t="n">
         <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.25</v>
+        <v>26.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2751,49 +2755,49 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.43</v>
+        <v>4.75</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2802,19 +2806,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CC5" t="n">
         <v>4.17</v>
@@ -2826,40 +2830,40 @@
         <v>1.59</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CI5" t="n">
         <v>1.62</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CM5" t="n">
         <v>1.97</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CQ5" t="n">
-        <v>5.03</v>
+        <v>5.05</v>
       </c>
       <c r="CR5" t="n">
         <v>1.58</v>
@@ -2877,7 +2881,7 @@
         <v>1.64</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CX5" t="n">
         <v>1.81</v>
@@ -2895,52 +2899,52 @@
         <v>1.58</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.71</v>
+        <v>5.68</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="DH5" t="n">
-        <v>89.56999999999999</v>
+        <v>87.37</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.43</v>
+        <v>47.25</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.29</v>
+        <v>10.38</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.86</v>
+        <v>13.88</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.71</v>
+        <v>8.5</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2952,28 +2956,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>11</v>
+        <v>11.38</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.29</v>
+        <v>7.88</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>26.57</v>
+        <v>24.75</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="6">
@@ -2983,13 +2987,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3073,52 +3077,52 @@
         <v>3.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>73.25</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>59</v>
+        <v>53.75</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.67</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.33</v>
+        <v>12.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3130,70 +3134,70 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>36.33</v>
+        <v>34</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>22.67</v>
+        <v>20.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.29</v>
+        <v>5.62</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3205,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BY6" t="n">
         <v>3.4</v>
@@ -3214,165 +3218,169 @@
         <v>3.67</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.67</v>
+        <v>5.56</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.96</v>
+        <v>6.9</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CF6" t="n">
-        <v>4.07</v>
+        <v>3.97</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CO6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DB6" t="n">
         <v>1.67</v>
       </c>
-      <c r="CP6" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="CR6" t="n">
+      <c r="DC6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF6" t="n">
         <v>1.62</v>
       </c>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>1.86</v>
-      </c>
       <c r="DG6" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="DH6" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>53.43</v>
+        <v>51.5</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.57</v>
+        <v>12.88</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13</v>
+        <v>12.38</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42</v>
+        <v>40.12</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.140000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.43</v>
+        <v>19.62</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3827,7 +3835,7 @@
         <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q8" t="n">
         <v>17</v>
@@ -3857,19 +3865,19 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB8" t="n">
         <v>3.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -4013,13 +4021,13 @@
         <v>1.71</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CA8" t="n">
         <v>3.29</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CC8" t="n">
         <v>2.51</v>
@@ -4067,13 +4075,13 @@
         <v>4.39</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CS8" t="n">
         <v>3.29</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CU8" t="n">
         <v>1.3</v>
@@ -4082,7 +4090,7 @@
         <v>1.55</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CX8" t="n">
         <v>1.74</v>
@@ -4094,16 +4102,16 @@
         <v>2.11</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.27</v>
+        <v>5.31</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
@@ -4139,7 +4147,7 @@
         <v>3.71</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ8" t="n">
         <v>15.86</v>
@@ -4163,19 +4171,19 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.14</v>
+        <v>11.29</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.14</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.57</v>
+        <v>21.71</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC8" t="n">
         <v>1.71</v>
@@ -4311,7 +4319,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR9" t="n">
         <v>14.5</v>
@@ -4422,13 +4430,13 @@
         <v>2.85</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CC9" t="n">
         <v>4.89</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.68</v>
+        <v>5.69</v>
       </c>
       <c r="CE9" t="n">
         <v>1.63</v>
@@ -4474,11 +4482,11 @@
       </c>
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CW9" t="n">
         <v>2.52</v>
@@ -4487,7 +4495,7 @@
         <v>1.87</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CZ9" t="n">
         <v>1.94</v>
@@ -4496,13 +4504,13 @@
         <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DC9" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="DD9" t="n">
-        <v>6.39</v>
+        <v>6.44</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -4538,7 +4546,7 @@
         <v>2.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.38</v>
+        <v>13.38</v>
       </c>
       <c r="DQ9" t="n">
         <v>12.75</v>
@@ -4587,10 +4595,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -4599,82 +4607,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>77.67</v>
+        <v>81.25</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>49.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.33</v>
+        <v>8.75</v>
       </c>
       <c r="R10" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="S10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="T10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.33</v>
+        <v>49.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.67</v>
+        <v>6.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.67</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4758,70 +4766,70 @@
         <v>1.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>6.86</v>
+        <v>7.12</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="BR10" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CC10" t="n">
         <v>3.83</v>
@@ -4833,40 +4841,40 @@
         <v>1.63</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CH10" t="n">
         <v>1.22</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CK10" t="n">
         <v>1.79</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="CM10" t="n">
         <v>1.96</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CQ10" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="CR10" t="n">
         <v>1.65</v>
@@ -4877,10 +4885,10 @@
       </c>
       <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CX10" t="n">
         <v>1.84</v>
@@ -4895,88 +4903,88 @@
         <v>1.6</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DH10" t="n">
-        <v>75.72</v>
+        <v>77.75</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DM10" t="n">
-        <v>42.57</v>
+        <v>45</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DP10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.43</v>
+        <v>12.12</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.43</v>
+        <v>9.75</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.86</v>
+        <v>49.25</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="EA10" t="n">
-        <v>23</v>
+        <v>21.88</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -4986,10 +4994,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -4998,49 +5006,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>78.33</v>
+        <v>85.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="K11" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>65.67</v>
+        <v>62.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>17.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.67</v>
+        <v>9.5</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5052,28 +5060,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.67</v>
+        <v>49</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.33</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.33</v>
+        <v>7.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>27</v>
+        <v>26.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5157,43 +5165,43 @@
         <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="BR11" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5208,19 +5216,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CC11" t="n">
         <v>4.73</v>
@@ -5229,57 +5237,57 @@
         <v>5.22</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CF11" t="n">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="CQ11" t="n">
-        <v>6.59</v>
+        <v>6.83</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CS11" t="inlineStr"/>
       <c r="CT11" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CX11" t="n">
         <v>1.77</v>
@@ -5294,10 +5302,10 @@
         <v>1.65</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.52</v>
+        <v>3.63</v>
       </c>
       <c r="DD11" t="n">
         <v>6.95</v>
@@ -5306,43 +5314,43 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.56999999999999</v>
+        <v>85.62</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="DM11" t="n">
-        <v>54.72</v>
+        <v>54.62</v>
       </c>
       <c r="DN11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>18.86</v>
+        <v>18.25</v>
       </c>
       <c r="DQ11" t="n">
-        <v>8.720000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5354,28 +5362,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.29</v>
+        <v>38.62</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.28</v>
+        <v>6.75</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.57</v>
+        <v>20.12</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC11" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="12">
@@ -5385,10 +5393,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
@@ -5397,82 +5405,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>63</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.67</v>
       </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>76.33</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P12" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5556,46 +5564,46 @@
         <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.859999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.29</v>
+        <v>4.88</v>
       </c>
       <c r="BR12" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BS12" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5607,19 +5615,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BY12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>2.22</v>
       </c>
-      <c r="BZ12" t="n">
-        <v>2.21</v>
-      </c>
       <c r="CA12" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CB12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CC12" t="n">
         <v>2.57</v>
@@ -5628,34 +5636,34 @@
         <v>2.75</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="CI12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CK12" t="n">
         <v>1.31</v>
       </c>
-      <c r="CJ12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="CL12" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="CO12" t="n">
         <v>1.59</v>
@@ -5664,7 +5672,7 @@
         <v>2.89</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.04</v>
+        <v>4.29</v>
       </c>
       <c r="CR12" t="n">
         <v>1.63</v>
@@ -5675,73 +5683,73 @@
       </c>
       <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.41</v>
+        <v>6.35</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.43000000000001</v>
+        <v>87</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM12" t="n">
-        <v>48.14</v>
+        <v>51.75</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.43</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5753,28 +5761,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.43</v>
+        <v>53</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
         <v>13</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.86</v>
+        <v>4.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.72</v>
+        <v>17.62</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -6183,13 +6191,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0.5</v>
@@ -6276,49 +6284,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>95.67</v>
+        <v>91.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.33</v>
+        <v>35.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.67</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6330,73 +6338,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>45.33</v>
+        <v>45.75</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.67</v>
+        <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.859999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="BQ14" t="n">
         <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6405,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>3.17</v>
@@ -6414,19 +6422,19 @@
         <v>3.16</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.27</v>
+        <v>4.34</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CF14" t="n">
         <v>3.74</v>
@@ -6447,22 +6455,22 @@
         <v>1.7</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CM14" t="n">
         <v>2.04</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CQ14" t="n">
-        <v>5.36</v>
+        <v>5.31</v>
       </c>
       <c r="CR14" t="n">
         <v>1.64</v>
@@ -6477,7 +6485,7 @@
         <v>1.32</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CW14" t="n">
         <v>2.39</v>
@@ -6486,13 +6494,13 @@
         <v>1.72</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB14" t="n">
         <v>1.62</v>
@@ -6504,79 +6512,79 @@
         <v>6.14</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DG14" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DH14" t="n">
-        <v>81</v>
+        <v>80.75</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.86</v>
+        <v>39.12</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>13</v>
+        <v>13.62</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.71</v>
+        <v>14</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.14</v>
+        <v>10.5</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>42.57</v>
+        <v>43.12</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.14</v>
+        <v>5.62</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.43</v>
+        <v>17.62</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -6709,7 +6717,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="AR15" t="n">
         <v>11.25</v>
@@ -6820,13 +6828,13 @@
         <v>2.94</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CC15" t="n">
         <v>5.31</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.18</v>
+        <v>6.19</v>
       </c>
       <c r="CE15" t="n">
         <v>1.65</v>
@@ -6868,13 +6876,13 @@
         <v>6.03</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CS15" t="n">
         <v>3.29</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CU15" t="n">
         <v>1.3</v>
@@ -6886,25 +6894,25 @@
         <v>2.56</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DB15" t="n">
         <v>1.66</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="DD15" t="n">
-        <v>6.44</v>
+        <v>6.47</v>
       </c>
       <c r="DE15" t="n">
         <v>0.25</v>
@@ -6940,7 +6948,7 @@
         <v>1.62</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.5</v>
+        <v>10.88</v>
       </c>
       <c r="DQ15" t="n">
         <v>11.5</v>
@@ -7430,7 +7438,7 @@
         <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="Q17" t="n">
         <v>13.25</v>
@@ -7622,7 +7630,7 @@
         <v>2.82</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CC17" t="n">
         <v>2.51</v>
@@ -7696,13 +7704,13 @@
         <v>1.57</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DC17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="DD17" t="n">
-        <v>6.39</v>
+        <v>6.44</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
@@ -7738,7 +7746,7 @@
         <v>3.38</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.5</v>
+        <v>10.88</v>
       </c>
       <c r="DQ17" t="n">
         <v>12.62</v>
@@ -7787,61 +7795,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H18" t="n">
-        <v>86.25</v>
+        <v>87</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M18" t="n">
-        <v>64</v>
+        <v>60.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7853,28 +7861,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>42.25</v>
+        <v>39.4</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.75</v>
+        <v>14.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AC18" t="n">
         <v>25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7958,70 +7966,70 @@
         <v>2.67</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.140000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BM18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO18" t="n">
         <v>1</v>
       </c>
-      <c r="BN18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>0.86</v>
-      </c>
       <c r="BP18" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.29</v>
+        <v>4.88</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT18" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="CA18" t="n">
         <v>2.9</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CC18" t="n">
         <v>3.96</v>
@@ -8030,43 +8038,43 @@
         <v>3.99</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CK18" t="n">
         <v>1.74</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="CM18" t="n">
         <v>2.02</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CQ18" t="n">
-        <v>5.49</v>
+        <v>5.34</v>
       </c>
       <c r="CR18" t="n">
         <v>1.63</v>
@@ -8077,10 +8085,10 @@
       </c>
       <c r="CU18" t="inlineStr"/>
       <c r="CV18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CX18" t="n">
         <v>1.81</v>
@@ -8095,55 +8103,55 @@
         <v>1.62</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>5.84</v>
+        <v>5.72</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.14</v>
+        <v>88.38</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.86</v>
+        <v>3.63</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM18" t="n">
-        <v>56</v>
+        <v>54.87</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8155,28 +8163,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>43.86</v>
+        <v>41.88</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.57</v>
+        <v>13.13</v>
       </c>
       <c r="DY18" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.57</v>
+        <v>4.63</v>
       </c>
       <c r="EA18" t="n">
-        <v>23</v>
+        <v>23.25</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="19">
@@ -8186,94 +8194,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H19" t="n">
-        <v>84.75</v>
+        <v>93.2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M19" t="n">
-        <v>50.25</v>
+        <v>51.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P19" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.75</v>
+        <v>14.4</v>
       </c>
       <c r="R19" t="n">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>52</v>
+        <v>54.2</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>21.25</v>
+        <v>21.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8357,49 +8365,49 @@
         <v>1.67</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BH19" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8408,19 +8416,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CA19" t="n">
         <v>2.81</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CC19" t="n">
         <v>3.11</v>
@@ -8432,7 +8440,7 @@
         <v>1.66</v>
       </c>
       <c r="CF19" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="CG19" t="n">
         <v>2.16</v>
@@ -8444,7 +8452,7 @@
         <v>1.58</v>
       </c>
       <c r="CJ19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CK19" t="n">
         <v>1.74</v>
@@ -8453,19 +8461,19 @@
         <v>2.25</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CN19" t="n">
         <v>1.61</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CP19" t="n">
         <v>2.9</v>
       </c>
       <c r="CQ19" t="n">
-        <v>6.33</v>
+        <v>6.21</v>
       </c>
       <c r="CR19" t="n">
         <v>1.68</v>
@@ -8476,106 +8484,106 @@
       </c>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="DD19" t="n">
-        <v>6.49</v>
+        <v>6.46</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DH19" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DM19" t="n">
-        <v>50.28</v>
+        <v>51</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DO19" t="n">
         <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.86</v>
+        <v>11.88</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.57</v>
+        <v>12.63</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.57</v>
+        <v>6.37</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.43</v>
+        <v>52.88</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.29</v>
+        <v>11.75</v>
       </c>
       <c r="DY19" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.43</v>
+        <v>21.63</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="EC19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="20">
@@ -8585,13 +8593,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8678,49 +8686,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>73</v>
+        <v>76.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AL20" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.33</v>
+        <v>40.75</v>
       </c>
       <c r="AO20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.67</v>
+        <v>13.25</v>
       </c>
       <c r="AR20" t="n">
-        <v>15.33</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="AT20" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8732,7 +8740,7 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
@@ -8741,52 +8749,52 @@
         <v>10</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.33</v>
+        <v>5.75</v>
       </c>
       <c r="BC20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ20" t="n">
         <v>4.67</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>4.8</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8795,19 +8803,19 @@
         <v>100</v>
       </c>
       <c r="BT20" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV20" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BY20" t="n">
         <v>2.04</v>
@@ -8816,55 +8824,55 @@
         <v>2.1</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="CM20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN20" t="n">
         <v>1.58</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CQ20" t="n">
-        <v>6.03</v>
+        <v>5.86</v>
       </c>
       <c r="CR20" t="n">
         <v>1.62</v>
@@ -8875,10 +8883,10 @@
       </c>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CX20" t="n">
         <v>1.78</v>
@@ -8893,52 +8901,52 @@
         <v>1.63</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="DC20" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DD20" t="n">
-        <v>5.86</v>
+        <v>5.77</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DH20" t="n">
-        <v>81.8</v>
+        <v>82.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DK20" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DM20" t="n">
-        <v>40</v>
+        <v>41.33</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DO20" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="DQ20" t="n">
-        <v>13.4</v>
+        <v>12.5</v>
       </c>
       <c r="DR20" t="n">
         <v>8</v>
@@ -8953,28 +8961,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>49.2</v>
+        <v>50.17</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.8</v>
+        <v>10.67</v>
       </c>
       <c r="DY20" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.2</v>
+        <v>16.5</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21">
@@ -8984,10 +8992,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
@@ -8999,46 +9007,46 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="H21" t="n">
-        <v>95.67</v>
+        <v>94.25</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M21" t="n">
-        <v>64</v>
+        <v>59.25</v>
       </c>
       <c r="N21" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P21" t="n">
-        <v>12.67</v>
+        <v>15.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R21" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9050,28 +9058,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>49</v>
+        <v>46.25</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>16.33</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>12</v>
+        <v>10.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>21.33</v>
+        <v>20.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9155,37 +9163,37 @@
         <v>2.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BH21" t="n">
-        <v>7.71</v>
+        <v>7.88</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="BN21" t="n">
         <v>2</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9194,31 +9202,31 @@
         <v>100</v>
       </c>
       <c r="BT21" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.91</v>
+        <v>3.07</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.21</v>
+        <v>3.69</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CC21" t="n">
         <v>4.47</v>
@@ -9230,10 +9238,10 @@
         <v>1.6</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CH21" t="n">
         <v>1.23</v>
@@ -9242,28 +9250,28 @@
         <v>1.58</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CK21" t="n">
         <v>1.67</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="CR21" t="n">
         <v>1.64</v>
@@ -9274,10 +9282,10 @@
       </c>
       <c r="CU21" t="inlineStr"/>
       <c r="CV21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CX21" t="n">
         <v>1.71</v>
@@ -9292,88 +9300,88 @@
         <v>1.7</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DD21" t="n">
-        <v>6.08</v>
+        <v>5.99</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DH21" t="n">
-        <v>74.29000000000001</v>
+        <v>76.25</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DM21" t="n">
-        <v>54.86</v>
+        <v>53.62</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.29</v>
+        <v>14.62</v>
       </c>
       <c r="DQ21" t="n">
-        <v>14.43</v>
+        <v>13.5</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.71</v>
+        <v>6.62</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.57</v>
+        <v>43.75</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.71</v>
+        <v>11.12</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.43</v>
+        <v>8</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="EA21" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -9383,13 +9391,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9476,13 +9484,13 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
@@ -9491,109 +9499,109 @@
         <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>34.33</v>
+        <v>39.25</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="AR22" t="n">
-        <v>9.67</v>
+        <v>10.75</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>41.67</v>
+        <v>46</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>10.33</v>
+        <v>9.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.67</v>
+        <v>6.75</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BD22" t="n">
-        <v>22.67</v>
+        <v>19.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BF22" t="n">
         <v>2</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.86</v>
+        <v>6.38</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BP22" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BR22" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BS22" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BT22" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
@@ -9605,7 +9613,7 @@
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BY22" t="n">
         <v>2.43</v>
@@ -9614,69 +9622,69 @@
         <v>2.34</v>
       </c>
       <c r="CA22" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="CC22" t="n">
-        <v>4.69</v>
+        <v>4.37</v>
       </c>
       <c r="CD22" t="n">
-        <v>5.52</v>
+        <v>5.04</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CF22" t="n">
-        <v>4.15</v>
+        <v>4.23</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CH22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CJ22" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="CK22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CM22" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CN22" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="CP22" t="n">
-        <v>3.03</v>
+        <v>3.14</v>
       </c>
       <c r="CQ22" t="n">
-        <v>5.9</v>
+        <v>6.22</v>
       </c>
       <c r="CR22" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CS22" t="inlineStr"/>
       <c r="CT22" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="CU22" t="inlineStr"/>
       <c r="CV22" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CW22" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="CX22" t="n">
         <v>1.91</v>
@@ -9691,10 +9699,10 @@
         <v>1.55</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="DC22" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="DD22" t="n">
         <v>6.79</v>
@@ -9703,13 +9711,13 @@
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DH22" t="n">
-        <v>87.56999999999999</v>
+        <v>89.12</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
@@ -9718,58 +9726,58 @@
         <v>2</v>
       </c>
       <c r="DK22" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="DL22" t="n">
         <v>0</v>
       </c>
       <c r="DM22" t="n">
-        <v>47.57</v>
+        <v>48.38</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DO22" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="DP22" t="n">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="DQ22" t="n">
-        <v>10.57</v>
+        <v>11</v>
       </c>
       <c r="DR22" t="n">
-        <v>5.86</v>
+        <v>5.38</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>47.86</v>
+        <v>49.25</v>
       </c>
       <c r="DW22" t="n">
         <v>0</v>
       </c>
       <c r="DX22" t="n">
-        <v>9.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.72</v>
+        <v>6.38</v>
       </c>
       <c r="DZ22" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.29</v>
+        <v>18.25</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="EC22" t="n">
         <v>2</v>
@@ -10185,13 +10193,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -10278,49 +10286,49 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>108.25</v>
+        <v>105</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL24" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN24" t="n">
-        <v>60</v>
+        <v>55.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>10.75</v>
+        <v>11.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AV24" t="n">
         <v>0</v>
@@ -10332,82 +10340,82 @@
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>62.25</v>
+        <v>64.2</v>
       </c>
       <c r="AZ24" t="n">
         <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BD24" t="n">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG24" t="n">
         <v>2</v>
       </c>
       <c r="BH24" t="n">
-        <v>9</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI24" t="n">
         <v>2</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN24" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BO24" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BP24" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="BR24" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS24" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BT24" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU24" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV24" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW24" t="n">
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BY24" t="n">
         <v>1.56</v>
@@ -10416,22 +10424,22 @@
         <v>1.63</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="CC24" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="CD24" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="CE24" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CF24" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CG24" t="n">
         <v>2.44</v>
@@ -10440,16 +10448,16 @@
         <v>1.26</v>
       </c>
       <c r="CI24" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CJ24" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CK24" t="n">
         <v>1.73</v>
       </c>
       <c r="CL24" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CM24" t="n">
         <v>2</v>
@@ -10458,13 +10466,13 @@
         <v>1.6</v>
       </c>
       <c r="CO24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CP24" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CQ24" t="n">
-        <v>4.71</v>
+        <v>4.65</v>
       </c>
       <c r="CR24" t="n">
         <v>1.54</v>
@@ -10479,10 +10487,10 @@
         <v>1.33</v>
       </c>
       <c r="CV24" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CW24" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CX24" t="n">
         <v>1.76</v>
@@ -10500,52 +10508,52 @@
         <v>1.5</v>
       </c>
       <c r="DC24" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DD24" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="DE24" t="n">
         <v>0</v>
       </c>
       <c r="DF24" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DG24" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DH24" t="n">
-        <v>111</v>
+        <v>108.63</v>
       </c>
       <c r="DI24" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ24" t="n">
         <v>3</v>
       </c>
       <c r="DK24" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="DM24" t="n">
-        <v>51.29</v>
+        <v>49.75</v>
       </c>
       <c r="DN24" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="DO24" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DP24" t="n">
-        <v>12.43</v>
+        <v>12</v>
       </c>
       <c r="DQ24" t="n">
-        <v>11.43</v>
+        <v>11.62</v>
       </c>
       <c r="DR24" t="n">
-        <v>6.43</v>
+        <v>6.38</v>
       </c>
       <c r="DS24" t="n">
         <v>0</v>
@@ -10557,28 +10565,28 @@
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>65.14</v>
+        <v>66</v>
       </c>
       <c r="DW24" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DX24" t="n">
-        <v>16.72</v>
+        <v>16.13</v>
       </c>
       <c r="DY24" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="DZ24" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="EA24" t="n">
-        <v>21.14</v>
+        <v>21.87</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="EC24" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="25">
@@ -10588,13 +10596,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -10678,52 +10686,52 @@
         <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG25" t="n">
         <v>2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AI25" t="n">
-        <v>87.33</v>
+        <v>89.75</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AN25" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11.33</v>
+        <v>10.25</v>
       </c>
       <c r="AR25" t="n">
-        <v>16.67</v>
+        <v>18.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AV25" t="n">
         <v>0</v>
@@ -10735,70 +10743,70 @@
         <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>48.67</v>
+        <v>52</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="BD25" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BG25" t="n">
         <v>2</v>
       </c>
       <c r="BH25" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI25" t="n">
         <v>2</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BN25" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BO25" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BP25" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BR25" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS25" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT25" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
@@ -10810,7 +10818,7 @@
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY25" t="n">
         <v>2.01</v>
@@ -10819,55 +10827,55 @@
         <v>2.02</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CB25" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CC25" t="n">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="CD25" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="CE25" t="n">
         <v>1.56</v>
       </c>
       <c r="CF25" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CG25" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CH25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CI25" t="n">
         <v>1.6</v>
       </c>
       <c r="CJ25" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CK25" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CL25" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="CM25" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CN25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CO25" t="n">
         <v>1.54</v>
       </c>
       <c r="CP25" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CQ25" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="CR25" t="n">
         <v>1.6</v>
@@ -10881,7 +10889,7 @@
         <v>1.62</v>
       </c>
       <c r="CW25" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CX25" t="n">
         <v>1.85</v>
@@ -10896,88 +10904,88 @@
         <v>1.58</v>
       </c>
       <c r="DB25" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DC25" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="DD25" t="n">
-        <v>5.82</v>
+        <v>5.76</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF25" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DG25" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="DH25" t="n">
-        <v>100</v>
+        <v>99.62</v>
       </c>
       <c r="DI25" t="n">
         <v>0</v>
       </c>
       <c r="DJ25" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DK25" t="n">
-        <v>4.86</v>
+        <v>5.25</v>
       </c>
       <c r="DL25" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="DM25" t="n">
-        <v>61.29</v>
+        <v>61.88</v>
       </c>
       <c r="DN25" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="DO25" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="DP25" t="n">
-        <v>9.279999999999999</v>
+        <v>9</v>
       </c>
       <c r="DQ25" t="n">
-        <v>15.72</v>
+        <v>16.75</v>
       </c>
       <c r="DR25" t="n">
-        <v>7</v>
+        <v>6.38</v>
       </c>
       <c r="DS25" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT25" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU25" t="n">
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>52.14</v>
+        <v>53.38</v>
       </c>
       <c r="DW25" t="n">
         <v>0</v>
       </c>
       <c r="DX25" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="DY25" t="n">
-        <v>7.57</v>
+        <v>7.25</v>
       </c>
       <c r="DZ25" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="EA25" t="n">
-        <v>18.43</v>
+        <v>19</v>
       </c>
       <c r="EB25" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="EC25" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="26">
@@ -10987,13 +10995,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>0.25</v>
@@ -11080,49 +11088,49 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AH26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>88</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AO26" t="n">
         <v>1</v>
       </c>
-      <c r="AI26" t="n">
-        <v>90.33</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AP26" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ26" t="n">
-        <v>16</v>
+        <v>14.25</v>
       </c>
       <c r="AR26" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>10.67</v>
+        <v>10.75</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -11134,82 +11142,82 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>46.67</v>
+        <v>45.75</v>
       </c>
       <c r="AZ26" t="n">
         <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.33</v>
+        <v>7.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="BD26" t="n">
-        <v>23.33</v>
+        <v>22.75</v>
       </c>
       <c r="BE26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL26" t="n">
         <v>0.75</v>
       </c>
-      <c r="BF26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>0.86</v>
-      </c>
       <c r="BM26" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BN26" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BP26" t="n">
-        <v>3.29</v>
+        <v>4.38</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BR26" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BS26" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BT26" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BU26" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV26" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW26" t="n">
         <v>0</v>
       </c>
       <c r="BX26" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BY26" t="n">
         <v>2.2</v>
@@ -11218,22 +11226,22 @@
         <v>2.23</v>
       </c>
       <c r="CA26" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CB26" t="n">
         <v>2.86</v>
       </c>
       <c r="CC26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="CD26" t="n">
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
       <c r="CE26" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CF26" t="n">
-        <v>4.37</v>
+        <v>4.32</v>
       </c>
       <c r="CG26" t="n">
         <v>2.06</v>
@@ -11245,31 +11253,31 @@
         <v>1.45</v>
       </c>
       <c r="CJ26" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CK26" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CL26" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CM26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CN26" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CO26" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CP26" t="n">
         <v>3.24</v>
       </c>
       <c r="CQ26" t="n">
-        <v>7.21</v>
+        <v>7.12</v>
       </c>
       <c r="CR26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CS26" t="inlineStr"/>
       <c r="CT26" t="n">
@@ -11277,19 +11285,19 @@
       </c>
       <c r="CU26" t="inlineStr"/>
       <c r="CV26" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CW26" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CX26" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CY26" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CZ26" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DA26" t="n">
         <v>1.54</v>
@@ -11304,79 +11312,79 @@
         <v>7.28</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DG26" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DH26" t="n">
-        <v>90.28</v>
+        <v>89.12</v>
       </c>
       <c r="DI26" t="n">
         <v>0</v>
       </c>
       <c r="DJ26" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="DK26" t="n">
-        <v>3.28</v>
+        <v>3.62</v>
       </c>
       <c r="DL26" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DM26" t="n">
-        <v>45.72</v>
+        <v>45.62</v>
       </c>
       <c r="DN26" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DO26" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="DP26" t="n">
-        <v>13.57</v>
+        <v>13</v>
       </c>
       <c r="DQ26" t="n">
-        <v>13.86</v>
+        <v>13.62</v>
       </c>
       <c r="DR26" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS26" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU26" t="n">
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>51.29</v>
+        <v>50.25</v>
       </c>
       <c r="DW26" t="n">
         <v>0</v>
       </c>
       <c r="DX26" t="n">
-        <v>9.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DY26" t="n">
-        <v>6.86</v>
+        <v>6.75</v>
       </c>
       <c r="DZ26" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="EA26" t="n">
-        <v>22.71</v>
+        <v>22.5</v>
       </c>
       <c r="EB26" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC26" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="27">
@@ -11785,10 +11793,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>4</v>
@@ -11797,49 +11805,49 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>46</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>78</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="K28" t="n">
-        <v>7</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="M28" t="n">
-        <v>42.67</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P28" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>11</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="T28" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -11851,28 +11859,28 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="n">
         <v>9</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="AC28" t="n">
-        <v>24</v>
+        <v>23.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -11956,46 +11964,46 @@
         <v>2.25</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="BH28" t="n">
-        <v>8.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BL28" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN28" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BP28" t="n">
-        <v>3</v>
+        <v>4.12</v>
       </c>
       <c r="BQ28" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="BR28" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BS28" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT28" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU28" t="n">
         <v>0</v>
@@ -12007,19 +12015,19 @@
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="CA28" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CB28" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CC28" t="n">
         <v>3.54</v>
@@ -12028,75 +12036,75 @@
         <v>4.01</v>
       </c>
       <c r="CE28" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CF28" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="CG28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CH28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CI28" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CJ28" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CK28" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CL28" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CM28" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CN28" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CO28" t="n">
         <v>1.58</v>
       </c>
       <c r="CP28" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="CQ28" t="n">
-        <v>5.9</v>
+        <v>5.98</v>
       </c>
       <c r="CR28" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CS28" t="inlineStr"/>
       <c r="CT28" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CW28" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CX28" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CY28" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CZ28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DA28" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB28" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DC28" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="DD28" t="n">
         <v>6.06</v>
@@ -12105,43 +12113,43 @@
         <v>0</v>
       </c>
       <c r="DF28" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DG28" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DH28" t="n">
-        <v>85</v>
+        <v>85.88</v>
       </c>
       <c r="DI28" t="n">
         <v>0</v>
       </c>
       <c r="DJ28" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DK28" t="n">
-        <v>5</v>
+        <v>5.88</v>
       </c>
       <c r="DL28" t="n">
         <v>0</v>
       </c>
       <c r="DM28" t="n">
-        <v>45.14</v>
+        <v>46.5</v>
       </c>
       <c r="DN28" t="n">
         <v>1</v>
       </c>
       <c r="DO28" t="n">
-        <v>1.28</v>
+        <v>2.25</v>
       </c>
       <c r="DP28" t="n">
-        <v>10.14</v>
+        <v>10.5</v>
       </c>
       <c r="DQ28" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="DR28" t="n">
-        <v>6.57</v>
+        <v>6.75</v>
       </c>
       <c r="DS28" t="n">
         <v>0</v>
@@ -12153,28 +12161,28 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>55.71</v>
+        <v>55.88</v>
       </c>
       <c r="DW28" t="n">
         <v>0</v>
       </c>
       <c r="DX28" t="n">
-        <v>13.14</v>
+        <v>13.38</v>
       </c>
       <c r="DY28" t="n">
-        <v>8.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ28" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="EA28" t="n">
-        <v>21.57</v>
+        <v>21.75</v>
       </c>
       <c r="EB28" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="EC28" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="29">
@@ -12184,10 +12192,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
@@ -12196,46 +12204,46 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H29" t="n">
-        <v>71.67</v>
+        <v>83.75</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M29" t="n">
-        <v>42</v>
+        <v>51.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>11.67</v>
+        <v>11.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14.25</v>
       </c>
       <c r="R29" t="n">
-        <v>10.67</v>
+        <v>9.5</v>
       </c>
       <c r="S29" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
@@ -12250,28 +12258,28 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>43</v>
+        <v>45.5</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>12.67</v>
+        <v>14.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB29" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>14.33</v>
+        <v>16</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
         <v>0.25</v>
@@ -12355,70 +12363,70 @@
         <v>1.75</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BH29" t="n">
-        <v>8.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BL29" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="BP29" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="BQ29" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="BR29" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS29" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT29" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU29" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BV29" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="BZ29" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="CA29" t="n">
         <v>2.98</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CC29" t="n">
         <v>3.84</v>
@@ -12427,13 +12435,13 @@
         <v>4.12</v>
       </c>
       <c r="CE29" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CF29" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CG29" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CH29" t="n">
         <v>1.21</v>
@@ -12445,51 +12453,51 @@
         <v>2.29</v>
       </c>
       <c r="CK29" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CL29" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="CM29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CN29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CO29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CP29" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CQ29" t="n">
-        <v>5.92</v>
+        <v>5.8</v>
       </c>
       <c r="CR29" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CS29" t="inlineStr"/>
       <c r="CT29" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CU29" t="inlineStr"/>
       <c r="CV29" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CW29" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CX29" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CY29" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CZ29" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DA29" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB29" t="n">
         <v>1.66</v>
@@ -12501,46 +12509,46 @@
         <v>6.46</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DG29" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="DH29" t="n">
-        <v>79.14</v>
+        <v>84.25</v>
       </c>
       <c r="DI29" t="n">
         <v>0</v>
       </c>
       <c r="DJ29" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DK29" t="n">
-        <v>3.71</v>
+        <v>4.38</v>
       </c>
       <c r="DL29" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DM29" t="n">
-        <v>44.29</v>
+        <v>48.75</v>
       </c>
       <c r="DN29" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DO29" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="DP29" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="DQ29" t="n">
-        <v>13</v>
+        <v>13.62</v>
       </c>
       <c r="DR29" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="DS29" t="n">
         <v>0</v>
@@ -12552,28 +12560,28 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>43.57</v>
+        <v>44.75</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
       </c>
       <c r="DX29" t="n">
-        <v>12.29</v>
+        <v>13.38</v>
       </c>
       <c r="DY29" t="n">
-        <v>7.29</v>
+        <v>8.25</v>
       </c>
       <c r="DZ29" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="EA29" t="n">
-        <v>15.14</v>
+        <v>15.88</v>
       </c>
       <c r="EB29" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="EC29" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="30">
@@ -12583,13 +12591,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
         <v>0.25</v>
@@ -12673,130 +12681,130 @@
         <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>90.67</v>
+        <v>93</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL30" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN30" t="n">
         <v>44</v>
       </c>
       <c r="AO30" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13.67</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>10.67</v>
+        <v>11.5</v>
       </c>
       <c r="AS30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB30" t="n">
         <v>9</v>
       </c>
-      <c r="AT30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>42.67</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>10.67</v>
-      </c>
       <c r="BC30" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>16.33</v>
+        <v>17</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="BF30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG30" t="n">
         <v>2</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>1.86</v>
       </c>
       <c r="BH30" t="n">
         <v>7</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BL30" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BN30" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BO30" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BP30" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BQ30" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BR30" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BS30" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BT30" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU30" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV30" t="n">
         <v>0</v>
@@ -12805,7 +12813,7 @@
         <v>0</v>
       </c>
       <c r="BX30" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BY30" t="n">
         <v>1.88</v>
@@ -12814,46 +12822,46 @@
         <v>1.88</v>
       </c>
       <c r="CA30" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CC30" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="CD30" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CE30" t="n">
         <v>1.65</v>
       </c>
       <c r="CF30" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CG30" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CH30" t="n">
         <v>1.2</v>
       </c>
       <c r="CI30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CJ30" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CK30" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CL30" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CM30" t="n">
         <v>1.94</v>
       </c>
       <c r="CN30" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO30" t="n">
         <v>1.63</v>
@@ -12862,7 +12870,7 @@
         <v>2.88</v>
       </c>
       <c r="CQ30" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="CR30" t="n">
         <v>1.63</v>
@@ -12873,106 +12881,106 @@
       </c>
       <c r="CU30" t="inlineStr"/>
       <c r="CV30" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CW30" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CY30" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CZ30" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DA30" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DB30" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DC30" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="DD30" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DF30" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="DG30" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DH30" t="n">
-        <v>91.43000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="DI30" t="n">
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DK30" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="DL30" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DM30" t="n">
-        <v>51.14</v>
+        <v>50.25</v>
       </c>
       <c r="DN30" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DO30" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="DP30" t="n">
-        <v>11.72</v>
+        <v>11.62</v>
       </c>
       <c r="DQ30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="DR30" t="n">
-        <v>8.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DS30" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT30" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU30" t="n">
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>48.43</v>
+        <v>47</v>
       </c>
       <c r="DW30" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX30" t="n">
-        <v>18</v>
+        <v>16.62</v>
       </c>
       <c r="DY30" t="n">
-        <v>12.72</v>
+        <v>11.62</v>
       </c>
       <c r="DZ30" t="n">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="EA30" t="n">
-        <v>20.28</v>
+        <v>20.12</v>
       </c>
       <c r="EB30" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="EC30" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="31">
@@ -12982,13 +12990,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
         <v>0.25</v>
@@ -13075,46 +13083,46 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>80.67</v>
+        <v>91</v>
       </c>
       <c r="AJ31" t="n">
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AN31" t="n">
-        <v>56.33</v>
+        <v>56.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31" t="n">
-        <v>12.67</v>
+        <v>11.25</v>
       </c>
       <c r="AR31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AU31" t="n">
         <v>1</v>
@@ -13129,70 +13137,70 @@
         <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>55.33</v>
+        <v>52.25</v>
       </c>
       <c r="AZ31" t="n">
         <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>10.33</v>
+        <v>9.75</v>
       </c>
       <c r="BB31" t="n">
         <v>7</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="BD31" t="n">
-        <v>19.33</v>
+        <v>19.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BF31" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BH31" t="n">
-        <v>8.859999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BN31" t="n">
         <v>1</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BP31" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="BQ31" t="n">
-        <v>4.57</v>
+        <v>5.12</v>
       </c>
       <c r="BR31" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS31" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BT31" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU31" t="n">
         <v>0</v>
@@ -13204,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="BX31" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY31" t="n">
         <v>2.55</v>
@@ -13213,43 +13221,43 @@
         <v>2.7</v>
       </c>
       <c r="CA31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CB31" t="n">
         <v>2.86</v>
       </c>
-      <c r="CB31" t="n">
-        <v>2.87</v>
-      </c>
       <c r="CC31" t="n">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
       <c r="CD31" t="n">
-        <v>3.17</v>
+        <v>3.44</v>
       </c>
       <c r="CE31" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CF31" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CG31" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CH31" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CI31" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CJ31" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CK31" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL31" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM31" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CN31" t="n">
         <v>1.64</v>
@@ -13258,10 +13266,10 @@
         <v>1.58</v>
       </c>
       <c r="CP31" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CQ31" t="n">
-        <v>5.84</v>
+        <v>5.86</v>
       </c>
       <c r="CR31" t="n">
         <v>1.64</v>
@@ -13275,70 +13283,70 @@
         <v>1.6</v>
       </c>
       <c r="CW31" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CX31" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY31" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CZ31" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DA31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DC31" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="DD31" t="n">
-        <v>6.47</v>
+        <v>6.41</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF31" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DG31" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DH31" t="n">
-        <v>95.72</v>
+        <v>99</v>
       </c>
       <c r="DI31" t="n">
         <v>0</v>
       </c>
       <c r="DJ31" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="DK31" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="DM31" t="n">
-        <v>52</v>
+        <v>52.62</v>
       </c>
       <c r="DN31" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="DP31" t="n">
-        <v>10.57</v>
+        <v>10.12</v>
       </c>
       <c r="DQ31" t="n">
-        <v>12.29</v>
+        <v>12.38</v>
       </c>
       <c r="DR31" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="DS31" t="n">
         <v>0</v>
@@ -13350,28 +13358,28 @@
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>53.86</v>
+        <v>52.5</v>
       </c>
       <c r="DW31" t="n">
         <v>0</v>
       </c>
       <c r="DX31" t="n">
-        <v>11</v>
+        <v>10.62</v>
       </c>
       <c r="DY31" t="n">
-        <v>7.43</v>
+        <v>7.38</v>
       </c>
       <c r="DZ31" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="EA31" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="EB31" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="EC31" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -2193,82 +2193,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>75.67</v>
+        <v>78.25</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>64.33</v>
+        <v>68</v>
       </c>
       <c r="N4" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.67</v>
+        <v>13.25</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="V4" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52.67</v>
+        <v>51.25</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>17</v>
+        <v>16.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.67</v>
+        <v>11.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>24</v>
+        <v>24.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2352,49 +2352,49 @@
         <v>3.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BH4" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.29</v>
+        <v>3.88</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2403,19 +2403,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CC4" t="n">
         <v>3.96</v>
@@ -2424,28 +2424,28 @@
         <v>4.5</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="CK4" t="n">
         <v>1.71</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CM4" t="n">
         <v>2.05</v>
@@ -2460,13 +2460,13 @@
         <v>2.49</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.78</v>
+        <v>4.73</v>
       </c>
       <c r="CR4" t="n">
         <v>1.58</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="CT4" t="n">
         <v>2.43</v>
@@ -2478,7 +2478,7 @@
         <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CX4" t="n">
         <v>1.77</v>
@@ -2490,13 +2490,13 @@
         <v>2.06</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="DD4" t="n">
         <v>5.27</v>
@@ -2505,76 +2505,76 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.29000000000001</v>
+        <v>85.38</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.57</v>
+        <v>4.88</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>57.57</v>
+        <v>60.25</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.28</v>
+        <v>12.88</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.57</v>
+        <v>12.88</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.29</v>
+        <v>49.88</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.57</v>
+        <v>12.75</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="EA4" t="n">
-        <v>25</v>
+        <v>25.25</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="EC4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3483,46 +3483,46 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>93.25</v>
+        <v>90.8</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL7" t="n">
         <v>3</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>52.75</v>
+        <v>52.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR7" t="n">
         <v>9</v>
       </c>
-      <c r="AR7" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
         <v>1</v>
@@ -3537,73 +3537,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>46.25</v>
+        <v>46.8</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.25</v>
+        <v>11.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.75</v>
+        <v>18.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="BF7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BG7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BO7" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BP7" t="n">
         <v>2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="BR7" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY7" t="n">
         <v>1.84</v>
@@ -3621,73 +3621,73 @@
         <v>1.86</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.73</v>
+        <v>5.02</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CS7" t="n">
         <v>3.39</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="CU7" t="n">
         <v>1.32</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="CX7" t="n">
         <v>1.75</v>
@@ -3714,43 +3714,43 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.56999999999999</v>
+        <v>94.62</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="DL7" t="n">
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>55</v>
+        <v>54.75</v>
       </c>
       <c r="DN7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DO7" t="n">
         <v>1</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.720000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.279999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.710000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.14</v>
+        <v>50.88</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.57</v>
+        <v>12.12</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.289999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.86</v>
+        <v>19.88</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
         <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="Q8" t="n">
         <v>17</v>
@@ -3886,49 +3886,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>62</v>
+        <v>51.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="AQ8" t="n">
         <v>8</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>11.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3940,70 +3940,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>21.5</v>
+        <v>19.67</v>
       </c>
       <c r="BE8" t="n">
         <v>1.26</v>
       </c>
       <c r="BF8" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BH8" t="n">
         <v>9</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.14</v>
+        <v>4.38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="BR8" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BS8" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY8" t="n">
         <v>1.71</v>
@@ -4024,46 +4024,46 @@
         <v>1.75</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="CM8" t="n">
         <v>1.76</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CO8" t="n">
         <v>1.5</v>
@@ -4072,7 +4072,7 @@
         <v>2.7</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="CR8" t="n">
         <v>1.56</v>
@@ -4087,106 +4087,106 @@
         <v>1.3</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.56999999999999</v>
+        <v>95.38</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.57</v>
+        <v>5.88</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>56.86</v>
+        <v>53.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.71</v>
+        <v>3.13</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.859999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.86</v>
+        <v>15</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.86</v>
+        <v>7.88</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.43</v>
+        <v>61.12</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.29</v>
+        <v>11.25</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.140000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.71</v>
+        <v>21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="9">
@@ -4667,10 +4667,10 @@
         <v>0.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
@@ -4679,7 +4679,7 @@
         <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
         <v>1.5</v>
@@ -4969,10 +4969,10 @@
         <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.880000000000001</v>
+        <v>9</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.62</v>
+        <v>5.75</v>
       </c>
       <c r="DZ10" t="n">
         <v>3.25</v>
@@ -5036,7 +5036,7 @@
         <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>17.75</v>
+        <v>17.5</v>
       </c>
       <c r="Q11" t="n">
         <v>9.5</v>
@@ -5060,16 +5060,16 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49</v>
+        <v>48.75</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
         <v>3.25</v>
@@ -5078,7 +5078,7 @@
         <v>26.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE11" t="n">
         <v>4.25</v>
@@ -5344,7 +5344,7 @@
         <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>18.25</v>
+        <v>18.12</v>
       </c>
       <c r="DQ11" t="n">
         <v>9.119999999999999</v>
@@ -5362,16 +5362,16 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.62</v>
+        <v>38.5</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.619999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="DZ11" t="n">
         <v>2.88</v>
@@ -5380,7 +5380,7 @@
         <v>20.12</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC11" t="n">
         <v>4.38</v>
@@ -5465,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="AB12" t="n">
         <v>5.5</v>
@@ -5477,7 +5477,7 @@
         <v>17.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
         <v>2.75</v>
@@ -5767,10 +5767,10 @@
         <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.5</v>
@@ -5792,13 +5792,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5885,49 +5885,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>84.75</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.5</v>
+        <v>59</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.25</v>
+        <v>13.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -5948,64 +5948,64 @@
         <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>28.25</v>
+        <v>26.8</v>
       </c>
       <c r="BE13" t="n">
         <v>1.24</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.71</v>
+        <v>4.62</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="BR13" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU13" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BY13" t="n">
         <v>4.2</v>
@@ -6023,55 +6023,55 @@
         <v>4.61</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CB13" t="n">
         <v>3.07</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.09</v>
+        <v>4.91</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.7</v>
+        <v>5.59</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CH13" t="n">
         <v>1.19</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="CQ13" t="n">
-        <v>6.23</v>
+        <v>6.07</v>
       </c>
       <c r="CR13" t="n">
         <v>1.63</v>
@@ -6085,7 +6085,7 @@
         <v>1.53</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CX13" t="n">
         <v>2.04</v>
@@ -6106,49 +6106,49 @@
         <v>2.98</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.28</v>
+        <v>6.3</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="DH13" t="n">
-        <v>79.56999999999999</v>
+        <v>82</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.71</v>
+        <v>4.25</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>52.71</v>
+        <v>54.25</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.86</v>
+        <v>11.63</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.57</v>
+        <v>12.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6160,28 +6160,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.29</v>
+        <v>43.75</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11</v>
+        <v>10.87</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.43</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>24</v>
+        <v>23.62</v>
       </c>
       <c r="EB13" t="n">
         <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="14">
@@ -6717,7 +6717,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
         <v>11.25</v>
@@ -6948,7 +6948,7 @@
         <v>1.62</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.88</v>
+        <v>10.5</v>
       </c>
       <c r="DQ15" t="n">
         <v>11.5</v>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
@@ -7012,16 +7012,16 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="H16" t="n">
-        <v>96</v>
+        <v>90.25</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -7030,28 +7030,28 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>43</v>
+        <v>43.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>13.67</v>
+        <v>13.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>19.67</v>
+        <v>17.5</v>
       </c>
       <c r="R16" t="n">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="S16" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7063,28 +7063,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54.67</v>
+        <v>53.75</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.33</v>
+        <v>11.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.33</v>
+        <v>7.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.33</v>
+        <v>17.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7168,49 +7168,49 @@
         <v>3.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.140000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.43</v>
+        <v>4.12</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="BR16" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS16" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CC16" t="n">
         <v>2.84</v>
@@ -7243,40 +7243,40 @@
         <v>1.74</v>
       </c>
       <c r="CF16" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CH16" t="n">
         <v>1.16</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CP16" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="CR16" t="n">
         <v>1.76</v>
@@ -7317,76 +7317,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="DH16" t="n">
-        <v>87</v>
+        <v>85.25</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DM16" t="n">
-        <v>41</v>
+        <v>41.38</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.86</v>
+        <v>12.75</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.57</v>
+        <v>15</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.71</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>56.14</v>
+        <v>55.5</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DX16" t="n">
-        <v>8.859999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.14</v>
+        <v>7</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="EA16" t="n">
-        <v>22.57</v>
+        <v>21</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -7861,16 +7861,16 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>39.4</v>
+        <v>39.6</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB18" t="n">
         <v>5.2</v>
@@ -7879,7 +7879,7 @@
         <v>25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="n">
         <v>1.2</v>
@@ -8163,16 +8163,16 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>41.88</v>
+        <v>42</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.13</v>
+        <v>13.38</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.63</v>
@@ -8181,7 +8181,7 @@
         <v>23.25</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="EC18" t="n">
         <v>1.75</v>
@@ -8593,10 +8593,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -8608,47 +8608,47 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>95</v>
+        <v>94.33</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="M20" t="n">
-        <v>42.5</v>
+        <v>46.67</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>9.5</v>
+        <v>8.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="R20" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="S20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
@@ -8659,28 +8659,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>52.5</v>
+        <v>51</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA20" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8767,34 +8767,34 @@
         <v>3</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI20" t="n">
         <v>3</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BN20" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BO20" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BP20" t="n">
-        <v>4</v>
+        <v>3.29</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.67</v>
+        <v>3.86</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8803,31 +8803,31 @@
         <v>100</v>
       </c>
       <c r="BT20" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BU20" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV20" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>83.33</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CC20" t="n">
         <v>3.28</v>
@@ -8839,40 +8839,40 @@
         <v>1.64</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="CG20" t="n">
         <v>2.17</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="CM20" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CO20" t="n">
         <v>1.57</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CQ20" t="n">
-        <v>5.86</v>
+        <v>5.81</v>
       </c>
       <c r="CR20" t="n">
         <v>1.62</v>
@@ -8883,22 +8883,22 @@
       </c>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="DB20" t="n">
         <v>1.63</v>
@@ -8907,49 +8907,49 @@
         <v>3</v>
       </c>
       <c r="DD20" t="n">
-        <v>5.77</v>
+        <v>5.88</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="DH20" t="n">
-        <v>82.5</v>
+        <v>84</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DK20" t="n">
-        <v>3.67</v>
+        <v>4.28</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.33</v>
+        <v>43.29</v>
       </c>
       <c r="DN20" t="n">
         <v>1</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DP20" t="n">
-        <v>12</v>
+        <v>11.29</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.5</v>
+        <v>11.86</v>
       </c>
       <c r="DR20" t="n">
-        <v>8</v>
+        <v>7.71</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8961,28 +8961,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>50.17</v>
+        <v>49.86</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.67</v>
+        <v>10.43</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.5</v>
+        <v>17.71</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="21">
@@ -9514,7 +9514,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="AR22" t="n">
         <v>10.75</v>
@@ -9538,16 +9538,16 @@
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>46</v>
+        <v>46.25</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="BC22" t="n">
         <v>2.75</v>
@@ -9556,7 +9556,7 @@
         <v>19.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BF22" t="n">
         <v>2</v>
@@ -9741,7 +9741,7 @@
         <v>1.12</v>
       </c>
       <c r="DP22" t="n">
-        <v>10.75</v>
+        <v>10.62</v>
       </c>
       <c r="DQ22" t="n">
         <v>11</v>
@@ -9759,16 +9759,16 @@
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>49.25</v>
+        <v>49.38</v>
       </c>
       <c r="DW22" t="n">
         <v>0</v>
       </c>
       <c r="DX22" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.38</v>
+        <v>6.62</v>
       </c>
       <c r="DZ22" t="n">
         <v>3.12</v>
@@ -9777,7 +9777,7 @@
         <v>18.25</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="EC22" t="n">
         <v>2</v>
@@ -9790,13 +9790,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -9883,127 +9883,127 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AI23" t="n">
-        <v>106.25</v>
+        <v>99.8</v>
       </c>
       <c r="AJ23" t="n">
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>35.25</v>
+        <v>42.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP23" t="n">
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AU23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>62.75</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BO23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BP23" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="BR23" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS23" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT23" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BU23" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY23" t="n">
         <v>2.2</v>
@@ -10021,22 +10021,22 @@
         <v>2.31</v>
       </c>
       <c r="CA23" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CC23" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CD23" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CE23" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="CG23" t="n">
         <v>2.46</v>
@@ -10045,19 +10045,19 @@
         <v>1.26</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK23" t="n">
         <v>1.75</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CM23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CN23" t="n">
         <v>1.58</v>
@@ -10069,16 +10069,16 @@
         <v>2.52</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.78</v>
+        <v>4.73</v>
       </c>
       <c r="CR23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CS23" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CU23" t="n">
         <v>1.32</v>
@@ -10087,16 +10087,16 @@
         <v>1.73</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CZ23" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DA23" t="n">
         <v>1.62</v>
@@ -10105,85 +10105,85 @@
         <v>1.51</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DD23" t="n">
-        <v>5.1</v>
+        <v>5.12</v>
       </c>
       <c r="DE23" t="n">
         <v>0</v>
       </c>
       <c r="DF23" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="DH23" t="n">
-        <v>100.28</v>
+        <v>97</v>
       </c>
       <c r="DI23" t="n">
         <v>0</v>
       </c>
       <c r="DJ23" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DK23" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM23" t="n">
-        <v>51</v>
+        <v>53.5</v>
       </c>
       <c r="DN23" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DP23" t="n">
-        <v>13.86</v>
+        <v>13.75</v>
       </c>
       <c r="DQ23" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="DR23" t="n">
-        <v>6.72</v>
+        <v>7.13</v>
       </c>
       <c r="DS23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU23" t="n">
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>60.43</v>
+        <v>59.5</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX23" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="DY23" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="EA23" t="n">
-        <v>22.28</v>
+        <v>21.37</v>
       </c>
       <c r="EB23" t="n">
         <v>1.46</v>
       </c>
       <c r="EC23" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="24">
@@ -10340,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>64.2</v>
+        <v>64</v>
       </c>
       <c r="AZ24" t="n">
         <v>0</v>
@@ -10565,7 +10565,7 @@
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>66</v>
+        <v>65.88</v>
       </c>
       <c r="DW24" t="n">
         <v>0.25</v>
@@ -11394,10 +11394,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
@@ -11406,82 +11406,82 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="H27" t="n">
-        <v>101.33</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="K27" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M27" t="n">
         <v>60</v>
       </c>
       <c r="N27" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>14.75</v>
       </c>
       <c r="R27" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="S27" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>57.67</v>
+        <v>56.5</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>16.33</v>
+        <v>15.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC27" t="n">
-        <v>22.33</v>
+        <v>25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -11565,49 +11565,49 @@
         <v>4.75</v>
       </c>
       <c r="BG27" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BH27" t="n">
-        <v>8.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI27" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BM27" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN27" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BP27" t="n">
-        <v>3.14</v>
+        <v>4.12</v>
       </c>
       <c r="BQ27" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="BR27" t="n">
         <v>100</v>
       </c>
       <c r="BS27" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BT27" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV27" t="n">
         <v>0</v>
@@ -11616,19 +11616,19 @@
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY27" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="BZ27" t="n">
-        <v>3.33</v>
+        <v>2.98</v>
       </c>
       <c r="CA27" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="CB27" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CC27" t="n">
         <v>6.21</v>
@@ -11643,44 +11643,44 @@
         <v>3.67</v>
       </c>
       <c r="CG27" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CH27" t="n">
         <v>1.23</v>
       </c>
       <c r="CI27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CJ27" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CK27" t="n">
         <v>1.72</v>
       </c>
       <c r="CL27" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CM27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CN27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO27" t="n">
         <v>1.56</v>
       </c>
       <c r="CP27" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CQ27" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="CR27" t="n">
         <v>1.6</v>
       </c>
       <c r="CS27" t="inlineStr"/>
       <c r="CT27" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="n">
@@ -11702,88 +11702,88 @@
         <v>1.66</v>
       </c>
       <c r="DB27" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DC27" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DD27" t="n">
-        <v>5.77</v>
+        <v>5.85</v>
       </c>
       <c r="DE27" t="n">
         <v>0</v>
       </c>
       <c r="DF27" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="DG27" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DH27" t="n">
-        <v>93.86</v>
+        <v>94.12</v>
       </c>
       <c r="DI27" t="n">
         <v>0</v>
       </c>
       <c r="DJ27" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="DK27" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="DM27" t="n">
-        <v>52.29</v>
+        <v>53.25</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DO27" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="DP27" t="n">
-        <v>14.86</v>
+        <v>14.75</v>
       </c>
       <c r="DQ27" t="n">
-        <v>12.86</v>
+        <v>12.62</v>
       </c>
       <c r="DR27" t="n">
-        <v>9.43</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS27" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DT27" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DU27" t="n">
         <v>0</v>
       </c>
       <c r="DV27" t="n">
-        <v>52</v>
+        <v>52.12</v>
       </c>
       <c r="DW27" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX27" t="n">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="DY27" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="DZ27" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="EA27" t="n">
-        <v>23.43</v>
+        <v>24.62</v>
       </c>
       <c r="EB27" t="n">
         <v>1.43</v>
       </c>
       <c r="EC27" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="28">
@@ -13143,10 +13143,10 @@
         <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="BB31" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="BC31" t="n">
         <v>2.75</v>
@@ -13155,7 +13155,7 @@
         <v>19.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BF31" t="n">
         <v>3</v>
@@ -13364,10 +13364,10 @@
         <v>0</v>
       </c>
       <c r="DX31" t="n">
-        <v>10.62</v>
+        <v>10.75</v>
       </c>
       <c r="DY31" t="n">
-        <v>7.38</v>
+        <v>7.5</v>
       </c>
       <c r="DZ31" t="n">
         <v>3.25</v>
@@ -13376,7 +13376,7 @@
         <v>20.25</v>
       </c>
       <c r="EB31" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC31" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -3886,10 +3886,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
         <v>83</v>
@@ -3898,13 +3898,13 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL8" t="n">
         <v>5</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>51.33</v>
@@ -3913,7 +3913,7 @@
         <v>0.33</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ8" t="n">
         <v>8</v>
@@ -3961,7 +3961,7 @@
         <v>1.26</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="BG8" t="n">
         <v>1.75</v>
@@ -3991,10 +3991,10 @@
         <v>0.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.38</v>
+        <v>4.75</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="BR8" t="n">
         <v>75</v>
@@ -4117,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="DH8" t="n">
         <v>95.38</v>
@@ -4129,13 +4129,13 @@
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="DK8" t="n">
         <v>5.88</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DM8" t="n">
         <v>53.5</v>
@@ -4144,7 +4144,7 @@
         <v>1.12</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="DP8" t="n">
         <v>9.380000000000001</v>
@@ -4186,7 +4186,7 @@
         <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="9">
@@ -8605,10 +8605,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3.33</v>
       </c>
       <c r="H20" t="n">
         <v>94.33</v>
@@ -8617,13 +8617,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>4.33</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>46.67</v>
@@ -8632,7 +8632,7 @@
         <v>0.33</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
         <v>8.67</v>
@@ -8668,19 +8668,19 @@
         <v>11</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC20" t="n">
         <v>19</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8791,10 +8791,10 @@
         <v>1.14</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.29</v>
+        <v>3.71</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.86</v>
+        <v>5</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8913,10 +8913,10 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="DG20" t="n">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="DH20" t="n">
         <v>84</v>
@@ -8925,13 +8925,13 @@
         <v>0.14</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="DK20" t="n">
         <v>4.28</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="DM20" t="n">
         <v>43.29</v>
@@ -8940,7 +8940,7 @@
         <v>1</v>
       </c>
       <c r="DO20" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="DP20" t="n">
         <v>11.29</v>
@@ -8970,19 +8970,19 @@
         <v>10.43</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.14</v>
+        <v>6.29</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.28</v>
+        <v>4.14</v>
       </c>
       <c r="EA20" t="n">
         <v>17.71</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1790,49 +1790,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>107.75</v>
+        <v>107.4</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>81.25</v>
+        <v>80</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1844,28 +1844,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>62.75</v>
+        <v>61.8</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.5</v>
+        <v>17.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.75</v>
+        <v>19.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1949,46 +1949,46 @@
         <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.5</v>
+        <v>7.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="BQ3" t="n">
         <v>4</v>
       </c>
       <c r="BR3" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BS3" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BT3" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2000,19 +2000,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="CC3" t="n">
         <v>2.42</v>
@@ -2021,34 +2021,34 @@
         <v>2.32</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CH3" t="n">
         <v>1.26</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CK3" t="n">
         <v>1.8</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO3" t="n">
         <v>1.48</v>
@@ -2057,88 +2057,88 @@
         <v>2.4</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.84</v>
+        <v>4.82</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CS3" t="n">
         <v>3.29</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="CU3" t="n">
         <v>1.3</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CX3" t="n">
         <v>1.95</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.89</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.21</v>
+        <v>5.34</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.33</v>
+        <v>103.71</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="DM3" t="n">
         <v>75</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.67</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.17</v>
+        <v>13.86</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2150,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.67</v>
+        <v>62</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.5</v>
+        <v>15.86</v>
       </c>
       <c r="DY3" t="n">
         <v>10</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.5</v>
+        <v>5.86</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.17</v>
+        <v>19.43</v>
       </c>
       <c r="EB3" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="4">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -2596,49 +2596,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="H5" t="n">
-        <v>87.40000000000001</v>
+        <v>88.17</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="M5" t="n">
-        <v>52.2</v>
+        <v>54.67</v>
       </c>
       <c r="N5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="P5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2650,28 +2650,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45</v>
+        <v>46.67</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>26.6</v>
+        <v>26.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2755,49 +2755,49 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU5" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2806,19 +2806,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CC5" t="n">
         <v>4.17</v>
@@ -2830,13 +2830,13 @@
         <v>1.59</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI5" t="n">
         <v>1.62</v>
@@ -2845,25 +2845,25 @@
         <v>2.2</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO5" t="n">
         <v>1.55</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CQ5" t="n">
-        <v>5.05</v>
+        <v>5.02</v>
       </c>
       <c r="CR5" t="n">
         <v>1.58</v>
@@ -2878,73 +2878,73 @@
         <v>1.33</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CW5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG5" t="n">
         <v>2.33</v>
       </c>
-      <c r="CX5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>2.12</v>
-      </c>
       <c r="DH5" t="n">
-        <v>87.37</v>
+        <v>87.89</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.25</v>
+        <v>49.45</v>
       </c>
       <c r="DN5" t="n">
         <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.38</v>
+        <v>10.45</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.88</v>
+        <v>13</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2956,28 +2956,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42</v>
+        <v>43.45</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.38</v>
+        <v>12</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.88</v>
+        <v>8.34</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="EA5" t="n">
-        <v>24.75</v>
+        <v>25.11</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="6">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -3805,82 +3805,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P8" t="n">
-        <v>10.2</v>
+        <v>9.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="R8" t="n">
-        <v>7.4</v>
+        <v>7.83</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>64.2</v>
+        <v>65.33</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.8</v>
+        <v>22.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3964,46 +3964,46 @@
         <v>1.33</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BH8" t="n">
-        <v>9</v>
+        <v>8.33</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.25</v>
+        <v>3.78</v>
       </c>
       <c r="BR8" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS8" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4015,19 +4015,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY8" t="n">
         <v>1.71</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CC8" t="n">
         <v>2.55</v>
@@ -4036,43 +4036,43 @@
         <v>2.75</v>
       </c>
       <c r="CE8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CI8" t="n">
         <v>1.36</v>
       </c>
-      <c r="CF8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CJ8" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="CL8" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.53</v>
+        <v>4.68</v>
       </c>
       <c r="CR8" t="n">
         <v>1.56</v>
@@ -4087,106 +4087,106 @@
         <v>1.3</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.38</v>
+        <v>96</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.88</v>
+        <v>5.33</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM8" t="n">
-        <v>53.5</v>
+        <v>50.66</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.380000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.88</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61.12</v>
+        <v>62.22</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.25</v>
+        <v>11.22</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.87</v>
+        <v>7.89</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="EA8" t="n">
-        <v>21</v>
+        <v>21.34</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="9">
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0.5</v>
@@ -6284,49 +6284,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>91.5</v>
+        <v>86.2</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>12.6</v>
       </c>
       <c r="AR14" t="n">
         <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.75</v>
+        <v>10.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6338,73 +6338,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>45.75</v>
+        <v>45.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.25</v>
+        <v>8.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.119999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="BR14" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY14" t="n">
         <v>3.17</v>
@@ -6422,169 +6422,169 @@
         <v>3.16</v>
       </c>
       <c r="CA14" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.26</v>
+        <v>4.07</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="CE14" t="n">
         <v>1.62</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CI14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CO14" t="n">
         <v>1.57</v>
       </c>
-      <c r="CJ14" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CN14" t="n">
+      <c r="CP14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="CR14" t="n">
         <v>1.63</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>1.64</v>
       </c>
       <c r="CS14" t="n">
         <v>3.42</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CU14" t="n">
         <v>1.32</v>
       </c>
       <c r="CV14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DB14" t="n">
         <v>1.61</v>
       </c>
-      <c r="CW14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>1.62</v>
-      </c>
       <c r="DC14" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="DD14" t="n">
-        <v>6.14</v>
+        <v>6.03</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DH14" t="n">
-        <v>80.75</v>
+        <v>79</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="DK14" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM14" t="n">
-        <v>39.12</v>
+        <v>38.22</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.62</v>
+        <v>12.89</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14</v>
+        <v>13.78</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>43.12</v>
+        <v>43.33</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.25</v>
+        <v>9.67</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.62</v>
+        <v>17.11</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="15">
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
@@ -7408,79 +7408,79 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H17" t="n">
-        <v>103.75</v>
+        <v>100.6</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K17" t="n">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="n">
-        <v>45.75</v>
+        <v>42.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>10.75</v>
+        <v>10.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.25</v>
+        <v>12.4</v>
       </c>
       <c r="R17" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>54.25</v>
+        <v>54.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.75</v>
+        <v>16.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.25</v>
+        <v>11.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AC17" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -7567,70 +7567,70 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="BH17" t="n">
         <v>10</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT17" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BU17" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="CC17" t="n">
         <v>2.51</v>
@@ -7639,43 +7639,43 @@
         <v>2.79</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CG17" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.87</v>
+        <v>4.82</v>
       </c>
       <c r="CR17" t="n">
         <v>1.64</v>
@@ -7686,10 +7686,10 @@
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="CX17" t="n">
         <v>1.87</v>
@@ -7704,13 +7704,13 @@
         <v>1.57</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DC17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="DD17" t="n">
-        <v>6.44</v>
+        <v>6.24</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
@@ -7719,73 +7719,73 @@
         <v>2</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.25</v>
+        <v>98.89</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DK17" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.38</v>
+        <v>49</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DO17" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.88</v>
+        <v>10.89</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.62</v>
+        <v>12.22</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.5</v>
+        <v>6.22</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.75</v>
+        <v>54.11</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DX17" t="n">
-        <v>14.12</v>
+        <v>14</v>
       </c>
       <c r="DY17" t="n">
-        <v>10</v>
+        <v>9.56</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.12</v>
+        <v>4.44</v>
       </c>
       <c r="EA17" t="n">
-        <v>26.5</v>
+        <v>26.22</v>
       </c>
       <c r="EB17" t="n">
         <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="18">
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
@@ -9004,49 +9004,49 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
-        <v>94.25</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M21" t="n">
-        <v>59.25</v>
+        <v>57</v>
       </c>
       <c r="N21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="P21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="R21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="T21" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9058,28 +9058,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>46.25</v>
+        <v>44.2</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>20.25</v>
+        <v>20.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9163,37 +9163,37 @@
         <v>2.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BH21" t="n">
-        <v>7.88</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN21" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.38</v>
+        <v>4.89</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9202,31 +9202,31 @@
         <v>100</v>
       </c>
       <c r="BT21" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU21" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV21" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CC21" t="n">
         <v>4.47</v>
@@ -9235,43 +9235,43 @@
         <v>5.34</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CI21" t="n">
         <v>1.58</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.41</v>
+        <v>5.61</v>
       </c>
       <c r="CR21" t="n">
         <v>1.64</v>
@@ -9282,106 +9282,106 @@
       </c>
       <c r="CU21" t="inlineStr"/>
       <c r="CV21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CW21" t="n">
         <v>2.48</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.99</v>
+        <v>6.1</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="DH21" t="n">
-        <v>76.25</v>
+        <v>76.22</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM21" t="n">
-        <v>53.62</v>
+        <v>53</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.62</v>
+        <v>14.44</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.5</v>
+        <v>13.56</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>43.75</v>
+        <v>42.89</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.12</v>
+        <v>10.56</v>
       </c>
       <c r="DY21" t="n">
-        <v>8</v>
+        <v>7.44</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.5</v>
+        <v>20.44</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="22">
@@ -9391,13 +9391,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9484,13 +9484,13 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>85</v>
+        <v>88.8</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
@@ -9499,109 +9499,109 @@
         <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN22" t="n">
-        <v>39.25</v>
+        <v>47</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>10.75</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>46.25</v>
+        <v>49.8</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>11.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.75</v>
+        <v>20.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="BF22" t="n">
         <v>2</v>
       </c>
       <c r="BG22" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BH22" t="n">
-        <v>6.38</v>
+        <v>6.89</v>
       </c>
       <c r="BI22" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BP22" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="BR22" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BS22" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BT22" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
@@ -9613,7 +9613,7 @@
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BY22" t="n">
         <v>2.43</v>
@@ -9625,19 +9625,19 @@
         <v>2.81</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CC22" t="n">
-        <v>4.37</v>
+        <v>4.02</v>
       </c>
       <c r="CD22" t="n">
-        <v>5.04</v>
+        <v>4.54</v>
       </c>
       <c r="CE22" t="n">
         <v>1.72</v>
       </c>
       <c r="CF22" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="CG22" t="n">
         <v>2.07</v>
@@ -9652,25 +9652,25 @@
         <v>2.51</v>
       </c>
       <c r="CK22" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="CM22" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CN22" t="n">
         <v>1.47</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CP22" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CQ22" t="n">
-        <v>6.22</v>
+        <v>6.33</v>
       </c>
       <c r="CR22" t="n">
         <v>1.73</v>
@@ -9684,13 +9684,13 @@
         <v>1.51</v>
       </c>
       <c r="CW22" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CX22" t="n">
         <v>1.91</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CZ22" t="n">
         <v>1.9</v>
@@ -9699,25 +9699,25 @@
         <v>1.55</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DC22" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DD22" t="n">
-        <v>6.79</v>
+        <v>6.81</v>
       </c>
       <c r="DE22" t="n">
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="DH22" t="n">
-        <v>89.12</v>
+        <v>90.78</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
@@ -9726,58 +9726,58 @@
         <v>2</v>
       </c>
       <c r="DK22" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="DL22" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DM22" t="n">
-        <v>48.38</v>
+        <v>51.67</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO22" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DP22" t="n">
-        <v>10.62</v>
+        <v>10.78</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="DR22" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>49.38</v>
+        <v>51</v>
       </c>
       <c r="DW22" t="n">
         <v>0</v>
       </c>
       <c r="DX22" t="n">
-        <v>9.75</v>
+        <v>10.78</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.62</v>
+        <v>7.22</v>
       </c>
       <c r="DZ22" t="n">
-        <v>3.12</v>
+        <v>3.56</v>
       </c>
       <c r="EA22" t="n">
-        <v>18.25</v>
+        <v>19</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="EC22" t="n">
         <v>2</v>
@@ -9790,13 +9790,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -9883,127 +9883,127 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AI23" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="AJ23" t="n">
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN23" t="n">
-        <v>42.4</v>
+        <v>43.83</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AP23" t="n">
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13.8</v>
+        <v>13.83</v>
       </c>
       <c r="AR23" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>7.83</v>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>60.8</v>
+        <v>58.67</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA23" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.4</v>
+        <v>6.83</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="BD23" t="n">
-        <v>20.2</v>
+        <v>22.17</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BH23" t="n">
-        <v>9.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN23" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BP23" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="BR23" t="n">
-        <v>87.5</v>
+        <v>77.78</v>
       </c>
       <c r="BS23" t="n">
-        <v>87.5</v>
+        <v>77.78</v>
       </c>
       <c r="BT23" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BU23" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY23" t="n">
         <v>2.2</v>
@@ -10021,64 +10021,64 @@
         <v>2.31</v>
       </c>
       <c r="CA23" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CC23" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="CD23" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CE23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CF23" t="n">
         <v>3.44</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CH23" t="n">
         <v>1.26</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CM23" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CO23" t="n">
         <v>1.48</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.73</v>
+        <v>4.79</v>
       </c>
       <c r="CR23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CS23" t="n">
         <v>3.32</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CU23" t="n">
         <v>1.32</v>
@@ -10087,103 +10087,103 @@
         <v>1.73</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DD23" t="n">
-        <v>5.12</v>
+        <v>5.19</v>
       </c>
       <c r="DE23" t="n">
         <v>0</v>
       </c>
       <c r="DF23" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="DH23" t="n">
-        <v>97</v>
+        <v>97.11</v>
       </c>
       <c r="DI23" t="n">
         <v>0</v>
       </c>
       <c r="DJ23" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="DK23" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM23" t="n">
-        <v>53.5</v>
+        <v>53.22</v>
       </c>
       <c r="DN23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DP23" t="n">
-        <v>13.75</v>
+        <v>13.78</v>
       </c>
       <c r="DQ23" t="n">
-        <v>10.75</v>
+        <v>10.45</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.13</v>
+        <v>7.44</v>
       </c>
       <c r="DS23" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT23" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU23" t="n">
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>59.5</v>
+        <v>58.22</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX23" t="n">
-        <v>12.75</v>
+        <v>12.33</v>
       </c>
       <c r="DY23" t="n">
-        <v>8.869999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="EA23" t="n">
-        <v>21.37</v>
+        <v>22.56</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC23" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="24">
@@ -10596,13 +10596,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -10686,52 +10686,52 @@
         <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2</v>
       </c>
-      <c r="AH25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AI25" t="n">
-        <v>89.75</v>
+        <v>88</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AN25" t="n">
-        <v>51</v>
+        <v>52.2</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10.25</v>
+        <v>10.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AS25" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AV25" t="n">
         <v>0</v>
@@ -10743,70 +10743,70 @@
         <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="BH25" t="n">
-        <v>8.119999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BI25" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN25" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BP25" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="BR25" t="n">
-        <v>87.5</v>
+        <v>77.78</v>
       </c>
       <c r="BS25" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BT25" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
@@ -10818,7 +10818,7 @@
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY25" t="n">
         <v>2.01</v>
@@ -10827,165 +10827,165 @@
         <v>2.02</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CB25" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CC25" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="CD25" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="CE25" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CF25" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CG25" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CH25" t="n">
         <v>1.23</v>
       </c>
       <c r="CI25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ25" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CK25" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CL25" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CM25" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN25" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CO25" t="n">
         <v>1.54</v>
       </c>
       <c r="CP25" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CQ25" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="CR25" t="n">
         <v>1.6</v>
       </c>
       <c r="CS25" t="inlineStr"/>
       <c r="CT25" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CU25" t="inlineStr"/>
       <c r="CV25" t="n">
         <v>1.62</v>
       </c>
       <c r="CW25" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CX25" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CY25" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CZ25" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DA25" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB25" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DC25" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="DD25" t="n">
-        <v>5.76</v>
+        <v>5.8</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF25" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DG25" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="DH25" t="n">
-        <v>99.62</v>
+        <v>97.56</v>
       </c>
       <c r="DI25" t="n">
         <v>0</v>
       </c>
       <c r="DJ25" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="DK25" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="DL25" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM25" t="n">
-        <v>61.88</v>
+        <v>61.33</v>
       </c>
       <c r="DN25" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO25" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="DP25" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DQ25" t="n">
-        <v>16.75</v>
+        <v>16.11</v>
       </c>
       <c r="DR25" t="n">
-        <v>6.38</v>
+        <v>6.78</v>
       </c>
       <c r="DS25" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT25" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU25" t="n">
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>53.38</v>
+        <v>52.11</v>
       </c>
       <c r="DW25" t="n">
         <v>0</v>
       </c>
       <c r="DX25" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="DY25" t="n">
-        <v>7.25</v>
+        <v>7.22</v>
       </c>
       <c r="DZ25" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="EA25" t="n">
-        <v>19</v>
+        <v>19.22</v>
       </c>
       <c r="EB25" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="EC25" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="26">
@@ -10995,13 +10995,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
         <v>0.25</v>
@@ -11088,49 +11088,49 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>88</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AL26" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN26" t="n">
-        <v>36.5</v>
+        <v>35</v>
       </c>
       <c r="AO26" t="n">
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14.25</v>
+        <v>13.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>10.75</v>
+        <v>11.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -11142,82 +11142,82 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>45.75</v>
+        <v>42.4</v>
       </c>
       <c r="AZ26" t="n">
         <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>22.75</v>
+        <v>21.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BH26" t="n">
-        <v>9.5</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL26" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BN26" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BP26" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.12</v>
+        <v>4.56</v>
       </c>
       <c r="BR26" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS26" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BT26" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BU26" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV26" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW26" t="n">
         <v>0</v>
       </c>
       <c r="BX26" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BY26" t="n">
         <v>2.2</v>
@@ -11226,40 +11226,40 @@
         <v>2.23</v>
       </c>
       <c r="CA26" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="CC26" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="CD26" t="n">
-        <v>3.86</v>
+        <v>4.39</v>
       </c>
       <c r="CE26" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CF26" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="CG26" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CH26" t="n">
         <v>1.16</v>
       </c>
       <c r="CI26" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CJ26" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CK26" t="n">
         <v>1.86</v>
       </c>
       <c r="CL26" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CM26" t="n">
         <v>1.87</v>
@@ -11268,13 +11268,13 @@
         <v>1.51</v>
       </c>
       <c r="CO26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CP26" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="CQ26" t="n">
-        <v>7.12</v>
+        <v>6.98</v>
       </c>
       <c r="CR26" t="n">
         <v>1.75</v>
@@ -11303,88 +11303,88 @@
         <v>1.54</v>
       </c>
       <c r="DB26" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DC26" t="n">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="DD26" t="n">
-        <v>7.28</v>
+        <v>7.14</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DG26" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DH26" t="n">
-        <v>89.12</v>
+        <v>87.56</v>
       </c>
       <c r="DI26" t="n">
         <v>0</v>
       </c>
       <c r="DJ26" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="DK26" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="DL26" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM26" t="n">
-        <v>45.62</v>
+        <v>43.78</v>
       </c>
       <c r="DN26" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO26" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DP26" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="DQ26" t="n">
         <v>13</v>
       </c>
-      <c r="DQ26" t="n">
-        <v>13.62</v>
-      </c>
       <c r="DR26" t="n">
-        <v>8.380000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS26" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU26" t="n">
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>50.25</v>
+        <v>47.89</v>
       </c>
       <c r="DW26" t="n">
         <v>0</v>
       </c>
       <c r="DX26" t="n">
-        <v>9.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="DY26" t="n">
-        <v>6.75</v>
+        <v>6.22</v>
       </c>
       <c r="DZ26" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="EA26" t="n">
-        <v>22.5</v>
+        <v>21.89</v>
       </c>
       <c r="EB26" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="EC26" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="27">
@@ -11394,10 +11394,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
@@ -11406,82 +11406,82 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M27" t="n">
-        <v>60</v>
+        <v>58.4</v>
       </c>
       <c r="N27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="P27" t="n">
-        <v>14.75</v>
+        <v>13.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>14.75</v>
+        <v>14.6</v>
       </c>
       <c r="R27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="S27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="T27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="U27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>56.5</v>
+        <v>55.6</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>15.25</v>
+        <v>13.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>9.25</v>
+        <v>8.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -11565,49 +11565,49 @@
         <v>4.75</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BH27" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM27" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN27" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BP27" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="BQ27" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="BR27" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="BS27" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BT27" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU27" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV27" t="n">
         <v>0</v>
@@ -11616,19 +11616,19 @@
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY27" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BZ27" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="CA27" t="n">
         <v>3.09</v>
       </c>
       <c r="CB27" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="CC27" t="n">
         <v>6.21</v>
@@ -11640,34 +11640,34 @@
         <v>1.59</v>
       </c>
       <c r="CF27" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CG27" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CH27" t="n">
         <v>1.23</v>
       </c>
       <c r="CI27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CJ27" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CK27" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL27" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CM27" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN27" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO27" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CP27" t="n">
         <v>2.61</v>
@@ -11680,110 +11680,110 @@
       </c>
       <c r="CS27" t="inlineStr"/>
       <c r="CT27" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CW27" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CX27" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY27" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CZ27" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DA27" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB27" t="n">
         <v>1.59</v>
       </c>
       <c r="DC27" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="DD27" t="n">
-        <v>5.85</v>
+        <v>5.83</v>
       </c>
       <c r="DE27" t="n">
         <v>0</v>
       </c>
       <c r="DF27" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="DG27" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="DH27" t="n">
-        <v>94.12</v>
+        <v>92.89</v>
       </c>
       <c r="DI27" t="n">
         <v>0</v>
       </c>
       <c r="DJ27" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="DK27" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DM27" t="n">
-        <v>53.25</v>
+        <v>53.11</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DO27" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DP27" t="n">
-        <v>14.75</v>
+        <v>14</v>
       </c>
       <c r="DQ27" t="n">
-        <v>12.62</v>
+        <v>12.78</v>
       </c>
       <c r="DR27" t="n">
-        <v>9.380000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS27" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT27" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU27" t="n">
         <v>0</v>
       </c>
       <c r="DV27" t="n">
-        <v>52.12</v>
+        <v>52.11</v>
       </c>
       <c r="DW27" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX27" t="n">
-        <v>11.62</v>
+        <v>11.22</v>
       </c>
       <c r="DY27" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="DZ27" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="EA27" t="n">
-        <v>24.62</v>
+        <v>24.11</v>
       </c>
       <c r="EB27" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="EC27" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -12192,10 +12192,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
@@ -12204,82 +12204,82 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="G29" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H29" t="n">
-        <v>83.75</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L29" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M29" t="n">
-        <v>51.5</v>
+        <v>48.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>11.25</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>14.25</v>
+        <v>13.8</v>
       </c>
       <c r="R29" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="S29" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE29" t="n">
         <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
         <v>0.25</v>
@@ -12363,70 +12363,70 @@
         <v>1.75</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BH29" t="n">
-        <v>9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL29" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN29" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO29" t="n">
         <v>1</v>
       </c>
       <c r="BP29" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BQ29" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="BR29" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS29" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT29" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BU29" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV29" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="BZ29" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CA29" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CC29" t="n">
         <v>3.84</v>
@@ -12435,16 +12435,16 @@
         <v>4.12</v>
       </c>
       <c r="CE29" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CF29" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CG29" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CH29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI29" t="n">
         <v>1.54</v>
@@ -12453,32 +12453,32 @@
         <v>2.29</v>
       </c>
       <c r="CK29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CM29" t="n">
         <v>1.88</v>
-      </c>
-      <c r="CL29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="CM29" t="n">
-        <v>1.87</v>
       </c>
       <c r="CN29" t="n">
         <v>1.51</v>
       </c>
       <c r="CO29" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CP29" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CQ29" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="CR29" t="n">
         <v>1.66</v>
       </c>
       <c r="CS29" t="inlineStr"/>
       <c r="CT29" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CU29" t="inlineStr"/>
       <c r="CV29" t="n">
@@ -12488,13 +12488,13 @@
         <v>2.52</v>
       </c>
       <c r="CX29" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CY29" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CZ29" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DA29" t="n">
         <v>1.57</v>
@@ -12509,46 +12509,46 @@
         <v>6.46</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="DG29" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DH29" t="n">
-        <v>84.25</v>
+        <v>85.22</v>
       </c>
       <c r="DI29" t="n">
         <v>0</v>
       </c>
       <c r="DJ29" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DK29" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="DL29" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM29" t="n">
-        <v>48.75</v>
+        <v>47.22</v>
       </c>
       <c r="DN29" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DO29" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="DQ29" t="n">
-        <v>13.62</v>
+        <v>13.44</v>
       </c>
       <c r="DR29" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="DS29" t="n">
         <v>0</v>
@@ -12560,28 +12560,28 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>44.75</v>
+        <v>44.33</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
       </c>
       <c r="DX29" t="n">
-        <v>13.38</v>
+        <v>13.67</v>
       </c>
       <c r="DY29" t="n">
-        <v>8.25</v>
+        <v>8.67</v>
       </c>
       <c r="DZ29" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="EA29" t="n">
-        <v>15.88</v>
+        <v>16.11</v>
       </c>
       <c r="EB29" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC29" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="30">
@@ -12591,13 +12591,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>0.25</v>
@@ -12681,139 +12681,139 @@
         <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="n">
-        <v>93</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN30" t="n">
-        <v>44</v>
+        <v>40.6</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>41.25</v>
+        <v>41.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD30" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="BH30" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="BI30" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="BL30" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN30" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="BO30" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="BP30" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="BQ30" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="BR30" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS30" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT30" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU30" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BX30" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY30" t="n">
         <v>1.88</v>
@@ -12822,55 +12822,55 @@
         <v>1.88</v>
       </c>
       <c r="CA30" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CC30" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="CD30" t="n">
-        <v>3.17</v>
+        <v>3.34</v>
       </c>
       <c r="CE30" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CF30" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="CG30" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="CH30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI30" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CJ30" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CK30" t="n">
         <v>1.81</v>
       </c>
       <c r="CL30" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CM30" t="n">
         <v>1.94</v>
       </c>
       <c r="CN30" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO30" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CP30" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="CQ30" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="CR30" t="n">
         <v>1.63</v>
@@ -12881,10 +12881,10 @@
       </c>
       <c r="CU30" t="inlineStr"/>
       <c r="CV30" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CW30" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CX30" t="n">
         <v>1.85</v>
@@ -12899,88 +12899,88 @@
         <v>1.58</v>
       </c>
       <c r="DB30" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="DC30" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="DD30" t="n">
-        <v>6.22</v>
+        <v>6.07</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF30" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DG30" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DH30" t="n">
-        <v>92.5</v>
+        <v>89.44</v>
       </c>
       <c r="DI30" t="n">
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DK30" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="DL30" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DM30" t="n">
-        <v>50.25</v>
+        <v>47.67</v>
       </c>
       <c r="DN30" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO30" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DP30" t="n">
-        <v>11.62</v>
+        <v>11.22</v>
       </c>
       <c r="DQ30" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="DR30" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="DS30" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DT30" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DU30" t="n">
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>47</v>
+        <v>46.56</v>
       </c>
       <c r="DW30" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX30" t="n">
-        <v>16.62</v>
+        <v>15.78</v>
       </c>
       <c r="DY30" t="n">
-        <v>11.62</v>
+        <v>10.67</v>
       </c>
       <c r="DZ30" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="EA30" t="n">
-        <v>20.12</v>
+        <v>19.89</v>
       </c>
       <c r="EB30" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="EC30" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="31">
@@ -12990,13 +12990,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
         <v>0.25</v>
@@ -13083,124 +13083,124 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>91</v>
+        <v>90.8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK31" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AL31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AN31" t="n">
-        <v>56.5</v>
+        <v>49.4</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="AR31" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AU31" t="n">
         <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX31" t="n">
         <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>52.25</v>
+        <v>53.6</v>
       </c>
       <c r="AZ31" t="n">
         <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.25</v>
+        <v>6.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>19.5</v>
+        <v>18.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BH31" t="n">
-        <v>9.380000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN31" t="n">
         <v>1</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BP31" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.12</v>
+        <v>4.89</v>
       </c>
       <c r="BR31" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS31" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT31" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU31" t="n">
         <v>0</v>
@@ -13212,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="BX31" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY31" t="n">
         <v>2.55</v>
@@ -13227,19 +13227,19 @@
         <v>2.86</v>
       </c>
       <c r="CC31" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="CD31" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="CE31" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CF31" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CG31" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CH31" t="n">
         <v>1.21</v>
@@ -13248,35 +13248,35 @@
         <v>1.59</v>
       </c>
       <c r="CJ31" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CK31" t="n">
         <v>1.74</v>
       </c>
       <c r="CL31" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="CM31" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CN31" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CP31" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CQ31" t="n">
-        <v>5.86</v>
+        <v>5.89</v>
       </c>
       <c r="CR31" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CS31" t="inlineStr"/>
       <c r="CT31" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CU31" t="inlineStr"/>
       <c r="CV31" t="n">
@@ -13286,13 +13286,13 @@
         <v>2.45</v>
       </c>
       <c r="CX31" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY31" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CZ31" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DA31" t="n">
         <v>1.65</v>
@@ -13307,79 +13307,79 @@
         <v>6.41</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF31" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DG31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DH31" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="DI31" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DJ31" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DK31" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM31" t="n">
-        <v>52.62</v>
+        <v>49.11</v>
       </c>
       <c r="DN31" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DP31" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="DQ31" t="n">
-        <v>12.38</v>
+        <v>12.67</v>
       </c>
       <c r="DR31" t="n">
-        <v>6.25</v>
+        <v>6.78</v>
       </c>
       <c r="DS31" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT31" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU31" t="n">
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>52.5</v>
+        <v>53.22</v>
       </c>
       <c r="DW31" t="n">
         <v>0</v>
       </c>
       <c r="DX31" t="n">
-        <v>10.75</v>
+        <v>10.56</v>
       </c>
       <c r="DY31" t="n">
-        <v>7.5</v>
+        <v>7.11</v>
       </c>
       <c r="DZ31" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="EA31" t="n">
-        <v>20.25</v>
+        <v>19.56</v>
       </c>
       <c r="EB31" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="EC31" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,127 +1472,127 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>59.75</v>
+        <v>55.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.25</v>
+        <v>11.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.25</v>
+        <v>10.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>56</v>
+        <v>52.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.25</v>
+        <v>11.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.25</v>
+        <v>10.2</v>
       </c>
       <c r="BC2" t="n">
         <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>7.43</v>
+        <v>8.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>3</v>
+        <v>4.12</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="BR2" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BS2" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BT2" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BY2" t="n">
         <v>2.97</v>
@@ -1610,165 +1610,169 @@
         <v>3.15</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.98</v>
+        <v>4.82</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.46</v>
+        <v>5.18</v>
       </c>
       <c r="CE2" t="n">
         <v>1.62</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="CG2" t="n">
         <v>2.25</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CQ2" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CS2" t="inlineStr"/>
+        <v>1.63</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>3.35</v>
+      </c>
       <c r="CT2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="CU2" t="inlineStr"/>
+        <v>2.31</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.31</v>
+      </c>
       <c r="CV2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DC2" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.37</v>
+        <v>6.27</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="DH2" t="n">
-        <v>91.70999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DM2" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.86</v>
+        <v>15</v>
       </c>
       <c r="DQ2" t="n">
         <v>10</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.28</v>
+        <v>50.37</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.57</v>
+        <v>11</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="EA2" t="n">
-        <v>25</v>
+        <v>24.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -2006,13 +2010,13 @@
         <v>1.71</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CA3" t="n">
         <v>3.25</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="CC3" t="n">
         <v>2.42</v>
@@ -2060,43 +2064,43 @@
         <v>4.82</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="CS3" t="n">
         <v>3.29</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="CU3" t="n">
         <v>1.3</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CX3" t="n">
         <v>1.95</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.89</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.34</v>
+        <v>5.15</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2181,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -2193,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>78.25</v>
+        <v>75.8</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.25</v>
+        <v>7.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>68</v>
+        <v>66.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.25</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.25</v>
+        <v>53.6</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.25</v>
+        <v>16.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.25</v>
+        <v>11.4</v>
       </c>
       <c r="AB4" t="n">
         <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>24.75</v>
+        <v>26.2</v>
       </c>
       <c r="AD4" t="n">
         <v>1.86</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2352,49 +2356,49 @@
         <v>3.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.75</v>
+        <v>8.67</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.88</v>
+        <v>4.78</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS4" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT4" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2403,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CC4" t="n">
         <v>3.96</v>
@@ -2424,28 +2428,28 @@
         <v>4.5</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI4" t="n">
         <v>1.69</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="CM4" t="n">
         <v>2.05</v>
@@ -2457,22 +2461,22 @@
         <v>1.48</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
       <c r="CR4" t="n">
         <v>1.58</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CV4" t="n">
         <v>1.68</v>
@@ -2481,100 +2485,100 @@
         <v>2.26</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB4" t="n">
         <v>1.54</v>
       </c>
       <c r="DC4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>83.22</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO4" t="n">
         <v>2.67</v>
       </c>
-      <c r="DD4" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>85.38</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>60.25</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>2.12</v>
-      </c>
       <c r="DP4" t="n">
-        <v>12.88</v>
+        <v>12.67</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.88</v>
+        <v>13.33</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.88</v>
+        <v>51.33</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.75</v>
+        <v>13.22</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.880000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.25</v>
+        <v>26</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5">
@@ -2650,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>46.67</v>
+        <v>46.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.5</v>
+        <v>14.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.17</v>
+        <v>10.33</v>
       </c>
       <c r="AB5" t="n">
         <v>4.33</v>
@@ -2668,7 +2672,7 @@
         <v>26.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
         <v>2.83</v>
@@ -2812,7 +2816,7 @@
         <v>2.48</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CA5" t="n">
         <v>3.01</v>
@@ -2878,31 +2882,31 @@
         <v>1.33</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CX5" t="n">
         <v>1.78</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB5" t="n">
         <v>1.57</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.64</v>
+        <v>5.62</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
@@ -2956,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43.45</v>
+        <v>43.33</v>
       </c>
       <c r="DW5" t="n">
         <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>12</v>
+        <v>12.11</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.34</v>
+        <v>8.44</v>
       </c>
       <c r="DZ5" t="n">
         <v>3.66</v>
@@ -2974,7 +2978,7 @@
         <v>25.11</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC5" t="n">
         <v>2.55</v>
@@ -2987,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3077,52 +3081,52 @@
         <v>3.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>73.25</v>
+        <v>73.8</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.25</v>
+        <v>-0.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>53.75</v>
+        <v>48.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3134,70 +3138,70 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>34</v>
+        <v>32.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="BR6" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS6" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3209,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY6" t="n">
         <v>3.4</v>
@@ -3218,31 +3222,31 @@
         <v>3.67</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.56</v>
+        <v>5.93</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.97</v>
+        <v>3.89</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CJ6" t="n">
         <v>2.48</v>
@@ -3251,136 +3255,136 @@
         <v>1.82</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="CQ6" t="n">
-        <v>6.14</v>
+        <v>5.96</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CV6" t="n">
         <v>1.52</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CX6" t="n">
         <v>1.94</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DA6" t="n">
         <v>1.55</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="DC6" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.24</v>
+        <v>6.05</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="DH6" t="n">
-        <v>88</v>
+        <v>86.67</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="DM6" t="n">
-        <v>51.5</v>
+        <v>48.89</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.88</v>
+        <v>12.56</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.619999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>40.12</v>
+        <v>38.67</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.62</v>
+        <v>19</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="7">
@@ -3390,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3483,46 +3487,46 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>90.8</v>
+        <v>89</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>52.8</v>
+        <v>51.67</v>
       </c>
       <c r="AO7" t="n">
         <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.4</v>
+        <v>9.17</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>8.17</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.6</v>
+        <v>10.33</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AU7" t="n">
         <v>1</v>
@@ -3537,73 +3541,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>46.8</v>
+        <v>46.83</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.2</v>
+        <v>19.67</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.119999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BP7" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="BR7" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY7" t="n">
         <v>1.84</v>
@@ -3621,55 +3625,55 @@
         <v>1.86</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.95</v>
+        <v>3.69</v>
       </c>
       <c r="CD7" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="CE7" t="n">
         <v>1.58</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
       <c r="CR7" t="n">
         <v>1.6</v>
@@ -3690,100 +3694,100 @@
         <v>2.39</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.36</v>
+        <v>5.52</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DG7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>93</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>8</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="EB7" t="n">
         <v>1.38</v>
       </c>
-      <c r="DH7" t="n">
-        <v>94.62</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>1.44</v>
-      </c>
       <c r="EC7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="8">
@@ -3835,7 +3839,7 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>9.83</v>
+        <v>9.67</v>
       </c>
       <c r="Q8" t="n">
         <v>16.5</v>
@@ -3859,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>65.33</v>
+        <v>65</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -3874,7 +3878,7 @@
         <v>3.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.17</v>
+        <v>22</v>
       </c>
       <c r="AD8" t="n">
         <v>1.34</v>
@@ -4027,7 +4031,7 @@
         <v>3.27</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC8" t="n">
         <v>2.55</v>
@@ -4075,28 +4079,28 @@
         <v>4.68</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CS8" t="n">
         <v>3.29</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="CU8" t="n">
         <v>1.3</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CW8" t="n">
         <v>2.57</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.05</v>
@@ -4147,7 +4151,7 @@
         <v>3</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DQ8" t="n">
         <v>14.89</v>
@@ -4165,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.22</v>
+        <v>62</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4180,7 +4184,7 @@
         <v>3.34</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.34</v>
+        <v>21.22</v>
       </c>
       <c r="EB8" t="n">
         <v>1.31</v>
@@ -4196,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4289,121 +4293,121 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>80.75</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>39.25</v>
+        <v>45</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.5</v>
+        <v>14.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.25</v>
+        <v>41.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>19</v>
+        <v>17.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="BR9" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS9" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -4418,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BY9" t="n">
         <v>3.08</v>
@@ -4427,25 +4431,25 @@
         <v>3.42</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.89</v>
+        <v>4.71</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.69</v>
+        <v>5.53</v>
       </c>
       <c r="CE9" t="n">
         <v>1.63</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CH9" t="n">
         <v>1.21</v>
@@ -4457,10 +4461,10 @@
         <v>2.28</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="CM9" t="n">
         <v>1.93</v>
@@ -4475,7 +4479,7 @@
         <v>2.72</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.79</v>
+        <v>5.76</v>
       </c>
       <c r="CR9" t="n">
         <v>1.67</v>
@@ -4495,7 +4499,7 @@
         <v>1.87</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CZ9" t="n">
         <v>1.94</v>
@@ -4504,88 +4508,88 @@
         <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DC9" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="DD9" t="n">
-        <v>6.44</v>
+        <v>6.37</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.75</v>
+        <v>85.67</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>46.62</v>
+        <v>49</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.38</v>
+        <v>12.89</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.75</v>
+        <v>12.78</v>
       </c>
       <c r="DR9" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.88</v>
+        <v>44.67</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>7</v>
+        <v>6.56</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.5</v>
+        <v>17.89</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="10">
@@ -4595,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -4607,82 +4611,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>81.25</v>
+        <v>84.8</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="K10" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>49.25</v>
+        <v>53.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>10.75</v>
+        <v>9.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>49.75</v>
+        <v>51.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z10" t="n">
         <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4766,70 +4770,70 @@
         <v>1.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="BR10" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CC10" t="n">
         <v>3.83</v>
@@ -4841,28 +4845,28 @@
         <v>1.63</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CH10" t="n">
         <v>1.22</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CK10" t="n">
         <v>1.79</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CN10" t="n">
         <v>1.58</v>
@@ -4874,7 +4878,7 @@
         <v>2.69</v>
       </c>
       <c r="CQ10" t="n">
-        <v>5.44</v>
+        <v>5.45</v>
       </c>
       <c r="CR10" t="n">
         <v>1.65</v>
@@ -4888,7 +4892,7 @@
         <v>1.62</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CX10" t="n">
         <v>1.84</v>
@@ -4897,10 +4901,10 @@
         <v>2.34</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DB10" t="n">
         <v>1.62</v>
@@ -4909,82 +4913,82 @@
         <v>2.94</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.1</v>
+        <v>6.08</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DH10" t="n">
-        <v>77.75</v>
+        <v>80.11</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DM10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>8.619999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.12</v>
+        <v>11.89</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.25</v>
+        <v>50.11</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.88</v>
+        <v>21.67</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="11">
@@ -4994,10 +4998,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -5006,49 +5010,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
-        <v>85.5</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>62.75</v>
+        <v>65.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="R11" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5060,28 +5064,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.75</v>
+        <v>50.2</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.25</v>
+        <v>11.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="n">
-        <v>26.25</v>
+        <v>26.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5165,43 +5169,43 @@
         <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.380000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="BR11" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BS11" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5216,19 +5220,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CC11" t="n">
         <v>4.73</v>
@@ -5240,7 +5244,7 @@
         <v>1.74</v>
       </c>
       <c r="CF11" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="CG11" t="n">
         <v>2.07</v>
@@ -5252,90 +5256,90 @@
         <v>1.46</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO11" t="n">
         <v>1.74</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CQ11" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CS11" t="inlineStr"/>
       <c r="CT11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="DD11" t="n">
-        <v>6.95</v>
+        <v>7.02</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="DH11" t="n">
-        <v>85.62</v>
+        <v>88.11</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.12</v>
+        <v>4.44</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM11" t="n">
-        <v>54.62</v>
+        <v>57.22</v>
       </c>
       <c r="DN11" t="n">
         <v>2</v>
@@ -5344,13 +5348,13 @@
         <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>18.12</v>
+        <v>18.11</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.119999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DR11" t="n">
-        <v>10</v>
+        <v>9.44</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5362,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>38.5</v>
+        <v>40.44</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.75</v>
+        <v>10.22</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.12</v>
+        <v>21.11</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="EC11" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="12">
@@ -5393,10 +5397,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
@@ -5405,49 +5409,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>88.75</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>63</v>
+        <v>58.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5459,28 +5463,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.5</v>
+        <v>52.8</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>13.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5564,46 +5568,46 @@
         <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="BR12" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS12" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5615,19 +5619,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CB12" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CC12" t="n">
         <v>2.57</v>
@@ -5636,43 +5640,43 @@
         <v>2.75</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="CO12" t="n">
         <v>1.59</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="CR12" t="n">
         <v>1.63</v>
@@ -5704,52 +5708,52 @@
         <v>1.65</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DH12" t="n">
-        <v>87</v>
+        <v>88.67</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.75</v>
+        <v>50.44</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.38</v>
+        <v>10</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>12.11</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.75</v>
+        <v>7.33</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5761,28 +5765,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53</v>
+        <v>53.56</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.88</v>
+        <v>13.33</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.62</v>
+        <v>17.67</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="13">
@@ -5792,10 +5796,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
@@ -5804,49 +5808,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="H13" t="n">
-        <v>72.67</v>
+        <v>81.75</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.33</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>46.33</v>
+        <v>53.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>12.67</v>
+        <v>10.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="R13" t="n">
-        <v>8.33</v>
+        <v>7.75</v>
       </c>
       <c r="S13" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5858,28 +5862,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.33</v>
+        <v>13.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>10</v>
+        <v>11.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>18.33</v>
+        <v>22.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5963,49 +5967,49 @@
         <v>2.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="BR13" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS13" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BT13" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU13" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6014,19 +6018,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.61</v>
+        <v>4.33</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CC13" t="n">
         <v>4.91</v>
@@ -6035,43 +6039,43 @@
         <v>5.59</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CH13" t="n">
         <v>1.19</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CN13" t="n">
         <v>1.5</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CQ13" t="n">
-        <v>6.07</v>
+        <v>5.98</v>
       </c>
       <c r="CR13" t="n">
         <v>1.63</v>
@@ -6082,73 +6086,73 @@
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CX13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CY13" t="n">
         <v>2.45</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.3</v>
+        <v>6.34</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="DH13" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.25</v>
+        <v>4.67</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>54.25</v>
+        <v>56.67</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.63</v>
+        <v>10.67</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6160,28 +6164,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.75</v>
+        <v>44.78</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.87</v>
+        <v>11.56</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.380000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.62</v>
+        <v>24.78</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="14">
@@ -6338,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.4</v>
@@ -6431,7 +6435,7 @@
         <v>4.07</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CE14" t="n">
         <v>1.62</v>
@@ -6473,13 +6477,13 @@
         <v>5.24</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CS14" t="n">
         <v>3.42</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CU14" t="n">
         <v>1.32</v>
@@ -6488,16 +6492,16 @@
         <v>1.63</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CX14" t="n">
         <v>1.71</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DA14" t="n">
         <v>1.7</v>
@@ -6506,10 +6510,10 @@
         <v>1.61</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="DD14" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="DE14" t="n">
         <v>0.22</v>
@@ -6563,7 +6567,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>43.33</v>
+        <v>43.44</v>
       </c>
       <c r="DW14" t="n">
         <v>0.22</v>
@@ -6594,13 +6598,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0.25</v>
@@ -6684,22 +6688,22 @@
         <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>70.5</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AL15" t="n">
         <v>2</v>
@@ -6708,28 +6712,28 @@
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>28.25</v>
+        <v>33</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.25</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6741,73 +6745,73 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>34.75</v>
+        <v>36.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.25</v>
+        <v>7.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.25</v>
+        <v>17.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="BR15" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="BS15" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BT15" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU15" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6816,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
         <v>2.95</v>
@@ -6825,73 +6829,73 @@
         <v>3.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.31</v>
+        <v>5.25</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.19</v>
+        <v>5.95</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CJ15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CL15" t="n">
         <v>2.36</v>
       </c>
-      <c r="CK15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>2.34</v>
-      </c>
       <c r="CM15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="CQ15" t="n">
-        <v>6.03</v>
+        <v>6.08</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CS15" t="n">
         <v>3.29</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="CU15" t="n">
         <v>1.3</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="CX15" t="n">
         <v>1.83</v>
@@ -6906,55 +6910,55 @@
         <v>1.59</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="DD15" t="n">
-        <v>6.47</v>
+        <v>6.57</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DH15" t="n">
-        <v>89</v>
+        <v>90.56</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.38</v>
+        <v>41.67</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.5</v>
+        <v>12.44</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6966,28 +6970,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.75</v>
+        <v>10.33</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.5</v>
+        <v>21.56</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="16">
@@ -6997,10 +7001,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
@@ -7009,82 +7013,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>44</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H16" t="n">
-        <v>90.25</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="T16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE16" t="n">
         <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P16" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7168,49 +7172,49 @@
         <v>3.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.88</v>
+        <v>7.89</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="BR16" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS16" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7219,19 +7223,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CC16" t="n">
         <v>2.84</v>
@@ -7240,28 +7244,28 @@
         <v>3.18</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CF16" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="CM16" t="n">
         <v>1.84</v>
@@ -7270,13 +7274,13 @@
         <v>1.5</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CP16" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.71</v>
+        <v>6.63</v>
       </c>
       <c r="CR16" t="n">
         <v>1.76</v>
@@ -7287,13 +7291,13 @@
       </c>
       <c r="CU16" t="inlineStr"/>
       <c r="CV16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CY16" t="n">
         <v>2.46</v>
@@ -7305,88 +7309,88 @@
         <v>1.53</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DC16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="DD16" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DH16" t="n">
-        <v>85.25</v>
+        <v>84.44</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.38</v>
+        <v>42</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.75</v>
+        <v>12.22</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15</v>
+        <v>14.33</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.380000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>55.5</v>
+        <v>53.78</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.25</v>
+        <v>10.78</v>
       </c>
       <c r="DY16" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="EA16" t="n">
         <v>21</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="EC16" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="17">
@@ -7795,61 +7799,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="H18" t="n">
-        <v>87</v>
+        <v>91.5</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>60.6</v>
+        <v>63.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7861,28 +7865,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>39.6</v>
+        <v>45.17</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>16.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.2</v>
+        <v>6.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7966,70 +7970,70 @@
         <v>2.67</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.62</v>
+        <v>7.56</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO18" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.88</v>
+        <v>4.22</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU18" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="CC18" t="n">
         <v>3.96</v>
@@ -8038,153 +8042,157 @@
         <v>3.99</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CH18" t="n">
         <v>1.23</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CN18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="CR18" t="n">
         <v>1.61</v>
       </c>
-      <c r="CO18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CQ18" t="n">
+      <c r="CS18" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>9</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="DZ18" t="n">
         <v>5.34</v>
       </c>
-      <c r="CR18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CS18" t="inlineStr"/>
-      <c r="CT18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CU18" t="inlineStr"/>
-      <c r="CV18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="CZ18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="DA18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DB18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DC18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="DD18" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="DE18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DF18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DG18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>88.38</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>54.87</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DP18" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="DQ18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="DR18" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="DS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV18" t="n">
-        <v>42</v>
-      </c>
-      <c r="DW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX18" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="DY18" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="DZ18" t="n">
-        <v>4.63</v>
-      </c>
       <c r="EA18" t="n">
-        <v>23.25</v>
+        <v>22.33</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="19">
@@ -8194,13 +8202,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
         <v>0.2</v>
@@ -8287,127 +8295,127 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG19" t="n">
         <v>2.33</v>
       </c>
-      <c r="AI19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>50.33</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU19" t="n">
+      <c r="BH19" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>0.67</v>
       </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>50.67</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>21.67</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.62</v>
-      </c>
       <c r="BK19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BU19" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8416,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY19" t="n">
         <v>2.44</v>
@@ -8425,55 +8433,55 @@
         <v>2.49</v>
       </c>
       <c r="CA19" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="CG19" t="n">
         <v>2.16</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CJ19" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CM19" t="n">
         <v>2.01</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CQ19" t="n">
-        <v>6.21</v>
+        <v>6.27</v>
       </c>
       <c r="CR19" t="n">
         <v>1.68</v>
@@ -8505,85 +8513,85 @@
         <v>1.67</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DD19" t="n">
-        <v>6.46</v>
+        <v>6.43</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="DH19" t="n">
-        <v>92</v>
+        <v>93.33</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.25</v>
+        <v>4.67</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DM19" t="n">
-        <v>51</v>
+        <v>51.56</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DO19" t="n">
         <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.88</v>
+        <v>12</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.63</v>
+        <v>12.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.37</v>
+        <v>5.78</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.88</v>
+        <v>53.56</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.75</v>
+        <v>12.33</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.75</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.63</v>
+        <v>21.89</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="20">
@@ -8593,13 +8601,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8686,136 +8694,136 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AI20" t="n">
-        <v>76.25</v>
+        <v>79</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG20" t="n">
         <v>2.75</v>
       </c>
-      <c r="AL20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>40.75</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP20" t="n">
+      <c r="BH20" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BN20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BL20" t="n">
+      <c r="BO20" t="n">
         <v>1</v>
       </c>
-      <c r="BM20" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BP20" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV20" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY20" t="n">
         <v>2.29</v>
@@ -8824,55 +8832,55 @@
         <v>2.45</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="CE20" t="n">
         <v>1.64</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="CG20" t="n">
         <v>2.17</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="CM20" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CP20" t="n">
         <v>2.73</v>
       </c>
       <c r="CQ20" t="n">
-        <v>5.81</v>
+        <v>5.72</v>
       </c>
       <c r="CR20" t="n">
         <v>1.62</v>
@@ -8883,10 +8891,10 @@
       </c>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CX20" t="n">
         <v>1.81</v>
@@ -8901,55 +8909,55 @@
         <v>1.61</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DC20" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="DD20" t="n">
-        <v>5.88</v>
+        <v>5.99</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DH20" t="n">
-        <v>84</v>
+        <v>84.75</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="DM20" t="n">
-        <v>43.29</v>
+        <v>40.63</v>
       </c>
       <c r="DN20" t="n">
         <v>1</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.29</v>
+        <v>11.5</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.86</v>
+        <v>11.25</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.71</v>
+        <v>7.75</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8961,28 +8969,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>49.86</v>
+        <v>48.88</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.43</v>
+        <v>10</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="21">
@@ -10193,13 +10201,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -10286,136 +10294,136 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>105</v>
+        <v>101.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN24" t="n">
-        <v>55.8</v>
+        <v>54.17</v>
       </c>
       <c r="AO24" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>11.2</v>
+        <v>10.83</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.8</v>
+        <v>7.33</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX24" t="n">
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>64</v>
+        <v>63.33</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>13.33</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>8.83</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>23.4</v>
+        <v>22.17</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="BG24" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BH24" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI24" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BP24" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="BR24" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS24" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT24" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BU24" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV24" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW24" t="n">
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY24" t="n">
         <v>1.56</v>
@@ -10424,55 +10432,55 @@
         <v>1.63</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="CC24" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="CD24" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="CE24" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CF24" t="n">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="CG24" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CH24" t="n">
         <v>1.26</v>
       </c>
       <c r="CI24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CJ24" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CK24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CL24" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CM24" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CN24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO24" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CP24" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="CQ24" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="CR24" t="n">
         <v>1.54</v>
@@ -10487,106 +10495,106 @@
         <v>1.33</v>
       </c>
       <c r="CV24" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CW24" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CX24" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CY24" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CZ24" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="DA24" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="DB24" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DC24" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="DD24" t="n">
-        <v>4.98</v>
+        <v>5.22</v>
       </c>
       <c r="DE24" t="n">
         <v>0</v>
       </c>
       <c r="DF24" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DG24" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DH24" t="n">
-        <v>108.63</v>
+        <v>105.78</v>
       </c>
       <c r="DI24" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ24" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="DK24" t="n">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="DM24" t="n">
-        <v>49.75</v>
+        <v>49.34</v>
       </c>
       <c r="DN24" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="DO24" t="n">
         <v>2</v>
       </c>
       <c r="DP24" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
       <c r="DQ24" t="n">
-        <v>11.62</v>
+        <v>11.33</v>
       </c>
       <c r="DR24" t="n">
-        <v>6.38</v>
+        <v>6.78</v>
       </c>
       <c r="DS24" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT24" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU24" t="n">
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>65.88</v>
+        <v>65.22</v>
       </c>
       <c r="DW24" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="DX24" t="n">
-        <v>16.13</v>
+        <v>15.44</v>
       </c>
       <c r="DY24" t="n">
-        <v>11</v>
+        <v>10.11</v>
       </c>
       <c r="DZ24" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="EA24" t="n">
-        <v>21.87</v>
+        <v>21.22</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="EC24" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="25">
@@ -10830,13 +10838,13 @@
         <v>3.07</v>
       </c>
       <c r="CB25" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CC25" t="n">
         <v>2.9</v>
       </c>
       <c r="CD25" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CE25" t="n">
         <v>1.57</v>
@@ -10878,39 +10886,39 @@
         <v>5.28</v>
       </c>
       <c r="CR25" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CS25" t="inlineStr"/>
       <c r="CT25" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CU25" t="inlineStr"/>
       <c r="CV25" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CW25" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CX25" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY25" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CZ25" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DA25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DB25" t="n">
         <v>1.57</v>
       </c>
-      <c r="DB25" t="n">
-        <v>1.59</v>
-      </c>
       <c r="DC25" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="DD25" t="n">
-        <v>5.8</v>
+        <v>5.66</v>
       </c>
       <c r="DE25" t="n">
         <v>0.11</v>
@@ -11118,7 +11126,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="AR26" t="n">
         <v>11.6</v>
@@ -11142,7 +11150,7 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>42.4</v>
+        <v>42.8</v>
       </c>
       <c r="AZ26" t="n">
         <v>0</v>
@@ -11157,7 +11165,7 @@
         <v>2.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="BE26" t="n">
         <v>0.85</v>
@@ -11235,7 +11243,7 @@
         <v>3.88</v>
       </c>
       <c r="CD26" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="CE26" t="n">
         <v>1.75</v>
@@ -11277,27 +11285,27 @@
         <v>6.98</v>
       </c>
       <c r="CR26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CS26" t="inlineStr"/>
       <c r="CT26" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CU26" t="inlineStr"/>
       <c r="CV26" t="n">
         <v>1.47</v>
       </c>
       <c r="CW26" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CX26" t="n">
         <v>1.9</v>
       </c>
       <c r="CY26" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CZ26" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DA26" t="n">
         <v>1.54</v>
@@ -11345,7 +11353,7 @@
         <v>1.56</v>
       </c>
       <c r="DP26" t="n">
-        <v>12.78</v>
+        <v>12.89</v>
       </c>
       <c r="DQ26" t="n">
         <v>13</v>
@@ -11363,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>47.89</v>
+        <v>48.11</v>
       </c>
       <c r="DW26" t="n">
         <v>0</v>
@@ -11378,7 +11386,7 @@
         <v>2.78</v>
       </c>
       <c r="EA26" t="n">
-        <v>21.89</v>
+        <v>22.11</v>
       </c>
       <c r="EB26" t="n">
         <v>1.09</v>
@@ -11793,10 +11801,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
         <v>4</v>
@@ -11805,49 +11813,49 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="G28" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H28" t="n">
-        <v>81.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>8.25</v>
+        <v>6.8</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="M28" t="n">
-        <v>46</v>
+        <v>41.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O28" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>10.75</v>
+        <v>12.2</v>
       </c>
       <c r="R28" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -11859,28 +11867,28 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>63</v>
+        <v>58.6</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>14</v>
+        <v>12.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>23.75</v>
+        <v>22</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -11964,46 +11972,46 @@
         <v>2.25</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH28" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL28" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN28" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BP28" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BQ28" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="BR28" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS28" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT28" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BU28" t="n">
         <v>0</v>
@@ -12015,19 +12023,19 @@
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="CA28" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CB28" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CC28" t="n">
         <v>3.54</v>
@@ -12036,43 +12044,43 @@
         <v>4.01</v>
       </c>
       <c r="CE28" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CF28" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="CG28" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CH28" t="n">
         <v>1.21</v>
       </c>
       <c r="CI28" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CJ28" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CK28" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CL28" t="n">
         <v>2.33</v>
       </c>
       <c r="CM28" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CO28" t="n">
         <v>1.59</v>
       </c>
-      <c r="CO28" t="n">
-        <v>1.58</v>
-      </c>
       <c r="CP28" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CQ28" t="n">
-        <v>5.98</v>
+        <v>6.07</v>
       </c>
       <c r="CR28" t="n">
         <v>1.65</v>
@@ -12086,7 +12094,7 @@
         <v>1.58</v>
       </c>
       <c r="CW28" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CX28" t="n">
         <v>1.84</v>
@@ -12107,49 +12115,49 @@
         <v>3</v>
       </c>
       <c r="DD28" t="n">
-        <v>6.06</v>
+        <v>6.08</v>
       </c>
       <c r="DE28" t="n">
         <v>0</v>
       </c>
       <c r="DF28" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DG28" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DH28" t="n">
-        <v>85.88</v>
+        <v>85.89</v>
       </c>
       <c r="DI28" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DJ28" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="DK28" t="n">
-        <v>5.88</v>
+        <v>5.33</v>
       </c>
       <c r="DL28" t="n">
         <v>0</v>
       </c>
       <c r="DM28" t="n">
-        <v>46.5</v>
+        <v>44</v>
       </c>
       <c r="DN28" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DO28" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="DP28" t="n">
-        <v>10.5</v>
+        <v>10.44</v>
       </c>
       <c r="DQ28" t="n">
-        <v>10.38</v>
+        <v>11.22</v>
       </c>
       <c r="DR28" t="n">
-        <v>6.75</v>
+        <v>7.56</v>
       </c>
       <c r="DS28" t="n">
         <v>0</v>
@@ -12161,28 +12169,28 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>55.88</v>
+        <v>54.22</v>
       </c>
       <c r="DW28" t="n">
         <v>0</v>
       </c>
       <c r="DX28" t="n">
-        <v>13.38</v>
+        <v>12.44</v>
       </c>
       <c r="DY28" t="n">
-        <v>8.619999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="DZ28" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="EA28" t="n">
-        <v>21.75</v>
+        <v>21</v>
       </c>
       <c r="EB28" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="EC28" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="29">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,125 +1875,125 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="AO3" t="n">
         <v>1</v>
       </c>
-      <c r="AH3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AP3" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
       <c r="AU3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BO3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
+      <c r="BP3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BR3" t="n">
         <v>62.5</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
+      <c r="BS3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="BT3" t="n">
         <v>12.5</v>
       </c>
-      <c r="BB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>14.29</v>
-      </c>
       <c r="BU3" t="n">
         <v>0</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BY3" t="n">
         <v>1.71</v>
@@ -2013,136 +2013,136 @@
         <v>1.77</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.43</v>
+        <v>3.48</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CI3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CR3" t="n">
         <v>1.59</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1.55</v>
       </c>
       <c r="CS3" t="n">
         <v>3.29</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="CU3" t="n">
         <v>1.3</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.15</v>
+        <v>5.47</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.71</v>
+        <v>99.63</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.71</v>
+        <v>5.25</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DM3" t="n">
-        <v>75</v>
+        <v>71.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.14</v>
+        <v>6.5</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62</v>
+        <v>62.37</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.86</v>
+        <v>14.88</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.43</v>
+        <v>18.75</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>87.33</v>
+        <v>84</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>39</v>
+        <v>42.25</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>13.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.33</v>
+        <v>10.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,73 +2735,73 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>37</v>
+        <v>34.75</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.67</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>2.48</v>
@@ -2819,64 +2819,64 @@
         <v>2.66</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.17</v>
+        <v>4.5</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.51</v>
+        <v>4.92</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CK5" t="n">
         <v>1.77</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN5" t="n">
         <v>1.59</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="CQ5" t="n">
-        <v>5.02</v>
+        <v>4.94</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CU5" t="n">
         <v>1.33</v>
@@ -2888,67 +2888,67 @@
         <v>2.31</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY5" t="n">
         <v>2.24</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA5" t="n">
         <v>1.64</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.62</v>
+        <v>5.51</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.89</v>
+        <v>86.5</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.45</v>
+        <v>49.7</v>
       </c>
       <c r="DN5" t="n">
         <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.45</v>
+        <v>10.3</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.109999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43.33</v>
+        <v>41.8</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.11</v>
+        <v>11.6</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.44</v>
+        <v>8.1</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>25.11</v>
+        <v>24.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3406,13 +3406,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H7" t="n">
-        <v>101</v>
+        <v>99.25</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3421,34 +3421,34 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>58</v>
+        <v>55.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P7" t="n">
-        <v>10.67</v>
+        <v>12.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.33</v>
+        <v>11.75</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="S7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,25 +3460,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>57.67</v>
+        <v>55.25</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>11.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.67</v>
+        <v>21.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -3565,49 +3565,49 @@
         <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.33</v>
+        <v>7.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BS7" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU7" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CC7" t="n">
         <v>3.69</v>
@@ -3640,10 +3640,10 @@
         <v>1.58</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CH7" t="n">
         <v>1.24</v>
@@ -3652,37 +3652,37 @@
         <v>1.63</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN7" t="n">
         <v>1.63</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.04</v>
+        <v>5.11</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CS7" t="n">
         <v>3.39</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CU7" t="n">
         <v>1.32</v>
@@ -3691,70 +3691,70 @@
         <v>1.62</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA7" t="n">
         <v>1.64</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.52</v>
+        <v>5.63</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DH7" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM7" t="n">
-        <v>53.78</v>
+        <v>53.2</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.67</v>
+        <v>10.4</v>
       </c>
       <c r="DQ7" t="n">
-        <v>8.890000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.220000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.44</v>
+        <v>50.2</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.67</v>
+        <v>11.3</v>
       </c>
       <c r="DY7" t="n">
         <v>8</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.67</v>
+        <v>20.5</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3893,46 +3893,46 @@
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>83</v>
+        <v>86.75</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>51.33</v>
+        <v>51</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>8</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.67</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,70 +3944,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.33</v>
+        <v>7.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.67</v>
+        <v>18.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
         <v>1</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="BR8" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>1.71</v>
@@ -4028,40 +4028,40 @@
         <v>1.74</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="CM8" t="n">
         <v>1.78</v>
@@ -4070,22 +4070,22 @@
         <v>1.43</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CP8" t="n">
         <v>2.71</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.68</v>
+        <v>4.76</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CS8" t="n">
         <v>3.29</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="CU8" t="n">
         <v>1.3</v>
@@ -4094,103 +4094,103 @@
         <v>1.56</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.64</v>
+        <v>5.76</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DH8" t="n">
-        <v>96</v>
+        <v>96.2</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.66</v>
+        <v>50.6</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DO8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.89</v>
+        <v>14.1</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.22</v>
+        <v>11.7</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.89</v>
+        <v>8.1</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.22</v>
+        <v>20.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5439,7 +5439,7 @@
         <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Q12" t="n">
         <v>13.4</v>
@@ -5747,7 +5747,7 @@
         <v>2.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DQ12" t="n">
         <v>12.11</v>
@@ -6195,94 +6195,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H14" t="n">
-        <v>70</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M14" t="n">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>13.25</v>
+        <v>12.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>40.5</v>
+        <v>42</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.25</v>
+        <v>17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6366,70 +6366,70 @@
         <v>3.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS14" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CC14" t="n">
         <v>4.07</v>
@@ -6438,28 +6438,28 @@
         <v>4.21</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CH14" t="n">
         <v>1.23</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CK14" t="n">
         <v>1.69</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CM14" t="n">
         <v>2.05</v>
@@ -6468,31 +6468,31 @@
         <v>1.64</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CQ14" t="n">
-        <v>5.24</v>
+        <v>5.15</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CS14" t="n">
         <v>3.42</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CU14" t="n">
         <v>1.32</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CX14" t="n">
         <v>1.71</v>
@@ -6507,88 +6507,88 @@
         <v>1.7</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="DD14" t="n">
-        <v>6.01</v>
+        <v>5.88</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DH14" t="n">
-        <v>79</v>
+        <v>77.8</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.22</v>
+        <v>38.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.89</v>
+        <v>12.7</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.78</v>
+        <v>13.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>43.44</v>
+        <v>43.9</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.67</v>
+        <v>9.6</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.78</v>
+        <v>5.8</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.11</v>
+        <v>17</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>0.17</v>
@@ -7892,49 +7892,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>90.67</v>
+        <v>90.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>45.33</v>
+        <v>44.75</v>
       </c>
       <c r="AO18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AT18" t="n">
         <v>1</v>
       </c>
-      <c r="AP18" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AU18" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7946,82 +7946,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>46</v>
+        <v>47.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.67</v>
+        <v>11.25</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.33</v>
+        <v>18</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.56</v>
+        <v>7.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY18" t="n">
         <v>2.16</v>
@@ -8030,73 +8030,73 @@
         <v>2.2</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.96</v>
+        <v>3.65</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.99</v>
+        <v>3.66</v>
       </c>
       <c r="CE18" t="n">
         <v>1.58</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM18" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN18" t="n">
         <v>1.6</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CQ18" t="n">
-        <v>5.26</v>
+        <v>5.16</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CS18" t="n">
         <v>3.43</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CU18" t="n">
         <v>1.32</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="CX18" t="n">
         <v>1.83</v>
@@ -8114,52 +8114,52 @@
         <v>1.56</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="DD18" t="n">
-        <v>5.61</v>
+        <v>5.54</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>91.22</v>
+        <v>91</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.44</v>
+        <v>56</v>
       </c>
       <c r="DN18" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.56</v>
+        <v>10.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.56</v>
+        <v>10.7</v>
       </c>
       <c r="DR18" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8171,28 +8171,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.45</v>
+        <v>46.1</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.34</v>
+        <v>14.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.34</v>
+        <v>5.1</v>
       </c>
       <c r="EA18" t="n">
-        <v>22.33</v>
+        <v>21.2</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -8724,7 +8724,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="AR20" t="n">
         <v>12.2</v>
@@ -8951,7 +8951,7 @@
         <v>1.5</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.5</v>
+        <v>10.88</v>
       </c>
       <c r="DQ20" t="n">
         <v>11.25</v>
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
         <v>5</v>
@@ -9411,19 +9411,19 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H22" t="n">
-        <v>93.25</v>
+        <v>87</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -9432,28 +9432,28 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O22" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>11.75</v>
+        <v>11.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="R22" t="n">
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T22" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -9465,28 +9465,28 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>16.75</v>
+        <v>18.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -9570,46 +9570,46 @@
         <v>2</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BH22" t="n">
-        <v>6.89</v>
+        <v>7.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BP22" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="BR22" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BS22" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BT22" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
@@ -9621,19 +9621,19 @@
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BY22" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="CA22" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CC22" t="n">
         <v>4.02</v>
@@ -9645,7 +9645,7 @@
         <v>1.72</v>
       </c>
       <c r="CF22" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="CG22" t="n">
         <v>2.07</v>
@@ -9654,31 +9654,31 @@
         <v>1.17</v>
       </c>
       <c r="CI22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CN22" t="n">
         <v>1.48</v>
       </c>
-      <c r="CJ22" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CK22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CL22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="CM22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CN22" t="n">
-        <v>1.47</v>
-      </c>
       <c r="CO22" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CP22" t="n">
         <v>3.13</v>
       </c>
       <c r="CQ22" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
       <c r="CR22" t="n">
         <v>1.73</v>
@@ -9689,19 +9689,19 @@
       </c>
       <c r="CU22" t="inlineStr"/>
       <c r="CV22" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CW22" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CZ22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DA22" t="n">
         <v>1.55</v>
@@ -9713,55 +9713,55 @@
         <v>3.34</v>
       </c>
       <c r="DD22" t="n">
-        <v>6.81</v>
+        <v>6.89</v>
       </c>
       <c r="DE22" t="n">
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DH22" t="n">
-        <v>90.78</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DK22" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM22" t="n">
-        <v>51.67</v>
+        <v>51.5</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DO22" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="DP22" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11.67</v>
+        <v>11.4</v>
       </c>
       <c r="DR22" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
@@ -9773,22 +9773,22 @@
         <v>0</v>
       </c>
       <c r="DX22" t="n">
-        <v>10.78</v>
+        <v>11.1</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.22</v>
+        <v>7.5</v>
       </c>
       <c r="DZ22" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="EA22" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="23">
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
@@ -10213,46 +10213,46 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>114.67</v>
+        <v>115</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="K24" t="n">
-        <v>6.33</v>
+        <v>7.25</v>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="M24" t="n">
-        <v>39.67</v>
+        <v>40.75</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3.33</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>12.33</v>
+        <v>13</v>
       </c>
       <c r="R24" t="n">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="S24" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
@@ -10267,28 +10267,28 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>69</v>
+        <v>71.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.67</v>
+        <v>23.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.67</v>
+        <v>15</v>
       </c>
       <c r="AB24" t="n">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>19.33</v>
+        <v>18.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -10372,70 +10372,70 @@
         <v>3.17</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BH24" t="n">
-        <v>8.33</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BP24" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.56</v>
+        <v>4</v>
       </c>
       <c r="BR24" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS24" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT24" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU24" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV24" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW24" t="n">
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="CC24" t="n">
         <v>2.55</v>
@@ -10444,43 +10444,43 @@
         <v>2.74</v>
       </c>
       <c r="CE24" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CF24" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CG24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CH24" t="n">
         <v>1.26</v>
       </c>
       <c r="CI24" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CJ24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CK24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CL24" t="n">
         <v>2.29</v>
       </c>
       <c r="CM24" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CN24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CO24" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CP24" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CQ24" t="n">
-        <v>4.8</v>
+        <v>4.72</v>
       </c>
       <c r="CR24" t="n">
         <v>1.54</v>
@@ -10495,19 +10495,19 @@
         <v>1.33</v>
       </c>
       <c r="CV24" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CW24" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CX24" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY24" t="n">
         <v>2.24</v>
       </c>
       <c r="CZ24" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DA24" t="n">
         <v>1.65</v>
@@ -10516,85 +10516,85 @@
         <v>1.52</v>
       </c>
       <c r="DC24" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DD24" t="n">
-        <v>5.22</v>
+        <v>5.17</v>
       </c>
       <c r="DE24" t="n">
         <v>0</v>
       </c>
       <c r="DF24" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DG24" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="DH24" t="n">
-        <v>105.78</v>
+        <v>106.8</v>
       </c>
       <c r="DI24" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ24" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="DK24" t="n">
-        <v>4.66</v>
+        <v>5.2</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="DM24" t="n">
-        <v>49.34</v>
+        <v>48.8</v>
       </c>
       <c r="DN24" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO24" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="DP24" t="n">
-        <v>11.67</v>
+        <v>11.6</v>
       </c>
       <c r="DQ24" t="n">
-        <v>11.33</v>
+        <v>11.7</v>
       </c>
       <c r="DR24" t="n">
-        <v>6.78</v>
+        <v>6.3</v>
       </c>
       <c r="DS24" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT24" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU24" t="n">
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>65.22</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="DW24" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="DX24" t="n">
-        <v>15.44</v>
+        <v>17.3</v>
       </c>
       <c r="DY24" t="n">
-        <v>10.11</v>
+        <v>11.3</v>
       </c>
       <c r="DZ24" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="EA24" t="n">
-        <v>21.22</v>
+        <v>20.6</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="EC24" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -10604,10 +10604,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
         <v>5</v>
@@ -10616,82 +10616,82 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H25" t="n">
-        <v>109.5</v>
+        <v>111.8</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K25" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M25" t="n">
-        <v>72.75</v>
+        <v>75.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="R25" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="S25" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>54.75</v>
+        <v>58.2</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>9.25</v>
+        <v>10.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>19.5</v>
+        <v>18.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
         <v>0.2</v>
@@ -10775,46 +10775,46 @@
         <v>2.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BH25" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BP25" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="BR25" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS25" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT25" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
@@ -10826,19 +10826,19 @@
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY25" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="BZ25" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="CB25" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="CC25" t="n">
         <v>2.9</v>
@@ -10847,153 +10847,157 @@
         <v>3.06</v>
       </c>
       <c r="CE25" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CF25" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="CG25" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CH25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI25" t="n">
         <v>1.61</v>
       </c>
       <c r="CJ25" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CK25" t="n">
         <v>1.75</v>
       </c>
       <c r="CL25" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CM25" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CN25" t="n">
         <v>1.58</v>
       </c>
       <c r="CO25" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CP25" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="CQ25" t="n">
-        <v>5.28</v>
+        <v>5.17</v>
       </c>
       <c r="CR25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CS25" t="inlineStr"/>
+        <v>1.58</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>3.38</v>
+      </c>
       <c r="CT25" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CU25" t="inlineStr"/>
+        <v>2.42</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>1.33</v>
+      </c>
       <c r="CV25" t="n">
         <v>1.64</v>
       </c>
       <c r="CW25" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CX25" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CY25" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CZ25" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DA25" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DB25" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DC25" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DD25" t="n">
-        <v>5.66</v>
+        <v>5.55</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF25" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DG25" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DH25" t="n">
-        <v>97.56</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="DI25" t="n">
         <v>0</v>
       </c>
       <c r="DJ25" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DK25" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="DL25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM25" t="n">
-        <v>61.33</v>
+        <v>63.7</v>
       </c>
       <c r="DN25" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="DO25" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="DP25" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DQ25" t="n">
-        <v>16.11</v>
+        <v>15.7</v>
       </c>
       <c r="DR25" t="n">
-        <v>6.78</v>
+        <v>6.6</v>
       </c>
       <c r="DS25" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT25" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU25" t="n">
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>52.11</v>
+        <v>54.1</v>
       </c>
       <c r="DW25" t="n">
         <v>0</v>
       </c>
       <c r="DX25" t="n">
-        <v>11.89</v>
+        <v>12.8</v>
       </c>
       <c r="DY25" t="n">
-        <v>7.22</v>
+        <v>8</v>
       </c>
       <c r="DZ25" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="EA25" t="n">
-        <v>19.22</v>
+        <v>18.7</v>
       </c>
       <c r="EB25" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="EC25" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="26">
@@ -11402,13 +11406,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -11495,13 +11499,13 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>88.25</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -11510,34 +11514,34 @@
         <v>5</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AN27" t="n">
-        <v>46.5</v>
+        <v>41.6</v>
       </c>
       <c r="AO27" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14.75</v>
+        <v>14.8</v>
       </c>
       <c r="AR27" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>10.75</v>
+        <v>11.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
@@ -11549,73 +11553,73 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>47.75</v>
+        <v>42.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>24.25</v>
+        <v>22</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BH27" t="n">
-        <v>8.890000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BM27" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BN27" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BP27" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="BQ27" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="BR27" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS27" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BT27" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU27" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV27" t="n">
         <v>0</v>
@@ -11624,7 +11628,7 @@
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BY27" t="n">
         <v>3</v>
@@ -11633,55 +11637,55 @@
         <v>3.12</v>
       </c>
       <c r="CA27" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="CB27" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="CC27" t="n">
-        <v>6.21</v>
+        <v>6.55</v>
       </c>
       <c r="CD27" t="n">
-        <v>7.48</v>
+        <v>7.68</v>
       </c>
       <c r="CE27" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CF27" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CG27" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CH27" t="n">
         <v>1.23</v>
       </c>
       <c r="CI27" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CJ27" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CK27" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CL27" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CM27" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN27" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO27" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CP27" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CQ27" t="n">
-        <v>5.18</v>
+        <v>5.07</v>
       </c>
       <c r="CR27" t="n">
         <v>1.6</v>
@@ -11692,16 +11696,16 @@
       </c>
       <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CW27" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CX27" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY27" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ27" t="n">
         <v>2.09</v>
@@ -11710,85 +11714,85 @@
         <v>1.67</v>
       </c>
       <c r="DB27" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DC27" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="DD27" t="n">
-        <v>5.83</v>
+        <v>5.72</v>
       </c>
       <c r="DE27" t="n">
         <v>0</v>
       </c>
       <c r="DF27" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="DG27" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="DH27" t="n">
-        <v>92.89</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="DI27" t="n">
         <v>0</v>
       </c>
       <c r="DJ27" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="DK27" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="DM27" t="n">
-        <v>53.11</v>
+        <v>50</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="DO27" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="DP27" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="DQ27" t="n">
-        <v>12.78</v>
+        <v>12.6</v>
       </c>
       <c r="DR27" t="n">
-        <v>9.109999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="DS27" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT27" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU27" t="n">
         <v>0</v>
       </c>
       <c r="DV27" t="n">
-        <v>52.11</v>
+        <v>49</v>
       </c>
       <c r="DW27" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DX27" t="n">
-        <v>11.22</v>
+        <v>10.3</v>
       </c>
       <c r="DY27" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="DZ27" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="EA27" t="n">
-        <v>24.11</v>
+        <v>23</v>
       </c>
       <c r="EB27" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="EC27" t="n">
         <v>4</v>
@@ -11801,13 +11805,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -11894,49 +11898,49 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>90.25</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN28" t="n">
-        <v>47</v>
+        <v>46.2</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AV28" t="n">
         <v>0</v>
@@ -11948,70 +11952,70 @@
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>48.75</v>
+        <v>49.4</v>
       </c>
       <c r="AZ28" t="n">
         <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>12.75</v>
+        <v>12.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.25</v>
+        <v>8.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
-        <v>19.75</v>
+        <v>20.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="BH28" t="n">
-        <v>9.890000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL28" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BN28" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BP28" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BQ28" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="BR28" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BS28" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BT28" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU28" t="n">
         <v>0</v>
@@ -12023,7 +12027,7 @@
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY28" t="n">
         <v>2.01</v>
@@ -12032,62 +12036,62 @@
         <v>2.07</v>
       </c>
       <c r="CA28" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CB28" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CC28" t="n">
-        <v>3.54</v>
+        <v>3.49</v>
       </c>
       <c r="CD28" t="n">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="CE28" t="n">
         <v>1.63</v>
       </c>
       <c r="CF28" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CG28" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CH28" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CI28" t="n">
         <v>1.55</v>
       </c>
       <c r="CJ28" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CK28" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CL28" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CM28" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CN28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CP28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CQ28" t="n">
-        <v>6.07</v>
+        <v>6.03</v>
       </c>
       <c r="CR28" t="n">
         <v>1.65</v>
       </c>
       <c r="CS28" t="inlineStr"/>
       <c r="CT28" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="n">
@@ -12097,25 +12101,25 @@
         <v>2.48</v>
       </c>
       <c r="CX28" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CY28" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CZ28" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DA28" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB28" t="n">
         <v>1.64</v>
       </c>
       <c r="DC28" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="DD28" t="n">
-        <v>6.08</v>
+        <v>6.13</v>
       </c>
       <c r="DE28" t="n">
         <v>0</v>
@@ -12124,40 +12128,40 @@
         <v>1</v>
       </c>
       <c r="DG28" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DH28" t="n">
-        <v>85.89</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="DI28" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ28" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DK28" t="n">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="DL28" t="n">
         <v>0</v>
       </c>
       <c r="DM28" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="DN28" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DO28" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DP28" t="n">
-        <v>10.44</v>
+        <v>11</v>
       </c>
       <c r="DQ28" t="n">
-        <v>11.22</v>
+        <v>11.8</v>
       </c>
       <c r="DR28" t="n">
-        <v>7.56</v>
+        <v>7.5</v>
       </c>
       <c r="DS28" t="n">
         <v>0</v>
@@ -12169,28 +12173,28 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>54.22</v>
+        <v>54</v>
       </c>
       <c r="DW28" t="n">
         <v>0</v>
       </c>
       <c r="DX28" t="n">
-        <v>12.44</v>
+        <v>12.3</v>
       </c>
       <c r="DY28" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="DZ28" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="EA28" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="EB28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC28" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -12200,10 +12204,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
@@ -12212,13 +12216,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G29" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="H29" t="n">
-        <v>85.59999999999999</v>
+        <v>79.67</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -12227,34 +12231,34 @@
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>5.6</v>
+        <v>4.83</v>
       </c>
       <c r="L29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M29" t="n">
-        <v>48.2</v>
+        <v>47</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.8</v>
+        <v>14.17</v>
       </c>
       <c r="R29" t="n">
-        <v>8.6</v>
+        <v>8.17</v>
       </c>
       <c r="S29" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="T29" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -12266,25 +12270,25 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>44.6</v>
+        <v>43</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AC29" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -12371,70 +12375,70 @@
         <v>1.75</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BH29" t="n">
-        <v>8.779999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL29" t="n">
         <v>1</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN29" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BP29" t="n">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BR29" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS29" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT29" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU29" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV29" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="BZ29" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="CA29" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CC29" t="n">
         <v>3.84</v>
@@ -12443,31 +12447,31 @@
         <v>4.12</v>
       </c>
       <c r="CE29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CF29" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CG29" t="n">
         <v>2.17</v>
       </c>
       <c r="CH29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CI29" t="n">
         <v>1.54</v>
       </c>
       <c r="CJ29" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CK29" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CL29" t="n">
         <v>2.52</v>
       </c>
       <c r="CM29" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CN29" t="n">
         <v>1.51</v>
@@ -12476,87 +12480,87 @@
         <v>1.57</v>
       </c>
       <c r="CP29" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CQ29" t="n">
-        <v>5.83</v>
+        <v>5.87</v>
       </c>
       <c r="CR29" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CS29" t="inlineStr"/>
       <c r="CT29" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CU29" t="inlineStr"/>
       <c r="CV29" t="n">
         <v>1.56</v>
       </c>
       <c r="CW29" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CX29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CY29" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CZ29" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DA29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB29" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DC29" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DD29" t="n">
-        <v>6.46</v>
+        <v>6.62</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DG29" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DH29" t="n">
-        <v>85.22</v>
+        <v>81.7</v>
       </c>
       <c r="DI29" t="n">
         <v>0</v>
       </c>
       <c r="DJ29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DK29" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="DL29" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM29" t="n">
-        <v>47.22</v>
+        <v>46.6</v>
       </c>
       <c r="DN29" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DO29" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DP29" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="DQ29" t="n">
-        <v>13.44</v>
+        <v>13.7</v>
       </c>
       <c r="DR29" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS29" t="n">
         <v>0</v>
@@ -12568,28 +12572,28 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>44.33</v>
+        <v>43.4</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
       </c>
       <c r="DX29" t="n">
-        <v>13.67</v>
+        <v>12.9</v>
       </c>
       <c r="DY29" t="n">
-        <v>8.67</v>
+        <v>8.1</v>
       </c>
       <c r="DZ29" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="EA29" t="n">
-        <v>16.11</v>
+        <v>16.2</v>
       </c>
       <c r="EB29" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="EC29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="30">
@@ -12599,25 +12603,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
         <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F30" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="G30" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="H30" t="n">
-        <v>92</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -12626,64 +12630,64 @@
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M30" t="n">
-        <v>56.5</v>
+        <v>57.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P30" t="n">
-        <v>10.25</v>
+        <v>9.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="U30" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>52.75</v>
+        <v>50.2</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>19.75</v>
+        <v>18.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>14.25</v>
+        <v>13.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AC30" t="n">
-        <v>23.25</v>
+        <v>23.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -12770,70 +12774,70 @@
         <v>1.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BH30" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BL30" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN30" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP30" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="BQ30" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="BR30" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS30" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT30" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU30" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV30" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW30" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX30" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="BZ30" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="CA30" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CC30" t="n">
         <v>3.12</v>
@@ -12842,153 +12846,153 @@
         <v>3.34</v>
       </c>
       <c r="CE30" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CF30" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CG30" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CH30" t="n">
         <v>1.21</v>
       </c>
       <c r="CI30" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CJ30" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CK30" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CL30" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="CM30" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CN30" t="n">
         <v>1.55</v>
       </c>
       <c r="CO30" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CP30" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CQ30" t="n">
         <v>5.55</v>
       </c>
       <c r="CR30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CS30" t="inlineStr"/>
       <c r="CT30" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CU30" t="inlineStr"/>
       <c r="CV30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CW30" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CY30" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CZ30" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DA30" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DC30" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="DD30" t="n">
-        <v>6.07</v>
+        <v>6.12</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF30" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG30" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="DH30" t="n">
-        <v>89.44</v>
+        <v>90.5</v>
       </c>
       <c r="DI30" t="n">
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DK30" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="DL30" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DM30" t="n">
-        <v>47.67</v>
+        <v>49.1</v>
       </c>
       <c r="DN30" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DO30" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DP30" t="n">
-        <v>11.22</v>
+        <v>10.8</v>
       </c>
       <c r="DQ30" t="n">
-        <v>10.56</v>
+        <v>10.3</v>
       </c>
       <c r="DR30" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="DS30" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT30" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU30" t="n">
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>46.56</v>
+        <v>45.9</v>
       </c>
       <c r="DW30" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX30" t="n">
-        <v>15.78</v>
+        <v>15.6</v>
       </c>
       <c r="DY30" t="n">
-        <v>10.67</v>
+        <v>10.7</v>
       </c>
       <c r="DZ30" t="n">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
       <c r="EA30" t="n">
-        <v>19.89</v>
+        <v>20.2</v>
       </c>
       <c r="EB30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="EC30" t="n">
         <v>1.7</v>
-      </c>
-      <c r="EC30" t="n">
-        <v>1.67</v>
       </c>
     </row>
     <row r="31">
@@ -12998,13 +13002,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
         <v>0.25</v>
@@ -13088,127 +13092,127 @@
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AI31" t="n">
-        <v>90.8</v>
+        <v>86.67</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AL31" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN31" t="n">
-        <v>49.4</v>
+        <v>47.83</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.4</v>
+        <v>7.83</v>
       </c>
       <c r="AT31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BM31" t="n">
         <v>0.6</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>0.5600000000000001</v>
       </c>
       <c r="BN31" t="n">
         <v>1</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BP31" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="BQ31" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="BR31" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS31" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT31" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BU31" t="n">
         <v>0</v>
@@ -13220,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="BX31" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY31" t="n">
         <v>2.55</v>
@@ -13229,25 +13233,25 @@
         <v>2.7</v>
       </c>
       <c r="CA31" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CC31" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="CD31" t="n">
-        <v>3.53</v>
+        <v>3.46</v>
       </c>
       <c r="CE31" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CF31" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="CG31" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CH31" t="n">
         <v>1.21</v>
@@ -13256,138 +13260,138 @@
         <v>1.59</v>
       </c>
       <c r="CJ31" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CK31" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CL31" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CM31" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CN31" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO31" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CP31" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CQ31" t="n">
-        <v>5.89</v>
+        <v>5.91</v>
       </c>
       <c r="CR31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CS31" t="inlineStr"/>
       <c r="CT31" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CU31" t="inlineStr"/>
       <c r="CV31" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CW31" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CX31" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CY31" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CZ31" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="DA31" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="DB31" t="n">
         <v>1.67</v>
       </c>
       <c r="DC31" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="DD31" t="n">
-        <v>6.41</v>
+        <v>6.55</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DF31" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="DG31" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="DH31" t="n">
-        <v>98</v>
+        <v>94.8</v>
       </c>
       <c r="DI31" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ31" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DK31" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM31" t="n">
-        <v>49.11</v>
+        <v>48.2</v>
       </c>
       <c r="DN31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DP31" t="n">
-        <v>10.11</v>
+        <v>9.9</v>
       </c>
       <c r="DQ31" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="DR31" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="DS31" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT31" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU31" t="n">
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>53.22</v>
+        <v>52.8</v>
       </c>
       <c r="DW31" t="n">
         <v>0</v>
       </c>
       <c r="DX31" t="n">
-        <v>10.56</v>
+        <v>10.9</v>
       </c>
       <c r="DY31" t="n">
-        <v>7.11</v>
+        <v>7.2</v>
       </c>
       <c r="DZ31" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="EA31" t="n">
-        <v>19.56</v>
+        <v>19.5</v>
       </c>
       <c r="EB31" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="EC31" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>87.33</v>
+        <v>90.25</v>
       </c>
       <c r="I2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>62.67</v>
+        <v>61.5</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
-        <v>18</v>
+        <v>17.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="R2" t="n">
-        <v>5.67</v>
+        <v>6.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47.33</v>
+        <v>45.5</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.67</v>
+        <v>24.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,49 +1550,49 @@
         <v>1.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BR2" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BT2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BU2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CC2" t="n">
         <v>4.82</v>
@@ -1625,76 +1625,76 @@
         <v>1.62</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.77</v>
+        <v>3.88</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="CQ2" t="n">
-        <v>5.58</v>
+        <v>5.79</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CS2" t="n">
         <v>3.35</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="CU2" t="n">
         <v>1.31</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DC2" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="DD2" t="n">
         <v>6.27</v>
@@ -1703,76 +1703,76 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.5</v>
+        <v>87.89</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM2" t="n">
         <v>58</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DP2" t="n">
-        <v>15</v>
+        <v>15.22</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.37</v>
+        <v>49.22</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.119999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.25</v>
+        <v>24.44</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,127 +2278,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>92.5</v>
+        <v>90.8</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>52.5</v>
+        <v>57.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.25</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48.5</v>
+        <v>49.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>25.75</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.67</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS4" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU4" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY4" t="n">
         <v>2.32</v>
@@ -2416,55 +2416,55 @@
         <v>2.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.96</v>
+        <v>3.71</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.5</v>
+        <v>4.17</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
         <v>2.12</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN4" t="n">
         <v>1.64</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="CR4" t="n">
         <v>1.58</v>
@@ -2473,7 +2473,7 @@
         <v>3.33</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CU4" t="n">
         <v>1.31</v>
@@ -2482,103 +2482,103 @@
         <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.31</v>
+        <v>5.42</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="DH4" t="n">
-        <v>83.22</v>
+        <v>83.3</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.56</v>
+        <v>5.3</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DM4" t="n">
-        <v>60.44</v>
+        <v>62.2</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.67</v>
+        <v>12.6</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.33</v>
+        <v>12.8</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51.33</v>
+        <v>51.7</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.220000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="EA4" t="n">
-        <v>26</v>
+        <v>25.1</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
-        <v>102.75</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>49.25</v>
+        <v>50.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>14.25</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="R6" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>46.25</v>
+        <v>46</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.75</v>
+        <v>18.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>0.2</v>
@@ -3162,46 +3162,46 @@
         <v>1.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="CC6" t="n">
         <v>5.93</v>
@@ -3237,7 +3237,7 @@
         <v>1.65</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CG6" t="n">
         <v>2.23</v>
@@ -3246,16 +3246,16 @@
         <v>1.2</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CK6" t="n">
         <v>1.82</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CM6" t="n">
         <v>1.94</v>
@@ -3270,34 +3270,34 @@
         <v>2.89</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.96</v>
+        <v>5.93</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CS6" t="n">
         <v>3.36</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CU6" t="n">
         <v>1.31</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CY6" t="n">
         <v>2.41</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DA6" t="n">
         <v>1.55</v>
@@ -3309,82 +3309,82 @@
         <v>3.01</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.05</v>
+        <v>6.09</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.67</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.89</v>
+        <v>49.5</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.56</v>
+        <v>12.1</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>38.67</v>
+        <v>39.3</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.44</v>
+        <v>9.4</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="EA6" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="EB6" t="n">
         <v>1.21</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -3920,7 +3920,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AR8" t="n">
         <v>10.5</v>
@@ -4151,7 +4151,7 @@
         <v>2.8</v>
       </c>
       <c r="DP8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DQ8" t="n">
         <v>14.1</v>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>90.75</v>
+        <v>92</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>54</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P9" t="n">
-        <v>11.25</v>
+        <v>10.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="R9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.25</v>
+        <v>7.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,43 +4371,43 @@
         <v>3.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.890000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="BR9" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS9" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -4422,19 +4422,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="CC9" t="n">
         <v>4.71</v>
@@ -4443,63 +4443,63 @@
         <v>5.53</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.77</v>
+        <v>3.9</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.76</v>
+        <v>6.02</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="CX9" t="n">
         <v>1.87</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CZ9" t="n">
         <v>1.94</v>
@@ -4508,10 +4508,10 @@
         <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="DC9" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="DD9" t="n">
         <v>6.37</v>
@@ -4520,76 +4520,76 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.67</v>
+        <v>86.8</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.89</v>
+        <v>12.4</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="DR9" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.67</v>
+        <v>45.4</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.109999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.56</v>
+        <v>6.1</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.89</v>
+        <v>18.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>74.25</v>
+        <v>67</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.75</v>
+        <v>39.6</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.75</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.5</v>
+        <v>13.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.75</v>
+        <v>9.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AU10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1</v>
       </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.92</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.89</v>
+        <v>1.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="BR10" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BS10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT10" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BU10" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>2.83</v>
@@ -4830,19 +4830,19 @@
         <v>2.95</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CC10" t="n">
         <v>3.83</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.08</v>
+        <v>4.13</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CF10" t="n">
         <v>3.68</v>
@@ -4854,141 +4854,141 @@
         <v>1.22</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CL10" t="n">
         <v>2.47</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CO10" t="n">
         <v>1.54</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>5.45</v>
+        <v>5.49</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CS10" t="inlineStr"/>
       <c r="CT10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="n">
         <v>1.62</v>
       </c>
       <c r="CW10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CY10" t="n">
         <v>2.38</v>
       </c>
-      <c r="CX10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>2.34</v>
-      </c>
       <c r="CZ10" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DB10" t="n">
         <v>1.62</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.08</v>
+        <v>6.15</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.11</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
-        <v>48</v>
+        <v>46.7</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DP10" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.89</v>
+        <v>11.1</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.220000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.11</v>
+        <v>49.8</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.220000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.67</v>
+        <v>20.7</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5091,49 +5091,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>85.75</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.5</v>
+        <v>55.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18.75</v>
+        <v>17.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.75</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5145,67 +5145,67 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>28.25</v>
+        <v>32.2</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>14</v>
+        <v>17.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.44</v>
+        <v>8.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BS11" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5220,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BY11" t="n">
         <v>2.39</v>
@@ -5229,87 +5229,87 @@
         <v>2.46</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.73</v>
+        <v>4.37</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.22</v>
+        <v>4.79</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CF11" t="n">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CI11" t="n">
         <v>1.46</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CN11" t="n">
         <v>1.55</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CQ11" t="n">
-        <v>6.79</v>
+        <v>6.95</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CS11" t="inlineStr"/>
       <c r="CT11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="n">
         <v>1.45</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="DD11" t="n">
         <v>7.02</v>
@@ -5318,43 +5318,43 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.11</v>
+        <v>92.2</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.22</v>
+        <v>60.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DO11" t="n">
         <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>18.11</v>
+        <v>17.6</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>40.44</v>
+        <v>41.2</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.11</v>
+        <v>22</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="EC11" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="12">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5490,49 +5490,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>85.25</v>
+        <v>85.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.5</v>
+        <v>41.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.25</v>
+        <v>11.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5544,70 +5544,70 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>54.5</v>
+        <v>55.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.75</v>
+        <v>12.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.75</v>
+        <v>16.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.67</v>
+        <v>9.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="BQ12" t="n">
         <v>5</v>
       </c>
       <c r="BR12" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS12" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BT12" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BY12" t="n">
         <v>2.2</v>
@@ -5628,132 +5628,132 @@
         <v>2.2</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CB12" t="n">
         <v>2.93</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.01</v>
+        <v>3.11</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.38</v>
+        <v>4.59</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="n">
         <v>1.57</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.4</v>
+        <v>6.46</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.67</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM12" t="n">
-        <v>50.44</v>
+        <v>50.1</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.779999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.11</v>
+        <v>11.9</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5765,28 +5765,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.56</v>
+        <v>54</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.33</v>
+        <v>13</v>
       </c>
       <c r="DY12" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.67</v>
+        <v>17.2</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5889,128 +5889,128 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>87.59999999999999</v>
+        <v>87.67</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.8</v>
+        <v>4.17</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>59</v>
+        <v>52.33</v>
       </c>
       <c r="AO13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM13" t="n">
         <v>0.2</v>
       </c>
-      <c r="AP13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
+      <c r="BN13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BU13" t="n">
         <v>10</v>
       </c>
-      <c r="BB13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>11.11</v>
-      </c>
       <c r="BV13" t="n">
         <v>0</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BY13" t="n">
         <v>3.95</v>
@@ -6027,55 +6027,55 @@
         <v>4.33</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.91</v>
+        <v>5.42</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.59</v>
+        <v>6.18</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.44</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.98</v>
+        <v>5.78</v>
       </c>
       <c r="CR13" t="n">
         <v>1.63</v>
@@ -6086,73 +6086,73 @@
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CX13" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DC13" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.34</v>
+        <v>6.13</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="DH13" t="n">
-        <v>85</v>
+        <v>85.3</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.67</v>
+        <v>4.3</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM13" t="n">
-        <v>56.67</v>
+        <v>52.9</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.67</v>
+        <v>10.9</v>
       </c>
       <c r="DQ13" t="n">
         <v>12</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6164,28 +6164,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.78</v>
+        <v>44.7</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.56</v>
+        <v>10.7</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.109999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="EA13" t="n">
-        <v>24.78</v>
+        <v>24.3</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6598,61 +6598,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="n">
-        <v>107.5</v>
+        <v>100.8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>52.5</v>
+        <v>51.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.75</v>
+        <v>12.8</v>
       </c>
       <c r="R15" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="S15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6664,28 +6664,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>52.5</v>
+        <v>50.4</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>26.75</v>
+        <v>25.4</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.2</v>
@@ -6769,49 +6769,49 @@
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS15" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BT15" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6820,19 +6820,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CC15" t="n">
         <v>5.25</v>
@@ -6841,43 +6841,43 @@
         <v>5.95</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CH15" t="n">
         <v>1.19</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO15" t="n">
         <v>1.64</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CQ15" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="CR15" t="n">
         <v>1.68</v>
@@ -6898,67 +6898,67 @@
         <v>2.62</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DB15" t="n">
         <v>1.7</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="DD15" t="n">
-        <v>6.57</v>
+        <v>6.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>90.56</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ15" t="n">
         <v>2</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>41.67</v>
+        <v>42.3</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.56</v>
+        <v>10.4</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.44</v>
+        <v>12.9</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6970,28 +6970,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.67</v>
+        <v>43.5</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.33</v>
+        <v>10.6</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.67</v>
+        <v>7.1</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.56</v>
+        <v>21.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="16">
@@ -7001,13 +7001,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7094,127 +7094,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>80.25</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>39.5</v>
+        <v>40.8</v>
       </c>
       <c r="AO16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.5</v>
+        <v>13.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AU16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BL16" t="n">
         <v>0.5</v>
       </c>
-      <c r="AV16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>57.25</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="BR16" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU16" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
         <v>2.46</v>
@@ -7235,19 +7235,19 @@
         <v>2.74</v>
       </c>
       <c r="CB16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CC16" t="n">
         <v>2.8</v>
       </c>
-      <c r="CC16" t="n">
-        <v>2.84</v>
-      </c>
       <c r="CD16" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="CE16" t="n">
         <v>1.72</v>
       </c>
       <c r="CF16" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="CG16" t="n">
         <v>2.04</v>
@@ -7259,35 +7259,35 @@
         <v>1.49</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CK16" t="n">
         <v>1.9</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CN16" t="n">
         <v>1.5</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CP16" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.63</v>
+        <v>6.71</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CS16" t="inlineStr"/>
       <c r="CT16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CU16" t="inlineStr"/>
       <c r="CV16" t="n">
@@ -7312,7 +7312,7 @@
         <v>1.79</v>
       </c>
       <c r="DC16" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="DD16" t="n">
         <v>7.07</v>
@@ -7321,76 +7321,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DH16" t="n">
-        <v>84.44</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DM16" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.22</v>
+        <v>12.1</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.33</v>
+        <v>14.6</v>
       </c>
       <c r="DR16" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.78</v>
+        <v>54.4</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.78</v>
+        <v>11.1</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.33</v>
+        <v>7.6</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="EA16" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="17">
@@ -7400,13 +7400,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7493,49 +7493,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>96.75</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>57</v>
+        <v>58.8</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7547,82 +7547,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.25</v>
+        <v>55.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>25</v>
+        <v>23.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="BF17" t="n">
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BH17" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.33</v>
+        <v>4.7</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT17" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BU17" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY17" t="n">
         <v>2.09</v>
@@ -7631,81 +7631,81 @@
         <v>2.13</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CB17" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CG17" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CO17" t="n">
         <v>1.59</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CS17" t="inlineStr"/>
       <c r="CT17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CZ17" t="n">
         <v>1.94</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB17" t="n">
         <v>1.63</v>
@@ -7723,10 +7723,10 @@
         <v>2</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="DH17" t="n">
-        <v>98.89</v>
+        <v>96.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
@@ -7735,61 +7735,61 @@
         <v>3</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.11</v>
+        <v>6.3</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="DM17" t="n">
-        <v>49</v>
+        <v>50.7</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO17" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.22</v>
+        <v>13</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.11</v>
+        <v>55.2</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DX17" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.56</v>
+        <v>9.4</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="EA17" t="n">
-        <v>26.22</v>
+        <v>25.3</v>
       </c>
       <c r="EB17" t="n">
         <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -8202,94 +8202,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="H19" t="n">
-        <v>93.2</v>
+        <v>86.83</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="M19" t="n">
-        <v>51.4</v>
+        <v>50.17</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="O19" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>14.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>54.2</v>
+        <v>51</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>21.6</v>
+        <v>19.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8373,49 +8373,49 @@
         <v>2.25</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BH19" t="n">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8424,16 +8424,16 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="CA19" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CB19" t="n">
         <v>2.92</v>
@@ -8445,57 +8445,57 @@
         <v>3.33</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CF19" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CJ19" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CK19" t="n">
         <v>1.75</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CM19" t="n">
         <v>2.01</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CQ19" t="n">
-        <v>6.27</v>
+        <v>6.15</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CS19" t="inlineStr"/>
       <c r="CT19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="n">
         <v>1.6</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CX19" t="n">
         <v>1.82</v>
@@ -8519,79 +8519,79 @@
         <v>6.43</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.33</v>
+        <v>89.5</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>51.56</v>
+        <v>50.8</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DO19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="DP19" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.33</v>
+        <v>12.3</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.78</v>
+        <v>6.5</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.56</v>
+        <v>51.7</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.33</v>
+        <v>12.2</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.89</v>
+        <v>20.8</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>5</v>
@@ -8613,13 +8613,13 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="H20" t="n">
-        <v>94.33</v>
+        <v>89</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -8628,64 +8628,64 @@
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M20" t="n">
-        <v>46.67</v>
+        <v>46.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>8.67</v>
+        <v>9.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.67</v>
+        <v>8.75</v>
       </c>
       <c r="R20" t="n">
-        <v>6.33</v>
+        <v>5.75</v>
       </c>
       <c r="S20" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>11</v>
+        <v>11.75</v>
       </c>
       <c r="AA20" t="n">
         <v>7</v>
       </c>
       <c r="AB20" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>19</v>
+        <v>18.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
         <v>2</v>
@@ -8772,70 +8772,70 @@
         <v>2.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BO20" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="BP20" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.12</v>
+        <v>4.56</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT20" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BV20" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="CC20" t="n">
         <v>3.46</v>
@@ -8844,16 +8844,16 @@
         <v>3.79</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CI20" t="n">
         <v>1.59</v>
@@ -8862,135 +8862,135 @@
         <v>2.18</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="CM20" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="CQ20" t="n">
-        <v>5.72</v>
+        <v>5.56</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CS20" t="inlineStr"/>
       <c r="CT20" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DC20" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="DD20" t="n">
-        <v>5.99</v>
+        <v>5.88</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.87</v>
+        <v>2.56</v>
       </c>
       <c r="DH20" t="n">
-        <v>84.75</v>
+        <v>83.44</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.37</v>
+        <v>4.67</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="DM20" t="n">
-        <v>40.63</v>
+        <v>41.22</v>
       </c>
       <c r="DN20" t="n">
         <v>1</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.5</v>
+        <v>2.11</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.25</v>
+        <v>10.67</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.75</v>
+        <v>7.33</v>
       </c>
       <c r="DS20" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT20" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>48.88</v>
+        <v>50.44</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>10</v>
+        <v>10.44</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="EA20" t="n">
-        <v>18</v>
+        <v>17.78</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="21">
@@ -9000,13 +9000,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9093,115 +9093,115 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>58.25</v>
+        <v>59.6</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN21" t="n">
-        <v>48</v>
+        <v>44.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.75</v>
+        <v>12.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="BF21" t="n">
         <v>2</v>
       </c>
-      <c r="AU21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BG21" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.89</v>
+        <v>4.4</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9210,19 +9210,19 @@
         <v>100</v>
       </c>
       <c r="BT21" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BU21" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BV21" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
         <v>3.08</v>
@@ -9231,165 +9231,165 @@
         <v>3.61</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="CC21" t="n">
-        <v>4.47</v>
+        <v>4.58</v>
       </c>
       <c r="CD21" t="n">
-        <v>5.34</v>
+        <v>5.49</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CI21" t="n">
         <v>1.58</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CK21" t="n">
         <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.61</v>
+        <v>5.48</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CS21" t="inlineStr"/>
       <c r="CT21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="CU21" t="inlineStr"/>
       <c r="CV21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CW21" t="n">
         <v>2.48</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="DD21" t="n">
-        <v>6.1</v>
+        <v>5.99</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DH21" t="n">
-        <v>76.22</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM21" t="n">
-        <v>53</v>
+        <v>50.9</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.44</v>
+        <v>13.7</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.56</v>
+        <v>13.4</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>42.89</v>
+        <v>42.3</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.56</v>
+        <v>10</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.44</v>
+        <v>7</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.44</v>
+        <v>19.4</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>6</v>
@@ -9810,49 +9810,49 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H23" t="n">
-        <v>92.33</v>
+        <v>93.25</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>72</v>
+        <v>64.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>13.67</v>
+        <v>13.25</v>
       </c>
       <c r="Q23" t="n">
         <v>12</v>
       </c>
       <c r="R23" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -9864,28 +9864,28 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>57.33</v>
+        <v>57</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>16</v>
+        <v>17.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>11.33</v>
+        <v>13</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>23.33</v>
+        <v>23</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -9969,49 +9969,49 @@
         <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BH23" t="n">
-        <v>9.56</v>
+        <v>9</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="BR23" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS23" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT23" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU23" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10020,19 +10020,19 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BZ23" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="CA23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="CC23" t="n">
         <v>2.44</v>
@@ -10044,40 +10044,40 @@
         <v>1.53</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CH23" t="n">
         <v>1.26</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.79</v>
+        <v>4.71</v>
       </c>
       <c r="CR23" t="n">
         <v>1.56</v>
@@ -10092,106 +10092,106 @@
         <v>1.32</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="DD23" t="n">
-        <v>5.19</v>
+        <v>5.12</v>
       </c>
       <c r="DE23" t="n">
         <v>0</v>
       </c>
       <c r="DF23" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="DH23" t="n">
-        <v>97.11</v>
+        <v>97</v>
       </c>
       <c r="DI23" t="n">
         <v>0</v>
       </c>
       <c r="DJ23" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="DK23" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM23" t="n">
-        <v>53.22</v>
+        <v>52.1</v>
       </c>
       <c r="DN23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DP23" t="n">
-        <v>13.78</v>
+        <v>13.6</v>
       </c>
       <c r="DQ23" t="n">
-        <v>10.45</v>
+        <v>10.6</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="DS23" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT23" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU23" t="n">
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>58.22</v>
+        <v>58</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX23" t="n">
-        <v>12.33</v>
+        <v>13.2</v>
       </c>
       <c r="DY23" t="n">
-        <v>8.33</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="EA23" t="n">
-        <v>22.56</v>
+        <v>22.5</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="EC23" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24">
@@ -10216,7 +10216,7 @@
         <v>1.75</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>115</v>
@@ -10231,7 +10231,7 @@
         <v>7.25</v>
       </c>
       <c r="L24" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
         <v>40.75</v>
@@ -10240,7 +10240,7 @@
         <v>0.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="P24" t="n">
         <v>11.75</v>
@@ -10399,10 +10399,10 @@
         <v>1.2</v>
       </c>
       <c r="BP24" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BR24" t="n">
         <v>90</v>
@@ -10528,7 +10528,7 @@
         <v>2</v>
       </c>
       <c r="DG24" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="DH24" t="n">
         <v>106.8</v>
@@ -10543,7 +10543,7 @@
         <v>5.2</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="DM24" t="n">
         <v>48.8</v>
@@ -10552,7 +10552,7 @@
         <v>0.8</v>
       </c>
       <c r="DO24" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="DP24" t="n">
         <v>11.6</v>
@@ -11007,94 +11007,94 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F26" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>90.25</v>
+        <v>87.8</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="M26" t="n">
-        <v>54.75</v>
+        <v>59.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>11.75</v>
+        <v>10.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>14.75</v>
+        <v>13</v>
       </c>
       <c r="R26" t="n">
         <v>6</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>54.75</v>
+        <v>54.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>11.75</v>
+        <v>12.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>8.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AC26" t="n">
-        <v>22.25</v>
+        <v>22</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -11178,70 +11178,70 @@
         <v>3.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="BH26" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BL26" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="BN26" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="BP26" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="BR26" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS26" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BT26" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BU26" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BV26" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX26" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BZ26" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CA26" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CC26" t="n">
         <v>3.88</v>
@@ -11250,22 +11250,22 @@
         <v>4.37</v>
       </c>
       <c r="CE26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CF26" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="CG26" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CH26" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CI26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CJ26" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CK26" t="n">
         <v>1.86</v>
@@ -11274,129 +11274,129 @@
         <v>2.55</v>
       </c>
       <c r="CM26" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CN26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CO26" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CP26" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CQ26" t="n">
-        <v>6.98</v>
+        <v>6.87</v>
       </c>
       <c r="CR26" t="n">
         <v>1.73</v>
       </c>
       <c r="CS26" t="inlineStr"/>
       <c r="CT26" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CU26" t="inlineStr"/>
       <c r="CV26" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CW26" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CX26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CY26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DF26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="DI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="DK26" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM26" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="DN26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DO26" t="n">
         <v>1.9</v>
       </c>
-      <c r="CY26" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CZ26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DA26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DB26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DC26" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="DD26" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="DE26" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DF26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DG26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DH26" t="n">
-        <v>87.56</v>
-      </c>
-      <c r="DI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ26" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DK26" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="DL26" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DM26" t="n">
-        <v>43.78</v>
-      </c>
-      <c r="DN26" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DO26" t="n">
-        <v>1.56</v>
-      </c>
       <c r="DP26" t="n">
-        <v>12.89</v>
+        <v>12</v>
       </c>
       <c r="DQ26" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="DR26" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="DS26" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU26" t="n">
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>48.11</v>
+        <v>48.6</v>
       </c>
       <c r="DW26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DX26" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY26" t="n">
-        <v>6.22</v>
+        <v>6.7</v>
       </c>
       <c r="DZ26" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="EA26" t="n">
-        <v>22.11</v>
+        <v>22</v>
       </c>
       <c r="EB26" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="EC26" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -11502,7 +11502,7 @@
         <v>2.6</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="AI27" t="n">
         <v>83.59999999999999</v>
@@ -11517,7 +11517,7 @@
         <v>2.2</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AN27" t="n">
         <v>41.6</v>
@@ -11526,10 +11526,10 @@
         <v>2.4</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="AR27" t="n">
         <v>10.6</v>
@@ -11604,10 +11604,10 @@
         <v>0.8</v>
       </c>
       <c r="BP27" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BQ27" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BR27" t="n">
         <v>90</v>
@@ -11729,7 +11729,7 @@
         <v>2.3</v>
       </c>
       <c r="DG27" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="DH27" t="n">
         <v>90.09999999999999</v>
@@ -11744,7 +11744,7 @@
         <v>3.9</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="DM27" t="n">
         <v>50</v>
@@ -11753,10 +11753,10 @@
         <v>1.9</v>
       </c>
       <c r="DO27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DP27" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="DQ27" t="n">
         <v>12.6</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -8643,7 +8643,7 @@
         <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q20" t="n">
         <v>8.75</v>
@@ -8951,7 +8951,7 @@
         <v>2.11</v>
       </c>
       <c r="DP20" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="DQ20" t="n">
         <v>10.67</v>
@@ -9123,7 +9123,7 @@
         <v>1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="AR21" t="n">
         <v>13.6</v>
@@ -9350,7 +9350,7 @@
         <v>1.3</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="DQ21" t="n">
         <v>13.4</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,127 +1472,127 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>86</v>
+        <v>85.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.2</v>
+        <v>57.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.2</v>
+        <v>12.17</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.8</v>
+        <v>11.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.8</v>
+        <v>10.17</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AU2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>0.4</v>
       </c>
-      <c r="AV2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.33</v>
-      </c>
       <c r="BK2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BS2" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BT2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BU2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BY2" t="n">
         <v>3</v>
@@ -1610,25 +1610,25 @@
         <v>3.2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.18</v>
+        <v>4.99</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CH2" t="n">
         <v>1.22</v>
@@ -1637,28 +1637,28 @@
         <v>1.54</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CL2" t="n">
         <v>2.46</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CP2" t="n">
         <v>2.87</v>
       </c>
       <c r="CQ2" t="n">
-        <v>5.79</v>
+        <v>5.84</v>
       </c>
       <c r="CR2" t="n">
         <v>1.66</v>
@@ -1667,7 +1667,7 @@
         <v>3.35</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CU2" t="n">
         <v>1.31</v>
@@ -1676,103 +1676,103 @@
         <v>1.56</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DB2" t="n">
         <v>1.67</v>
       </c>
       <c r="DC2" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.27</v>
+        <v>6.34</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.89</v>
+        <v>87.5</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DM2" t="n">
-        <v>58</v>
+        <v>59.1</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.22</v>
+        <v>14.4</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.22</v>
+        <v>50.1</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.11</v>
+        <v>11.3</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.44</v>
+        <v>23.8</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -2197,13 +2197,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="H4" t="n">
-        <v>75.8</v>
+        <v>77.83</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2212,64 +2212,64 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>66.8</v>
+        <v>65.33</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="P4" t="n">
-        <v>12.2</v>
+        <v>11.67</v>
       </c>
       <c r="Q4" t="n">
         <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>53.6</v>
+        <v>50.83</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.4</v>
+        <v>16.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.4</v>
+        <v>11.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2356,49 +2356,49 @@
         <v>3.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS4" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CC4" t="n">
         <v>3.71</v>
@@ -2428,13 +2428,13 @@
         <v>4.17</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CH4" t="n">
         <v>1.25</v>
@@ -2446,25 +2446,25 @@
         <v>2.12</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="CR4" t="n">
         <v>1.58</v>
@@ -2473,7 +2473,7 @@
         <v>3.33</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CU4" t="n">
         <v>1.31</v>
@@ -2482,7 +2482,7 @@
         <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CX4" t="n">
         <v>1.77</v>
@@ -2497,88 +2497,88 @@
         <v>1.64</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DH4" t="n">
-        <v>83.3</v>
+        <v>83.73</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="DM4" t="n">
-        <v>62.2</v>
+        <v>61.82</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.6</v>
+        <v>12.27</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.8</v>
+        <v>12.91</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.3</v>
+        <v>7.64</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51.7</v>
+        <v>50.36</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.2</v>
+        <v>13.45</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.1</v>
+        <v>24.55</v>
       </c>
       <c r="EB4" t="n">
         <v>1.56</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>88.17</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.14</v>
       </c>
       <c r="L5" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>54.67</v>
+        <v>50.14</v>
       </c>
       <c r="N5" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="P5" t="n">
-        <v>9.17</v>
+        <v>9.57</v>
       </c>
       <c r="Q5" t="n">
         <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>7.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>46.5</v>
+        <v>43.86</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.67</v>
+        <v>14.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>26.83</v>
+        <v>24.86</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,49 +2759,49 @@
         <v>1.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU5" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2810,19 +2810,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CC5" t="n">
         <v>4.5</v>
@@ -2831,124 +2831,124 @@
         <v>4.92</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CI5" t="n">
         <v>1.63</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO5" t="n">
         <v>1.53</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.94</v>
+        <v>5.01</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CS5" t="n">
         <v>3.37</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="CU5" t="n">
         <v>1.33</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="DA5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
         <v>1.64</v>
       </c>
-      <c r="DB5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="DG5" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.5</v>
+        <v>84.27</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.7</v>
+        <v>47.27</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.3</v>
+        <v>10.45</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.6</v>
+        <v>9.27</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>41.8</v>
+        <v>40.55</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.6</v>
+        <v>11.64</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="EA5" t="n">
-        <v>24.5</v>
+        <v>23.46</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="6">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3406,13 +3406,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="n">
-        <v>99.25</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3421,34 +3421,34 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>55.5</v>
+        <v>54.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>12.25</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.75</v>
+        <v>12.6</v>
       </c>
       <c r="R7" t="n">
-        <v>6.75</v>
+        <v>5.8</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,25 +3460,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.25</v>
+        <v>53.4</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.75</v>
+        <v>22.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -3565,49 +3565,49 @@
         <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.9</v>
+        <v>8.09</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="BR7" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BT7" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="CA7" t="n">
         <v>3.04</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CC7" t="n">
         <v>3.69</v>
@@ -3640,25 +3640,25 @@
         <v>1.58</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CH7" t="n">
         <v>1.24</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CM7" t="n">
         <v>2.02</v>
@@ -3670,10 +3670,10 @@
         <v>1.52</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.11</v>
+        <v>5.09</v>
       </c>
       <c r="CR7" t="n">
         <v>1.61</v>
@@ -3688,16 +3688,16 @@
         <v>1.32</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.06</v>
@@ -3709,52 +3709,52 @@
         <v>1.57</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.63</v>
+        <v>5.6</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="DH7" t="n">
-        <v>93.09999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM7" t="n">
-        <v>53.2</v>
+        <v>53</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.6</v>
+        <v>10.18</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.9</v>
+        <v>8.27</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.2</v>
+        <v>49.82</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.3</v>
+        <v>11.45</v>
       </c>
       <c r="DY7" t="n">
         <v>8</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="H8" t="n">
-        <v>102.5</v>
+        <v>104.14</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>5.71</v>
       </c>
       <c r="L8" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>50.33</v>
+        <v>48.86</v>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="P8" t="n">
-        <v>9.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.5</v>
+        <v>15.57</v>
       </c>
       <c r="R8" t="n">
-        <v>7.83</v>
+        <v>7.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="T8" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>65</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.83</v>
+        <v>12.71</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>22</v>
+        <v>21.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,46 +3968,46 @@
         <v>1.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.4</v>
+        <v>8.82</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN8" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.1</v>
+        <v>4.36</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT8" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY8" t="n">
         <v>1.71</v>
@@ -4031,7 +4031,7 @@
         <v>3.22</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CC8" t="n">
         <v>2.62</v>
@@ -4040,43 +4040,43 @@
         <v>2.83</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF8" t="n">
         <v>3.28</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="CR8" t="n">
         <v>1.6</v>
@@ -4091,106 +4091,106 @@
         <v>1.3</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY8" t="n">
         <v>2.3</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA8" t="n">
         <v>1.62</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.76</v>
+        <v>5.65</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.2</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.6</v>
+        <v>49.64</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.1</v>
+        <v>13.73</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.1</v>
+        <v>7.91</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61.8</v>
+        <v>62.45</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.7</v>
+        <v>12.27</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.1</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.5</v>
+        <v>20.45</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="9">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -4611,82 +4611,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>84.8</v>
+        <v>82</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>53.8</v>
+        <v>49.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="P10" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.2</v>
+        <v>48.67</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Z10" t="n">
         <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.2</v>
+        <v>17.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
         <v>0.2</v>
@@ -4770,67 +4770,67 @@
         <v>1.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.5</v>
+        <v>7.82</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="BR10" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BS10" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BT10" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV10" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CB10" t="n">
         <v>2.93</v>
@@ -4845,25 +4845,25 @@
         <v>1.62</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CM10" t="n">
         <v>1.94</v>
@@ -4872,13 +4872,13 @@
         <v>1.56</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CQ10" t="n">
-        <v>5.49</v>
+        <v>5.43</v>
       </c>
       <c r="CR10" t="n">
         <v>1.66</v>
@@ -4889,19 +4889,19 @@
       </c>
       <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DA10" t="n">
         <v>1.58</v>
@@ -4910,85 +4910,85 @@
         <v>1.62</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.15</v>
+        <v>6.06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DH10" t="n">
-        <v>75.90000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.7</v>
+        <v>45</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="DP10" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.1</v>
+        <v>11.18</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.5</v>
+        <v>9.73</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.8</v>
+        <v>48.55</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.4</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.7</v>
+        <v>19.82</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="11">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -5808,82 +5808,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H13" t="n">
-        <v>81.75</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>41</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AC13" t="n">
-        <v>22.25</v>
+        <v>21.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5967,49 +5967,49 @@
         <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.6</v>
+        <v>8.91</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.1</v>
+        <v>4.64</v>
       </c>
       <c r="BR13" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS13" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BT13" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU13" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6018,19 +6018,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.95</v>
+        <v>4.56</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.33</v>
+        <v>5.08</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CC13" t="n">
         <v>5.42</v>
@@ -6039,13 +6039,13 @@
         <v>6.18</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CH13" t="n">
         <v>1.21</v>
@@ -6054,28 +6054,28 @@
         <v>1.5</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CK13" t="n">
         <v>1.89</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO13" t="n">
         <v>1.59</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.78</v>
+        <v>5.68</v>
       </c>
       <c r="CR13" t="n">
         <v>1.63</v>
@@ -6104,55 +6104,55 @@
         <v>1.55</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.13</v>
+        <v>6.03</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.3</v>
+        <v>83</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.3</v>
+        <v>4.37</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM13" t="n">
-        <v>52.9</v>
+        <v>52.27</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.9</v>
+        <v>10.54</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12</v>
+        <v>11.64</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.5</v>
+        <v>7.73</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6164,28 +6164,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.7</v>
+        <v>44.46</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.7</v>
+        <v>10.45</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.5</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="EA13" t="n">
-        <v>24.3</v>
+        <v>23.64</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="14">
@@ -6195,13 +6195,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0.6</v>
@@ -6288,19 +6288,19 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>86.2</v>
+        <v>88</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="AL14" t="n">
         <v>4</v>
@@ -6309,115 +6309,115 @@
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>34.6</v>
+        <v>38.33</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR14" t="n">
         <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.2</v>
+        <v>10.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BN14" t="n">
         <v>1</v>
       </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BO14" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="BR14" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU14" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV14" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY14" t="n">
         <v>3.13</v>
@@ -6426,73 +6426,73 @@
         <v>3.14</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="CE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CI14" t="n">
         <v>1.61</v>
       </c>
-      <c r="CF14" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>1.6</v>
-      </c>
       <c r="CJ14" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CQ14" t="n">
-        <v>5.15</v>
+        <v>5.11</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CS14" t="n">
         <v>3.42</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CU14" t="n">
         <v>1.32</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CX14" t="n">
         <v>1.71</v>
@@ -6507,88 +6507,88 @@
         <v>1.7</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="DD14" t="n">
-        <v>5.88</v>
+        <v>5.79</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="DH14" t="n">
-        <v>77.8</v>
+        <v>79.55</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.5</v>
+        <v>40.18</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.5</v>
+        <v>13.36</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.2</v>
+        <v>10.46</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>43.9</v>
+        <v>45.64</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.8</v>
+        <v>6.09</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="EA14" t="n">
-        <v>17</v>
+        <v>17.55</v>
       </c>
       <c r="EB14" t="n">
         <v>1.15</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="15">
@@ -6598,13 +6598,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0.2</v>
@@ -6688,52 +6688,52 @@
         <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="AI15" t="n">
-        <v>77</v>
+        <v>76.33</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>33</v>
+        <v>33.83</v>
       </c>
       <c r="AO15" t="n">
         <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.2</v>
+        <v>10.67</v>
       </c>
       <c r="AR15" t="n">
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>9.17</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6745,73 +6745,73 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>36.6</v>
+        <v>37.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>7.67</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="BC15" t="n">
         <v>3</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.4</v>
+        <v>16.17</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.2</v>
+        <v>3.73</v>
       </c>
       <c r="BR15" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS15" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BT15" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY15" t="n">
         <v>3.13</v>
@@ -6829,40 +6829,40 @@
         <v>3.65</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.25</v>
+        <v>4.91</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.95</v>
+        <v>5.54</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CH15" t="n">
         <v>1.19</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CM15" t="n">
         <v>1.95</v>
@@ -6871,13 +6871,13 @@
         <v>1.59</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CP15" t="n">
         <v>2.87</v>
       </c>
       <c r="CQ15" t="n">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="CR15" t="n">
         <v>1.68</v>
@@ -6895,13 +6895,13 @@
         <v>1.53</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CX15" t="n">
         <v>1.82</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CZ15" t="n">
         <v>1.99</v>
@@ -6916,49 +6916,49 @@
         <v>3.18</v>
       </c>
       <c r="DD15" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="DH15" t="n">
-        <v>88.90000000000001</v>
+        <v>87.45</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="DL15" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.3</v>
+        <v>41.91</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.4</v>
+        <v>10.64</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.9</v>
+        <v>12.91</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6970,28 +6970,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.5</v>
+        <v>43.36</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.6</v>
+        <v>10.55</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.4</v>
+        <v>20.37</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="16">
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
@@ -7412,82 +7412,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>100.6</v>
+        <v>93.83</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="M17" t="n">
-        <v>42.6</v>
+        <v>44</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="P17" t="n">
-        <v>10.8</v>
+        <v>10.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>54.8</v>
+        <v>54.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.8</v>
+        <v>16.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.8</v>
+        <v>11.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>27.2</v>
+        <v>25.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7571,70 +7571,70 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.1</v>
+        <v>10.18</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT17" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BU17" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW17" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX17" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CC17" t="n">
         <v>2.6</v>
@@ -7643,43 +7643,43 @@
         <v>2.81</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CI17" t="n">
         <v>1.6</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.84</v>
+        <v>4.89</v>
       </c>
       <c r="CR17" t="n">
         <v>1.63</v>
@@ -7696,100 +7696,100 @@
         <v>2.42</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CZ17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DA17" t="n">
         <v>1.58</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="DD17" t="n">
-        <v>6.24</v>
+        <v>6.15</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.5</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DJ17" t="n">
         <v>3</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.7</v>
+        <v>50.73</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO17" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.9</v>
+        <v>10.55</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13</v>
+        <v>13.27</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.2</v>
+        <v>54.91</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.4</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="EA17" t="n">
-        <v>25.3</v>
+        <v>24.73</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="18">
@@ -8202,13 +8202,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
         <v>0.17</v>
@@ -8295,49 +8295,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>93.5</v>
+        <v>86</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>51.75</v>
+        <v>46</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.75</v>
+        <v>10.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.75</v>
+        <v>8.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8349,73 +8349,73 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>52.75</v>
+        <v>48.4</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.25</v>
+        <v>13.2</v>
       </c>
       <c r="BB19" t="n">
         <v>8</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>22.25</v>
+        <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BH19" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU19" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY19" t="n">
         <v>2.46</v>
@@ -8433,28 +8433,28 @@
         <v>2.55</v>
       </c>
       <c r="CA19" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.33</v>
+        <v>3.87</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI19" t="n">
         <v>1.58</v>
@@ -8466,7 +8466,7 @@
         <v>1.75</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="CM19" t="n">
         <v>2.01</v>
@@ -8475,13 +8475,13 @@
         <v>1.59</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="CQ19" t="n">
-        <v>6.15</v>
+        <v>6.04</v>
       </c>
       <c r="CR19" t="n">
         <v>1.66</v>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CW19" t="n">
         <v>2.43</v>
@@ -8510,88 +8510,88 @@
         <v>1.6</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="DD19" t="n">
-        <v>6.43</v>
+        <v>6.27</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="DH19" t="n">
-        <v>89.5</v>
+        <v>86.45</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM19" t="n">
-        <v>50.8</v>
+        <v>48.27</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.8</v>
+        <v>12.55</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.3</v>
+        <v>11.45</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.7</v>
+        <v>49.82</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.2</v>
+        <v>12.27</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.8</v>
+        <v>19.91</v>
       </c>
       <c r="EB19" t="n">
         <v>1.42</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="20">
@@ -8601,13 +8601,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8643,7 +8643,7 @@
         <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q20" t="n">
         <v>8.75</v>
@@ -8694,136 +8694,136 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AM20" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AN20" t="n">
-        <v>37</v>
+        <v>40.33</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12.2</v>
+        <v>12.83</v>
       </c>
       <c r="AR20" t="n">
-        <v>12.2</v>
+        <v>12.17</v>
       </c>
       <c r="AS20" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH20" t="n">
         <v>8.6</v>
       </c>
-      <c r="AT20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>8.890000000000001</v>
-      </c>
       <c r="BI20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL20" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BT20" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV20" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
         <v>2.14</v>
@@ -8832,25 +8832,25 @@
         <v>2.26</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CB20" t="n">
         <v>2.99</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CE20" t="n">
         <v>1.63</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CH20" t="n">
         <v>1.23</v>
@@ -8859,25 +8859,25 @@
         <v>1.59</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CK20" t="n">
         <v>1.77</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CM20" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO20" t="n">
         <v>1.56</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CQ20" t="n">
         <v>5.56</v>
@@ -8887,20 +8887,20 @@
       </c>
       <c r="CS20" t="inlineStr"/>
       <c r="CT20" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CX20" t="n">
         <v>1.79</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.02</v>
@@ -8921,76 +8921,76 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="DL20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DP20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DQ20" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="DR20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="DS20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DT20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV20" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="DW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="DY20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="DZ20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="EA20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="EB20" t="n">
         <v>1.33</v>
       </c>
-      <c r="DG20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="DH20" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="DI20" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DJ20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DK20" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="DL20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DM20" t="n">
-        <v>41.22</v>
-      </c>
-      <c r="DN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DP20" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="DQ20" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="DR20" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="DS20" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DT20" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV20" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="DW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX20" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="DY20" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="DZ20" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="EA20" t="n">
-        <v>17.78</v>
-      </c>
-      <c r="EB20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="EC20" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -9012,49 +9012,49 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>90.59999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>57</v>
+        <v>60.67</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>15</v>
+        <v>14.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="R21" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9066,28 +9066,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>44.2</v>
+        <v>46.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.4</v>
+        <v>12.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="AC21" t="n">
-        <v>20.2</v>
+        <v>20.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9123,7 +9123,7 @@
         <v>1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="AR21" t="n">
         <v>13.6</v>
@@ -9171,70 +9171,70 @@
         <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.1</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.4</v>
+        <v>3.91</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>100</v>
+        <v>90.91</v>
       </c>
       <c r="BT21" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU21" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV21" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.61</v>
+        <v>3.44</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CC21" t="n">
         <v>4.58</v>
@@ -9243,50 +9243,50 @@
         <v>5.49</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="CG21" t="n">
         <v>2.24</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CI21" t="n">
         <v>1.58</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CK21" t="n">
         <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.48</v>
+        <v>5.61</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CS21" t="inlineStr"/>
       <c r="CT21" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CU21" t="inlineStr"/>
       <c r="CV21" t="n">
@@ -9299,97 +9299,97 @@
         <v>1.74</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB21" t="n">
         <v>1.62</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.99</v>
+        <v>6.07</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="DH21" t="n">
-        <v>75.09999999999999</v>
+        <v>77.64</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="DM21" t="n">
-        <v>50.9</v>
+        <v>53.46</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.6</v>
+        <v>13.45</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.4</v>
+        <v>13.55</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.5</v>
+        <v>6.64</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>42.3</v>
+        <v>43.73</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DX21" t="n">
-        <v>10</v>
+        <v>10.45</v>
       </c>
       <c r="DY21" t="n">
-        <v>7</v>
+        <v>7.27</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.4</v>
+        <v>19.46</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="22">
@@ -9798,13 +9798,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -9891,127 +9891,127 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AI23" t="n">
-        <v>99.5</v>
+        <v>97</v>
       </c>
       <c r="AJ23" t="n">
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN23" t="n">
-        <v>43.83</v>
+        <v>43.57</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.67</v>
+        <v>9.43</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.83</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>58.67</v>
+        <v>58</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.83</v>
+        <v>6.29</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BD23" t="n">
-        <v>22.17</v>
+        <v>22</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BF23" t="n">
         <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="BH23" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BN23" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BO23" t="n">
         <v>1</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="BR23" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS23" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU23" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY23" t="n">
         <v>2</v>
@@ -10029,25 +10029,25 @@
         <v>2.09</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CC23" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CD23" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CE23" t="n">
         <v>1.53</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CH23" t="n">
         <v>1.26</v>
@@ -10056,13 +10056,13 @@
         <v>1.68</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CM23" t="n">
         <v>2.02</v>
@@ -10074,10 +10074,10 @@
         <v>1.47</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="CR23" t="n">
         <v>1.56</v>
@@ -10092,22 +10092,22 @@
         <v>1.32</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CX23" t="n">
         <v>1.78</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ23" t="n">
         <v>2.04</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB23" t="n">
         <v>1.51</v>
@@ -10116,82 +10116,82 @@
         <v>2.61</v>
       </c>
       <c r="DD23" t="n">
-        <v>5.12</v>
+        <v>5.13</v>
       </c>
       <c r="DE23" t="n">
         <v>0</v>
       </c>
       <c r="DF23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="DH23" t="n">
-        <v>97</v>
+        <v>95.64</v>
       </c>
       <c r="DI23" t="n">
         <v>0</v>
       </c>
       <c r="DJ23" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="DK23" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM23" t="n">
-        <v>52.1</v>
+        <v>51.18</v>
       </c>
       <c r="DN23" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DP23" t="n">
-        <v>13.6</v>
+        <v>13.64</v>
       </c>
       <c r="DQ23" t="n">
-        <v>10.6</v>
+        <v>10.36</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.5</v>
+        <v>7.73</v>
       </c>
       <c r="DS23" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT23" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU23" t="n">
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>58</v>
+        <v>57.64</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX23" t="n">
-        <v>13.2</v>
+        <v>12.64</v>
       </c>
       <c r="DY23" t="n">
-        <v>9.300000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="EA23" t="n">
-        <v>22.5</v>
+        <v>22.36</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="EC23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="24">
@@ -10201,13 +10201,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" t="n">
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -10294,136 +10294,136 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="AI24" t="n">
-        <v>101.33</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AL24" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN24" t="n">
-        <v>54.17</v>
+        <v>54.86</v>
       </c>
       <c r="AO24" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>10.83</v>
+        <v>10.14</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.33</v>
+        <v>7.14</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AX24" t="n">
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>63.33</v>
+        <v>62.57</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA24" t="n">
-        <v>13.33</v>
+        <v>12.71</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.83</v>
+        <v>8.43</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="BD24" t="n">
-        <v>22.17</v>
+        <v>22.14</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BH24" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP24" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.6</v>
+        <v>5.09</v>
       </c>
       <c r="BR24" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS24" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BT24" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU24" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV24" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW24" t="n">
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY24" t="n">
         <v>1.54</v>
@@ -10432,43 +10432,43 @@
         <v>1.59</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CC24" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="CD24" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="CE24" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CF24" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CG24" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CH24" t="n">
         <v>1.26</v>
       </c>
       <c r="CI24" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CJ24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CK24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL24" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CM24" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CN24" t="n">
         <v>1.6</v>
@@ -10477,10 +10477,10 @@
         <v>1.45</v>
       </c>
       <c r="CP24" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CQ24" t="n">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
       <c r="CR24" t="n">
         <v>1.54</v>
@@ -10495,10 +10495,10 @@
         <v>1.33</v>
       </c>
       <c r="CV24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CW24" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CX24" t="n">
         <v>1.77</v>
@@ -10519,82 +10519,82 @@
         <v>2.61</v>
       </c>
       <c r="DD24" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="DE24" t="n">
         <v>0</v>
       </c>
       <c r="DF24" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="DG24" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="DH24" t="n">
-        <v>106.8</v>
+        <v>105.09</v>
       </c>
       <c r="DI24" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DJ24" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DK24" t="n">
-        <v>5.2</v>
+        <v>5.37</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DM24" t="n">
-        <v>48.8</v>
+        <v>49.73</v>
       </c>
       <c r="DN24" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="DO24" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DP24" t="n">
-        <v>11.6</v>
+        <v>11.27</v>
       </c>
       <c r="DQ24" t="n">
-        <v>11.7</v>
+        <v>11.18</v>
       </c>
       <c r="DR24" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="DS24" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DT24" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DU24" t="n">
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>66.59999999999999</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="DW24" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DX24" t="n">
-        <v>17.3</v>
+        <v>16.54</v>
       </c>
       <c r="DY24" t="n">
-        <v>11.3</v>
+        <v>10.82</v>
       </c>
       <c r="DZ24" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="EA24" t="n">
-        <v>20.6</v>
+        <v>20.73</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="EC24" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="25">
@@ -11406,10 +11406,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
         <v>5</v>
@@ -11418,82 +11418,82 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="G27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H27" t="n">
-        <v>96.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="K27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="M27" t="n">
-        <v>58.4</v>
+        <v>56.67</v>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O27" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>13.4</v>
+        <v>12.33</v>
       </c>
       <c r="Q27" t="n">
-        <v>14.6</v>
+        <v>13.33</v>
       </c>
       <c r="R27" t="n">
-        <v>7.8</v>
+        <v>8.67</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>55.6</v>
+        <v>53.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>13.8</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>8.4</v>
+        <v>7.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>5.4</v>
+        <v>5.17</v>
       </c>
       <c r="AC27" t="n">
-        <v>24</v>
+        <v>23.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -11577,49 +11577,49 @@
         <v>4.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BH27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BM27" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BN27" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BP27" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="BQ27" t="n">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="BR27" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS27" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BT27" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU27" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV27" t="n">
         <v>0</v>
@@ -11628,19 +11628,19 @@
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BY27" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BZ27" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="CA27" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CB27" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CC27" t="n">
         <v>6.55</v>
@@ -11649,13 +11649,13 @@
         <v>7.68</v>
       </c>
       <c r="CE27" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CF27" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="CG27" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CH27" t="n">
         <v>1.23</v>
@@ -11664,16 +11664,16 @@
         <v>1.54</v>
       </c>
       <c r="CJ27" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="CK27" t="n">
         <v>1.69</v>
       </c>
       <c r="CL27" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM27" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN27" t="n">
         <v>1.65</v>
@@ -11682,17 +11682,17 @@
         <v>1.53</v>
       </c>
       <c r="CP27" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CQ27" t="n">
-        <v>5.07</v>
+        <v>5.18</v>
       </c>
       <c r="CR27" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CS27" t="inlineStr"/>
       <c r="CT27" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="n">
@@ -11705,97 +11705,97 @@
         <v>1.73</v>
       </c>
       <c r="CY27" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ27" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA27" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB27" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DC27" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="DD27" t="n">
-        <v>5.72</v>
+        <v>5.82</v>
       </c>
       <c r="DE27" t="n">
         <v>0</v>
       </c>
       <c r="DF27" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="DG27" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DH27" t="n">
-        <v>90.09999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="DI27" t="n">
         <v>0</v>
       </c>
       <c r="DJ27" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="DK27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="DM27" t="n">
-        <v>50</v>
+        <v>49.82</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DO27" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="DP27" t="n">
-        <v>13.9</v>
+        <v>13.27</v>
       </c>
       <c r="DQ27" t="n">
-        <v>12.6</v>
+        <v>12.09</v>
       </c>
       <c r="DR27" t="n">
-        <v>9.6</v>
+        <v>9.91</v>
       </c>
       <c r="DS27" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DT27" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DU27" t="n">
         <v>0</v>
       </c>
       <c r="DV27" t="n">
-        <v>49</v>
+        <v>48.36</v>
       </c>
       <c r="DW27" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DX27" t="n">
-        <v>10.3</v>
+        <v>10.18</v>
       </c>
       <c r="DY27" t="n">
-        <v>6.4</v>
+        <v>6.27</v>
       </c>
       <c r="DZ27" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="EA27" t="n">
-        <v>23</v>
+        <v>22.91</v>
       </c>
       <c r="EB27" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC27" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="28">
@@ -11805,13 +11805,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" t="n">
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -11898,13 +11898,13 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>87.40000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
@@ -11913,34 +11913,34 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN28" t="n">
-        <v>46.2</v>
+        <v>45.17</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>11.4</v>
+        <v>10.83</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AV28" t="n">
         <v>0</v>
@@ -11952,70 +11952,70 @@
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>49.4</v>
+        <v>49.17</v>
       </c>
       <c r="AZ28" t="n">
         <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>12.4</v>
+        <v>11.67</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.4</v>
+        <v>7.67</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
       </c>
       <c r="BD28" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BF28" t="n">
         <v>2</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BH28" t="n">
-        <v>9.300000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL28" t="n">
         <v>1</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="BN28" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BP28" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BQ28" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="BR28" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS28" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT28" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BU28" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY28" t="n">
         <v>2.01</v>
@@ -12036,40 +12036,40 @@
         <v>2.07</v>
       </c>
       <c r="CA28" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CB28" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CC28" t="n">
-        <v>3.49</v>
+        <v>3.59</v>
       </c>
       <c r="CD28" t="n">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="CE28" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CF28" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CG28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CH28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI28" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CJ28" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CK28" t="n">
         <v>1.78</v>
       </c>
       <c r="CL28" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CM28" t="n">
         <v>1.98</v>
@@ -12078,13 +12078,13 @@
         <v>1.59</v>
       </c>
       <c r="CO28" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CP28" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CQ28" t="n">
-        <v>6.03</v>
+        <v>5.98</v>
       </c>
       <c r="CR28" t="n">
         <v>1.65</v>
@@ -12095,16 +12095,16 @@
       </c>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CW28" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CX28" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY28" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CZ28" t="n">
         <v>2</v>
@@ -12116,10 +12116,10 @@
         <v>1.64</v>
       </c>
       <c r="DC28" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="DD28" t="n">
-        <v>6.13</v>
+        <v>6.06</v>
       </c>
       <c r="DE28" t="n">
         <v>0</v>
@@ -12128,25 +12128,25 @@
         <v>1</v>
       </c>
       <c r="DG28" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DH28" t="n">
-        <v>84.90000000000001</v>
+        <v>82.91</v>
       </c>
       <c r="DI28" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ28" t="n">
         <v>2</v>
       </c>
       <c r="DK28" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="DL28" t="n">
         <v>0</v>
       </c>
       <c r="DM28" t="n">
-        <v>43.9</v>
+        <v>43.55</v>
       </c>
       <c r="DN28" t="n">
         <v>1</v>
@@ -12155,13 +12155,13 @@
         <v>2</v>
       </c>
       <c r="DP28" t="n">
-        <v>11</v>
+        <v>11.45</v>
       </c>
       <c r="DQ28" t="n">
-        <v>11.8</v>
+        <v>11.45</v>
       </c>
       <c r="DR28" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="DS28" t="n">
         <v>0</v>
@@ -12173,25 +12173,25 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>54</v>
+        <v>53.46</v>
       </c>
       <c r="DW28" t="n">
         <v>0</v>
       </c>
       <c r="DX28" t="n">
-        <v>12.3</v>
+        <v>11.91</v>
       </c>
       <c r="DY28" t="n">
-        <v>8</v>
+        <v>7.64</v>
       </c>
       <c r="DZ28" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="EA28" t="n">
-        <v>21.3</v>
+        <v>20.91</v>
       </c>
       <c r="EB28" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="EC28" t="n">
         <v>2</v>
@@ -12204,13 +12204,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" t="n">
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -12294,52 +12294,52 @@
         <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>84.75</v>
+        <v>89</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>46</v>
+        <v>51.2</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT29" t="n">
         <v>1</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AV29" t="n">
         <v>0</v>
@@ -12351,82 +12351,82 @@
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>44</v>
+        <v>49.6</v>
       </c>
       <c r="AZ29" t="n">
         <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>15.75</v>
+        <v>15.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BH29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL29" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN29" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BP29" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="BQ29" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="BR29" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS29" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BT29" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU29" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV29" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BY29" t="n">
         <v>2.45</v>
@@ -12435,16 +12435,16 @@
         <v>2.52</v>
       </c>
       <c r="CA29" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CB29" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CC29" t="n">
-        <v>3.84</v>
+        <v>3.57</v>
       </c>
       <c r="CD29" t="n">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="CE29" t="n">
         <v>1.65</v>
@@ -12459,22 +12459,22 @@
         <v>1.21</v>
       </c>
       <c r="CI29" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CJ29" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CK29" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CL29" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CM29" t="n">
         <v>1.86</v>
       </c>
       <c r="CN29" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CO29" t="n">
         <v>1.57</v>
@@ -12483,30 +12483,30 @@
         <v>2.81</v>
       </c>
       <c r="CQ29" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="CR29" t="n">
         <v>1.68</v>
       </c>
       <c r="CS29" t="inlineStr"/>
       <c r="CT29" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CU29" t="inlineStr"/>
       <c r="CV29" t="n">
         <v>1.56</v>
       </c>
       <c r="CW29" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CX29" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CY29" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CZ29" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DA29" t="n">
         <v>1.56</v>
@@ -12515,52 +12515,52 @@
         <v>1.68</v>
       </c>
       <c r="DC29" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="DD29" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DG29" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DH29" t="n">
-        <v>81.7</v>
+        <v>83.91</v>
       </c>
       <c r="DI29" t="n">
         <v>0</v>
       </c>
       <c r="DJ29" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DK29" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="DL29" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DM29" t="n">
-        <v>46.6</v>
+        <v>48.91</v>
       </c>
       <c r="DN29" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="DO29" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="DP29" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="DQ29" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="DR29" t="n">
-        <v>8.699999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="DS29" t="n">
         <v>0</v>
@@ -12572,28 +12572,28 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>43.4</v>
+        <v>46</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
       </c>
       <c r="DX29" t="n">
-        <v>12.9</v>
+        <v>13.82</v>
       </c>
       <c r="DY29" t="n">
-        <v>8.1</v>
+        <v>9.09</v>
       </c>
       <c r="DZ29" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="EA29" t="n">
-        <v>16.2</v>
+        <v>16.18</v>
       </c>
       <c r="EB29" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="EC29" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -12603,13 +12603,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
         <v>0.2</v>
@@ -12693,139 +12693,139 @@
         <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG30" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>89</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="AO30" t="n">
         <v>1</v>
       </c>
-      <c r="AH30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AP30" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="BB30" t="n">
         <v>9</v>
       </c>
-      <c r="AT30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC30" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="BD30" t="n">
-        <v>17.2</v>
+        <v>18.17</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BH30" t="n">
-        <v>7.5</v>
+        <v>7.82</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BL30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO30" t="n">
         <v>1</v>
       </c>
-      <c r="BM30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BP30" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="BQ30" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BR30" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS30" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BT30" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU30" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV30" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW30" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX30" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY30" t="n">
         <v>2.09</v>
@@ -12834,55 +12834,55 @@
         <v>2.1</v>
       </c>
       <c r="CA30" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CC30" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="CD30" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="CE30" t="n">
         <v>1.62</v>
       </c>
       <c r="CF30" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="CG30" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CH30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI30" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CJ30" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CK30" t="n">
         <v>1.82</v>
       </c>
       <c r="CL30" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CM30" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN30" t="n">
         <v>1.55</v>
       </c>
       <c r="CO30" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CP30" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CQ30" t="n">
-        <v>5.55</v>
+        <v>5.48</v>
       </c>
       <c r="CR30" t="n">
         <v>1.64</v>
@@ -12893,106 +12893,106 @@
       </c>
       <c r="CU30" t="inlineStr"/>
       <c r="CV30" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CW30" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY30" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CZ30" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DA30" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB30" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DC30" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="DD30" t="n">
-        <v>6.12</v>
+        <v>6.04</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF30" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DG30" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="DH30" t="n">
-        <v>90.5</v>
+        <v>91.09</v>
       </c>
       <c r="DI30" t="n">
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DK30" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="DL30" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM30" t="n">
-        <v>49.1</v>
+        <v>52.18</v>
       </c>
       <c r="DN30" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="DO30" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="DP30" t="n">
-        <v>10.8</v>
+        <v>10.91</v>
       </c>
       <c r="DQ30" t="n">
-        <v>10.3</v>
+        <v>10.18</v>
       </c>
       <c r="DR30" t="n">
-        <v>8.4</v>
+        <v>8.18</v>
       </c>
       <c r="DS30" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT30" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU30" t="n">
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>45.9</v>
+        <v>47.54</v>
       </c>
       <c r="DW30" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX30" t="n">
-        <v>15.6</v>
+        <v>15.91</v>
       </c>
       <c r="DY30" t="n">
-        <v>10.7</v>
+        <v>11.09</v>
       </c>
       <c r="DZ30" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="EA30" t="n">
-        <v>20.2</v>
+        <v>20.46</v>
       </c>
       <c r="EB30" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="EC30" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="31">
@@ -13002,25 +13002,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G31" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H31" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -13029,34 +13029,34 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M31" t="n">
-        <v>48.75</v>
+        <v>55.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="P31" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>13.25</v>
+        <v>14.2</v>
       </c>
       <c r="R31" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="T31" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -13068,25 +13068,25 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>52.75</v>
+        <v>54</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>7.75</v>
+        <v>7.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AC31" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -13173,46 +13173,46 @@
         <v>3.33</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BH31" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BN31" t="n">
         <v>1</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BP31" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BQ31" t="n">
         <v>5</v>
       </c>
       <c r="BR31" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS31" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BT31" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU31" t="n">
         <v>0</v>
@@ -13224,19 +13224,19 @@
         <v>0</v>
       </c>
       <c r="BX31" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY31" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="BZ31" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="CA31" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CC31" t="n">
         <v>3.06</v>
@@ -13248,10 +13248,10 @@
         <v>1.63</v>
       </c>
       <c r="CF31" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CG31" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CH31" t="n">
         <v>1.21</v>
@@ -13260,48 +13260,48 @@
         <v>1.59</v>
       </c>
       <c r="CJ31" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CK31" t="n">
         <v>1.75</v>
       </c>
       <c r="CL31" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CM31" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN31" t="n">
         <v>1.62</v>
       </c>
       <c r="CO31" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CP31" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CQ31" t="n">
-        <v>5.91</v>
+        <v>5.88</v>
       </c>
       <c r="CR31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CS31" t="inlineStr"/>
       <c r="CT31" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CU31" t="inlineStr"/>
       <c r="CV31" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CW31" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CX31" t="n">
         <v>1.79</v>
       </c>
       <c r="CY31" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CZ31" t="n">
         <v>2.03</v>
@@ -13319,79 +13319,79 @@
         <v>6.55</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF31" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DG31" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DH31" t="n">
-        <v>94.8</v>
+        <v>94.55</v>
       </c>
       <c r="DI31" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ31" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="DK31" t="n">
         <v>4</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="DM31" t="n">
-        <v>48.2</v>
+        <v>51.18</v>
       </c>
       <c r="DN31" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="DP31" t="n">
-        <v>9.9</v>
+        <v>10.09</v>
       </c>
       <c r="DQ31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="DR31" t="n">
-        <v>7.1</v>
+        <v>7.27</v>
       </c>
       <c r="DS31" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT31" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU31" t="n">
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>52.8</v>
+        <v>53.36</v>
       </c>
       <c r="DW31" t="n">
         <v>0</v>
       </c>
       <c r="DX31" t="n">
-        <v>10.9</v>
+        <v>10.82</v>
       </c>
       <c r="DY31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="DZ31" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="EA31" t="n">
-        <v>19.5</v>
+        <v>19.55</v>
       </c>
       <c r="EB31" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC31" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1502,7 +1502,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.17</v>
+        <v>12.33</v>
       </c>
       <c r="AR2" t="n">
         <v>11.33</v>
@@ -1532,10 +1532,10 @@
         <v>0.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.33</v>
+        <v>10.17</v>
       </c>
       <c r="BC2" t="n">
         <v>1.17</v>
@@ -1544,7 +1544,7 @@
         <v>23.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BF2" t="n">
         <v>2</v>
@@ -1613,13 +1613,13 @@
         <v>3</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CC2" t="n">
         <v>4.65</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.99</v>
+        <v>4.94</v>
       </c>
       <c r="CE2" t="n">
         <v>1.63</v>
@@ -1661,13 +1661,13 @@
         <v>5.84</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CS2" t="n">
         <v>3.35</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CU2" t="n">
         <v>1.31</v>
@@ -1691,13 +1691,13 @@
         <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DC2" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.34</v>
+        <v>6.42</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>1.9</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="DQ2" t="n">
         <v>10.1</v>
@@ -1757,10 +1757,10 @@
         <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ2" t="n">
         <v>1.9</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="H3" t="n">
-        <v>107.4</v>
+        <v>108.67</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4</v>
+        <v>5.17</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>80</v>
+        <v>76.83</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="P3" t="n">
-        <v>7.2</v>
+        <v>8.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.8</v>
+        <v>12.83</v>
       </c>
       <c r="R3" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>61.8</v>
+        <v>63.17</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.2</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.2</v>
+        <v>20.33</v>
       </c>
       <c r="AD3" t="n">
         <v>2.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,46 +1953,46 @@
         <v>2.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.25</v>
+        <v>7.22</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="BR3" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CC3" t="n">
         <v>2.53</v>
@@ -2025,157 +2025,157 @@
         <v>2.6</v>
       </c>
       <c r="CE3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CI3" t="n">
         <v>1.57</v>
       </c>
-      <c r="CF3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>1.58</v>
-      </c>
       <c r="CJ3" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CQ3" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CS3" t="n">
         <v>3.29</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CU3" t="n">
         <v>1.3</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.47</v>
+        <v>5.58</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DH3" t="n">
-        <v>99.63</v>
+        <v>101.34</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>71.5</v>
+        <v>70.33</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.5</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14</v>
+        <v>13.89</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.37</v>
+        <v>63.22</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.88</v>
+        <v>15.67</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.380000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.75</v>
+        <v>19.55</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="4">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,52 +3081,52 @@
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>73.8</v>
+        <v>71.83</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.6</v>
+        <v>50.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.2</v>
+        <v>11.17</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,70 +3138,70 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>32.6</v>
+        <v>32.33</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>7.33</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.2</v>
+        <v>18.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.6</v>
+        <v>6.18</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BT6" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY6" t="n">
         <v>3.28</v>
@@ -3225,19 +3225,19 @@
         <v>3.06</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.93</v>
+        <v>5.82</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
       <c r="CE6" t="n">
         <v>1.65</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="CG6" t="n">
         <v>2.23</v>
@@ -3246,145 +3246,145 @@
         <v>1.2</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO6" t="n">
         <v>1.62</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CS6" t="n">
         <v>3.36</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CU6" t="n">
         <v>1.31</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CY6" t="n">
         <v>2.41</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="DA6" t="n">
         <v>1.55</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DC6" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.09</v>
+        <v>6.25</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.09999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DM6" t="n">
-        <v>49.5</v>
+        <v>50.45</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.2</v>
+        <v>11.91</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.1</v>
+        <v>10.36</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>39.3</v>
+        <v>38.54</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.7</v>
+        <v>5.54</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.7</v>
+        <v>18.36</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="7">
@@ -4025,7 +4025,7 @@
         <v>1.71</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CA8" t="n">
         <v>3.22</v>
@@ -4103,7 +4103,7 @@
         <v>2.3</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DA8" t="n">
         <v>1.62</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI9" t="n">
-        <v>81.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AL9" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="AO9" t="n">
         <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.2</v>
+        <v>13.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.2</v>
+        <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.4</v>
+        <v>11.17</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.6</v>
+        <v>42.17</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>6.33</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.8</v>
+        <v>17.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.5</v>
+        <v>8.82</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.7</v>
+        <v>1.09</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BR9" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BY9" t="n">
         <v>3.07</v>
@@ -4431,165 +4431,165 @@
         <v>3.38</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="CB9" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.71</v>
+        <v>5.28</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.53</v>
+        <v>5.99</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI9" t="n">
         <v>1.56</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CQ9" t="n">
-        <v>6.02</v>
+        <v>5.9</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>87.36</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="DZ9" t="n">
         <v>2.37</v>
       </c>
-      <c r="CZ9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>2.5</v>
-      </c>
       <c r="EA9" t="n">
-        <v>18.2</v>
+        <v>18.09</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="10">
@@ -4671,13 +4671,13 @@
         <v>0.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.5</v>
+        <v>6.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AC10" t="n">
         <v>17.83</v>
@@ -4973,13 +4973,13 @@
         <v>0.27</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.550000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.64</v>
+        <v>5.46</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="EA10" t="n">
         <v>19.82</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
@@ -5409,49 +5409,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="H12" t="n">
-        <v>91.40000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="K12" t="n">
-        <v>5.8</v>
+        <v>6.17</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M12" t="n">
-        <v>58.4</v>
+        <v>60</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="P12" t="n">
-        <v>9.4</v>
+        <v>9.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.4</v>
+        <v>13.33</v>
       </c>
       <c r="R12" t="n">
-        <v>6.4</v>
+        <v>5.83</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5463,28 +5463,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.8</v>
+        <v>53.17</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.8</v>
+        <v>15.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.6</v>
+        <v>17.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5568,70 +5568,70 @@
         <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.4</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="BR12" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BT12" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="CB12" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="CC12" t="n">
         <v>2.47</v>
@@ -5640,120 +5640,120 @@
         <v>2.64</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.46</v>
+        <v>6.34</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.59999999999999</v>
+        <v>90.09</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DM12" t="n">
-        <v>50.1</v>
+        <v>51.73</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.3</v>
+        <v>10.37</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.5</v>
+        <v>7.09</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5765,28 +5765,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54</v>
+        <v>54.09</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>13</v>
+        <v>13.91</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.5</v>
+        <v>5.27</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="13">
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="AB13" t="n">
         <v>2</v>
@@ -5880,7 +5880,7 @@
         <v>21.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
         <v>2.2</v>
@@ -6024,13 +6024,13 @@
         <v>4.56</v>
       </c>
       <c r="BZ13" t="n">
-        <v>5.08</v>
+        <v>5.26</v>
       </c>
       <c r="CA13" t="n">
         <v>3.06</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CC13" t="n">
         <v>5.42</v>
@@ -6089,7 +6089,7 @@
         <v>1.53</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CX13" t="n">
         <v>1.98</v>
@@ -6104,13 +6104,13 @@
         <v>1.55</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DC13" t="n">
         <v>2.9</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.03</v>
+        <v>6.04</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.45</v>
+        <v>10.36</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.369999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DZ13" t="n">
         <v>2.09</v>
@@ -6182,7 +6182,7 @@
         <v>23.64</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="EC13" t="n">
         <v>2.46</v>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -7013,82 +7013,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="H16" t="n">
-        <v>87.8</v>
+        <v>88.17</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M16" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="R16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.8</v>
+        <v>8.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.4</v>
+        <v>17.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7172,49 +7172,49 @@
         <v>3.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.9</v>
+        <v>8.27</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BP16" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.8</v>
+        <v>4.09</v>
       </c>
       <c r="BR16" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BS16" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BT16" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU16" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7223,19 +7223,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CC16" t="n">
         <v>2.8</v>
@@ -7244,66 +7244,66 @@
         <v>3.09</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CF16" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CH16" t="n">
         <v>1.17</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CN16" t="n">
         <v>1.5</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CP16" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.71</v>
+        <v>6.62</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CS16" t="inlineStr"/>
       <c r="CT16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CU16" t="inlineStr"/>
       <c r="CV16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CZ16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DA16" t="n">
         <v>1.53</v>
@@ -7315,82 +7315,82 @@
         <v>3.48</v>
       </c>
       <c r="DD16" t="n">
-        <v>7.07</v>
+        <v>7.18</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DH16" t="n">
-        <v>85.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.4</v>
+        <v>46.36</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.1</v>
+        <v>11.73</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.6</v>
+        <v>14.55</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.4</v>
+        <v>55.73</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.1</v>
+        <v>11.45</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.6</v>
+        <v>7.91</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.6</v>
+        <v>20.09</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="17">
@@ -7799,61 +7799,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="H18" t="n">
-        <v>91.5</v>
+        <v>88.86</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>63.5</v>
+        <v>58.86</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>10.86</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>8</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7865,28 +7865,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>45.17</v>
+        <v>42.86</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.17</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>10</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="AC18" t="n">
-        <v>23.33</v>
+        <v>22.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7970,70 +7970,70 @@
         <v>2.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.4</v>
+        <v>7.27</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU18" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CC18" t="n">
         <v>3.65</v>
@@ -8045,7 +8045,7 @@
         <v>1.58</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CG18" t="n">
         <v>2.34</v>
@@ -8054,31 +8054,31 @@
         <v>1.24</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CL18" t="n">
         <v>2.53</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO18" t="n">
         <v>1.52</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CQ18" t="n">
-        <v>5.16</v>
+        <v>5.11</v>
       </c>
       <c r="CR18" t="n">
         <v>1.6</v>
@@ -8087,16 +8087,16 @@
         <v>3.43</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CU18" t="n">
         <v>1.32</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CX18" t="n">
         <v>1.83</v>
@@ -8114,52 +8114,52 @@
         <v>1.56</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DD18" t="n">
-        <v>5.54</v>
+        <v>5.6</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DG18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>89.37</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DJ18" t="n">
         <v>2</v>
       </c>
-      <c r="DH18" t="n">
-        <v>91</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>2.2</v>
-      </c>
       <c r="DK18" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>56</v>
+        <v>53.73</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.7</v>
+        <v>10.64</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.699999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8171,28 +8171,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.1</v>
+        <v>44.55</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.2</v>
+        <v>13.64</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.1</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.2</v>
+        <v>20.91</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8355,19 +8355,19 @@
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="BB19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC19" t="n">
         <v>5.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BF19" t="n">
         <v>2.2</v>
@@ -8442,7 +8442,7 @@
         <v>3.65</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.87</v>
+        <v>3.98</v>
       </c>
       <c r="CE19" t="n">
         <v>1.63</v>
@@ -8516,7 +8516,7 @@
         <v>3.04</v>
       </c>
       <c r="DD19" t="n">
-        <v>6.27</v>
+        <v>6.26</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
@@ -8576,19 +8576,19 @@
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.27</v>
+        <v>12.18</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="DZ19" t="n">
         <v>4.18</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.91</v>
+        <v>20</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC19" t="n">
         <v>2.64</v>
@@ -9072,10 +9072,10 @@
         <v>0.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.83</v>
+        <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>9</v>
+        <v>9.17</v>
       </c>
       <c r="AB21" t="n">
         <v>3.83</v>
@@ -9084,7 +9084,7 @@
         <v>20.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
         <v>2.67</v>
@@ -9374,10 +9374,10 @@
         <v>0.18</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.45</v>
+        <v>10.55</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.27</v>
+        <v>7.37</v>
       </c>
       <c r="DZ21" t="n">
         <v>3.18</v>
@@ -9386,7 +9386,7 @@
         <v>19.46</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC21" t="n">
         <v>2.37</v>
@@ -9399,13 +9399,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" t="n">
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9492,124 +9492,124 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" t="n">
-        <v>88.8</v>
+        <v>88.67</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AL22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN22" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>12</v>
+        <v>12.17</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.2</v>
+        <v>7.33</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>49.8</v>
+        <v>46.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>11.8</v>
+        <v>11.33</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="BD22" t="n">
-        <v>20.8</v>
+        <v>21.33</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="BF22" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BH22" t="n">
-        <v>7.3</v>
+        <v>7.27</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BP22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BR22" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BS22" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BT22" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
@@ -9621,7 +9621,7 @@
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BY22" t="n">
         <v>2.52</v>
@@ -9630,22 +9630,22 @@
         <v>2.46</v>
       </c>
       <c r="CA22" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CC22" t="n">
-        <v>4.02</v>
+        <v>4.15</v>
       </c>
       <c r="CD22" t="n">
-        <v>4.54</v>
+        <v>4.77</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CF22" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="CG22" t="n">
         <v>2.07</v>
@@ -9657,138 +9657,138 @@
         <v>1.49</v>
       </c>
       <c r="CJ22" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CK22" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CL22" t="n">
         <v>2.61</v>
       </c>
       <c r="CM22" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CN22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CP22" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CQ22" t="n">
-        <v>6.31</v>
+        <v>6.24</v>
       </c>
       <c r="CR22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CS22" t="inlineStr"/>
       <c r="CT22" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CU22" t="inlineStr"/>
       <c r="CV22" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CW22" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CZ22" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DA22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DB22" t="n">
         <v>1.74</v>
       </c>
       <c r="DC22" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="DD22" t="n">
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="DE22" t="n">
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="DH22" t="n">
-        <v>87.90000000000001</v>
+        <v>87.91</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DK22" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM22" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="DO22" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="DP22" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11.4</v>
+        <v>11.55</v>
       </c>
       <c r="DR22" t="n">
-        <v>5.1</v>
+        <v>6.27</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>51</v>
+        <v>49.09</v>
       </c>
       <c r="DW22" t="n">
         <v>0</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.1</v>
+        <v>10.91</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="DZ22" t="n">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.8</v>
+        <v>20.18</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="EC22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -10435,13 +10435,13 @@
         <v>3.32</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CC24" t="n">
         <v>2.42</v>
       </c>
       <c r="CD24" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CE24" t="n">
         <v>1.52</v>
@@ -10495,10 +10495,10 @@
         <v>1.33</v>
       </c>
       <c r="CV24" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CW24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CX24" t="n">
         <v>1.77</v>
@@ -10516,10 +10516,10 @@
         <v>1.52</v>
       </c>
       <c r="DC24" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DD24" t="n">
-        <v>5.16</v>
+        <v>5.18</v>
       </c>
       <c r="DE24" t="n">
         <v>0</v>
@@ -10604,13 +10604,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -10694,52 +10694,52 @@
         <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH25" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI25" t="n">
-        <v>88</v>
+        <v>87.17</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL25" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN25" t="n">
-        <v>52.2</v>
+        <v>51.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AV25" t="n">
         <v>0</v>
@@ -10751,70 +10751,70 @@
         <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>50</v>
+        <v>53.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.6</v>
+        <v>6.33</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="BD25" t="n">
-        <v>19</v>
+        <v>20.33</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BH25" t="n">
-        <v>8.1</v>
+        <v>7.91</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BP25" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="BR25" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS25" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT25" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
@@ -10826,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY25" t="n">
         <v>1.92</v>
@@ -10835,55 +10835,55 @@
         <v>1.95</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB25" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CC25" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CD25" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CE25" t="n">
         <v>1.56</v>
       </c>
       <c r="CF25" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CG25" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CH25" t="n">
         <v>1.24</v>
       </c>
       <c r="CI25" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CJ25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CK25" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CL25" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CM25" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CN25" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CO25" t="n">
         <v>1.52</v>
       </c>
       <c r="CP25" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CQ25" t="n">
-        <v>5.17</v>
+        <v>5.12</v>
       </c>
       <c r="CR25" t="n">
         <v>1.58</v>
@@ -10892,7 +10892,7 @@
         <v>3.38</v>
       </c>
       <c r="CT25" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CU25" t="n">
         <v>1.33</v>
@@ -10901,7 +10901,7 @@
         <v>1.64</v>
       </c>
       <c r="CW25" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CX25" t="n">
         <v>1.83</v>
@@ -10919,85 +10919,85 @@
         <v>1.56</v>
       </c>
       <c r="DC25" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DD25" t="n">
-        <v>5.55</v>
+        <v>5.61</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF25" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="DG25" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="DH25" t="n">
-        <v>99.90000000000001</v>
+        <v>98.37</v>
       </c>
       <c r="DI25" t="n">
         <v>0</v>
       </c>
       <c r="DJ25" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DK25" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
       <c r="DL25" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM25" t="n">
-        <v>63.7</v>
+        <v>62.27</v>
       </c>
       <c r="DN25" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DO25" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DP25" t="n">
-        <v>9.1</v>
+        <v>9.18</v>
       </c>
       <c r="DQ25" t="n">
-        <v>15.7</v>
+        <v>15.55</v>
       </c>
       <c r="DR25" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
       <c r="DS25" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT25" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU25" t="n">
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>54.1</v>
+        <v>55.64</v>
       </c>
       <c r="DW25" t="n">
         <v>0</v>
       </c>
       <c r="DX25" t="n">
-        <v>12.8</v>
+        <v>12.82</v>
       </c>
       <c r="DY25" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="DZ25" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="EA25" t="n">
-        <v>18.7</v>
+        <v>19.45</v>
       </c>
       <c r="EB25" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC25" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="26">
@@ -11448,7 +11448,7 @@
         <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>12.33</v>
+        <v>12.67</v>
       </c>
       <c r="Q27" t="n">
         <v>13.33</v>
@@ -11634,13 +11634,13 @@
         <v>2.86</v>
       </c>
       <c r="BZ27" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="CA27" t="n">
         <v>3.17</v>
       </c>
       <c r="CB27" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CC27" t="n">
         <v>6.55</v>
@@ -11688,7 +11688,7 @@
         <v>5.18</v>
       </c>
       <c r="CR27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CS27" t="inlineStr"/>
       <c r="CT27" t="n">
@@ -11714,13 +11714,13 @@
         <v>1.68</v>
       </c>
       <c r="DB27" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DC27" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="DD27" t="n">
-        <v>5.82</v>
+        <v>5.89</v>
       </c>
       <c r="DE27" t="n">
         <v>0</v>
@@ -11756,7 +11756,7 @@
         <v>1.82</v>
       </c>
       <c r="DP27" t="n">
-        <v>13.27</v>
+        <v>13.46</v>
       </c>
       <c r="DQ27" t="n">
         <v>12.09</v>
@@ -12357,10 +12357,10 @@
         <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="BB29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC29" t="n">
         <v>4.4</v>
@@ -12369,7 +12369,7 @@
         <v>15.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BF29" t="n">
         <v>2</v>
@@ -12578,10 +12578,10 @@
         <v>0</v>
       </c>
       <c r="DX29" t="n">
-        <v>13.82</v>
+        <v>13.73</v>
       </c>
       <c r="DY29" t="n">
-        <v>9.09</v>
+        <v>9</v>
       </c>
       <c r="DZ29" t="n">
         <v>4.73</v>
@@ -12732,7 +12732,7 @@
         <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="AT30" t="n">
         <v>1.83</v>
@@ -12959,7 +12959,7 @@
         <v>10.18</v>
       </c>
       <c r="DR30" t="n">
-        <v>8.18</v>
+        <v>8.09</v>
       </c>
       <c r="DS30" t="n">
         <v>0.18</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="G3" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="H3" t="n">
-        <v>108.67</v>
+        <v>109.86</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="K3" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>76.83</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O3" t="n">
-        <v>0.83</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.83</v>
+        <v>12.86</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="S3" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="U3" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>63.17</v>
+        <v>63</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17.71</v>
       </c>
       <c r="AA3" t="n">
-        <v>12</v>
+        <v>11.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.33</v>
+        <v>19.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,46 +1953,46 @@
         <v>2.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.22</v>
+        <v>7.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BR3" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BS3" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BT3" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="CC3" t="n">
         <v>2.53</v>
@@ -2025,13 +2025,13 @@
         <v>2.6</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CH3" t="n">
         <v>1.24</v>
@@ -2040,19 +2040,19 @@
         <v>1.57</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO3" t="n">
         <v>1.5</v>
@@ -2061,7 +2061,7 @@
         <v>2.51</v>
       </c>
       <c r="CQ3" t="n">
-        <v>5.06</v>
+        <v>5.03</v>
       </c>
       <c r="CR3" t="n">
         <v>1.6</v>
@@ -2079,103 +2079,103 @@
         <v>1.58</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CX3" t="n">
         <v>1.97</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DA3" t="n">
         <v>1.56</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.58</v>
+        <v>5.66</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.34</v>
+        <v>102.9</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.11</v>
+        <v>5.3</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>70.33</v>
+        <v>69.3</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.89</v>
+        <v>13.8</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>63.22</v>
+        <v>63.1</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.67</v>
+        <v>15.7</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.33</v>
+        <v>10.4</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.55</v>
+        <v>19.3</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -5010,49 +5010,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="K11" t="n">
-        <v>5.8</v>
+        <v>5.17</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="M11" t="n">
-        <v>65.8</v>
+        <v>65</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="P11" t="n">
-        <v>17.6</v>
+        <v>16.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.2</v>
+        <v>10.83</v>
       </c>
       <c r="R11" t="n">
-        <v>8.6</v>
+        <v>7.83</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5064,28 +5064,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.2</v>
+        <v>47.67</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.8</v>
+        <v>11.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>26.8</v>
+        <v>26.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5169,43 +5169,43 @@
         <v>4.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.1</v>
+        <v>7.91</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="BR11" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BS11" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5220,19 +5220,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CC11" t="n">
         <v>4.37</v>
@@ -5241,43 +5241,43 @@
         <v>4.79</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CF11" t="n">
-        <v>4.35</v>
+        <v>4.41</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CH11" t="n">
         <v>1.16</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CQ11" t="n">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
       <c r="CR11" t="n">
         <v>1.81</v>
@@ -5291,25 +5291,25 @@
         <v>1.45</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB11" t="n">
         <v>1.88</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="DD11" t="n">
         <v>7.02</v>
@@ -5318,43 +5318,43 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DH11" t="n">
-        <v>92.2</v>
+        <v>90.91</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM11" t="n">
-        <v>60.5</v>
+        <v>60.55</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.6</v>
+        <v>17.18</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>41.2</v>
+        <v>40.64</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.3</v>
+        <v>10.18</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="EA11" t="n">
-        <v>22</v>
+        <v>22.37</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -5469,10 +5469,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.33</v>
+        <v>15.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="AB12" t="n">
         <v>6.33</v>
@@ -5481,7 +5481,7 @@
         <v>17.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AE12" t="n">
         <v>2.67</v>
@@ -5771,10 +5771,10 @@
         <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.91</v>
+        <v>14.09</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.640000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="DZ12" t="n">
         <v>5.27</v>
@@ -5783,7 +5783,7 @@
         <v>17</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="EC12" t="n">
         <v>2.73</v>
@@ -8601,13 +8601,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8694,49 +8694,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI20" t="n">
-        <v>79.5</v>
+        <v>80.14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AL20" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AN20" t="n">
-        <v>40.33</v>
+        <v>40.43</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12.83</v>
+        <v>12.71</v>
       </c>
       <c r="AR20" t="n">
-        <v>12.17</v>
+        <v>11.86</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8748,82 +8748,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>46.5</v>
+        <v>45.29</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.67</v>
+        <v>10.71</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.33</v>
+        <v>6.86</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.67</v>
+        <v>18.14</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU20" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV20" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY20" t="n">
         <v>2.14</v>
@@ -8832,25 +8832,25 @@
         <v>2.26</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CH20" t="n">
         <v>1.23</v>
@@ -8865,22 +8865,22 @@
         <v>1.77</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CM20" t="n">
         <v>2</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CQ20" t="n">
-        <v>5.56</v>
+        <v>5.49</v>
       </c>
       <c r="CR20" t="n">
         <v>1.6</v>
@@ -8891,106 +8891,106 @@
       </c>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CW20" t="n">
         <v>2.38</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="DD20" t="n">
-        <v>5.88</v>
+        <v>5.93</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="DH20" t="n">
-        <v>83.3</v>
+        <v>83.36</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.8</v>
+        <v>42.64</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.6</v>
+        <v>7.73</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>49.5</v>
+        <v>48.46</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.6</v>
+        <v>6.91</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.5</v>
+        <v>18.18</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="21">
@@ -11007,13 +11007,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
         <v>0.2</v>
@@ -11100,49 +11100,49 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" t="n">
-        <v>85.40000000000001</v>
+        <v>85.17</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>35</v>
+        <v>37.83</v>
       </c>
       <c r="AO26" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>11.2</v>
+        <v>10.83</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -11154,82 +11154,82 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>42.8</v>
+        <v>46.5</v>
       </c>
       <c r="AZ26" t="n">
         <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.8</v>
+        <v>6.83</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BD26" t="n">
-        <v>22</v>
+        <v>23.33</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BH26" t="n">
-        <v>9</v>
+        <v>8.73</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL26" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BN26" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BP26" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="BR26" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS26" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BT26" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU26" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV26" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW26" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX26" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY26" t="n">
         <v>2.18</v>
@@ -11238,25 +11238,25 @@
         <v>2.24</v>
       </c>
       <c r="CA26" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CC26" t="n">
         <v>3.88</v>
       </c>
       <c r="CD26" t="n">
-        <v>4.37</v>
+        <v>4.28</v>
       </c>
       <c r="CE26" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CF26" t="n">
-        <v>4.23</v>
+        <v>4.3</v>
       </c>
       <c r="CG26" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CH26" t="n">
         <v>1.17</v>
@@ -11265,42 +11265,42 @@
         <v>1.45</v>
       </c>
       <c r="CJ26" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CK26" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CL26" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CM26" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CN26" t="n">
         <v>1.5</v>
       </c>
       <c r="CO26" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CP26" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CQ26" t="n">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="CR26" t="n">
         <v>1.73</v>
       </c>
       <c r="CS26" t="inlineStr"/>
       <c r="CT26" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CU26" t="inlineStr"/>
       <c r="CV26" t="n">
         <v>1.48</v>
       </c>
       <c r="CW26" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CX26" t="n">
         <v>1.92</v>
@@ -11318,85 +11318,85 @@
         <v>1.78</v>
       </c>
       <c r="DC26" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="DD26" t="n">
         <v>7.09</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DG26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DH26" t="n">
-        <v>86.59999999999999</v>
+        <v>86.37</v>
       </c>
       <c r="DI26" t="n">
         <v>0</v>
       </c>
       <c r="DJ26" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="DK26" t="n">
         <v>4</v>
       </c>
       <c r="DL26" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DM26" t="n">
-        <v>47.2</v>
+        <v>47.63</v>
       </c>
       <c r="DN26" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DO26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DP26" t="n">
-        <v>12</v>
+        <v>12.27</v>
       </c>
       <c r="DQ26" t="n">
-        <v>12.3</v>
+        <v>12.45</v>
       </c>
       <c r="DR26" t="n">
-        <v>8.6</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DS26" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU26" t="n">
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>48.6</v>
+        <v>50.09</v>
       </c>
       <c r="DW26" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY26" t="n">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="DZ26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="EA26" t="n">
-        <v>22</v>
+        <v>22.73</v>
       </c>
       <c r="EB26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="EC26" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="27">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>90.25</v>
+        <v>88</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>61.5</v>
+        <v>56</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P2" t="n">
-        <v>17.75</v>
+        <v>16.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.5</v>
+        <v>41.8</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1454,19 +1454,19 @@
         <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.25</v>
+        <v>22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>12.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.33</v>
+        <v>11.17</v>
       </c>
       <c r="AS2" t="n">
         <v>10.17</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>53.17</v>
+        <v>53.33</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.17</v>
@@ -1550,49 +1550,49 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.6</v>
+        <v>4.36</v>
       </c>
       <c r="BR2" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BT2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BU2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BY2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CB2" t="n">
         <v>3</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>2.99</v>
       </c>
       <c r="CC2" t="n">
         <v>4.65</v>
@@ -1625,7 +1625,7 @@
         <v>1.63</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CG2" t="n">
         <v>2.22</v>
@@ -1634,16 +1634,16 @@
         <v>1.22</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CK2" t="n">
         <v>1.79</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CM2" t="n">
         <v>1.98</v>
@@ -1652,13 +1652,13 @@
         <v>1.59</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CP2" t="n">
         <v>2.87</v>
       </c>
       <c r="CQ2" t="n">
-        <v>5.84</v>
+        <v>5.79</v>
       </c>
       <c r="CR2" t="n">
         <v>1.67</v>
@@ -1676,25 +1676,25 @@
         <v>1.56</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB2" t="n">
         <v>1.68</v>
       </c>
       <c r="DC2" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DD2" t="n">
         <v>6.42</v>
@@ -1703,76 +1703,76 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.5</v>
+        <v>86.73</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DM2" t="n">
-        <v>59.1</v>
+        <v>56.82</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.5</v>
+        <v>14.36</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.1</v>
+        <v>48.09</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.2</v>
+        <v>11.18</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.8</v>
+        <v>22.82</v>
       </c>
       <c r="EB2" t="n">
         <v>1.27</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
@@ -1782,19 +1782,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="G3" t="n">
         <v>2.71</v>
@@ -1806,7 +1806,7 @@
         <v>-0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="K3" t="n">
         <v>5.43</v>
@@ -1824,7 +1824,7 @@
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>8.289999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>12.86</v>
@@ -1869,56 +1869,56 @@
         <v>2.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>86.67</v>
+        <v>94.25</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.33</v>
+        <v>54.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.33</v>
+        <v>12.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>15.25</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.67</v>
+        <v>8.25</v>
       </c>
       <c r="AT3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU3" t="n">
         <v>1</v>
       </c>
-      <c r="AU3" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
@@ -1929,70 +1929,70 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>63.33</v>
+        <v>66</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>17.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BR3" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BS3" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BT3" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY3" t="n">
         <v>1.75</v>
@@ -2013,64 +2013,64 @@
         <v>1.82</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CH3" t="n">
         <v>1.24</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CK3" t="n">
         <v>1.84</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CM3" t="n">
         <v>1.92</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="CQ3" t="n">
-        <v>5.03</v>
+        <v>5.05</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CS3" t="n">
         <v>3.29</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CU3" t="n">
         <v>1.3</v>
@@ -2079,13 +2079,13 @@
         <v>1.58</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.87</v>
@@ -2094,88 +2094,88 @@
         <v>1.56</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.66</v>
+        <v>5.73</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.9</v>
+        <v>104.18</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM3" t="n">
-        <v>69.3</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.8</v>
+        <v>13.73</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>63.1</v>
+        <v>64.09</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.7</v>
+        <v>14.72</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.4</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.3</v>
+        <v>5.18</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.3</v>
+        <v>19.09</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="4">
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.83</v>
+        <v>51</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.33</v>
+        <v>16.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.83</v>
+        <v>11.67</v>
       </c>
       <c r="AB4" t="n">
         <v>4.5</v>
@@ -2269,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AL4" t="n">
         <v>3.4</v>
@@ -2302,7 +2302,7 @@
         <v>57.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AP4" t="n">
         <v>1.4</v>
@@ -2347,13 +2347,13 @@
         <v>2.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="BE4" t="n">
         <v>1.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
         <v>2.55</v>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="DK4" t="n">
         <v>5.36</v>
@@ -2533,7 +2533,7 @@
         <v>61.82</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
         <v>2.64</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.36</v>
+        <v>50.45</v>
       </c>
       <c r="DW4" t="n">
         <v>0.27</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.45</v>
+        <v>13.37</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.73</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.73</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.55</v>
+        <v>24.64</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="5">
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="G5" t="n">
         <v>2.86</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
         <v>5.14</v>
@@ -2630,7 +2630,7 @@
         <v>2.29</v>
       </c>
       <c r="P5" t="n">
-        <v>9.57</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>12</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>43.86</v>
+        <v>44</v>
       </c>
       <c r="Y5" t="n">
         <v>0.29</v>
@@ -2675,7 +2675,7 @@
         <v>1.57</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>34.75</v>
+        <v>35</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.25</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="DG5" t="n">
         <v>1.91</v>
@@ -2924,7 +2924,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="DK5" t="n">
         <v>3.82</v>
@@ -2942,7 +2942,7 @@
         <v>1.91</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.45</v>
+        <v>10.54</v>
       </c>
       <c r="DQ5" t="n">
         <v>12.64</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>40.55</v>
+        <v>40.73</v>
       </c>
       <c r="DW5" t="n">
         <v>0.28</v>
@@ -2981,7 +2981,7 @@
         <v>1.33</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="6">
@@ -3036,7 +3036,7 @@
         <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="R6" t="n">
         <v>10.4</v>
@@ -3084,7 +3084,7 @@
         <v>0.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AH6" t="n">
         <v>0.5</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL6" t="n">
         <v>1.5</v>
@@ -3108,13 +3108,13 @@
         <v>50.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
         <v>11.5</v>
@@ -3159,7 +3159,7 @@
         <v>1.04</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="BG6" t="n">
         <v>1.73</v>
@@ -3315,7 +3315,7 @@
         <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="DG6" t="n">
         <v>0.64</v>
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="DK6" t="n">
         <v>1.64</v>
@@ -3339,16 +3339,16 @@
         <v>50.45</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DO6" t="n">
         <v>0.45</v>
       </c>
       <c r="DP6" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="DQ6" t="n">
         <v>12</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>11.91</v>
       </c>
       <c r="DR6" t="n">
         <v>10.36</v>
@@ -3384,7 +3384,7 @@
         <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="7">
@@ -3469,16 +3469,16 @@
         <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC7" t="n">
         <v>22.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -3775,16 +3775,16 @@
         <v>11.45</v>
       </c>
       <c r="DY7" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="EA7" t="n">
         <v>21</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC7" t="n">
         <v>2.27</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>57</v>
+        <v>57.25</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.45</v>
+        <v>62.54</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AH9" t="n">
         <v>1.83</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.17</v>
+        <v>3.33</v>
       </c>
       <c r="AL9" t="n">
         <v>3.17</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.17</v>
+        <v>42</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -4368,7 +4368,7 @@
         <v>0.89</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.17</v>
+        <v>3.33</v>
       </c>
       <c r="BG9" t="n">
         <v>1.55</v>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="DG9" t="n">
         <v>1.82</v>
@@ -4532,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="DK9" t="n">
         <v>3.91</v>
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.37</v>
+        <v>45.27</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>1.04</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="10">
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="G10" t="n">
         <v>1.67</v>
@@ -4635,7 +4635,7 @@
         <v>49.5</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="O10" t="n">
         <v>2.83</v>
@@ -4919,7 +4919,7 @@
         <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="DG10" t="n">
         <v>1.55</v>
@@ -4943,7 +4943,7 @@
         <v>45</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="DO10" t="n">
         <v>2.09</v>
@@ -5103,7 +5103,7 @@
         <v>0.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AL11" t="n">
         <v>2.8</v>
@@ -5115,7 +5115,7 @@
         <v>55.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AP11" t="n">
         <v>0.8</v>
@@ -5145,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>1.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0.91</v>
@@ -5330,7 +5330,7 @@
         <v>0.18</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="DK11" t="n">
         <v>4.09</v>
@@ -5342,7 +5342,7 @@
         <v>60.55</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="DO11" t="n">
         <v>1.82</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>40.64</v>
+        <v>40.73</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>1.31</v>
       </c>
       <c r="EC11" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="12">
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>53.17</v>
+        <v>52.83</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54.09</v>
+        <v>53.91</v>
       </c>
       <c r="DW12" t="n">
         <v>0.09</v>
@@ -5922,7 +5922,7 @@
         <v>11.33</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="AS13" t="n">
         <v>7.33</v>
@@ -5943,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.17</v>
+        <v>47</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -5958,7 +5958,7 @@
         <v>2.17</v>
       </c>
       <c r="BD13" t="n">
-        <v>25.67</v>
+        <v>25.5</v>
       </c>
       <c r="BE13" t="n">
         <v>1.09</v>
@@ -6149,7 +6149,7 @@
         <v>10.54</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.64</v>
+        <v>11.73</v>
       </c>
       <c r="DR13" t="n">
         <v>7.73</v>
@@ -6164,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.46</v>
+        <v>44.36</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>2.09</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.64</v>
+        <v>23.55</v>
       </c>
       <c r="EB13" t="n">
         <v>1.18</v>
@@ -6207,7 +6207,7 @@
         <v>0.6</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
         <v>2.4</v>
@@ -6219,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
@@ -6264,7 +6264,7 @@
         <v>42</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z14" t="n">
         <v>10.8</v>
@@ -6288,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="n">
         <v>2.67</v>
@@ -6300,7 +6300,7 @@
         <v>0.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="AL14" t="n">
         <v>4</v>
@@ -6357,13 +6357,13 @@
         <v>2.83</v>
       </c>
       <c r="BD14" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="BE14" t="n">
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BG14" t="n">
         <v>2.55</v>
@@ -6519,7 +6519,7 @@
         <v>0.27</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="DG14" t="n">
         <v>2.55</v>
@@ -6531,7 +6531,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.73</v>
+        <v>3.63</v>
       </c>
       <c r="DK14" t="n">
         <v>3.91</v>
@@ -6570,7 +6570,7 @@
         <v>45.64</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="DX14" t="n">
         <v>9.640000000000001</v>
@@ -6582,13 +6582,13 @@
         <v>3.54</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.55</v>
+        <v>17.73</v>
       </c>
       <c r="EB14" t="n">
         <v>1.15</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.36</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="15">
@@ -6646,7 +6646,7 @@
         <v>12.8</v>
       </c>
       <c r="R15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -6691,7 +6691,7 @@
         <v>0.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="n">
         <v>0.17</v>
@@ -6703,7 +6703,7 @@
         <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AL15" t="n">
         <v>2.5</v>
@@ -6745,7 +6745,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>37.5</v>
+        <v>37.67</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.17</v>
@@ -6766,7 +6766,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="BG15" t="n">
         <v>1.73</v>
@@ -6922,7 +6922,7 @@
         <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="DG15" t="n">
         <v>1.27</v>
@@ -6934,7 +6934,7 @@
         <v>0.18</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="DK15" t="n">
         <v>3.55</v>
@@ -6958,7 +6958,7 @@
         <v>12.91</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.640000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.36</v>
+        <v>43.46</v>
       </c>
       <c r="DW15" t="n">
         <v>0.09</v>
@@ -6991,7 +6991,7 @@
         <v>1.21</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="16">
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
         <v>1.83</v>
@@ -7025,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>3.83</v>
@@ -7043,7 +7043,7 @@
         <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>11.5</v>
+        <v>11.17</v>
       </c>
       <c r="Q16" t="n">
         <v>15.5</v>
@@ -7073,10 +7073,10 @@
         <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.5</v>
+        <v>12.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="AB16" t="n">
         <v>4.17</v>
@@ -7085,10 +7085,10 @@
         <v>17.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>57.8</v>
+        <v>57.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.6</v>
@@ -7321,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DG16" t="n">
         <v>1.45</v>
@@ -7333,7 +7333,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.73</v>
+        <v>3.64</v>
       </c>
       <c r="DK16" t="n">
         <v>3.82</v>
@@ -7351,7 +7351,7 @@
         <v>2.27</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.73</v>
+        <v>11.55</v>
       </c>
       <c r="DQ16" t="n">
         <v>14.55</v>
@@ -7369,16 +7369,16 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>55.73</v>
+        <v>55.55</v>
       </c>
       <c r="DW16" t="n">
         <v>0.37</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.45</v>
+        <v>11.55</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
         <v>3.55</v>
@@ -7390,7 +7390,7 @@
         <v>1.31</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="17">
@@ -7466,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>54.33</v>
+        <v>54.5</v>
       </c>
       <c r="Y17" t="n">
         <v>0.5</v>
@@ -7553,10 +7553,10 @@
         <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC17" t="n">
         <v>3.8</v>
@@ -7565,7 +7565,7 @@
         <v>23.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BF17" t="n">
         <v>3</v>
@@ -7768,16 +7768,16 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.91</v>
+        <v>55</v>
       </c>
       <c r="DW17" t="n">
         <v>0.36</v>
       </c>
       <c r="DX17" t="n">
-        <v>14</v>
+        <v>13.91</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.630000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.36</v>
@@ -7786,7 +7786,7 @@
         <v>24.73</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC17" t="n">
         <v>2.36</v>
@@ -7811,7 +7811,7 @@
         <v>0.14</v>
       </c>
       <c r="F18" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="G18" t="n">
         <v>1.86</v>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="K18" t="n">
         <v>3.86</v>
@@ -7835,7 +7835,7 @@
         <v>58.86</v>
       </c>
       <c r="N18" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="O18" t="n">
         <v>0.86</v>
@@ -7871,10 +7871,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>15.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.140000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB18" t="n">
         <v>5.86</v>
@@ -7883,10 +7883,10 @@
         <v>22.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -8123,7 +8123,7 @@
         <v>0.09</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="DG18" t="n">
         <v>2.09</v>
@@ -8135,7 +8135,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="DK18" t="n">
         <v>3.64</v>
@@ -8147,7 +8147,7 @@
         <v>53.73</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="DO18" t="n">
         <v>0.82</v>
@@ -8177,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.64</v>
+        <v>13.73</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.630000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="DZ18" t="n">
         <v>5</v>
@@ -8192,7 +8192,7 @@
         <v>1.6</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="19">
@@ -8214,7 +8214,7 @@
         <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
         <v>1.67</v>
@@ -8226,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="K19" t="n">
         <v>3.67</v>
@@ -8247,7 +8247,7 @@
         <v>14.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>14.17</v>
       </c>
       <c r="R19" t="n">
         <v>7.5</v>
@@ -8289,7 +8289,7 @@
         <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8522,7 +8522,7 @@
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DG19" t="n">
         <v>2.46</v>
@@ -8534,7 +8534,7 @@
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="DK19" t="n">
         <v>4.64</v>
@@ -8555,7 +8555,7 @@
         <v>12.55</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.45</v>
+        <v>11.55</v>
       </c>
       <c r="DR19" t="n">
         <v>6.55</v>
@@ -8591,7 +8591,7 @@
         <v>1.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="20">
@@ -8643,7 +8643,7 @@
         <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q20" t="n">
         <v>8.75</v>
@@ -8694,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
         <v>2.29</v>
@@ -8706,7 +8706,7 @@
         <v>0.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="AL20" t="n">
         <v>3.57</v>
@@ -8748,28 +8748,28 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>45.29</v>
+        <v>45.43</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.71</v>
+        <v>10.57</v>
       </c>
       <c r="BB20" t="n">
         <v>6.86</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.86</v>
+        <v>3.71</v>
       </c>
       <c r="BD20" t="n">
         <v>18.14</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="BG20" t="n">
         <v>2.82</v>
@@ -8921,7 +8921,7 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="DG20" t="n">
         <v>2.37</v>
@@ -8933,7 +8933,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="DK20" t="n">
         <v>4.09</v>
@@ -8951,7 +8951,7 @@
         <v>1.73</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.54</v>
+        <v>11.63</v>
       </c>
       <c r="DQ20" t="n">
         <v>10.73</v>
@@ -8969,28 +8969,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>48.46</v>
+        <v>48.55</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.09</v>
+        <v>11</v>
       </c>
       <c r="DY20" t="n">
         <v>6.91</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="EA20" t="n">
         <v>18.18</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="21">
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -9066,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>46.5</v>
+        <v>46.33</v>
       </c>
       <c r="Y21" t="n">
         <v>0.17</v>
@@ -9075,19 +9075,19 @@
         <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.17</v>
+        <v>9.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.83</v>
+        <v>3.67</v>
       </c>
       <c r="AC21" t="n">
         <v>20.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9123,7 +9123,7 @@
         <v>1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="AR21" t="n">
         <v>13.6</v>
@@ -9320,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="DG21" t="n">
         <v>1.64</v>
@@ -9350,7 +9350,7 @@
         <v>1.09</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.45</v>
+        <v>13.36</v>
       </c>
       <c r="DQ21" t="n">
         <v>13.55</v>
@@ -9368,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>43.73</v>
+        <v>43.63</v>
       </c>
       <c r="DW21" t="n">
         <v>0.18</v>
@@ -9377,19 +9377,19 @@
         <v>10.55</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.37</v>
+        <v>7.45</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="EA21" t="n">
         <v>19.46</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="22">
@@ -9870,10 +9870,10 @@
         <v>0.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.25</v>
+        <v>17.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="AB23" t="n">
         <v>4.25</v>
@@ -9882,7 +9882,7 @@
         <v>23</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AE23" t="n">
         <v>2.5</v>
@@ -9945,16 +9945,16 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>58</v>
+        <v>58.14</v>
       </c>
       <c r="AZ23" t="n">
         <v>0.14</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.29</v>
+        <v>6.14</v>
       </c>
       <c r="BC23" t="n">
         <v>3.71</v>
@@ -9963,7 +9963,7 @@
         <v>22</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BF23" t="n">
         <v>4</v>
@@ -10170,7 +10170,7 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>57.64</v>
+        <v>57.73</v>
       </c>
       <c r="DW23" t="n">
         <v>0.18</v>
@@ -10324,7 +10324,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="AR24" t="n">
         <v>10.14</v>
@@ -10348,7 +10348,7 @@
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>62.57</v>
+        <v>62.29</v>
       </c>
       <c r="AZ24" t="n">
         <v>0.14</v>
@@ -10555,7 +10555,7 @@
         <v>2.46</v>
       </c>
       <c r="DP24" t="n">
-        <v>11.27</v>
+        <v>11.18</v>
       </c>
       <c r="DQ24" t="n">
         <v>11.18</v>
@@ -10573,7 +10573,7 @@
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>65.81999999999999</v>
+        <v>65.64</v>
       </c>
       <c r="DW24" t="n">
         <v>0.27</v>
@@ -10670,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>58.2</v>
+        <v>57.8</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>53.5</v>
+        <v>53.67</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>55.64</v>
+        <v>55.55</v>
       </c>
       <c r="DW25" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
       <c r="Y26" t="n">
         <v>0.2</v>
@@ -11100,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
         <v>1.17</v>
@@ -11112,7 +11112,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="AL26" t="n">
         <v>3.17</v>
@@ -11154,7 +11154,7 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>46.5</v>
+        <v>46.33</v>
       </c>
       <c r="AZ26" t="n">
         <v>0</v>
@@ -11175,7 +11175,7 @@
         <v>0.87</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="BG26" t="n">
         <v>2.09</v>
@@ -11327,7 +11327,7 @@
         <v>0.09</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DG26" t="n">
         <v>2</v>
@@ -11339,7 +11339,7 @@
         <v>0</v>
       </c>
       <c r="DJ26" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="DK26" t="n">
         <v>4</v>
@@ -11396,7 +11396,7 @@
         <v>1.17</v>
       </c>
       <c r="EC26" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="27">
@@ -11418,10 +11418,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H27" t="n">
         <v>92.5</v>
@@ -11430,22 +11430,22 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.67</v>
+        <v>3.33</v>
       </c>
       <c r="K27" t="n">
         <v>5.5</v>
       </c>
       <c r="L27" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>56.67</v>
       </c>
       <c r="N27" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
         <v>12.67</v>
@@ -11472,16 +11472,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>53.33</v>
+        <v>53.17</v>
       </c>
       <c r="Y27" t="n">
         <v>0.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="AA27" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="AB27" t="n">
         <v>5.17</v>
@@ -11490,16 +11490,16 @@
         <v>23.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AH27" t="n">
         <v>1.2</v>
@@ -11511,7 +11511,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AL27" t="n">
         <v>2.2</v>
@@ -11529,13 +11529,13 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14.4</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
         <v>10.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="AT27" t="n">
         <v>1.4</v>
@@ -11553,16 +11553,16 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="AZ27" t="n">
         <v>0.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC27" t="n">
         <v>2.4</v>
@@ -11571,10 +11571,10 @@
         <v>22</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG27" t="n">
         <v>1.73</v>
@@ -11604,10 +11604,10 @@
         <v>0.82</v>
       </c>
       <c r="BP27" t="n">
-        <v>4.36</v>
+        <v>4.64</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.09</v>
+        <v>4.82</v>
       </c>
       <c r="BR27" t="n">
         <v>90.91</v>
@@ -11726,10 +11726,10 @@
         <v>0</v>
       </c>
       <c r="DF27" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DG27" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="DH27" t="n">
         <v>88.45</v>
@@ -11738,31 +11738,31 @@
         <v>0</v>
       </c>
       <c r="DJ27" t="n">
-        <v>4.27</v>
+        <v>4.18</v>
       </c>
       <c r="DK27" t="n">
         <v>4</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="DM27" t="n">
         <v>49.82</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="DO27" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="DP27" t="n">
-        <v>13.46</v>
+        <v>12.82</v>
       </c>
       <c r="DQ27" t="n">
         <v>12.09</v>
       </c>
       <c r="DR27" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="DS27" t="n">
         <v>0.27</v>
@@ -11774,16 +11774,16 @@
         <v>0</v>
       </c>
       <c r="DV27" t="n">
-        <v>48.36</v>
+        <v>48.37</v>
       </c>
       <c r="DW27" t="n">
         <v>0.27</v>
       </c>
       <c r="DX27" t="n">
-        <v>10.18</v>
+        <v>10.37</v>
       </c>
       <c r="DY27" t="n">
-        <v>6.27</v>
+        <v>6.45</v>
       </c>
       <c r="DZ27" t="n">
         <v>3.91</v>
@@ -11792,10 +11792,10 @@
         <v>22.91</v>
       </c>
       <c r="EB27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC27" t="n">
-        <v>3.91</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="28">
@@ -11817,7 +11817,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="G28" t="n">
         <v>1.2</v>
@@ -11829,7 +11829,7 @@
         <v>0.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="K28" t="n">
         <v>6.8</v>
@@ -11850,7 +11850,7 @@
         <v>9.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="R28" t="n">
         <v>8</v>
@@ -11892,7 +11892,7 @@
         <v>1.39</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -11952,7 +11952,7 @@
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>49.17</v>
+        <v>49.33</v>
       </c>
       <c r="AZ28" t="n">
         <v>0</v>
@@ -12125,7 +12125,7 @@
         <v>0</v>
       </c>
       <c r="DF28" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DG28" t="n">
         <v>1.82</v>
@@ -12137,7 +12137,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ28" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="DK28" t="n">
         <v>5.09</v>
@@ -12158,7 +12158,7 @@
         <v>11.45</v>
       </c>
       <c r="DQ28" t="n">
-        <v>11.45</v>
+        <v>11.54</v>
       </c>
       <c r="DR28" t="n">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>53.46</v>
+        <v>53.54</v>
       </c>
       <c r="DW28" t="n">
         <v>0</v>
@@ -12194,7 +12194,7 @@
         <v>1.36</v>
       </c>
       <c r="EC28" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="29">
@@ -12615,7 +12615,7 @@
         <v>0.2</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G30" t="n">
         <v>1.8</v>
@@ -12627,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K30" t="n">
         <v>3.6</v>
@@ -12669,7 +12669,7 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -12690,16 +12690,16 @@
         <v>1.93</v>
       </c>
       <c r="AE30" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
         <v>0.17</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AI30" t="n">
         <v>89</v>
@@ -12714,16 +12714,16 @@
         <v>3.67</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AN30" t="n">
         <v>47.67</v>
       </c>
       <c r="AO30" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
@@ -12801,10 +12801,10 @@
         <v>1</v>
       </c>
       <c r="BP30" t="n">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="BQ30" t="n">
-        <v>3.45</v>
+        <v>4.18</v>
       </c>
       <c r="BR30" t="n">
         <v>81.81999999999999</v>
@@ -12923,10 +12923,10 @@
         <v>0.18</v>
       </c>
       <c r="DF30" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="DG30" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="DH30" t="n">
         <v>91.09</v>
@@ -12935,22 +12935,22 @@
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="DK30" t="n">
         <v>3.64</v>
       </c>
       <c r="DL30" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="DM30" t="n">
         <v>52.18</v>
       </c>
       <c r="DN30" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="DO30" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="DP30" t="n">
         <v>10.91</v>
@@ -12971,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>47.54</v>
+        <v>47.45</v>
       </c>
       <c r="DW30" t="n">
         <v>0.09</v>
@@ -12992,7 +12992,7 @@
         <v>1.72</v>
       </c>
       <c r="EC30" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="31">
@@ -13026,7 +13026,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K31" t="n">
         <v>4.2</v>
@@ -13038,7 +13038,7 @@
         <v>55.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O31" t="n">
         <v>2.4</v>
@@ -13089,7 +13089,7 @@
         <v>1.39</v>
       </c>
       <c r="AE31" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AF31" t="n">
         <v>0.17</v>
@@ -13149,7 +13149,7 @@
         <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>52.83</v>
+        <v>52.67</v>
       </c>
       <c r="AZ31" t="n">
         <v>0</v>
@@ -13334,7 +13334,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ31" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="DK31" t="n">
         <v>4</v>
@@ -13346,7 +13346,7 @@
         <v>51.18</v>
       </c>
       <c r="DN31" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DO31" t="n">
         <v>2.18</v>
@@ -13370,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>53.36</v>
+        <v>53.27</v>
       </c>
       <c r="DW31" t="n">
         <v>0</v>
@@ -13391,7 +13391,7 @@
         <v>1.32</v>
       </c>
       <c r="EC31" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1397,7 +1397,7 @@
         <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>88</v>
+        <v>88.2</v>
       </c>
       <c r="I2" t="n">
         <v>0.2</v>
@@ -1421,7 +1421,7 @@
         <v>1.6</v>
       </c>
       <c r="P2" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="Q2" t="n">
         <v>8.800000000000001</v>
@@ -1460,7 +1460,7 @@
         <v>3.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AD2" t="n">
         <v>1.34</v>
@@ -1607,13 +1607,13 @@
         <v>3.27</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.51</v>
+        <v>3.63</v>
       </c>
       <c r="CA2" t="n">
         <v>3.01</v>
       </c>
       <c r="CB2" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CC2" t="n">
         <v>4.65</v>
@@ -1661,13 +1661,13 @@
         <v>5.79</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CS2" t="n">
         <v>3.35</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CU2" t="n">
         <v>1.31</v>
@@ -1691,13 +1691,13 @@
         <v>1.6</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DC2" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.42</v>
+        <v>6.39</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         <v>2.36</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.73</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.18</v>
@@ -1733,7 +1733,7 @@
         <v>1.91</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.36</v>
+        <v>14.45</v>
       </c>
       <c r="DQ2" t="n">
         <v>10.09</v>
@@ -1766,7 +1766,7 @@
         <v>2.18</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.82</v>
+        <v>22.73</v>
       </c>
       <c r="EB2" t="n">
         <v>1.27</v>
@@ -1881,7 +1881,7 @@
         <v>2.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>94.25</v>
+        <v>94.75</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.5</v>
+        <v>54.75</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1905,10 +1905,10 @@
         <v>2.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
         <v>8.25</v>
@@ -1944,7 +1944,7 @@
         <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.75</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
         <v>1.28</v>
@@ -2016,13 +2016,13 @@
         <v>3.18</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CC3" t="n">
         <v>2.38</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CE3" t="n">
         <v>1.58</v>
@@ -2094,13 +2094,13 @@
         <v>1.56</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.73</v>
+        <v>5.7</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>2.63</v>
       </c>
       <c r="DH3" t="n">
-        <v>104.18</v>
+        <v>104.37</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.09</v>
@@ -2127,7 +2127,7 @@
         <v>0.18</v>
       </c>
       <c r="DM3" t="n">
-        <v>67.18000000000001</v>
+        <v>67.27</v>
       </c>
       <c r="DN3" t="n">
         <v>0.82</v>
@@ -2136,10 +2136,10 @@
         <v>1.91</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.18</v>
+        <v>10.36</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.73</v>
+        <v>13.82</v>
       </c>
       <c r="DR3" t="n">
         <v>6.73</v>
@@ -2169,7 +2169,7 @@
         <v>5.18</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.09</v>
+        <v>19.18</v>
       </c>
       <c r="EB3" t="n">
         <v>1.78</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>98.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>50.4</v>
+        <v>51.33</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="P6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.8</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>46</v>
+        <v>46.17</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.2</v>
+        <v>16.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0.17</v>
@@ -3162,46 +3162,46 @@
         <v>1.33</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="BH6" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="BR6" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.53</v>
+        <v>3.35</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CC6" t="n">
         <v>5.82</v>
@@ -3237,40 +3237,40 @@
         <v>1.65</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CH6" t="n">
         <v>1.2</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO6" t="n">
         <v>1.62</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.91</v>
+        <v>5.95</v>
       </c>
       <c r="CR6" t="n">
         <v>1.6</v>
@@ -3306,85 +3306,85 @@
         <v>1.66</v>
       </c>
       <c r="DC6" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.91</v>
+        <v>84.92</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DM6" t="n">
-        <v>50.45</v>
+        <v>50.92</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.91</v>
+        <v>11.92</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12</v>
+        <v>12.08</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.36</v>
+        <v>10.08</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>38.54</v>
+        <v>39.25</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9</v>
+        <v>9.42</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.54</v>
+        <v>6</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.36</v>
+        <v>17.58</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3893,121 +3893,121 @@
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>86.75</v>
+        <v>88.2</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>51</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>57.25</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF8" t="n">
+      <c r="BH8" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="BI8" t="n">
         <v>1.75</v>
       </c>
-      <c r="BG8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BJ8" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY8" t="n">
         <v>1.71</v>
@@ -4028,55 +4028,55 @@
         <v>1.73</v>
       </c>
       <c r="CA8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CB8" t="n">
         <v>3.22</v>
       </c>
-      <c r="CB8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="CC8" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CH8" t="n">
         <v>1.13</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CN8" t="n">
         <v>1.44</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CP8" t="n">
         <v>2.68</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="CR8" t="n">
         <v>1.6</v>
@@ -4085,7 +4085,7 @@
         <v>3.29</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CU8" t="n">
         <v>1.3</v>
@@ -4097,13 +4097,13 @@
         <v>2.53</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA8" t="n">
         <v>1.62</v>
@@ -4112,85 +4112,85 @@
         <v>1.58</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.81999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.36</v>
+        <v>5.16</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.64</v>
+        <v>48.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.27</v>
+        <v>8.16</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.73</v>
+        <v>13.33</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.91</v>
+        <v>8.42</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>62.54</v>
+        <v>61.67</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.27</v>
+        <v>11.91</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.45</v>
+        <v>19.91</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="9">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -7892,136 +7892,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>90.25</v>
+        <v>88.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>44.75</v>
+        <v>46.2</v>
       </c>
       <c r="AO18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>0.75</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="BK18" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM18" t="n">
         <v>0.75</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.73</v>
-      </c>
       <c r="BN18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BY18" t="n">
         <v>2.25</v>
@@ -8036,16 +8036,16 @@
         <v>3.15</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="CE18" t="n">
         <v>1.58</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CG18" t="n">
         <v>2.34</v>
@@ -8057,13 +8057,13 @@
         <v>1.63</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM18" t="n">
         <v>1.98</v>
@@ -8075,10 +8075,10 @@
         <v>1.52</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CQ18" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="CR18" t="n">
         <v>1.6</v>
@@ -8099,28 +8099,28 @@
         <v>2.32</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CY18" t="n">
         <v>2.3</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB18" t="n">
         <v>1.56</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="DD18" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -8129,37 +8129,37 @@
         <v>2.09</v>
       </c>
       <c r="DH18" t="n">
-        <v>89.37</v>
+        <v>88.58</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>53.73</v>
+        <v>53.58</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.73</v>
+        <v>11.17</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.64</v>
+        <v>10.92</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.359999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8171,28 +8171,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44.55</v>
+        <v>45.08</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.73</v>
+        <v>13.66</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.73</v>
+        <v>8.75</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.91</v>
+        <v>21.08</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="19">
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
@@ -8613,82 +8613,82 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M20" t="n">
-        <v>46.5</v>
+        <v>49.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>9.75</v>
+        <v>8.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>11.75</v>
+        <v>11.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.25</v>
+        <v>20.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8772,70 +8772,70 @@
         <v>2.71</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.550000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL20" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="BO20" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.45</v>
+        <v>4.17</v>
       </c>
       <c r="BR20" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="BS20" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT20" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV20" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CC20" t="n">
         <v>3.64</v>
@@ -8850,44 +8850,44 @@
         <v>3.73</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CH20" t="n">
         <v>1.23</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CM20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CQ20" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CS20" t="inlineStr"/>
       <c r="CT20" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
@@ -8897,16 +8897,16 @@
         <v>2.38</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB20" t="n">
         <v>1.63</v>
@@ -8921,76 +8921,76 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="DH20" t="n">
-        <v>83.36</v>
+        <v>84.25</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.64</v>
+        <v>44.08</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.63</v>
+        <v>11</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.73</v>
+        <v>10.75</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.73</v>
+        <v>7.34</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>48.55</v>
+        <v>49.42</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11</v>
+        <v>11.08</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.91</v>
+        <v>7.25</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.18</v>
+        <v>19.17</v>
       </c>
       <c r="EB20" t="n">
         <v>1.29</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="21">
@@ -9399,13 +9399,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9492,124 +9492,124 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI22" t="n">
-        <v>88.67</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL22" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AM22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>0.17</v>
       </c>
-      <c r="AN22" t="n">
-        <v>45</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV22" t="n">
+      <c r="BK22" t="n">
         <v>0.17</v>
       </c>
-      <c r="AW22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>0.18</v>
-      </c>
       <c r="BL22" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BP22" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="BR22" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BS22" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BT22" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
@@ -9621,7 +9621,7 @@
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BY22" t="n">
         <v>2.52</v>
@@ -9636,19 +9636,19 @@
         <v>2.94</v>
       </c>
       <c r="CC22" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="CD22" t="n">
-        <v>4.77</v>
+        <v>4.66</v>
       </c>
       <c r="CE22" t="n">
         <v>1.71</v>
       </c>
       <c r="CF22" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CH22" t="n">
         <v>1.17</v>
@@ -9657,13 +9657,13 @@
         <v>1.49</v>
       </c>
       <c r="CJ22" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CK22" t="n">
         <v>1.92</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CM22" t="n">
         <v>1.82</v>
@@ -9672,20 +9672,20 @@
         <v>1.47</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CP22" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CQ22" t="n">
-        <v>6.24</v>
+        <v>6.15</v>
       </c>
       <c r="CR22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CS22" t="inlineStr"/>
       <c r="CT22" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CU22" t="inlineStr"/>
       <c r="CV22" t="n">
@@ -9698,13 +9698,13 @@
         <v>1.93</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CZ22" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DA22" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DB22" t="n">
         <v>1.74</v>
@@ -9719,13 +9719,13 @@
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="DH22" t="n">
-        <v>87.91</v>
+        <v>86.17</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
@@ -9734,58 +9734,58 @@
         <v>2</v>
       </c>
       <c r="DK22" t="n">
-        <v>3.73</v>
+        <v>3.59</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM22" t="n">
-        <v>50</v>
+        <v>48.75</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="DO22" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="DP22" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11.55</v>
+        <v>11.09</v>
       </c>
       <c r="DR22" t="n">
-        <v>6.27</v>
+        <v>6.17</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>49.09</v>
+        <v>48.41</v>
       </c>
       <c r="DW22" t="n">
         <v>0</v>
       </c>
       <c r="DX22" t="n">
-        <v>10.91</v>
+        <v>10.25</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.55</v>
+        <v>7.17</v>
       </c>
       <c r="DZ22" t="n">
-        <v>3.37</v>
+        <v>3.08</v>
       </c>
       <c r="EA22" t="n">
-        <v>20.18</v>
+        <v>20.42</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="EC22" t="n">
         <v>2</v>
@@ -11406,13 +11406,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -11499,127 +11499,127 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" t="n">
-        <v>83.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN27" t="n">
-        <v>41.6</v>
+        <v>42.67</v>
       </c>
       <c r="AO27" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AP27" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE27" t="n">
+      <c r="BF27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN27" t="n">
         <v>0.92</v>
       </c>
-      <c r="BF27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>0.91</v>
-      </c>
       <c r="BO27" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BP27" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="BR27" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS27" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BT27" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU27" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV27" t="n">
         <v>0</v>
@@ -11628,7 +11628,7 @@
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BY27" t="n">
         <v>2.86</v>
@@ -11637,55 +11637,55 @@
         <v>3.02</v>
       </c>
       <c r="CA27" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CB27" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="CC27" t="n">
-        <v>6.55</v>
+        <v>5.97</v>
       </c>
       <c r="CD27" t="n">
-        <v>7.68</v>
+        <v>7.01</v>
       </c>
       <c r="CE27" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CF27" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="CG27" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CH27" t="n">
         <v>1.23</v>
       </c>
       <c r="CI27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CO27" t="n">
         <v>1.54</v>
       </c>
-      <c r="CJ27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CK27" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CL27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CM27" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CN27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CO27" t="n">
-        <v>1.53</v>
-      </c>
       <c r="CP27" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CQ27" t="n">
-        <v>5.18</v>
+        <v>5.29</v>
       </c>
       <c r="CR27" t="n">
         <v>1.62</v>
@@ -11717,85 +11717,85 @@
         <v>1.6</v>
       </c>
       <c r="DC27" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="DD27" t="n">
-        <v>5.89</v>
+        <v>5.97</v>
       </c>
       <c r="DE27" t="n">
         <v>0</v>
       </c>
       <c r="DF27" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DG27" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DH27" t="n">
-        <v>88.45</v>
+        <v>89</v>
       </c>
       <c r="DI27" t="n">
         <v>0</v>
       </c>
       <c r="DJ27" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="DK27" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="DM27" t="n">
-        <v>49.82</v>
+        <v>49.67</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DO27" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="DP27" t="n">
-        <v>12.82</v>
+        <v>12.92</v>
       </c>
       <c r="DQ27" t="n">
-        <v>12.09</v>
+        <v>12.08</v>
       </c>
       <c r="DR27" t="n">
         <v>10</v>
       </c>
       <c r="DS27" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT27" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU27" t="n">
         <v>0</v>
       </c>
       <c r="DV27" t="n">
-        <v>48.37</v>
+        <v>48.75</v>
       </c>
       <c r="DW27" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX27" t="n">
-        <v>10.37</v>
+        <v>10.58</v>
       </c>
       <c r="DY27" t="n">
-        <v>6.45</v>
+        <v>6.75</v>
       </c>
       <c r="DZ27" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="EA27" t="n">
-        <v>22.91</v>
+        <v>22.17</v>
       </c>
       <c r="EB27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC27" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="28">
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>6</v>
@@ -11817,49 +11817,49 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="H28" t="n">
-        <v>82.40000000000001</v>
+        <v>84.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="K28" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="M28" t="n">
-        <v>41.6</v>
+        <v>45.33</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="P28" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="R28" t="n">
-        <v>8</v>
+        <v>7.83</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="T28" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -11871,28 +11871,28 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>58.6</v>
+        <v>56.83</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>12.2</v>
+        <v>12.67</v>
       </c>
       <c r="AA28" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.6</v>
+        <v>4.17</v>
       </c>
       <c r="AC28" t="n">
-        <v>22</v>
+        <v>21.17</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -11976,46 +11976,46 @@
         <v>2</v>
       </c>
       <c r="BG28" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BH28" t="n">
-        <v>9.449999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="BI28" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL28" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN28" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BP28" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="BQ28" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BR28" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS28" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT28" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU28" t="n">
         <v>0</v>
@@ -12027,19 +12027,19 @@
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY28" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="BZ28" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="CA28" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CB28" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CC28" t="n">
         <v>3.59</v>
@@ -12051,31 +12051,31 @@
         <v>1.62</v>
       </c>
       <c r="CF28" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CG28" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CH28" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CI28" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CJ28" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CK28" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CL28" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CM28" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CN28" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO28" t="n">
         <v>1.59</v>
@@ -12084,14 +12084,14 @@
         <v>2.73</v>
       </c>
       <c r="CQ28" t="n">
-        <v>5.98</v>
+        <v>5.89</v>
       </c>
       <c r="CR28" t="n">
         <v>1.65</v>
       </c>
       <c r="CS28" t="inlineStr"/>
       <c r="CT28" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="n">
@@ -12101,52 +12101,52 @@
         <v>2.46</v>
       </c>
       <c r="CX28" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY28" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CZ28" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA28" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB28" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DC28" t="n">
         <v>2.98</v>
       </c>
       <c r="DD28" t="n">
-        <v>6.06</v>
+        <v>6.07</v>
       </c>
       <c r="DE28" t="n">
         <v>0</v>
       </c>
       <c r="DF28" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DG28" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DH28" t="n">
-        <v>82.91</v>
+        <v>83.75</v>
       </c>
       <c r="DI28" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ28" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DK28" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="DL28" t="n">
         <v>0</v>
       </c>
       <c r="DM28" t="n">
-        <v>43.55</v>
+        <v>45.25</v>
       </c>
       <c r="DN28" t="n">
         <v>1</v>
@@ -12155,13 +12155,13 @@
         <v>2</v>
       </c>
       <c r="DP28" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="DQ28" t="n">
-        <v>11.54</v>
+        <v>11.16</v>
       </c>
       <c r="DR28" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="DS28" t="n">
         <v>0</v>
@@ -12173,28 +12173,28 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>53.54</v>
+        <v>53.08</v>
       </c>
       <c r="DW28" t="n">
         <v>0</v>
       </c>
       <c r="DX28" t="n">
-        <v>11.91</v>
+        <v>12.17</v>
       </c>
       <c r="DY28" t="n">
-        <v>7.64</v>
+        <v>8.08</v>
       </c>
       <c r="DZ28" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="EA28" t="n">
-        <v>20.91</v>
+        <v>20.58</v>
       </c>
       <c r="EB28" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="EC28" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="29">
@@ -12204,10 +12204,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
         <v>5</v>
@@ -12216,49 +12216,49 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G29" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="H29" t="n">
-        <v>79.67</v>
+        <v>81.14</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="K29" t="n">
-        <v>4.83</v>
+        <v>4.43</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M29" t="n">
-        <v>47</v>
+        <v>50.71</v>
       </c>
       <c r="N29" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O29" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="P29" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>14.17</v>
+        <v>14.43</v>
       </c>
       <c r="R29" t="n">
-        <v>8.17</v>
+        <v>7.57</v>
       </c>
       <c r="S29" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -12270,28 +12270,28 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>43</v>
+        <v>43.86</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>13.5</v>
+        <v>14.14</v>
       </c>
       <c r="AA29" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AB29" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>16.5</v>
+        <v>18.86</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
         <v>0.2</v>
@@ -12375,70 +12375,70 @@
         <v>2</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BH29" t="n">
-        <v>8.359999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL29" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BN29" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP29" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="BQ29" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="BR29" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS29" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT29" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BU29" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV29" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="BZ29" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="CA29" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CB29" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CC29" t="n">
         <v>3.57</v>
@@ -12447,43 +12447,43 @@
         <v>3.85</v>
       </c>
       <c r="CE29" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CF29" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CG29" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CH29" t="n">
         <v>1.21</v>
       </c>
       <c r="CI29" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CJ29" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CK29" t="n">
         <v>1.87</v>
       </c>
       <c r="CL29" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CM29" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CN29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CO29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CP29" t="n">
         <v>2.81</v>
       </c>
       <c r="CQ29" t="n">
-        <v>5.86</v>
+        <v>5.82</v>
       </c>
       <c r="CR29" t="n">
         <v>1.68</v>
@@ -12500,67 +12500,67 @@
         <v>2.52</v>
       </c>
       <c r="CX29" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CY29" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CZ29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DA29" t="n">
         <v>1.56</v>
       </c>
       <c r="DB29" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DC29" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="DD29" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DG29" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DH29" t="n">
-        <v>83.91</v>
+        <v>84.42</v>
       </c>
       <c r="DI29" t="n">
         <v>0</v>
       </c>
       <c r="DJ29" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DK29" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="DL29" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM29" t="n">
-        <v>48.91</v>
+        <v>50.91</v>
       </c>
       <c r="DN29" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DO29" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="DP29" t="n">
-        <v>11.18</v>
+        <v>11.08</v>
       </c>
       <c r="DQ29" t="n">
-        <v>13.73</v>
+        <v>13.92</v>
       </c>
       <c r="DR29" t="n">
-        <v>8.73</v>
+        <v>8.33</v>
       </c>
       <c r="DS29" t="n">
         <v>0</v>
@@ -12572,28 +12572,28 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>46</v>
+        <v>46.25</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
       </c>
       <c r="DX29" t="n">
-        <v>13.73</v>
+        <v>14.08</v>
       </c>
       <c r="DY29" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="DZ29" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="EA29" t="n">
-        <v>16.18</v>
+        <v>17.58</v>
       </c>
       <c r="EB29" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="EC29" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="30">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>88.2</v>
+        <v>90.17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>56</v>
+        <v>55.67</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>17</v>
+        <v>16.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="R2" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>41.8</v>
+        <v>40.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.8</v>
+        <v>21.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,49 +1550,49 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.73</v>
+        <v>9.17</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.36</v>
+        <v>3.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.36</v>
+        <v>3.92</v>
       </c>
       <c r="BR2" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.27</v>
+        <v>3.09</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.63</v>
+        <v>3.39</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CB2" t="n">
         <v>3.02</v>
@@ -1622,52 +1622,52 @@
         <v>4.94</v>
       </c>
       <c r="CE2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CO2" t="n">
         <v>1.63</v>
       </c>
-      <c r="CF2" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.62</v>
-      </c>
       <c r="CP2" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="CQ2" t="n">
-        <v>5.79</v>
+        <v>5.92</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CS2" t="n">
         <v>3.35</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CU2" t="n">
         <v>1.31</v>
@@ -1691,88 +1691,88 @@
         <v>1.6</v>
       </c>
       <c r="DB2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>87.92</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO2" t="n">
         <v>1.67</v>
       </c>
-      <c r="DC2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>86.81999999999999</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1.91</v>
-      </c>
       <c r="DP2" t="n">
-        <v>14.45</v>
+        <v>14.58</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.09</v>
+        <v>46.83</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.18</v>
+        <v>11.08</v>
       </c>
       <c r="DY2" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.73</v>
+        <v>22.67</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="3">
@@ -1905,10 +1905,10 @@
         <v>2.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>15.25</v>
       </c>
       <c r="AS3" t="n">
         <v>8.25</v>
@@ -2136,10 +2136,10 @@
         <v>1.91</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.36</v>
+        <v>10.18</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.82</v>
+        <v>13.73</v>
       </c>
       <c r="DR3" t="n">
         <v>6.73</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,127 +2278,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>90.8</v>
+        <v>88.33</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.6</v>
+        <v>55.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.6</v>
+        <v>11.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>8.17</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>49.8</v>
+        <v>47</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BD4" t="n">
-        <v>24.2</v>
+        <v>22</v>
       </c>
       <c r="BE4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1.25</v>
       </c>
-      <c r="BF4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BP4" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.82</v>
+        <v>4.25</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
         <v>2.29</v>
@@ -2416,49 +2416,49 @@
         <v>2.38</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.71</v>
+        <v>4.06</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.17</v>
+        <v>4.39</v>
       </c>
       <c r="CE4" t="n">
         <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CK4" t="n">
         <v>1.7</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CP4" t="n">
         <v>2.51</v>
@@ -2473,7 +2473,7 @@
         <v>3.33</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CU4" t="n">
         <v>1.31</v>
@@ -2488,7 +2488,7 @@
         <v>1.77</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.05</v>
@@ -2500,85 +2500,85 @@
         <v>1.54</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.38</v>
+        <v>5.34</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="DH4" t="n">
-        <v>83.73</v>
+        <v>83.08</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.82</v>
+        <v>60.5</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.27</v>
+        <v>12.25</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.91</v>
+        <v>12.84</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.64</v>
+        <v>8.08</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.45</v>
+        <v>49</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.37</v>
+        <v>13.58</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.64</v>
+        <v>23.5</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5091,49 +5091,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>55.2</v>
+        <v>52.33</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.4</v>
+        <v>8.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5145,67 +5145,67 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>32.4</v>
+        <v>31.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.2</v>
+        <v>16.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="BR11" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5220,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BY11" t="n">
         <v>2.38</v>
@@ -5229,62 +5229,62 @@
         <v>2.47</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.79</v>
+        <v>4.89</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CF11" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CI11" t="n">
         <v>1.45</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CN11" t="n">
         <v>1.54</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="CQ11" t="n">
-        <v>7.05</v>
+        <v>6.94</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CS11" t="inlineStr"/>
       <c r="CT11" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="n">
@@ -5294,67 +5294,67 @@
         <v>2.88</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.73</v>
+        <v>3.66</v>
       </c>
       <c r="DD11" t="n">
-        <v>7.02</v>
+        <v>6.9</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DH11" t="n">
-        <v>90.91</v>
+        <v>89.5</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.09</v>
+        <v>3.75</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM11" t="n">
-        <v>60.55</v>
+        <v>58.66</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.18</v>
+        <v>17.16</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.359999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>40.73</v>
+        <v>39.58</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.18</v>
+        <v>10</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.91</v>
+        <v>6.58</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.37</v>
+        <v>21.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="12">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5490,136 +5490,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>85.8</v>
+        <v>86.17</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3</v>
       </c>
-      <c r="AL12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BG12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.640000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BR12" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BU12" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BY12" t="n">
         <v>2.08</v>
@@ -5628,55 +5628,55 @@
         <v>2.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CB12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.6</v>
+        <v>4.72</v>
       </c>
       <c r="CR12" t="n">
         <v>1.63</v>
@@ -5696,7 +5696,7 @@
         <v>1.76</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.06</v>
@@ -5705,55 +5705,55 @@
         <v>1.65</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.34</v>
+        <v>6.46</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.09</v>
+        <v>89.92</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.73</v>
+        <v>51.66</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.37</v>
+        <v>10.75</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.09</v>
+        <v>6.75</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5765,28 +5765,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.91</v>
+        <v>54.75</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.82</v>
+        <v>8.75</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="EA12" t="n">
-        <v>17</v>
+        <v>16.67</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="13">
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5889,127 +5889,127 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AH13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>90.86</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG13" t="n">
         <v>1.67</v>
       </c>
-      <c r="AI13" t="n">
-        <v>87.67</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AL13" t="n">
+      <c r="BH13" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>4.17</v>
       </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>47</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.64</v>
-      </c>
       <c r="BR13" t="n">
-        <v>90.91</v>
+        <v>83.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6018,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BY13" t="n">
         <v>4.56</v>
@@ -6027,25 +6027,25 @@
         <v>5.26</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.42</v>
+        <v>5.21</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.18</v>
+        <v>5.88</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CH13" t="n">
         <v>1.21</v>
@@ -6054,13 +6054,13 @@
         <v>1.5</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CK13" t="n">
         <v>1.89</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CM13" t="n">
         <v>1.89</v>
@@ -6069,20 +6069,20 @@
         <v>1.53</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.68</v>
+        <v>5.81</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CS13" t="inlineStr"/>
       <c r="CT13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
@@ -6104,13 +6104,13 @@
         <v>1.55</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.04</v>
+        <v>6.16</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6119,40 +6119,40 @@
         <v>2</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="DH13" t="n">
-        <v>83</v>
+        <v>85.25</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.37</v>
+        <v>4.75</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="DM13" t="n">
-        <v>52.27</v>
+        <v>54.59</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.54</v>
+        <v>10.59</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.73</v>
+        <v>12.08</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6164,28 +6164,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.36</v>
+        <v>46.25</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.36</v>
+        <v>10.42</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.55</v>
+        <v>23</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="14">
@@ -6598,62 +6598,62 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
-        <v>100.8</v>
+        <v>99</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>10.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.8</v>
+        <v>12.67</v>
       </c>
       <c r="R15" t="n">
-        <v>7.8</v>
+        <v>8.17</v>
       </c>
       <c r="S15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
-        <v>0.6</v>
-      </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
@@ -6664,28 +6664,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50.4</v>
+        <v>49.33</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>14.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
+        <v>4.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>25.4</v>
+        <v>24.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6769,67 +6769,67 @@
         <v>2.67</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.449999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BT15" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.13</v>
+        <v>3.24</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.65</v>
+        <v>3.77</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CB15" t="n">
         <v>3.01</v>
@@ -6844,10 +6844,10 @@
         <v>1.66</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CH15" t="n">
         <v>1.19</v>
@@ -6862,22 +6862,22 @@
         <v>1.79</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN15" t="n">
         <v>1.59</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CQ15" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="CR15" t="n">
         <v>1.68</v>
@@ -6904,61 +6904,61 @@
         <v>2.3</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DA15" t="n">
         <v>1.6</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="DD15" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="DH15" t="n">
-        <v>87.45</v>
+        <v>87.66</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DM15" t="n">
-        <v>41.91</v>
+        <v>42.92</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.64</v>
+        <v>10.75</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.91</v>
+        <v>12.84</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.550000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6970,28 +6970,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.46</v>
+        <v>43.5</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.55</v>
+        <v>11</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.37</v>
+        <v>20.25</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="16">
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
@@ -7412,82 +7412,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="H17" t="n">
-        <v>93.83</v>
+        <v>92.86</v>
       </c>
       <c r="I17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J17" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="K17" t="n">
-        <v>7.33</v>
+        <v>7.14</v>
       </c>
       <c r="L17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>44</v>
+        <v>46.86</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O17" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="P17" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>13.29</v>
       </c>
       <c r="R17" t="n">
-        <v>4.83</v>
+        <v>5.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T17" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>54.5</v>
+        <v>53.86</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.67</v>
+        <v>15.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.83</v>
+        <v>10.86</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>25.83</v>
+        <v>25.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7571,70 +7571,70 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>90.91</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CC17" t="n">
         <v>2.6</v>
@@ -7646,40 +7646,40 @@
         <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="CI17" t="n">
         <v>1.6</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CK17" t="n">
         <v>1.62</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="CR17" t="n">
         <v>1.63</v>
@@ -7696,100 +7696,100 @@
         <v>2.42</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CZ17" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DB17" t="n">
         <v>1.62</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="DD17" t="n">
-        <v>6.15</v>
+        <v>6.07</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DH17" t="n">
-        <v>93.18000000000001</v>
+        <v>92.67</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.73</v>
+        <v>51.84</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO17" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.55</v>
+        <v>10.42</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.27</v>
+        <v>13.42</v>
       </c>
       <c r="DR17" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55</v>
+        <v>54.58</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.91</v>
+        <v>13.42</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.539999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="EA17" t="n">
-        <v>24.73</v>
+        <v>24.83</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="18">
@@ -7946,7 +7946,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.08</v>
+        <v>45.25</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
@@ -8643,7 +8643,7 @@
         <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
         <v>9.199999999999999</v>
@@ -8951,7 +8951,7 @@
         <v>1.67</v>
       </c>
       <c r="DP20" t="n">
-        <v>11</v>
+        <v>11.16</v>
       </c>
       <c r="DQ20" t="n">
         <v>10.75</v>
@@ -9522,7 +9522,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.14</v>
+        <v>10.57</v>
       </c>
       <c r="AR22" t="n">
         <v>11.29</v>
@@ -9749,7 +9749,7 @@
         <v>1.33</v>
       </c>
       <c r="DP22" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="DQ22" t="n">
         <v>11.09</v>
@@ -9798,13 +9798,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -9891,127 +9891,127 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ23" t="n">
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN23" t="n">
-        <v>43.57</v>
+        <v>45.25</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.140000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>58.14</v>
+        <v>57.12</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.859999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.14</v>
+        <v>6.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="BD23" t="n">
-        <v>22</v>
+        <v>22.25</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BF23" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BH23" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO23" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="BR23" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS23" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT23" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU23" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY23" t="n">
         <v>2</v>
@@ -10029,25 +10029,25 @@
         <v>2.09</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC23" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="CD23" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="CE23" t="n">
         <v>1.53</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CH23" t="n">
         <v>1.26</v>
@@ -10059,7 +10059,7 @@
         <v>2.09</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL23" t="n">
         <v>2.42</v>
@@ -10071,7 +10071,7 @@
         <v>1.61</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CP23" t="n">
         <v>2.5</v>
@@ -10101,97 +10101,97 @@
         <v>1.78</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DD23" t="n">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
       <c r="DE23" t="n">
         <v>0</v>
       </c>
       <c r="DF23" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="DH23" t="n">
-        <v>95.64</v>
+        <v>95.08</v>
       </c>
       <c r="DI23" t="n">
         <v>0</v>
       </c>
       <c r="DJ23" t="n">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="DK23" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM23" t="n">
-        <v>51.18</v>
+        <v>51.67</v>
       </c>
       <c r="DN23" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="DP23" t="n">
-        <v>13.64</v>
+        <v>13.75</v>
       </c>
       <c r="DQ23" t="n">
-        <v>10.36</v>
+        <v>10.17</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.73</v>
+        <v>7.41</v>
       </c>
       <c r="DS23" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT23" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU23" t="n">
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>57.73</v>
+        <v>57.08</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX23" t="n">
-        <v>12.64</v>
+        <v>12.42</v>
       </c>
       <c r="DY23" t="n">
-        <v>8.73</v>
+        <v>8.75</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
       <c r="EA23" t="n">
-        <v>22.36</v>
+        <v>22.5</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC23" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="24">
@@ -10604,10 +10604,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -10619,79 +10619,79 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="H25" t="n">
-        <v>111.8</v>
+        <v>109.17</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M25" t="n">
-        <v>75.2</v>
+        <v>71.67</v>
       </c>
       <c r="N25" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="O25" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P25" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>14.4</v>
+        <v>13.83</v>
       </c>
       <c r="R25" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>57.8</v>
+        <v>59.33</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="AB25" t="n">
-        <v>5.8</v>
+        <v>6.17</v>
       </c>
       <c r="AC25" t="n">
-        <v>18.4</v>
+        <v>17.83</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AF25" t="n">
         <v>0.17</v>
@@ -10775,46 +10775,46 @@
         <v>2.33</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BH25" t="n">
-        <v>7.91</v>
+        <v>8.17</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN25" t="n">
         <v>1</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BP25" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.18</v>
+        <v>4.58</v>
       </c>
       <c r="BR25" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS25" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT25" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
@@ -10826,19 +10826,19 @@
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CB25" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CC25" t="n">
         <v>2.88</v>
@@ -10850,25 +10850,25 @@
         <v>1.56</v>
       </c>
       <c r="CF25" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CG25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CH25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI25" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CJ25" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CK25" t="n">
         <v>1.77</v>
       </c>
       <c r="CL25" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CM25" t="n">
         <v>1.95</v>
@@ -10877,13 +10877,13 @@
         <v>1.57</v>
       </c>
       <c r="CO25" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CP25" t="n">
         <v>2.6</v>
       </c>
       <c r="CQ25" t="n">
-        <v>5.12</v>
+        <v>5.09</v>
       </c>
       <c r="CR25" t="n">
         <v>1.58</v>
@@ -10892,7 +10892,7 @@
         <v>3.38</v>
       </c>
       <c r="CT25" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CU25" t="n">
         <v>1.33</v>
@@ -10904,7 +10904,7 @@
         <v>2.35</v>
       </c>
       <c r="CX25" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY25" t="n">
         <v>2.34</v>
@@ -10919,85 +10919,85 @@
         <v>1.56</v>
       </c>
       <c r="DC25" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="DD25" t="n">
-        <v>5.61</v>
+        <v>5.55</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF25" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DG25" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="DH25" t="n">
-        <v>98.37</v>
+        <v>98.17</v>
       </c>
       <c r="DI25" t="n">
         <v>0</v>
       </c>
       <c r="DJ25" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DK25" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="DL25" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM25" t="n">
-        <v>62.27</v>
+        <v>61.58</v>
       </c>
       <c r="DN25" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="DO25" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DP25" t="n">
-        <v>9.18</v>
+        <v>9.42</v>
       </c>
       <c r="DQ25" t="n">
-        <v>15.55</v>
+        <v>15.16</v>
       </c>
       <c r="DR25" t="n">
-        <v>6.64</v>
+        <v>6.58</v>
       </c>
       <c r="DS25" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT25" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU25" t="n">
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>55.55</v>
+        <v>56.5</v>
       </c>
       <c r="DW25" t="n">
         <v>0</v>
       </c>
       <c r="DX25" t="n">
-        <v>12.82</v>
+        <v>13.25</v>
       </c>
       <c r="DY25" t="n">
-        <v>8.18</v>
+        <v>8.33</v>
       </c>
       <c r="DZ25" t="n">
-        <v>4.64</v>
+        <v>4.92</v>
       </c>
       <c r="EA25" t="n">
-        <v>19.45</v>
+        <v>19.08</v>
       </c>
       <c r="EB25" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="EC25" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="26">
@@ -11007,94 +11007,94 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="G26" t="n">
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>87.8</v>
+        <v>88.5</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M26" t="n">
-        <v>59.4</v>
+        <v>57</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P26" t="n">
-        <v>10.2</v>
+        <v>10.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="R26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S26" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>54.6</v>
+        <v>51.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>12.8</v>
+        <v>12.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="AB26" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="AC26" t="n">
-        <v>22</v>
+        <v>20.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -11178,64 +11178,64 @@
         <v>2.83</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BH26" t="n">
-        <v>8.73</v>
+        <v>8.58</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL26" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN26" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BP26" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="BR26" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS26" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BT26" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BU26" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV26" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW26" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX26" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY26" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BZ26" t="n">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="CA26" t="n">
         <v>2.76</v>
@@ -11250,13 +11250,13 @@
         <v>4.28</v>
       </c>
       <c r="CE26" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CF26" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="CG26" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CH26" t="n">
         <v>1.17</v>
@@ -11265,28 +11265,28 @@
         <v>1.45</v>
       </c>
       <c r="CJ26" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CK26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CL26" t="n">
         <v>2.58</v>
       </c>
       <c r="CM26" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CN26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CO26" t="n">
         <v>1.73</v>
       </c>
       <c r="CP26" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CQ26" t="n">
-        <v>6.98</v>
+        <v>6.9</v>
       </c>
       <c r="CR26" t="n">
         <v>1.73</v>
@@ -11303,16 +11303,16 @@
         <v>2.75</v>
       </c>
       <c r="CX26" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CY26" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CZ26" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DA26" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DB26" t="n">
         <v>1.78</v>
@@ -11321,82 +11321,82 @@
         <v>3.43</v>
       </c>
       <c r="DD26" t="n">
-        <v>7.09</v>
+        <v>7.15</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="DG26" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DH26" t="n">
-        <v>86.37</v>
+        <v>86.84</v>
       </c>
       <c r="DI26" t="n">
         <v>0</v>
       </c>
       <c r="DJ26" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="DK26" t="n">
         <v>4</v>
       </c>
       <c r="DL26" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM26" t="n">
-        <v>47.63</v>
+        <v>47.42</v>
       </c>
       <c r="DN26" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="DO26" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DP26" t="n">
-        <v>12.27</v>
+        <v>12.42</v>
       </c>
       <c r="DQ26" t="n">
-        <v>12.45</v>
+        <v>12.34</v>
       </c>
       <c r="DR26" t="n">
-        <v>8.630000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="DS26" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU26" t="n">
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>50.09</v>
+        <v>48.92</v>
       </c>
       <c r="DW26" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX26" t="n">
-        <v>9.539999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="DY26" t="n">
-        <v>6.55</v>
+        <v>6.42</v>
       </c>
       <c r="DZ26" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="EA26" t="n">
-        <v>22.73</v>
+        <v>21.83</v>
       </c>
       <c r="EB26" t="n">
         <v>1.17</v>
       </c>
       <c r="EC26" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="27">
@@ -12246,7 +12246,7 @@
         <v>2.29</v>
       </c>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>12.57</v>
       </c>
       <c r="Q29" t="n">
         <v>14.43</v>
@@ -12270,7 +12270,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>43.86</v>
+        <v>43.57</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -12554,7 +12554,7 @@
         <v>1.92</v>
       </c>
       <c r="DP29" t="n">
-        <v>11.08</v>
+        <v>11.42</v>
       </c>
       <c r="DQ29" t="n">
         <v>13.92</v>
@@ -12572,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>46.25</v>
+        <v>46.08</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
@@ -12603,94 +12603,94 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>93.59999999999999</v>
+        <v>98.17</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="M30" t="n">
-        <v>57.6</v>
+        <v>62</v>
       </c>
       <c r="N30" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O30" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>9.6</v>
+        <v>9.67</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.199999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="R30" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="T30" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>50</v>
+        <v>53.83</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.6</v>
+        <v>19.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>13.6</v>
+        <v>14.17</v>
       </c>
       <c r="AB30" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>23.2</v>
+        <v>22.17</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF30" t="n">
         <v>0.17</v>
@@ -12774,70 +12774,70 @@
         <v>1.67</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>7.82</v>
+        <v>7.92</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL30" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BN30" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BO30" t="n">
         <v>1</v>
       </c>
       <c r="BP30" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="BQ30" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="BR30" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS30" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT30" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU30" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV30" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW30" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX30" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY30" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="BZ30" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="CA30" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CC30" t="n">
         <v>3.04</v>
@@ -12849,28 +12849,28 @@
         <v>1.62</v>
       </c>
       <c r="CF30" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CG30" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CH30" t="n">
         <v>1.22</v>
       </c>
       <c r="CI30" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CJ30" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CK30" t="n">
         <v>1.82</v>
       </c>
       <c r="CL30" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CM30" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN30" t="n">
         <v>1.55</v>
@@ -12882,7 +12882,7 @@
         <v>2.79</v>
       </c>
       <c r="CQ30" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="CR30" t="n">
         <v>1.64</v>
@@ -12899,100 +12899,100 @@
         <v>2.42</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CY30" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CZ30" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DA30" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB30" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DC30" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="DD30" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF30" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="DG30" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="DH30" t="n">
-        <v>91.09</v>
+        <v>93.58</v>
       </c>
       <c r="DI30" t="n">
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DL30" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="DM30" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="DN30" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DO30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DP30" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="DQ30" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="DR30" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="DS30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV30" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="DW30" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DX30" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="DY30" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="DZ30" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="EA30" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="EB30" t="n">
         <v>1.82</v>
       </c>
-      <c r="DK30" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="DL30" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DM30" t="n">
-        <v>52.18</v>
-      </c>
-      <c r="DN30" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DP30" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="DQ30" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="DR30" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="DS30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DT30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV30" t="n">
-        <v>47.45</v>
-      </c>
-      <c r="DW30" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DX30" t="n">
-        <v>15.91</v>
-      </c>
-      <c r="DY30" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="DZ30" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="EA30" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="EB30" t="n">
-        <v>1.72</v>
-      </c>
       <c r="EC30" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="31">
@@ -13002,13 +13002,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C31" t="n">
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
         <v>0.2</v>
@@ -13092,139 +13092,139 @@
         <v>0.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI31" t="n">
-        <v>86.67</v>
+        <v>87.86</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK31" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AL31" t="n">
-        <v>3.83</v>
+        <v>3.29</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN31" t="n">
-        <v>47.83</v>
+        <v>46.71</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP31" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ31" t="n">
-        <v>10.5</v>
+        <v>10.71</v>
       </c>
       <c r="AR31" t="n">
         <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BL31" t="n">
         <v>0.5</v>
       </c>
-      <c r="AU31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>52.67</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>0.36</v>
-      </c>
       <c r="BM31" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN31" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="BP31" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BR31" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS31" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT31" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW31" t="n">
         <v>0</v>
       </c>
       <c r="BX31" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY31" t="n">
         <v>2.49</v>
@@ -13233,16 +13233,16 @@
         <v>2.63</v>
       </c>
       <c r="CA31" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CC31" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="CD31" t="n">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="CE31" t="n">
         <v>1.63</v>
@@ -13251,13 +13251,13 @@
         <v>3.79</v>
       </c>
       <c r="CG31" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CH31" t="n">
         <v>1.21</v>
       </c>
       <c r="CI31" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CJ31" t="n">
         <v>2.27</v>
@@ -13266,7 +13266,7 @@
         <v>1.75</v>
       </c>
       <c r="CL31" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CM31" t="n">
         <v>2.01</v>
@@ -13278,10 +13278,10 @@
         <v>1.6</v>
       </c>
       <c r="CP31" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CQ31" t="n">
-        <v>5.88</v>
+        <v>5.87</v>
       </c>
       <c r="CR31" t="n">
         <v>1.65</v>
@@ -13313,85 +13313,85 @@
         <v>1.67</v>
       </c>
       <c r="DC31" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DD31" t="n">
         <v>6.55</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DG31" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="DH31" t="n">
-        <v>94.55</v>
+        <v>94.58</v>
       </c>
       <c r="DI31" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ31" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DK31" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM31" t="n">
-        <v>51.18</v>
+        <v>50.25</v>
       </c>
       <c r="DN31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="DP31" t="n">
-        <v>10.09</v>
+        <v>10.25</v>
       </c>
       <c r="DQ31" t="n">
-        <v>13</v>
+        <v>12.92</v>
       </c>
       <c r="DR31" t="n">
-        <v>7.27</v>
+        <v>7.42</v>
       </c>
       <c r="DS31" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT31" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU31" t="n">
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>53.27</v>
+        <v>53.5</v>
       </c>
       <c r="DW31" t="n">
         <v>0</v>
       </c>
       <c r="DX31" t="n">
-        <v>10.82</v>
+        <v>10.83</v>
       </c>
       <c r="DY31" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="DZ31" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="EA31" t="n">
-        <v>19.55</v>
+        <v>19.08</v>
       </c>
       <c r="EB31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC31" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1406,7 +1406,7 @@
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>40.33</v>
+        <v>40.67</v>
       </c>
       <c r="Y2" t="n">
         <v>0.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="AB2" t="n">
         <v>3.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.83</v>
+        <v>23.17</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
         <v>3.33</v>
@@ -1553,7 +1553,7 @@
         <v>1.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.17</v>
+        <v>9.33</v>
       </c>
       <c r="BI2" t="n">
         <v>1.33</v>
@@ -1718,7 +1718,7 @@
         <v>2.92</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
       <c r="DL2" t="n">
         <v>0.16</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.83</v>
+        <v>47</v>
       </c>
       <c r="DW2" t="n">
         <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.08</v>
+        <v>11.16</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.83</v>
+        <v>8.92</v>
       </c>
       <c r="DZ2" t="n">
         <v>2.25</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.67</v>
+        <v>23.33</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC2" t="n">
         <v>2.66</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>109.86</v>
+        <v>109.62</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.43</v>
+        <v>5.88</v>
       </c>
       <c r="L3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>74.43000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="N3" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>8.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.86</v>
+        <v>12.5</v>
       </c>
       <c r="R3" t="n">
-        <v>5.86</v>
+        <v>6.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="U3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>63</v>
+        <v>63.5</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.71</v>
+        <v>17.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.86</v>
+        <v>11.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.86</v>
+        <v>20.25</v>
       </c>
       <c r="AD3" t="n">
         <v>2.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.36</v>
+        <v>7.58</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="BR3" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS3" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BT3" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="CC3" t="n">
         <v>2.38</v>
@@ -2025,16 +2025,16 @@
         <v>2.41</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI3" t="n">
         <v>1.56</v>
@@ -2046,34 +2046,34 @@
         <v>1.84</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CM3" t="n">
         <v>1.92</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CQ3" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CV3" t="n">
         <v>1.58</v>
@@ -2082,25 +2082,25 @@
         <v>2.49</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CY3" t="n">
         <v>2.4</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DA3" t="n">
         <v>1.56</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2109,73 +2109,73 @@
         <v>1.09</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>104.37</v>
+        <v>104.66</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.36</v>
+        <v>5.67</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM3" t="n">
-        <v>67.27</v>
+        <v>67.33</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.18</v>
+        <v>10.08</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.73</v>
+        <v>13.42</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.73</v>
+        <v>6.92</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>64.09</v>
+        <v>64.33</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.72</v>
+        <v>14.91</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.18</v>
+        <v>5.33</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.18</v>
+        <v>19.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="4">
@@ -2338,10 +2338,10 @@
         <v>0.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>11.17</v>
       </c>
       <c r="BB4" t="n">
-        <v>8</v>
+        <v>8.17</v>
       </c>
       <c r="BC4" t="n">
         <v>3</v>
@@ -2350,7 +2350,7 @@
         <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BF4" t="n">
         <v>3.5</v>
@@ -2563,10 +2563,10 @@
         <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.58</v>
+        <v>13.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.83</v>
+        <v>9.92</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.75</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>84</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>42.25</v>
+        <v>42.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.75</v>
+        <v>12.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.25</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>0.5</v>
       </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>35</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BP5" t="n">
         <v>4.75</v>
       </c>
-      <c r="BC5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>4.91</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>3.91</v>
+        <v>4.17</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>2.56</v>
@@ -2819,28 +2819,28 @@
         <v>2.73</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.92</v>
+        <v>5.13</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI5" t="n">
         <v>1.63</v>
@@ -2849,10 +2849,10 @@
         <v>2.2</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CM5" t="n">
         <v>1.97</v>
@@ -2861,22 +2861,22 @@
         <v>1.58</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CQ5" t="n">
-        <v>5.01</v>
+        <v>4.96</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CU5" t="n">
         <v>1.33</v>
@@ -2888,67 +2888,67 @@
         <v>2.32</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.64</v>
+        <v>5.54</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="DH5" t="n">
-        <v>84.27</v>
+        <v>84</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.27</v>
+        <v>47</v>
       </c>
       <c r="DN5" t="n">
         <v>1.09</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.54</v>
+        <v>10.5</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.64</v>
+        <v>12.33</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.27</v>
+        <v>9.08</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>40.73</v>
+        <v>40.08</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.64</v>
+        <v>11.42</v>
       </c>
       <c r="DY5" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="EA5" t="n">
-        <v>23.46</v>
+        <v>22.33</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,127 +3487,127 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM7" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>89</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>46.83</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.73</v>
-      </c>
       <c r="BN7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BR7" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>2.13</v>
@@ -3625,25 +3625,25 @@
         <v>2.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.69</v>
+        <v>3.95</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CH7" t="n">
         <v>1.24</v>
@@ -3655,34 +3655,34 @@
         <v>2.17</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CM7" t="n">
         <v>2.02</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CU7" t="n">
         <v>1.32</v>
@@ -3694,67 +3694,67 @@
         <v>2.37</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.6</v>
+        <v>5.46</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DH7" t="n">
-        <v>91.91</v>
+        <v>89.75</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DK7" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM7" t="n">
-        <v>53</v>
+        <v>51.5</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DP7" t="n">
         <v>10</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.18</v>
+        <v>10.58</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.27</v>
+        <v>8.75</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.82</v>
+        <v>48.42</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.09</v>
+        <v>7.92</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="EA7" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="8">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>52.8</v>
+        <v>51.33</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.6</v>
+        <v>11.33</v>
       </c>
       <c r="R9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49.2</v>
+        <v>47.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.4</v>
+        <v>9.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.8</v>
+        <v>7.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,67 +4371,67 @@
         <v>3.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.82</v>
+        <v>8.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.73</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BR9" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.07</v>
+        <v>2.91</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CB9" t="n">
         <v>3.05</v>
@@ -4446,10 +4446,10 @@
         <v>1.64</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CH9" t="n">
         <v>1.21</v>
@@ -4458,19 +4458,19 @@
         <v>1.56</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CM9" t="n">
         <v>1.93</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO9" t="n">
         <v>1.6</v>
@@ -4479,14 +4479,14 @@
         <v>2.78</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5.9</v>
+        <v>5.89</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
@@ -4496,100 +4496,100 @@
         <v>2.58</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DC9" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="DD9" t="n">
-        <v>6.27</v>
+        <v>6.22</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>87.36</v>
+        <v>84.75</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM9" t="n">
-        <v>48.82</v>
+        <v>48.42</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.27</v>
+        <v>12.58</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.64</v>
+        <v>12.42</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.37</v>
+        <v>10.08</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.27</v>
+        <v>44.66</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.82</v>
+        <v>5.67</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.09</v>
+        <v>18.08</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>67</v>
+        <v>69.33</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>39.6</v>
+        <v>41.33</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.2</v>
+        <v>0.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.2</v>
+        <v>13.17</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48.4</v>
+        <v>50.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="BD10" t="n">
-        <v>22.2</v>
+        <v>22.67</v>
       </c>
       <c r="BE10" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.82</v>
+        <v>8</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.18</v>
+        <v>3.75</v>
       </c>
       <c r="BR10" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS10" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
         <v>2.86</v>
@@ -4830,25 +4830,25 @@
         <v>2.97</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CH10" t="n">
         <v>1.23</v>
@@ -4857,13 +4857,13 @@
         <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CM10" t="n">
         <v>1.94</v>
@@ -4875,10 +4875,10 @@
         <v>1.53</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CQ10" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="CR10" t="n">
         <v>1.66</v>
@@ -4895,100 +4895,100 @@
         <v>2.36</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.06</v>
+        <v>5.99</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="DH10" t="n">
-        <v>75.18000000000001</v>
+        <v>75.67</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>45</v>
+        <v>45.42</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="DP10" t="n">
-        <v>8.91</v>
+        <v>8.75</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.18</v>
+        <v>11.34</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.55</v>
+        <v>49.58</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.46</v>
+        <v>5.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.82</v>
+        <v>20.25</v>
       </c>
       <c r="EB10" t="n">
         <v>1.2</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="11">
@@ -5127,7 +5127,7 @@
         <v>8.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.67</v>
+        <v>9.83</v>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
@@ -5145,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>31.5</v>
+        <v>31.67</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.17</v>
@@ -5354,7 +5354,7 @@
         <v>9.75</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.75</v>
+        <v>8.83</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>39.58</v>
+        <v>39.67</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
@@ -5523,7 +5523,7 @@
         <v>11.83</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.17</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
         <v>7.67</v>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>56.67</v>
+        <v>55.33</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.33</v>
@@ -5750,7 +5750,7 @@
         <v>10.75</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.75</v>
+        <v>12.16</v>
       </c>
       <c r="DR12" t="n">
         <v>6.75</v>
@@ -5765,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54.75</v>
+        <v>54.08</v>
       </c>
       <c r="DW12" t="n">
         <v>0.16</v>
@@ -5904,7 +5904,7 @@
         <v>2.57</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
         <v>-0.14</v>
@@ -5925,7 +5925,7 @@
         <v>13.57</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.43</v>
+        <v>7.57</v>
       </c>
       <c r="AT13" t="n">
         <v>1.86</v>
@@ -5943,25 +5943,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.86</v>
+        <v>49.57</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.140000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>7.29</v>
       </c>
       <c r="BC13" t="n">
         <v>2.14</v>
       </c>
       <c r="BD13" t="n">
-        <v>24.29</v>
+        <v>24.43</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BF13" t="n">
         <v>2.57</v>
@@ -5970,7 +5970,7 @@
         <v>1.67</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="BI13" t="n">
         <v>1.67</v>
@@ -6131,7 +6131,7 @@
         <v>2.42</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.75</v>
+        <v>4.83</v>
       </c>
       <c r="DL13" t="n">
         <v>0.08</v>
@@ -6152,7 +6152,7 @@
         <v>12.08</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.75</v>
+        <v>7.83</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6164,25 +6164,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.25</v>
+        <v>46.08</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.42</v>
+        <v>10.58</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="DZ13" t="n">
         <v>2.08</v>
       </c>
       <c r="EA13" t="n">
-        <v>23</v>
+        <v>23.08</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC13" t="n">
         <v>2.42</v>
@@ -6195,94 +6195,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="H14" t="n">
-        <v>69.40000000000001</v>
+        <v>70.17</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M14" t="n">
-        <v>42.4</v>
+        <v>48.67</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>12.8</v>
+        <v>11.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>15.67</v>
       </c>
       <c r="R14" t="n">
-        <v>10.2</v>
+        <v>9</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.8</v>
+        <v>13.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.4</v>
+        <v>8.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6366,70 +6366,70 @@
         <v>3.67</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.09</v>
+        <v>9.42</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.91</v>
+        <v>5.08</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CC14" t="n">
         <v>4</v>
@@ -6441,16 +6441,16 @@
         <v>1.6</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CJ14" t="n">
         <v>2.21</v>
@@ -6459,31 +6459,31 @@
         <v>1.68</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN14" t="n">
         <v>1.66</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CQ14" t="n">
-        <v>5.11</v>
+        <v>5.17</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CS14" t="n">
         <v>3.42</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CU14" t="n">
         <v>1.32</v>
@@ -6498,97 +6498,97 @@
         <v>1.71</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DA14" t="n">
         <v>1.7</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="DD14" t="n">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="DH14" t="n">
-        <v>79.55</v>
+        <v>79.08</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.91</v>
+        <v>4.25</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.18</v>
+        <v>43.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.64</v>
+        <v>12.08</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.36</v>
+        <v>13.84</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.46</v>
+        <v>9.83</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>45.64</v>
+        <v>47.34</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.640000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.09</v>
+        <v>7.25</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.73</v>
+        <v>17.92</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -7001,13 +7001,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7094,127 +7094,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AI16" t="n">
-        <v>83.40000000000001</v>
+        <v>81.17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>40.8</v>
+        <v>41.33</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>13.17</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.4</v>
+        <v>12.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>57.4</v>
+        <v>53.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.2</v>
+        <v>10.17</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="BD16" t="n">
-        <v>22.8</v>
+        <v>21.17</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.27</v>
+        <v>8.67</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.09</v>
+        <v>4.25</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="BR16" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS16" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY16" t="n">
         <v>2.36</v>
@@ -7238,56 +7238,56 @@
         <v>2.8</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CF16" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CH16" t="n">
         <v>1.17</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CP16" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.62</v>
+        <v>6.55</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CS16" t="inlineStr"/>
       <c r="CT16" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CU16" t="inlineStr"/>
       <c r="CV16" t="n">
@@ -7297,100 +7297,100 @@
         <v>2.75</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CZ16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DC16" t="n">
-        <v>3.48</v>
+        <v>3.43</v>
       </c>
       <c r="DD16" t="n">
-        <v>7.18</v>
+        <v>7.08</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="DH16" t="n">
-        <v>86</v>
+        <v>84.67</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.36</v>
+        <v>46.16</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.55</v>
+        <v>12.17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.55</v>
+        <v>13.84</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.09</v>
+        <v>9</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>55.55</v>
+        <v>53.75</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.55</v>
+        <v>11.42</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.09</v>
+        <v>19.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="17">
@@ -7946,7 +7946,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.25</v>
+        <v>45.08</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
@@ -8202,94 +8202,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="H19" t="n">
-        <v>86.83</v>
+        <v>84.86</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="K19" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="L19" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="M19" t="n">
-        <v>50.17</v>
+        <v>48.71</v>
       </c>
       <c r="N19" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O19" t="n">
-        <v>1.17</v>
+        <v>0.86</v>
       </c>
       <c r="P19" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.17</v>
+        <v>13.14</v>
       </c>
       <c r="R19" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="S19" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>51</v>
+        <v>49.29</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.5</v>
+        <v>11.86</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.17</v>
+        <v>8.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.83</v>
+        <v>19.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8373,49 +8373,49 @@
         <v>2.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BH19" t="n">
-        <v>8</v>
+        <v>8.17</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.73</v>
+        <v>3.33</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8424,19 +8424,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="CA19" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CC19" t="n">
         <v>3.65</v>
@@ -8448,10 +8448,10 @@
         <v>1.63</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CH19" t="n">
         <v>1.21</v>
@@ -8460,13 +8460,13 @@
         <v>1.58</v>
       </c>
       <c r="CJ19" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CM19" t="n">
         <v>2.01</v>
@@ -8475,13 +8475,13 @@
         <v>1.59</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CQ19" t="n">
-        <v>6.04</v>
+        <v>5.97</v>
       </c>
       <c r="CR19" t="n">
         <v>1.66</v>
@@ -8501,97 +8501,97 @@
         <v>1.82</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CZ19" t="n">
         <v>1.99</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="DD19" t="n">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.46</v>
+        <v>2.17</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.45</v>
+        <v>85.34</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.27</v>
+        <v>47.58</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.55</v>
+        <v>12.58</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.55</v>
+        <v>11.16</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.18</v>
+        <v>12.34</v>
       </c>
       <c r="DY19" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="EA19" t="n">
-        <v>20</v>
+        <v>19.91</v>
       </c>
       <c r="EB19" t="n">
         <v>1.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="20">
@@ -9000,13 +9000,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9090,139 +9090,139 @@
         <v>2.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG21" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>64.83</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>47</v>
+      </c>
+      <c r="AO21" t="n">
         <v>1</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.2</v>
+        <v>11.83</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>40.4</v>
+        <v>44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.2</v>
+        <v>5.67</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.6</v>
+        <v>19.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="BF21" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.359999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT21" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU21" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
         <v>3</v>
@@ -9231,46 +9231,46 @@
         <v>3.44</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CB21" t="n">
         <v>3.13</v>
       </c>
       <c r="CC21" t="n">
-        <v>4.58</v>
+        <v>4.43</v>
       </c>
       <c r="CD21" t="n">
-        <v>5.49</v>
+        <v>5.11</v>
       </c>
       <c r="CE21" t="n">
         <v>1.61</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CH21" t="n">
         <v>1.22</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO21" t="n">
         <v>1.59</v>
@@ -9279,10 +9279,10 @@
         <v>2.7</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CS21" t="inlineStr"/>
       <c r="CT21" t="n">
@@ -9296,100 +9296,100 @@
         <v>2.48</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB21" t="n">
         <v>1.62</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DD21" t="n">
-        <v>6.07</v>
+        <v>6.05</v>
       </c>
       <c r="DE21" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DH21" t="n">
-        <v>77.64</v>
+        <v>78.75</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM21" t="n">
-        <v>53.46</v>
+        <v>53.84</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.36</v>
+        <v>13.08</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.55</v>
+        <v>13.75</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.64</v>
+        <v>6.25</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>43.63</v>
+        <v>45.16</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.55</v>
+        <v>10.75</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.46</v>
+        <v>19.84</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="22">
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
         <v>7</v>
@@ -10213,49 +10213,49 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>115</v>
+        <v>111.2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="K24" t="n">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>40.75</v>
+        <v>42.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O24" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P24" t="n">
-        <v>11.75</v>
+        <v>12.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="R24" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -10267,28 +10267,28 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>71.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>23.25</v>
+        <v>22.6</v>
       </c>
       <c r="AA24" t="n">
         <v>15</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>18.25</v>
+        <v>17.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -10372,70 +10372,70 @@
         <v>3</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BH24" t="n">
         <v>9</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP24" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BR24" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS24" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT24" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU24" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV24" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW24" t="n">
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BZ24" t="n">
         <v>1.59</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="CC24" t="n">
         <v>2.42</v>
@@ -10444,55 +10444,55 @@
         <v>2.57</v>
       </c>
       <c r="CE24" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CF24" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CG24" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CH24" t="n">
         <v>1.26</v>
       </c>
       <c r="CI24" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CJ24" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CK24" t="n">
         <v>1.74</v>
       </c>
       <c r="CL24" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CM24" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN24" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO24" t="n">
         <v>1.45</v>
       </c>
       <c r="CP24" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CQ24" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="CR24" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CS24" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CT24" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CU24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CV24" t="n">
         <v>1.63</v>
@@ -10501,100 +10501,100 @@
         <v>2.38</v>
       </c>
       <c r="CX24" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY24" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ24" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB24" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DC24" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="DD24" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="DE24" t="n">
         <v>0</v>
       </c>
       <c r="DF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>104.33</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DK24" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="DL24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DM24" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="DN24" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DO24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DP24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DQ24" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="DR24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="DS24" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DT24" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV24" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="DW24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DX24" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="DY24" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="DZ24" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="EA24" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="EB24" t="n">
         <v>1.82</v>
       </c>
-      <c r="DG24" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="DH24" t="n">
-        <v>105.09</v>
-      </c>
-      <c r="DI24" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DJ24" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="DK24" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="DL24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DM24" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="DN24" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="DO24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="DP24" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="DQ24" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="DR24" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="DS24" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DT24" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV24" t="n">
-        <v>65.64</v>
-      </c>
-      <c r="DW24" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DX24" t="n">
-        <v>16.54</v>
-      </c>
-      <c r="DY24" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="DZ24" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="EA24" t="n">
-        <v>20.73</v>
-      </c>
-      <c r="EB24" t="n">
-        <v>1.81</v>
-      </c>
       <c r="EC24" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="25">
@@ -11052,10 +11052,10 @@
         <v>10.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>12.67</v>
+        <v>13.33</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>6.83</v>
       </c>
       <c r="S26" t="n">
         <v>1.5</v>
@@ -11073,7 +11073,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>51.5</v>
+        <v>52.83</v>
       </c>
       <c r="Y26" t="n">
         <v>0.17</v>
@@ -11360,10 +11360,10 @@
         <v>12.42</v>
       </c>
       <c r="DQ26" t="n">
-        <v>12.34</v>
+        <v>12.66</v>
       </c>
       <c r="DR26" t="n">
-        <v>8.92</v>
+        <v>8.83</v>
       </c>
       <c r="DS26" t="n">
         <v>0.08</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>48.92</v>
+        <v>49.58</v>
       </c>
       <c r="DW26" t="n">
         <v>0.08</v>
@@ -11880,16 +11880,16 @@
         <v>12.67</v>
       </c>
       <c r="AA28" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AC28" t="n">
         <v>21.17</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE28" t="n">
         <v>2.33</v>
@@ -12182,10 +12182,10 @@
         <v>12.17</v>
       </c>
       <c r="DY28" t="n">
-        <v>8.08</v>
+        <v>8.17</v>
       </c>
       <c r="DZ28" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="EA28" t="n">
         <v>20.58</v>
@@ -12270,7 +12270,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>43.57</v>
+        <v>43.86</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>46.08</v>
+        <v>46.25</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
@@ -12651,7 +12651,7 @@
         <v>10.33</v>
       </c>
       <c r="R30" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="S30" t="n">
         <v>0.17</v>
@@ -12669,7 +12669,7 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>53.83</v>
+        <v>53.67</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -12959,7 +12959,7 @@
         <v>10.66</v>
       </c>
       <c r="DR30" t="n">
-        <v>7.66</v>
+        <v>7.83</v>
       </c>
       <c r="DS30" t="n">
         <v>0.25</v>
@@ -12971,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>49.58</v>
+        <v>49.5</v>
       </c>
       <c r="DW30" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -9153,10 +9153,10 @@
         <v>0.17</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="BC21" t="n">
         <v>2.83</v>
@@ -9165,7 +9165,7 @@
         <v>19.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BF21" t="n">
         <v>1.67</v>
@@ -9374,10 +9374,10 @@
         <v>0.17</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.75</v>
+        <v>10.84</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="DZ21" t="n">
         <v>3.25</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,127 +1472,127 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.67</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN2" t="n">
-        <v>57.5</v>
+        <v>54.57</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.33</v>
+        <v>13.29</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.17</v>
+        <v>10.43</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>53.33</v>
+        <v>50.14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.33</v>
+        <v>10.86</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BP2" t="n">
         <v>3.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="BR2" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BY2" t="n">
         <v>3.09</v>
@@ -1610,55 +1610,55 @@
         <v>3.39</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.65</v>
+        <v>5.14</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.94</v>
+        <v>5.53</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CJ2" t="n">
         <v>2.39</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="CQ2" t="n">
-        <v>5.92</v>
+        <v>5.83</v>
       </c>
       <c r="CR2" t="n">
         <v>1.67</v>
@@ -1679,67 +1679,67 @@
         <v>2.52</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DC2" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.48</v>
+        <v>6.35</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.92</v>
+        <v>86.62</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.42</v>
+        <v>4.23</v>
       </c>
       <c r="DL2" t="n">
         <v>0.16</v>
       </c>
       <c r="DM2" t="n">
-        <v>56.58</v>
+        <v>55.08</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.58</v>
+        <v>14.92</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.17</v>
+        <v>9.85</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47</v>
+        <v>45.77</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.16</v>
+        <v>10.92</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.92</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.33</v>
+        <v>23.08</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,46 +1875,46 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>94.75</v>
+        <v>92</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.75</v>
+        <v>52.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.75</v>
+        <v>13.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.25</v>
+        <v>14.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AU3" t="n">
         <v>1</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>66</v>
+        <v>63.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>16.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.58</v>
+        <v>7.69</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN3" t="n">
         <v>0.92</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="BR3" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS3" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT3" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY3" t="n">
         <v>1.72</v>
@@ -2013,40 +2013,40 @@
         <v>1.8</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="CE3" t="n">
         <v>1.57</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CH3" t="n">
         <v>1.25</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CM3" t="n">
         <v>1.92</v>
@@ -2055,13 +2055,13 @@
         <v>1.56</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CQ3" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="CR3" t="n">
         <v>1.59</v>
@@ -2082,100 +2082,100 @@
         <v>2.49</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DA3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DB3" t="n">
         <v>1.56</v>
       </c>
-      <c r="DB3" t="n">
-        <v>1.57</v>
-      </c>
       <c r="DC3" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DH3" t="n">
-        <v>104.66</v>
+        <v>102.84</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.67</v>
+        <v>5.54</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM3" t="n">
-        <v>67.33</v>
+        <v>65.61</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
         <v>1.92</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.08</v>
+        <v>10.54</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.42</v>
+        <v>13.38</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.92</v>
+        <v>7.23</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>64.33</v>
+        <v>63.54</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.91</v>
+        <v>14.3</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.58</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.5</v>
+        <v>18.85</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,127 +3081,127 @@
         <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AI6" t="n">
-        <v>71.83</v>
+        <v>72.14</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.33</v>
+        <v>-0.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>50.5</v>
+        <v>49.57</v>
       </c>
       <c r="AO6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BN6" t="n">
         <v>1</v>
       </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>32.33</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BL6" t="n">
+      <c r="BO6" t="n">
         <v>0.92</v>
       </c>
-      <c r="BM6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BP6" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY6" t="n">
         <v>3.17</v>
@@ -3222,25 +3222,25 @@
         <v>3.35</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.82</v>
+        <v>5.52</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CH6" t="n">
         <v>1.2</v>
@@ -3249,28 +3249,28 @@
         <v>1.51</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CK6" t="n">
         <v>1.87</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CN6" t="n">
         <v>1.56</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.95</v>
+        <v>6.02</v>
       </c>
       <c r="CR6" t="n">
         <v>1.6</v>
@@ -3291,10 +3291,10 @@
         <v>2.65</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.85</v>
@@ -3303,13 +3303,13 @@
         <v>1.55</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DC6" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="DE6" t="n">
         <v>0.08</v>
@@ -3318,16 +3318,16 @@
         <v>1.08</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.92</v>
+        <v>84.08</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DK6" t="n">
         <v>1.92</v>
@@ -3336,55 +3336,55 @@
         <v>-0.08</v>
       </c>
       <c r="DM6" t="n">
-        <v>50.92</v>
+        <v>50.38</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.92</v>
+        <v>12.38</v>
       </c>
       <c r="DQ6" t="n">
         <v>12.08</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.08</v>
+        <v>10.3</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>39.25</v>
+        <v>38.16</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.42</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY6" t="n">
         <v>6</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.58</v>
+        <v>17.54</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>95.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>54.6</v>
+        <v>56.17</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>10.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.6</v>
+        <v>13.67</v>
       </c>
       <c r="R7" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.4</v>
+        <v>56</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,49 +3565,49 @@
         <v>1.71</v>
       </c>
       <c r="BG7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.17</v>
+        <v>7.92</v>
       </c>
       <c r="BI7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="BR7" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS7" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="CC7" t="n">
         <v>3.95</v>
@@ -3649,19 +3649,19 @@
         <v>1.24</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CK7" t="n">
         <v>1.72</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN7" t="n">
         <v>1.64</v>
@@ -3670,10 +3670,10 @@
         <v>1.51</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="CR7" t="n">
         <v>1.58</v>
@@ -3694,7 +3694,7 @@
         <v>2.37</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY7" t="n">
         <v>2.23</v>
@@ -3709,85 +3709,85 @@
         <v>1.55</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.46</v>
+        <v>5.42</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DH7" t="n">
-        <v>89.75</v>
+        <v>90.69</v>
       </c>
       <c r="DI7" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="DL7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>50</v>
+      </c>
+      <c r="DW7" t="n">
         <v>0.08</v>
       </c>
-      <c r="DM7" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>10</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0</v>
-      </c>
       <c r="DX7" t="n">
-        <v>11.25</v>
+        <v>11.54</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.92</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.5</v>
+        <v>20.62</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G8" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="H8" t="n">
-        <v>104.14</v>
+        <v>109.62</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="K8" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="L8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>48.86</v>
+        <v>51.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>8.710000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.57</v>
+        <v>15.62</v>
       </c>
       <c r="R8" t="n">
-        <v>7.57</v>
+        <v>7.12</v>
       </c>
       <c r="S8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>65.56999999999999</v>
+        <v>65</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.71</v>
+        <v>12.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.71</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,46 +3968,46 @@
         <v>1.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.83</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT8" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4019,19 +4019,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CC8" t="n">
         <v>2.73</v>
@@ -4040,34 +4040,34 @@
         <v>2.96</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL8" t="n">
         <v>2.22</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CO8" t="n">
         <v>1.53</v>
@@ -4076,16 +4076,16 @@
         <v>2.68</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.8</v>
+        <v>4.84</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CS8" t="n">
         <v>3.29</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CU8" t="n">
         <v>1.3</v>
@@ -4097,100 +4097,100 @@
         <v>2.53</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY8" t="n">
         <v>2.31</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.5</v>
+        <v>101.38</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM8" t="n">
-        <v>48.5</v>
+        <v>50.31</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.16</v>
+        <v>7.84</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.33</v>
+        <v>13.54</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.42</v>
+        <v>8.07</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>61.67</v>
+        <v>61.62</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.91</v>
+        <v>11.92</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.34</v>
+        <v>8.23</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.91</v>
+        <v>19.62</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="9">
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -5010,49 +5010,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="H11" t="n">
-        <v>88</v>
+        <v>92.14</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="K11" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="L11" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="M11" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="O11" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="P11" t="n">
-        <v>16.83</v>
+        <v>16.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.83</v>
+        <v>11.43</v>
       </c>
       <c r="R11" t="n">
-        <v>7.83</v>
+        <v>7.86</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="T11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5064,28 +5064,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>47.67</v>
+        <v>48.43</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.33</v>
+        <v>11.71</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AC11" t="n">
-        <v>26.67</v>
+        <v>27.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5172,40 +5172,40 @@
         <v>1</v>
       </c>
       <c r="BH11" t="n">
-        <v>8</v>
+        <v>8.31</v>
       </c>
       <c r="BI11" t="n">
         <v>1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.67</v>
+        <v>3.92</v>
       </c>
       <c r="BR11" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BS11" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5220,19 +5220,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CC11" t="n">
         <v>4.39</v>
@@ -5244,47 +5244,47 @@
         <v>1.75</v>
       </c>
       <c r="CF11" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CH11" t="n">
         <v>1.17</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO11" t="n">
         <v>1.74</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CQ11" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CS11" t="inlineStr"/>
       <c r="CT11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="n">
@@ -5309,52 +5309,52 @@
         <v>1.85</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="DD11" t="n">
-        <v>6.9</v>
+        <v>7.01</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.5</v>
+        <v>91.61</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.66</v>
+        <v>62.38</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DP11" t="n">
-        <v>17.16</v>
+        <v>16.77</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.75</v>
+        <v>10.16</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>39.67</v>
+        <v>40.69</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>10</v>
+        <v>10.31</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.58</v>
+        <v>6.85</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.5</v>
+        <v>22.38</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="12">
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
@@ -5409,49 +5409,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="G12" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="n">
-        <v>93.67</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="J12" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="L12" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M12" t="n">
         <v>60</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="O12" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>9.67</v>
+        <v>10.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.33</v>
+        <v>13.43</v>
       </c>
       <c r="R12" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5463,28 +5463,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.83</v>
+        <v>54.29</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.67</v>
+        <v>15.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.17</v>
+        <v>16.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5568,70 +5568,70 @@
         <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="BR12" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS12" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BT12" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BU12" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CB12" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CC12" t="n">
         <v>2.5</v>
@@ -5640,40 +5640,40 @@
         <v>2.62</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CJ12" t="n">
         <v>2.14</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CQ12" t="n">
         <v>4.72</v>
@@ -5702,58 +5702,58 @@
         <v>2.06</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.46</v>
+        <v>6.36</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.92</v>
+        <v>90.77</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.66</v>
+        <v>52.31</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.75</v>
+        <v>11.15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.16</v>
+        <v>12.31</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.75</v>
+        <v>6.61</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5765,28 +5765,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54.08</v>
+        <v>54.77</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX12" t="n">
-        <v>14</v>
+        <v>13.84</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.75</v>
+        <v>8.69</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.67</v>
+        <v>16.46</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
@@ -5808,49 +5808,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="H13" t="n">
-        <v>77.40000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>52.2</v>
+        <v>57.17</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="R13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5862,28 +5862,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>41.2</v>
+        <v>46.83</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.2</v>
+        <v>12.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5967,49 +5967,49 @@
         <v>2.57</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BR13" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS13" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT13" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BU13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6018,19 +6018,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>5.26</v>
+        <v>4.78</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CC13" t="n">
         <v>5.21</v>
@@ -6039,10 +6039,10 @@
         <v>5.88</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="CG13" t="n">
         <v>2.19</v>
@@ -6054,16 +6054,16 @@
         <v>1.5</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CN13" t="n">
         <v>1.53</v>
@@ -6072,10 +6072,10 @@
         <v>1.61</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.81</v>
+        <v>5.88</v>
       </c>
       <c r="CR13" t="n">
         <v>1.64</v>
@@ -6095,64 +6095,64 @@
         <v>1.98</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CZ13" t="n">
         <v>1.85</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.16</v>
+        <v>6.27</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.25</v>
+        <v>86.23</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DM13" t="n">
-        <v>54.59</v>
+        <v>56.7</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.59</v>
+        <v>10.69</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.08</v>
+        <v>12.69</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.83</v>
+        <v>7.46</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6164,28 +6164,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.08</v>
+        <v>48.31</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.58</v>
+        <v>11</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.5</v>
+        <v>8.77</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.08</v>
+        <v>21.85</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="14">
@@ -7400,13 +7400,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7490,52 +7490,52 @@
         <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AI17" t="n">
-        <v>92.40000000000001</v>
+        <v>95.33</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AL17" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.8</v>
+        <v>57.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>7.67</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7547,82 +7547,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>55.6</v>
+        <v>52.83</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.6</v>
+        <v>10.33</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>23.4</v>
+        <v>22.83</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BF17" t="n">
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.17</v>
+        <v>9.85</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.83</v>
+        <v>4.69</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT17" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY17" t="n">
         <v>2.1</v>
@@ -7634,55 +7634,55 @@
         <v>2.88</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CO17" t="n">
         <v>1.57</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CS17" t="inlineStr"/>
       <c r="CT17" t="n">
@@ -7711,52 +7711,52 @@
         <v>1.62</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="DD17" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
       <c r="DE17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DG17" t="n">
         <v>1.92</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.67</v>
+        <v>94</v>
       </c>
       <c r="DI17" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.84</v>
+        <v>51.77</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO17" t="n">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.42</v>
+        <v>10.23</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.42</v>
+        <v>12.93</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.17</v>
+        <v>6.39</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7768,28 +7768,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.58</v>
+        <v>53.38</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.42</v>
+        <v>13.08</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.17</v>
+        <v>9.08</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>24.83</v>
+        <v>24.46</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="18">
@@ -7799,61 +7799,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="F18" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>88.86</v>
+        <v>89.75</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="K18" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>58.86</v>
+        <v>58</v>
       </c>
       <c r="N18" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="O18" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>10.88</v>
       </c>
       <c r="R18" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7865,28 +7865,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>42.86</v>
+        <v>43.25</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.14</v>
+        <v>14.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.289999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="AC18" t="n">
-        <v>22.57</v>
+        <v>20.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7970,70 +7970,70 @@
         <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.25</v>
+        <v>7.38</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CC18" t="n">
         <v>3.64</v>
@@ -8045,7 +8045,7 @@
         <v>1.58</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CG18" t="n">
         <v>2.34</v>
@@ -8054,22 +8054,22 @@
         <v>1.24</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CK18" t="n">
         <v>1.77</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CM18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO18" t="n">
         <v>1.52</v>
@@ -8078,7 +8078,7 @@
         <v>2.64</v>
       </c>
       <c r="CQ18" t="n">
-        <v>5.13</v>
+        <v>5.07</v>
       </c>
       <c r="CR18" t="n">
         <v>1.6</v>
@@ -8102,7 +8102,7 @@
         <v>1.84</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CZ18" t="n">
         <v>1.99</v>
@@ -8111,55 +8111,55 @@
         <v>1.6</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="DD18" t="n">
-        <v>5.56</v>
+        <v>5.51</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DF18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.58</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="DI18" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>53.58</v>
+        <v>53.46</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="DO18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.17</v>
+        <v>11.23</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.92</v>
+        <v>11.39</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.08</v>
+        <v>8.93</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8171,28 +8171,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.08</v>
+        <v>45.15</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.66</v>
+        <v>13.46</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.08</v>
+        <v>20.08</v>
       </c>
       <c r="EB18" t="n">
         <v>1.59</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="19">
@@ -8202,13 +8202,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>0.14</v>
@@ -8295,49 +8295,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AI19" t="n">
-        <v>86</v>
+        <v>84.5</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>47.33</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.6</v>
+        <v>11.17</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>5.83</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8349,73 +8349,73 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>48.4</v>
+        <v>48.17</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.8</v>
+        <v>8.17</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="BD19" t="n">
-        <v>20.2</v>
+        <v>19.67</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.17</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP19" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU19" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY19" t="n">
         <v>2.42</v>
@@ -8433,25 +8433,25 @@
         <v>2.47</v>
       </c>
       <c r="CA19" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
       <c r="CE19" t="n">
         <v>1.63</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CH19" t="n">
         <v>1.21</v>
@@ -8460,13 +8460,13 @@
         <v>1.58</v>
       </c>
       <c r="CJ19" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CM19" t="n">
         <v>2.01</v>
@@ -8475,20 +8475,20 @@
         <v>1.59</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CQ19" t="n">
-        <v>5.97</v>
+        <v>6</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CS19" t="inlineStr"/>
       <c r="CT19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="n">
@@ -8510,88 +8510,88 @@
         <v>1.61</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="DD19" t="n">
-        <v>6.16</v>
+        <v>6.3</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.34</v>
+        <v>84.69</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM19" t="n">
-        <v>47.58</v>
+        <v>48.07</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.58</v>
+        <v>12.69</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.16</v>
+        <v>11.23</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.67</v>
+        <v>6.77</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>48.92</v>
+        <v>48.77</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.34</v>
+        <v>12.62</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.25</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.09</v>
+        <v>4.23</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.91</v>
+        <v>19.69</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="20">
@@ -12603,13 +12603,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" t="n">
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
         <v>0.17</v>
@@ -12693,139 +12693,139 @@
         <v>1.67</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AI30" t="n">
-        <v>89</v>
+        <v>92.14</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AL30" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN30" t="n">
-        <v>47.67</v>
+        <v>49.71</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>12.29</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>11.86</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>45.33</v>
+        <v>44.14</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA30" t="n">
-        <v>13.67</v>
+        <v>13.43</v>
       </c>
       <c r="BB30" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="BD30" t="n">
-        <v>18.17</v>
+        <v>18.14</v>
       </c>
       <c r="BE30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BN30" t="n">
         <v>1.54</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>1.5</v>
       </c>
       <c r="BO30" t="n">
         <v>1</v>
       </c>
       <c r="BP30" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="BQ30" t="n">
-        <v>4.08</v>
+        <v>4.31</v>
       </c>
       <c r="BR30" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS30" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT30" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU30" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV30" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW30" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX30" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY30" t="n">
         <v>2.06</v>
@@ -12834,22 +12834,22 @@
         <v>2.06</v>
       </c>
       <c r="CA30" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CC30" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CD30" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CE30" t="n">
         <v>1.62</v>
       </c>
       <c r="CF30" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CG30" t="n">
         <v>2.23</v>
@@ -12861,28 +12861,28 @@
         <v>1.57</v>
       </c>
       <c r="CJ30" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CK30" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CL30" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CM30" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN30" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO30" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CP30" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CQ30" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="CR30" t="n">
         <v>1.64</v>
@@ -12899,13 +12899,13 @@
         <v>2.42</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY30" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CZ30" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DA30" t="n">
         <v>1.57</v>
@@ -12914,37 +12914,37 @@
         <v>1.62</v>
       </c>
       <c r="DC30" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="DD30" t="n">
-        <v>6.05</v>
+        <v>5.99</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF30" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="DG30" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="DH30" t="n">
-        <v>93.58</v>
+        <v>94.92</v>
       </c>
       <c r="DI30" t="n">
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="DK30" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="DL30" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="DM30" t="n">
-        <v>54.84</v>
+        <v>55.38</v>
       </c>
       <c r="DN30" t="n">
         <v>0.92</v>
@@ -12953,46 +12953,46 @@
         <v>1.92</v>
       </c>
       <c r="DP30" t="n">
-        <v>10.84</v>
+        <v>11.08</v>
       </c>
       <c r="DQ30" t="n">
-        <v>10.66</v>
+        <v>11.15</v>
       </c>
       <c r="DR30" t="n">
-        <v>7.83</v>
+        <v>7.77</v>
       </c>
       <c r="DS30" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT30" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU30" t="n">
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>49.5</v>
+        <v>48.54</v>
       </c>
       <c r="DW30" t="n">
         <v>0.08</v>
       </c>
       <c r="DX30" t="n">
-        <v>16.75</v>
+        <v>16.38</v>
       </c>
       <c r="DY30" t="n">
-        <v>11.58</v>
+        <v>11.46</v>
       </c>
       <c r="DZ30" t="n">
-        <v>5.17</v>
+        <v>4.93</v>
       </c>
       <c r="EA30" t="n">
-        <v>20.17</v>
+        <v>20</v>
       </c>
       <c r="EB30" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="EC30" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="31">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2026.xlsx
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3475,136 +3475,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AI7" t="n">
-        <v>89.90000000000001</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>51</v>
+        <v>50.73</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.4</v>
+        <v>11.36</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>10.09</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47</v>
+        <v>46.18</v>
       </c>
       <c r="AZ7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK7" t="n">
         <v>0.2</v>
       </c>
-      <c r="BA7" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.16</v>
-      </c>
       <c r="BL7" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="BR7" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS7" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BT7" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU7" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
         <v>2.03</v>
@@ -3613,25 +3613,25 @@
         <v>2.13</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="CE7" t="n">
         <v>1.58</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CH7" t="n">
         <v>1.23</v>
@@ -3640,28 +3640,28 @@
         <v>1.62</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CK7" t="n">
         <v>1.76</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CM7" t="n">
         <v>1.99</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.11</v>
+        <v>5.16</v>
       </c>
       <c r="CR7" t="n">
         <v>1.61</v>
@@ -3688,7 +3688,7 @@
         <v>2.24</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DA7" t="n">
         <v>1.64</v>
@@ -3706,76 +3706,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="DH7" t="n">
-        <v>91.47</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.37</v>
+        <v>52.15</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.68</v>
+        <v>10.7</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.16</v>
+        <v>10.9</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.69</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.42</v>
+        <v>49.8</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.58</v>
+        <v>11.65</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.210000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.79</v>
+        <v>19.65</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="8">
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
         <v>8</v>
@@ -10221,82 +10221,82 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="G24" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="H24" t="n">
-        <v>114.36</v>
+        <v>112.83</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J24" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="K24" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="L24" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M24" t="n">
-        <v>63.36</v>
+        <v>61.58</v>
       </c>
       <c r="N24" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="P24" t="n">
-        <v>13.27</v>
+        <v>12.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>14.45</v>
+        <v>14.17</v>
       </c>
       <c r="R24" t="n">
-        <v>4.36</v>
+        <v>4.67</v>
       </c>
       <c r="S24" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="T24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V24" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>68.55</v>
+        <v>68</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.73</v>
+        <v>19.67</v>
       </c>
       <c r="AA24" t="n">
-        <v>13.91</v>
+        <v>13.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.82</v>
+        <v>6.58</v>
       </c>
       <c r="AC24" t="n">
-        <v>21.45</v>
+        <v>21.33</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -10380,70 +10380,70 @@
         <v>3</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BH24" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BN24" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BO24" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP24" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="BR24" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS24" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT24" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU24" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV24" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW24" t="n">
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CC24" t="n">
         <v>2.46</v>
@@ -10455,10 +10455,10 @@
         <v>1.52</v>
       </c>
       <c r="CF24" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="CG24" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CH24" t="n">
         <v>1.26</v>
@@ -10482,13 +10482,13 @@
         <v>1.63</v>
       </c>
       <c r="CO24" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CP24" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CQ24" t="n">
-        <v>4.58</v>
+        <v>4.66</v>
       </c>
       <c r="CR24" t="n">
         <v>1.53</v>
@@ -10509,7 +10509,7 @@
         <v>2.38</v>
       </c>
       <c r="CX24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY24" t="n">
         <v>2.22</v>
@@ -10533,76 +10533,76 @@
         <v>0</v>
       </c>
       <c r="DF24" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="DG24" t="n">
         <v>3</v>
       </c>
       <c r="DH24" t="n">
-        <v>107.31</v>
+        <v>106.75</v>
       </c>
       <c r="DI24" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DJ24" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="DK24" t="n">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM24" t="n">
-        <v>58.47</v>
+        <v>57.65</v>
       </c>
       <c r="DN24" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO24" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="DP24" t="n">
-        <v>12.05</v>
+        <v>11.8</v>
       </c>
       <c r="DQ24" t="n">
-        <v>12.95</v>
+        <v>12.85</v>
       </c>
       <c r="DR24" t="n">
-        <v>5.42</v>
+        <v>5.55</v>
       </c>
       <c r="DS24" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT24" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU24" t="n">
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>65.27</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="DW24" t="n">
         <v>0.15</v>
       </c>
       <c r="DX24" t="n">
-        <v>17.21</v>
+        <v>16.75</v>
       </c>
       <c r="DY24" t="n">
-        <v>11.47</v>
+        <v>11.1</v>
       </c>
       <c r="DZ24" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="EA24" t="n">
-        <v>21.63</v>
+        <v>21.55</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="EC24" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="25">
